--- a/backend/templates/master_template.xlsx
+++ b/backend/templates/master_template.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,14 +42,8 @@
       <name val="宋体"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,8 +55,13 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -76,11 +75,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,11 +95,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -781,7 +794,7 @@
       </c>
       <c r="AS5" s="2" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML (婚假)</t>
         </is>
       </c>
       <c r="AT5" s="3" t="n"/>
@@ -3238,145 +3251,344 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="36" max="36"/>
-    <col width="4" customWidth="1" min="37" max="37"/>
-    <col width="4" customWidth="1" min="38" max="38"/>
-    <col width="4" customWidth="1" min="39" max="39"/>
-    <col width="4" customWidth="1" min="40" max="40"/>
-    <col width="4" customWidth="1" min="41" max="41"/>
-    <col width="4" customWidth="1" min="42" max="42"/>
-    <col width="4" customWidth="1" min="43" max="43"/>
-    <col width="4" customWidth="1" min="44" max="44"/>
-    <col width="4" customWidth="1" min="45" max="45"/>
-    <col width="4" customWidth="1" min="46" max="46"/>
-    <col width="4" customWidth="1" min="47" max="47"/>
-    <col width="4" customWidth="1" min="48" max="48"/>
-    <col width="4" customWidth="1" min="49" max="49"/>
-    <col width="4" customWidth="1" min="50" max="50"/>
-    <col width="4" customWidth="1" min="51" max="51"/>
-    <col width="4" customWidth="1" min="52" max="52"/>
-    <col width="4" customWidth="1" min="53" max="53"/>
-    <col width="4" customWidth="1" min="54" max="54"/>
-    <col width="4" customWidth="1" min="55" max="55"/>
-    <col width="4" customWidth="1" min="56" max="56"/>
-    <col width="4" customWidth="1" min="57" max="57"/>
-    <col width="4" customWidth="1" min="58" max="58"/>
-    <col width="4" customWidth="1" min="59" max="59"/>
-    <col width="4" customWidth="1" min="60" max="60"/>
-    <col width="4" customWidth="1" min="61" max="61"/>
-    <col width="4" customWidth="1" min="62" max="62"/>
-    <col width="4" customWidth="1" min="63" max="63"/>
-    <col width="4" customWidth="1" min="64" max="64"/>
-    <col width="4" customWidth="1" min="65" max="65"/>
-    <col width="4" customWidth="1" min="66" max="66"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+    <col width="3" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="16" max="16"/>
+    <col width="3" customWidth="1" min="17" max="17"/>
+    <col width="3" customWidth="1" min="18" max="18"/>
+    <col width="3" customWidth="1" min="19" max="19"/>
+    <col width="3" customWidth="1" min="20" max="20"/>
+    <col width="3" customWidth="1" min="21" max="21"/>
+    <col width="3" customWidth="1" min="22" max="22"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="3" customWidth="1" min="25" max="25"/>
+    <col width="3" customWidth="1" min="26" max="26"/>
+    <col width="3" customWidth="1" min="27" max="27"/>
+    <col width="3" customWidth="1" min="28" max="28"/>
+    <col width="3" customWidth="1" min="29" max="29"/>
+    <col width="3" customWidth="1" min="30" max="30"/>
+    <col width="3" customWidth="1" min="31" max="31"/>
+    <col width="3" customWidth="1" min="32" max="32"/>
+    <col width="3" customWidth="1" min="33" max="33"/>
+    <col width="3" customWidth="1" min="34" max="34"/>
+    <col width="3" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="AJ1" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK1" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL1" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM1" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN1" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO1" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP1" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ1" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR1" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS1" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT1" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU1" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV1" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW1" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX1" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY1" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ1" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA1" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB1" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC1" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD1" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE1" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF1" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG1" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH1" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BI1" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BJ1" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BK1" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BL1" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BM1" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BN1" s="6" t="n">
-        <v>31</v>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>月度汇总 统计日期：2026-05-01 至 2026-05-31</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="8" t="n"/>
+      <c r="M1" s="8" t="n"/>
+      <c r="N1" s="8" t="n"/>
+      <c r="O1" s="8" t="n"/>
+      <c r="P1" s="8" t="n"/>
+      <c r="Q1" s="8" t="n"/>
+      <c r="R1" s="8" t="n"/>
+      <c r="S1" s="8" t="n"/>
+      <c r="T1" s="8" t="n"/>
+      <c r="U1" s="8" t="n"/>
+      <c r="V1" s="8" t="n"/>
+      <c r="W1" s="8" t="n"/>
+      <c r="X1" s="8" t="n"/>
+      <c r="Y1" s="8" t="n"/>
+      <c r="Z1" s="8" t="n"/>
+      <c r="AA1" s="8" t="n"/>
+      <c r="AB1" s="8" t="n"/>
+      <c r="AC1" s="8" t="n"/>
+      <c r="AD1" s="8" t="n"/>
+      <c r="AE1" s="8" t="n"/>
+      <c r="AF1" s="8" t="n"/>
+      <c r="AG1" s="8" t="n"/>
+      <c r="AH1" s="8" t="n"/>
+      <c r="AI1" s="8" t="n"/>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK1" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="AL1" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ1" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AR1" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="AS1" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AT1" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AU1" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AV1" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AW1" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AX1" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AY1" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="AZ1" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="BA1" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BB1" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BC1" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BD1" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BE1" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BF1" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="BG1" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="BH1" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BI1" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BJ1" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BK1" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BL1" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BM1" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="BN1" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>创崎新能源技术（上海）有限公司2026年5月考勤月度汇总</t>
-        </is>
-      </c>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>报表生成时间：2026-06-16 08:12</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="8" t="n"/>
+      <c r="N2" s="8" t="n"/>
+      <c r="O2" s="8" t="n"/>
+      <c r="P2" s="8" t="n"/>
+      <c r="Q2" s="8" t="n"/>
+      <c r="R2" s="8" t="n"/>
+      <c r="S2" s="8" t="n"/>
+      <c r="T2" s="8" t="n"/>
+      <c r="U2" s="8" t="n"/>
+      <c r="V2" s="8" t="n"/>
+      <c r="W2" s="8" t="n"/>
+      <c r="X2" s="8" t="n"/>
+      <c r="Y2" s="8" t="n"/>
+      <c r="Z2" s="8" t="n"/>
+      <c r="AA2" s="8" t="n"/>
+      <c r="AB2" s="8" t="n"/>
+      <c r="AC2" s="8" t="n"/>
+      <c r="AD2" s="8" t="n"/>
+      <c r="AE2" s="8" t="n"/>
+      <c r="AF2" s="8" t="n"/>
+      <c r="AG2" s="8" t="n"/>
+      <c r="AH2" s="8" t="n"/>
+      <c r="AI2" s="8" t="n"/>
+      <c r="AJ2" s="4" t="n"/>
+      <c r="AK2" s="11" t="n"/>
+      <c r="AL2" s="11" t="n"/>
+      <c r="AM2" s="4" t="n"/>
+      <c r="AN2" s="4" t="n"/>
+      <c r="AO2" s="4" t="n"/>
+      <c r="AP2" s="4" t="n"/>
+      <c r="AQ2" s="4" t="n"/>
+      <c r="AR2" s="11" t="n"/>
+      <c r="AS2" s="11" t="n"/>
+      <c r="AT2" s="4" t="n"/>
+      <c r="AU2" s="4" t="n"/>
+      <c r="AV2" s="4" t="n"/>
+      <c r="AW2" s="4" t="n"/>
+      <c r="AX2" s="4" t="n"/>
+      <c r="AY2" s="11" t="n"/>
+      <c r="AZ2" s="11" t="n"/>
+      <c r="BA2" s="4" t="n"/>
+      <c r="BB2" s="4" t="n"/>
+      <c r="BC2" s="4" t="n"/>
+      <c r="BD2" s="4" t="n"/>
+      <c r="BE2" s="4" t="n"/>
+      <c r="BF2" s="11" t="n"/>
+      <c r="BG2" s="11" t="n"/>
+      <c r="BH2" s="4" t="n"/>
+      <c r="BI2" s="4" t="n"/>
+      <c r="BJ2" s="4" t="n"/>
+      <c r="BK2" s="4" t="n"/>
+      <c r="BL2" s="4" t="n"/>
+      <c r="BM2" s="11" t="n"/>
+      <c r="BN2" s="11" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3384,1372 +3596,1372 @@
           <t>员工信息</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="n"/>
-      <c r="T3" s="3" t="n"/>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3" t="n"/>
-      <c r="W3" s="3" t="n"/>
-      <c r="X3" s="3" t="n"/>
-      <c r="Y3" s="3" t="n"/>
-      <c r="Z3" s="3" t="n"/>
-      <c r="AA3" s="3" t="n"/>
-      <c r="AB3" s="3" t="n"/>
-      <c r="AC3" s="3" t="n"/>
-      <c r="AD3" s="3" t="n"/>
-      <c r="AE3" s="3" t="n"/>
-      <c r="AF3" s="3" t="n"/>
-      <c r="AG3" s="3" t="n"/>
-      <c r="AH3" s="3" t="n"/>
-      <c r="AI3" s="3" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="8" t="n"/>
+      <c r="Q3" s="8" t="n"/>
+      <c r="R3" s="8" t="n"/>
+      <c r="S3" s="8" t="n"/>
+      <c r="T3" s="8" t="n"/>
+      <c r="U3" s="8" t="n"/>
+      <c r="V3" s="8" t="n"/>
+      <c r="W3" s="8" t="n"/>
+      <c r="X3" s="8" t="n"/>
+      <c r="Y3" s="8" t="n"/>
+      <c r="Z3" s="8" t="n"/>
+      <c r="AA3" s="8" t="n"/>
+      <c r="AB3" s="8" t="n"/>
+      <c r="AC3" s="8" t="n"/>
+      <c r="AD3" s="8" t="n"/>
+      <c r="AE3" s="8" t="n"/>
+      <c r="AF3" s="8" t="n"/>
+      <c r="AG3" s="8" t="n"/>
+      <c r="AH3" s="8" t="n"/>
+      <c r="AI3" s="8" t="n"/>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
           <t>每日考勤状态</t>
         </is>
       </c>
-      <c r="AK3" s="3" t="n"/>
-      <c r="AL3" s="3" t="n"/>
-      <c r="AM3" s="3" t="n"/>
-      <c r="AN3" s="3" t="n"/>
-      <c r="AO3" s="3" t="n"/>
-      <c r="AP3" s="3" t="n"/>
-      <c r="AQ3" s="3" t="n"/>
-      <c r="AR3" s="3" t="n"/>
-      <c r="AS3" s="3" t="n"/>
-      <c r="AT3" s="3" t="n"/>
-      <c r="AU3" s="3" t="n"/>
-      <c r="AV3" s="3" t="n"/>
-      <c r="AW3" s="3" t="n"/>
-      <c r="AX3" s="3" t="n"/>
-      <c r="AY3" s="3" t="n"/>
-      <c r="AZ3" s="3" t="n"/>
-      <c r="BA3" s="3" t="n"/>
-      <c r="BB3" s="3" t="n"/>
-      <c r="BC3" s="3" t="n"/>
-      <c r="BD3" s="3" t="n"/>
-      <c r="BE3" s="3" t="n"/>
-      <c r="BF3" s="3" t="n"/>
-      <c r="BG3" s="3" t="n"/>
-      <c r="BH3" s="3" t="n"/>
-      <c r="BI3" s="3" t="n"/>
-      <c r="BJ3" s="3" t="n"/>
-      <c r="BK3" s="3" t="n"/>
-      <c r="BL3" s="3" t="n"/>
-      <c r="BM3" s="3" t="n"/>
-      <c r="BN3" s="3" t="n"/>
-      <c r="BO3" s="3" t="n"/>
-      <c r="BP3" s="3" t="n"/>
-      <c r="BQ3" s="3" t="n"/>
+      <c r="AK3" s="11" t="n"/>
+      <c r="AL3" s="11" t="n"/>
+      <c r="AM3" s="4" t="n"/>
+      <c r="AN3" s="4" t="n"/>
+      <c r="AO3" s="4" t="n"/>
+      <c r="AP3" s="4" t="n"/>
+      <c r="AQ3" s="4" t="n"/>
+      <c r="AR3" s="11" t="n"/>
+      <c r="AS3" s="11" t="n"/>
+      <c r="AT3" s="4" t="n"/>
+      <c r="AU3" s="4" t="n"/>
+      <c r="AV3" s="4" t="n"/>
+      <c r="AW3" s="4" t="n"/>
+      <c r="AX3" s="4" t="n"/>
+      <c r="AY3" s="11" t="n"/>
+      <c r="AZ3" s="11" t="n"/>
+      <c r="BA3" s="4" t="n"/>
+      <c r="BB3" s="4" t="n"/>
+      <c r="BC3" s="4" t="n"/>
+      <c r="BD3" s="4" t="n"/>
+      <c r="BE3" s="4" t="n"/>
+      <c r="BF3" s="11" t="n"/>
+      <c r="BG3" s="11" t="n"/>
+      <c r="BH3" s="4" t="n"/>
+      <c r="BI3" s="4" t="n"/>
+      <c r="BJ3" s="4" t="n"/>
+      <c r="BK3" s="4" t="n"/>
+      <c r="BL3" s="4" t="n"/>
+      <c r="BM3" s="11" t="n"/>
+      <c r="BN3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>考勤组</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>工号</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>职位</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="3" t="n"/>
-      <c r="Y4" s="3" t="n"/>
-      <c r="Z4" s="3" t="n"/>
-      <c r="AA4" s="3" t="n"/>
-      <c r="AB4" s="3" t="n"/>
-      <c r="AC4" s="3" t="n"/>
-      <c r="AD4" s="3" t="n"/>
-      <c r="AE4" s="3" t="n"/>
-      <c r="AF4" s="3" t="n"/>
-      <c r="AG4" s="3" t="n"/>
-      <c r="AH4" s="3" t="n"/>
-      <c r="AI4" s="3" t="n"/>
-      <c r="AJ4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT4" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV4" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW4" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB4" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD4" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE4" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG4" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BI4" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="BJ4" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BK4" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BL4" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BM4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BN4" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="BO4" s="7" t="inlineStr">
-        <is>
-          <t>异常汇总</t>
-        </is>
-      </c>
-      <c r="BP4" s="7" t="inlineStr">
-        <is>
-          <t>是否补单</t>
-        </is>
-      </c>
-      <c r="BQ4" s="7" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="8" t="n"/>
+      <c r="O4" s="8" t="n"/>
+      <c r="P4" s="8" t="n"/>
+      <c r="Q4" s="8" t="n"/>
+      <c r="R4" s="8" t="n"/>
+      <c r="S4" s="8" t="n"/>
+      <c r="T4" s="8" t="n"/>
+      <c r="U4" s="8" t="n"/>
+      <c r="V4" s="8" t="n"/>
+      <c r="W4" s="8" t="n"/>
+      <c r="X4" s="8" t="n"/>
+      <c r="Y4" s="8" t="n"/>
+      <c r="Z4" s="8" t="n"/>
+      <c r="AA4" s="8" t="n"/>
+      <c r="AB4" s="8" t="n"/>
+      <c r="AC4" s="8" t="n"/>
+      <c r="AD4" s="8" t="n"/>
+      <c r="AE4" s="8" t="n"/>
+      <c r="AF4" s="8" t="n"/>
+      <c r="AG4" s="8" t="n"/>
+      <c r="AH4" s="8" t="n"/>
+      <c r="AI4" s="8" t="n"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK4" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="AL4" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AP4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AR4" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="AS4" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AT4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AU4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AV4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AW4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AX4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AY4" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="AZ4" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="BA4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BB4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BC4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BD4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BE4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BF4" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="BG4" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="BH4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BJ4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BM4" s="9" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="BN4" s="9" t="inlineStr">
+        <is>
+          <t>日</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="3" t="n"/>
-      <c r="U5" s="3" t="n"/>
-      <c r="V5" s="3" t="n"/>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" s="3" t="n"/>
-      <c r="Y5" s="3" t="n"/>
-      <c r="Z5" s="3" t="n"/>
-      <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="3" t="n"/>
-      <c r="AC5" s="3" t="n"/>
-      <c r="AD5" s="3" t="n"/>
-      <c r="AE5" s="3" t="n"/>
-      <c r="AF5" s="3" t="n"/>
-      <c r="AG5" s="3" t="n"/>
-      <c r="AH5" s="3" t="n"/>
-      <c r="AI5" s="3" t="n"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr"/>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr"/>
-      <c r="BC5" s="3" t="inlineStr"/>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr"/>
-      <c r="BF5" s="3" t="inlineStr"/>
-      <c r="BG5" s="3" t="inlineStr"/>
-      <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr"/>
-      <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
-      <c r="BM5" s="3" t="inlineStr"/>
-      <c r="BN5" s="3" t="inlineStr"/>
-      <c r="BO5" s="3" t="inlineStr"/>
-      <c r="BP5" s="3" t="inlineStr"/>
-      <c r="BQ5" s="3" t="inlineStr"/>
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="8" t="n"/>
+      <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8" t="n"/>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="8" t="n"/>
+      <c r="T5" s="8" t="n"/>
+      <c r="U5" s="8" t="n"/>
+      <c r="V5" s="8" t="n"/>
+      <c r="W5" s="8" t="n"/>
+      <c r="X5" s="8" t="n"/>
+      <c r="Y5" s="8" t="n"/>
+      <c r="Z5" s="8" t="n"/>
+      <c r="AA5" s="8" t="n"/>
+      <c r="AB5" s="8" t="n"/>
+      <c r="AC5" s="8" t="n"/>
+      <c r="AD5" s="8" t="n"/>
+      <c r="AE5" s="8" t="n"/>
+      <c r="AF5" s="8" t="n"/>
+      <c r="AG5" s="8" t="n"/>
+      <c r="AH5" s="8" t="n"/>
+      <c r="AI5" s="8" t="n"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="11" t="inlineStr"/>
+      <c r="AL5" s="11" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="11" t="inlineStr"/>
+      <c r="AS5" s="11" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr"/>
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="11" t="inlineStr"/>
+      <c r="AZ5" s="11" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr"/>
+      <c r="BC5" s="4" t="inlineStr"/>
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr"/>
+      <c r="BF5" s="11" t="inlineStr"/>
+      <c r="BG5" s="11" t="inlineStr"/>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BM5" s="11" t="inlineStr"/>
+      <c r="BN5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n"/>
-      <c r="T6" s="3" t="n"/>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="3" t="n"/>
-      <c r="W6" s="3" t="n"/>
-      <c r="X6" s="3" t="n"/>
-      <c r="Y6" s="3" t="n"/>
-      <c r="Z6" s="3" t="n"/>
-      <c r="AA6" s="3" t="n"/>
-      <c r="AB6" s="3" t="n"/>
-      <c r="AC6" s="3" t="n"/>
-      <c r="AD6" s="3" t="n"/>
-      <c r="AE6" s="3" t="n"/>
-      <c r="AF6" s="3" t="n"/>
-      <c r="AG6" s="3" t="n"/>
-      <c r="AH6" s="3" t="n"/>
-      <c r="AI6" s="3" t="n"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr"/>
-      <c r="BC6" s="3" t="inlineStr"/>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr"/>
-      <c r="BG6" s="3" t="inlineStr"/>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
-      <c r="BM6" s="3" t="inlineStr"/>
-      <c r="BN6" s="3" t="inlineStr"/>
-      <c r="BO6" s="3" t="inlineStr"/>
-      <c r="BP6" s="3" t="inlineStr"/>
-      <c r="BQ6" s="3" t="inlineStr"/>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="8" t="n"/>
+      <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="8" t="n"/>
+      <c r="T6" s="8" t="n"/>
+      <c r="U6" s="8" t="n"/>
+      <c r="V6" s="8" t="n"/>
+      <c r="W6" s="8" t="n"/>
+      <c r="X6" s="8" t="n"/>
+      <c r="Y6" s="8" t="n"/>
+      <c r="Z6" s="8" t="n"/>
+      <c r="AA6" s="8" t="n"/>
+      <c r="AB6" s="8" t="n"/>
+      <c r="AC6" s="8" t="n"/>
+      <c r="AD6" s="8" t="n"/>
+      <c r="AE6" s="8" t="n"/>
+      <c r="AF6" s="8" t="n"/>
+      <c r="AG6" s="8" t="n"/>
+      <c r="AH6" s="8" t="n"/>
+      <c r="AI6" s="8" t="n"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="11" t="inlineStr"/>
+      <c r="AL6" s="11" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="11" t="inlineStr"/>
+      <c r="AS6" s="11" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr"/>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="11" t="inlineStr"/>
+      <c r="AZ6" s="11" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr"/>
+      <c r="BC6" s="4" t="inlineStr"/>
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr"/>
+      <c r="BF6" s="11" t="inlineStr"/>
+      <c r="BG6" s="11" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BM6" s="11" t="inlineStr"/>
+      <c r="BN6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="n"/>
-      <c r="T7" s="3" t="n"/>
-      <c r="U7" s="3" t="n"/>
-      <c r="V7" s="3" t="n"/>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" s="3" t="n"/>
-      <c r="Y7" s="3" t="n"/>
-      <c r="Z7" s="3" t="n"/>
-      <c r="AA7" s="3" t="n"/>
-      <c r="AB7" s="3" t="n"/>
-      <c r="AC7" s="3" t="n"/>
-      <c r="AD7" s="3" t="n"/>
-      <c r="AE7" s="3" t="n"/>
-      <c r="AF7" s="3" t="n"/>
-      <c r="AG7" s="3" t="n"/>
-      <c r="AH7" s="3" t="n"/>
-      <c r="AI7" s="3" t="n"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr"/>
-      <c r="BC7" s="3" t="inlineStr"/>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr"/>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr"/>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
-      <c r="BM7" s="3" t="inlineStr"/>
-      <c r="BN7" s="3" t="inlineStr"/>
-      <c r="BO7" s="3" t="inlineStr"/>
-      <c r="BP7" s="3" t="inlineStr"/>
-      <c r="BQ7" s="3" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8" t="n"/>
+      <c r="AI7" s="8" t="n"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="11" t="inlineStr"/>
+      <c r="AL7" s="11" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr"/>
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="11" t="inlineStr"/>
+      <c r="AS7" s="11" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr"/>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="11" t="inlineStr"/>
+      <c r="AZ7" s="11" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr"/>
+      <c r="BC7" s="4" t="inlineStr"/>
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr"/>
+      <c r="BF7" s="11" t="inlineStr"/>
+      <c r="BG7" s="11" t="inlineStr"/>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr"/>
+      <c r="BL7" s="4" t="inlineStr"/>
+      <c r="BM7" s="11" t="inlineStr"/>
+      <c r="BN7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="n"/>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
-      <c r="V8" s="3" t="n"/>
-      <c r="W8" s="3" t="n"/>
-      <c r="X8" s="3" t="n"/>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
-      <c r="AA8" s="3" t="n"/>
-      <c r="AB8" s="3" t="n"/>
-      <c r="AC8" s="3" t="n"/>
-      <c r="AD8" s="3" t="n"/>
-      <c r="AE8" s="3" t="n"/>
-      <c r="AF8" s="3" t="n"/>
-      <c r="AG8" s="3" t="n"/>
-      <c r="AH8" s="3" t="n"/>
-      <c r="AI8" s="3" t="n"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr"/>
-      <c r="BC8" s="3" t="inlineStr"/>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr"/>
-      <c r="BG8" s="3" t="inlineStr"/>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
-      <c r="BM8" s="3" t="inlineStr"/>
-      <c r="BN8" s="3" t="inlineStr"/>
-      <c r="BO8" s="3" t="inlineStr"/>
-      <c r="BP8" s="3" t="inlineStr"/>
-      <c r="BQ8" s="3" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8" t="n"/>
+      <c r="AI8" s="8" t="n"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="11" t="inlineStr"/>
+      <c r="AL8" s="11" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="11" t="inlineStr"/>
+      <c r="AS8" s="11" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="11" t="inlineStr"/>
+      <c r="AZ8" s="11" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr"/>
+      <c r="BC8" s="4" t="inlineStr"/>
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr"/>
+      <c r="BF8" s="11" t="inlineStr"/>
+      <c r="BG8" s="11" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr"/>
+      <c r="BL8" s="4" t="inlineStr"/>
+      <c r="BM8" s="11" t="inlineStr"/>
+      <c r="BN8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
-      <c r="U9" s="3" t="n"/>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
-      <c r="X9" s="3" t="n"/>
-      <c r="Y9" s="3" t="n"/>
-      <c r="Z9" s="3" t="n"/>
-      <c r="AA9" s="3" t="n"/>
-      <c r="AB9" s="3" t="n"/>
-      <c r="AC9" s="3" t="n"/>
-      <c r="AD9" s="3" t="n"/>
-      <c r="AE9" s="3" t="n"/>
-      <c r="AF9" s="3" t="n"/>
-      <c r="AG9" s="3" t="n"/>
-      <c r="AH9" s="3" t="n"/>
-      <c r="AI9" s="3" t="n"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr"/>
-      <c r="BC9" s="3" t="inlineStr"/>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr"/>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr"/>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
-      <c r="BM9" s="3" t="inlineStr"/>
-      <c r="BN9" s="3" t="inlineStr"/>
-      <c r="BO9" s="3" t="inlineStr"/>
-      <c r="BP9" s="3" t="inlineStr"/>
-      <c r="BQ9" s="3" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="8" t="n"/>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8" t="n"/>
+      <c r="R9" s="8" t="n"/>
+      <c r="S9" s="8" t="n"/>
+      <c r="T9" s="8" t="n"/>
+      <c r="U9" s="8" t="n"/>
+      <c r="V9" s="8" t="n"/>
+      <c r="W9" s="8" t="n"/>
+      <c r="X9" s="8" t="n"/>
+      <c r="Y9" s="8" t="n"/>
+      <c r="Z9" s="8" t="n"/>
+      <c r="AA9" s="8" t="n"/>
+      <c r="AB9" s="8" t="n"/>
+      <c r="AC9" s="8" t="n"/>
+      <c r="AD9" s="8" t="n"/>
+      <c r="AE9" s="8" t="n"/>
+      <c r="AF9" s="8" t="n"/>
+      <c r="AG9" s="8" t="n"/>
+      <c r="AH9" s="8" t="n"/>
+      <c r="AI9" s="8" t="n"/>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="11" t="inlineStr"/>
+      <c r="AL9" s="11" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="11" t="inlineStr"/>
+      <c r="AS9" s="11" t="inlineStr"/>
+      <c r="AT9" s="4" t="inlineStr"/>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr"/>
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="11" t="inlineStr"/>
+      <c r="AZ9" s="11" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr"/>
+      <c r="BC9" s="4" t="inlineStr"/>
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr"/>
+      <c r="BF9" s="11" t="inlineStr"/>
+      <c r="BG9" s="11" t="inlineStr"/>
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr"/>
+      <c r="BL9" s="4" t="inlineStr"/>
+      <c r="BM9" s="11" t="inlineStr"/>
+      <c r="BN9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
-      <c r="Y10" s="3" t="n"/>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
-      <c r="AC10" s="3" t="n"/>
-      <c r="AD10" s="3" t="n"/>
-      <c r="AE10" s="3" t="n"/>
-      <c r="AF10" s="3" t="n"/>
-      <c r="AG10" s="3" t="n"/>
-      <c r="AH10" s="3" t="n"/>
-      <c r="AI10" s="3" t="n"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr"/>
-      <c r="BC10" s="3" t="inlineStr"/>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr"/>
-      <c r="BG10" s="3" t="inlineStr"/>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
-      <c r="BM10" s="3" t="inlineStr"/>
-      <c r="BN10" s="3" t="inlineStr"/>
-      <c r="BO10" s="3" t="inlineStr"/>
-      <c r="BP10" s="3" t="inlineStr"/>
-      <c r="BQ10" s="3" t="inlineStr"/>
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8" t="n"/>
+      <c r="AI10" s="8" t="n"/>
+      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="11" t="inlineStr"/>
+      <c r="AL10" s="11" t="inlineStr"/>
+      <c r="AM10" s="4" t="inlineStr"/>
+      <c r="AN10" s="4" t="inlineStr"/>
+      <c r="AO10" s="4" t="inlineStr"/>
+      <c r="AP10" s="4" t="inlineStr"/>
+      <c r="AQ10" s="4" t="inlineStr"/>
+      <c r="AR10" s="11" t="inlineStr"/>
+      <c r="AS10" s="11" t="inlineStr"/>
+      <c r="AT10" s="4" t="inlineStr"/>
+      <c r="AU10" s="4" t="inlineStr"/>
+      <c r="AV10" s="4" t="inlineStr"/>
+      <c r="AW10" s="4" t="inlineStr"/>
+      <c r="AX10" s="4" t="inlineStr"/>
+      <c r="AY10" s="11" t="inlineStr"/>
+      <c r="AZ10" s="11" t="inlineStr"/>
+      <c r="BA10" s="4" t="inlineStr"/>
+      <c r="BB10" s="4" t="inlineStr"/>
+      <c r="BC10" s="4" t="inlineStr"/>
+      <c r="BD10" s="4" t="inlineStr"/>
+      <c r="BE10" s="4" t="inlineStr"/>
+      <c r="BF10" s="11" t="inlineStr"/>
+      <c r="BG10" s="11" t="inlineStr"/>
+      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BI10" s="4" t="inlineStr"/>
+      <c r="BJ10" s="4" t="inlineStr"/>
+      <c r="BK10" s="4" t="inlineStr"/>
+      <c r="BL10" s="4" t="inlineStr"/>
+      <c r="BM10" s="11" t="inlineStr"/>
+      <c r="BN10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
-      <c r="R11" s="3" t="n"/>
-      <c r="S11" s="3" t="n"/>
-      <c r="T11" s="3" t="n"/>
-      <c r="U11" s="3" t="n"/>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
-      <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="3" t="n"/>
-      <c r="Z11" s="3" t="n"/>
-      <c r="AA11" s="3" t="n"/>
-      <c r="AB11" s="3" t="n"/>
-      <c r="AC11" s="3" t="n"/>
-      <c r="AD11" s="3" t="n"/>
-      <c r="AE11" s="3" t="n"/>
-      <c r="AF11" s="3" t="n"/>
-      <c r="AG11" s="3" t="n"/>
-      <c r="AH11" s="3" t="n"/>
-      <c r="AI11" s="3" t="n"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr"/>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr"/>
-      <c r="BC11" s="3" t="inlineStr"/>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr"/>
-      <c r="BF11" s="3" t="inlineStr"/>
-      <c r="BG11" s="3" t="inlineStr"/>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr"/>
-      <c r="BL11" s="3" t="inlineStr"/>
-      <c r="BM11" s="3" t="inlineStr"/>
-      <c r="BN11" s="3" t="inlineStr"/>
-      <c r="BO11" s="3" t="inlineStr"/>
-      <c r="BP11" s="3" t="inlineStr"/>
-      <c r="BQ11" s="3" t="inlineStr"/>
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8" t="n"/>
+      <c r="AI11" s="8" t="n"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="11" t="inlineStr"/>
+      <c r="AL11" s="11" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr"/>
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="11" t="inlineStr"/>
+      <c r="AS11" s="11" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr"/>
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="11" t="inlineStr"/>
+      <c r="AZ11" s="11" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr"/>
+      <c r="BC11" s="4" t="inlineStr"/>
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr"/>
+      <c r="BF11" s="11" t="inlineStr"/>
+      <c r="BG11" s="11" t="inlineStr"/>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr"/>
+      <c r="BL11" s="4" t="inlineStr"/>
+      <c r="BM11" s="11" t="inlineStr"/>
+      <c r="BN11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3" t="n"/>
-      <c r="R12" s="3" t="n"/>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="n"/>
-      <c r="U12" s="3" t="n"/>
-      <c r="V12" s="3" t="n"/>
-      <c r="W12" s="3" t="n"/>
-      <c r="X12" s="3" t="n"/>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="n"/>
-      <c r="AA12" s="3" t="n"/>
-      <c r="AB12" s="3" t="n"/>
-      <c r="AC12" s="3" t="n"/>
-      <c r="AD12" s="3" t="n"/>
-      <c r="AE12" s="3" t="n"/>
-      <c r="AF12" s="3" t="n"/>
-      <c r="AG12" s="3" t="n"/>
-      <c r="AH12" s="3" t="n"/>
-      <c r="AI12" s="3" t="n"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr"/>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr"/>
-      <c r="BC12" s="3" t="inlineStr"/>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr"/>
-      <c r="BF12" s="3" t="inlineStr"/>
-      <c r="BG12" s="3" t="inlineStr"/>
-      <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
-      <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr"/>
-      <c r="BL12" s="3" t="inlineStr"/>
-      <c r="BM12" s="3" t="inlineStr"/>
-      <c r="BN12" s="3" t="inlineStr"/>
-      <c r="BO12" s="3" t="inlineStr"/>
-      <c r="BP12" s="3" t="inlineStr"/>
-      <c r="BQ12" s="3" t="inlineStr"/>
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="10" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="8" t="n"/>
+      <c r="S12" s="8" t="n"/>
+      <c r="T12" s="8" t="n"/>
+      <c r="U12" s="8" t="n"/>
+      <c r="V12" s="8" t="n"/>
+      <c r="W12" s="8" t="n"/>
+      <c r="X12" s="8" t="n"/>
+      <c r="Y12" s="8" t="n"/>
+      <c r="Z12" s="8" t="n"/>
+      <c r="AA12" s="8" t="n"/>
+      <c r="AB12" s="8" t="n"/>
+      <c r="AC12" s="8" t="n"/>
+      <c r="AD12" s="8" t="n"/>
+      <c r="AE12" s="8" t="n"/>
+      <c r="AF12" s="8" t="n"/>
+      <c r="AG12" s="8" t="n"/>
+      <c r="AH12" s="8" t="n"/>
+      <c r="AI12" s="8" t="n"/>
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="11" t="inlineStr"/>
+      <c r="AL12" s="11" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr"/>
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="11" t="inlineStr"/>
+      <c r="AS12" s="11" t="inlineStr"/>
+      <c r="AT12" s="4" t="inlineStr"/>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr"/>
+      <c r="AX12" s="4" t="inlineStr"/>
+      <c r="AY12" s="11" t="inlineStr"/>
+      <c r="AZ12" s="11" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr"/>
+      <c r="BC12" s="4" t="inlineStr"/>
+      <c r="BD12" s="4" t="inlineStr"/>
+      <c r="BE12" s="4" t="inlineStr"/>
+      <c r="BF12" s="11" t="inlineStr"/>
+      <c r="BG12" s="11" t="inlineStr"/>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr"/>
+      <c r="BL12" s="4" t="inlineStr"/>
+      <c r="BM12" s="11" t="inlineStr"/>
+      <c r="BN12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" s="3" t="n"/>
-      <c r="S13" s="3" t="n"/>
-      <c r="T13" s="3" t="n"/>
-      <c r="U13" s="3" t="n"/>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n"/>
-      <c r="X13" s="3" t="n"/>
-      <c r="Y13" s="3" t="n"/>
-      <c r="Z13" s="3" t="n"/>
-      <c r="AA13" s="3" t="n"/>
-      <c r="AB13" s="3" t="n"/>
-      <c r="AC13" s="3" t="n"/>
-      <c r="AD13" s="3" t="n"/>
-      <c r="AE13" s="3" t="n"/>
-      <c r="AF13" s="3" t="n"/>
-      <c r="AG13" s="3" t="n"/>
-      <c r="AH13" s="3" t="n"/>
-      <c r="AI13" s="3" t="n"/>
-      <c r="AJ13" s="3" t="inlineStr"/>
-      <c r="AK13" s="3" t="inlineStr"/>
-      <c r="AL13" s="3" t="inlineStr"/>
-      <c r="AM13" s="3" t="inlineStr"/>
-      <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
-      <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr"/>
-      <c r="AX13" s="3" t="inlineStr"/>
-      <c r="AY13" s="3" t="inlineStr"/>
-      <c r="AZ13" s="3" t="inlineStr"/>
-      <c r="BA13" s="3" t="inlineStr"/>
-      <c r="BB13" s="3" t="inlineStr"/>
-      <c r="BC13" s="3" t="inlineStr"/>
-      <c r="BD13" s="3" t="inlineStr"/>
-      <c r="BE13" s="3" t="inlineStr"/>
-      <c r="BF13" s="3" t="inlineStr"/>
-      <c r="BG13" s="3" t="inlineStr"/>
-      <c r="BH13" s="3" t="inlineStr"/>
-      <c r="BI13" s="3" t="inlineStr"/>
-      <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
-      <c r="BM13" s="3" t="inlineStr"/>
-      <c r="BN13" s="3" t="inlineStr"/>
-      <c r="BO13" s="3" t="inlineStr"/>
-      <c r="BP13" s="3" t="inlineStr"/>
-      <c r="BQ13" s="3" t="inlineStr"/>
+      <c r="C13" s="10" t="inlineStr"/>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8" t="n"/>
+      <c r="AI13" s="8" t="n"/>
+      <c r="AJ13" s="4" t="inlineStr"/>
+      <c r="AK13" s="11" t="inlineStr"/>
+      <c r="AL13" s="11" t="inlineStr"/>
+      <c r="AM13" s="4" t="inlineStr"/>
+      <c r="AN13" s="4" t="inlineStr"/>
+      <c r="AO13" s="4" t="inlineStr"/>
+      <c r="AP13" s="4" t="inlineStr"/>
+      <c r="AQ13" s="4" t="inlineStr"/>
+      <c r="AR13" s="11" t="inlineStr"/>
+      <c r="AS13" s="11" t="inlineStr"/>
+      <c r="AT13" s="4" t="inlineStr"/>
+      <c r="AU13" s="4" t="inlineStr"/>
+      <c r="AV13" s="4" t="inlineStr"/>
+      <c r="AW13" s="4" t="inlineStr"/>
+      <c r="AX13" s="4" t="inlineStr"/>
+      <c r="AY13" s="11" t="inlineStr"/>
+      <c r="AZ13" s="11" t="inlineStr"/>
+      <c r="BA13" s="4" t="inlineStr"/>
+      <c r="BB13" s="4" t="inlineStr"/>
+      <c r="BC13" s="4" t="inlineStr"/>
+      <c r="BD13" s="4" t="inlineStr"/>
+      <c r="BE13" s="4" t="inlineStr"/>
+      <c r="BF13" s="11" t="inlineStr"/>
+      <c r="BG13" s="11" t="inlineStr"/>
+      <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BI13" s="4" t="inlineStr"/>
+      <c r="BJ13" s="4" t="inlineStr"/>
+      <c r="BK13" s="4" t="inlineStr"/>
+      <c r="BL13" s="4" t="inlineStr"/>
+      <c r="BM13" s="11" t="inlineStr"/>
+      <c r="BN13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n"/>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
-      <c r="Y14" s="3" t="n"/>
-      <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="3" t="n"/>
-      <c r="AC14" s="3" t="n"/>
-      <c r="AD14" s="3" t="n"/>
-      <c r="AE14" s="3" t="n"/>
-      <c r="AF14" s="3" t="n"/>
-      <c r="AG14" s="3" t="n"/>
-      <c r="AH14" s="3" t="n"/>
-      <c r="AI14" s="3" t="n"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr"/>
-      <c r="BC14" s="3" t="inlineStr"/>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr"/>
-      <c r="BG14" s="3" t="inlineStr"/>
-      <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr"/>
-      <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
-      <c r="BM14" s="3" t="inlineStr"/>
-      <c r="BN14" s="3" t="inlineStr"/>
-      <c r="BO14" s="3" t="inlineStr"/>
-      <c r="BP14" s="3" t="inlineStr"/>
-      <c r="BQ14" s="3" t="inlineStr"/>
+      <c r="C14" s="10" t="inlineStr"/>
+      <c r="D14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8" t="n"/>
+      <c r="AI14" s="8" t="n"/>
+      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="11" t="inlineStr"/>
+      <c r="AL14" s="11" t="inlineStr"/>
+      <c r="AM14" s="4" t="inlineStr"/>
+      <c r="AN14" s="4" t="inlineStr"/>
+      <c r="AO14" s="4" t="inlineStr"/>
+      <c r="AP14" s="4" t="inlineStr"/>
+      <c r="AQ14" s="4" t="inlineStr"/>
+      <c r="AR14" s="11" t="inlineStr"/>
+      <c r="AS14" s="11" t="inlineStr"/>
+      <c r="AT14" s="4" t="inlineStr"/>
+      <c r="AU14" s="4" t="inlineStr"/>
+      <c r="AV14" s="4" t="inlineStr"/>
+      <c r="AW14" s="4" t="inlineStr"/>
+      <c r="AX14" s="4" t="inlineStr"/>
+      <c r="AY14" s="11" t="inlineStr"/>
+      <c r="AZ14" s="11" t="inlineStr"/>
+      <c r="BA14" s="4" t="inlineStr"/>
+      <c r="BB14" s="4" t="inlineStr"/>
+      <c r="BC14" s="4" t="inlineStr"/>
+      <c r="BD14" s="4" t="inlineStr"/>
+      <c r="BE14" s="4" t="inlineStr"/>
+      <c r="BF14" s="11" t="inlineStr"/>
+      <c r="BG14" s="11" t="inlineStr"/>
+      <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr"/>
+      <c r="BL14" s="4" t="inlineStr"/>
+      <c r="BM14" s="11" t="inlineStr"/>
+      <c r="BN14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="n"/>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n"/>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
-      <c r="Y15" s="3" t="n"/>
-      <c r="Z15" s="3" t="n"/>
-      <c r="AA15" s="3" t="n"/>
-      <c r="AB15" s="3" t="n"/>
-      <c r="AC15" s="3" t="n"/>
-      <c r="AD15" s="3" t="n"/>
-      <c r="AE15" s="3" t="n"/>
-      <c r="AF15" s="3" t="n"/>
-      <c r="AG15" s="3" t="n"/>
-      <c r="AH15" s="3" t="n"/>
-      <c r="AI15" s="3" t="n"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr"/>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr"/>
-      <c r="BC15" s="3" t="inlineStr"/>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr"/>
-      <c r="BF15" s="3" t="inlineStr"/>
-      <c r="BG15" s="3" t="inlineStr"/>
-      <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
-      <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
-      <c r="BM15" s="3" t="inlineStr"/>
-      <c r="BN15" s="3" t="inlineStr"/>
-      <c r="BO15" s="3" t="inlineStr"/>
-      <c r="BP15" s="3" t="inlineStr"/>
-      <c r="BQ15" s="3" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="8" t="n"/>
+      <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8" t="n"/>
+      <c r="R15" s="8" t="n"/>
+      <c r="S15" s="8" t="n"/>
+      <c r="T15" s="8" t="n"/>
+      <c r="U15" s="8" t="n"/>
+      <c r="V15" s="8" t="n"/>
+      <c r="W15" s="8" t="n"/>
+      <c r="X15" s="8" t="n"/>
+      <c r="Y15" s="8" t="n"/>
+      <c r="Z15" s="8" t="n"/>
+      <c r="AA15" s="8" t="n"/>
+      <c r="AB15" s="8" t="n"/>
+      <c r="AC15" s="8" t="n"/>
+      <c r="AD15" s="8" t="n"/>
+      <c r="AE15" s="8" t="n"/>
+      <c r="AF15" s="8" t="n"/>
+      <c r="AG15" s="8" t="n"/>
+      <c r="AH15" s="8" t="n"/>
+      <c r="AI15" s="8" t="n"/>
+      <c r="AJ15" s="4" t="inlineStr"/>
+      <c r="AK15" s="11" t="inlineStr"/>
+      <c r="AL15" s="11" t="inlineStr"/>
+      <c r="AM15" s="4" t="inlineStr"/>
+      <c r="AN15" s="4" t="inlineStr"/>
+      <c r="AO15" s="4" t="inlineStr"/>
+      <c r="AP15" s="4" t="inlineStr"/>
+      <c r="AQ15" s="4" t="inlineStr"/>
+      <c r="AR15" s="11" t="inlineStr"/>
+      <c r="AS15" s="11" t="inlineStr"/>
+      <c r="AT15" s="4" t="inlineStr"/>
+      <c r="AU15" s="4" t="inlineStr"/>
+      <c r="AV15" s="4" t="inlineStr"/>
+      <c r="AW15" s="4" t="inlineStr"/>
+      <c r="AX15" s="4" t="inlineStr"/>
+      <c r="AY15" s="11" t="inlineStr"/>
+      <c r="AZ15" s="11" t="inlineStr"/>
+      <c r="BA15" s="4" t="inlineStr"/>
+      <c r="BB15" s="4" t="inlineStr"/>
+      <c r="BC15" s="4" t="inlineStr"/>
+      <c r="BD15" s="4" t="inlineStr"/>
+      <c r="BE15" s="4" t="inlineStr"/>
+      <c r="BF15" s="11" t="inlineStr"/>
+      <c r="BG15" s="11" t="inlineStr"/>
+      <c r="BH15" s="4" t="inlineStr"/>
+      <c r="BI15" s="4" t="inlineStr"/>
+      <c r="BJ15" s="4" t="inlineStr"/>
+      <c r="BK15" s="4" t="inlineStr"/>
+      <c r="BL15" s="4" t="inlineStr"/>
+      <c r="BM15" s="11" t="inlineStr"/>
+      <c r="BN15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n"/>
-      <c r="U16" s="3" t="n"/>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
-      <c r="Y16" s="3" t="n"/>
-      <c r="Z16" s="3" t="n"/>
-      <c r="AA16" s="3" t="n"/>
-      <c r="AB16" s="3" t="n"/>
-      <c r="AC16" s="3" t="n"/>
-      <c r="AD16" s="3" t="n"/>
-      <c r="AE16" s="3" t="n"/>
-      <c r="AF16" s="3" t="n"/>
-      <c r="AG16" s="3" t="n"/>
-      <c r="AH16" s="3" t="n"/>
-      <c r="AI16" s="3" t="n"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
-      <c r="AM16" s="3" t="inlineStr"/>
-      <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr"/>
-      <c r="AX16" s="3" t="inlineStr"/>
-      <c r="AY16" s="3" t="inlineStr"/>
-      <c r="AZ16" s="3" t="inlineStr"/>
-      <c r="BA16" s="3" t="inlineStr"/>
-      <c r="BB16" s="3" t="inlineStr"/>
-      <c r="BC16" s="3" t="inlineStr"/>
-      <c r="BD16" s="3" t="inlineStr"/>
-      <c r="BE16" s="3" t="inlineStr"/>
-      <c r="BF16" s="3" t="inlineStr"/>
-      <c r="BG16" s="3" t="inlineStr"/>
-      <c r="BH16" s="3" t="inlineStr"/>
-      <c r="BI16" s="3" t="inlineStr"/>
-      <c r="BJ16" s="3" t="inlineStr"/>
-      <c r="BK16" s="3" t="inlineStr"/>
-      <c r="BL16" s="3" t="inlineStr"/>
-      <c r="BM16" s="3" t="inlineStr"/>
-      <c r="BN16" s="3" t="inlineStr"/>
-      <c r="BO16" s="3" t="inlineStr"/>
-      <c r="BP16" s="3" t="inlineStr"/>
-      <c r="BQ16" s="3" t="inlineStr"/>
+      <c r="C16" s="10" t="inlineStr"/>
+      <c r="D16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8" t="n"/>
+      <c r="AI16" s="8" t="n"/>
+      <c r="AJ16" s="4" t="inlineStr"/>
+      <c r="AK16" s="11" t="inlineStr"/>
+      <c r="AL16" s="11" t="inlineStr"/>
+      <c r="AM16" s="4" t="inlineStr"/>
+      <c r="AN16" s="4" t="inlineStr"/>
+      <c r="AO16" s="4" t="inlineStr"/>
+      <c r="AP16" s="4" t="inlineStr"/>
+      <c r="AQ16" s="4" t="inlineStr"/>
+      <c r="AR16" s="11" t="inlineStr"/>
+      <c r="AS16" s="11" t="inlineStr"/>
+      <c r="AT16" s="4" t="inlineStr"/>
+      <c r="AU16" s="4" t="inlineStr"/>
+      <c r="AV16" s="4" t="inlineStr"/>
+      <c r="AW16" s="4" t="inlineStr"/>
+      <c r="AX16" s="4" t="inlineStr"/>
+      <c r="AY16" s="11" t="inlineStr"/>
+      <c r="AZ16" s="11" t="inlineStr"/>
+      <c r="BA16" s="4" t="inlineStr"/>
+      <c r="BB16" s="4" t="inlineStr"/>
+      <c r="BC16" s="4" t="inlineStr"/>
+      <c r="BD16" s="4" t="inlineStr"/>
+      <c r="BE16" s="4" t="inlineStr"/>
+      <c r="BF16" s="11" t="inlineStr"/>
+      <c r="BG16" s="11" t="inlineStr"/>
+      <c r="BH16" s="4" t="inlineStr"/>
+      <c r="BI16" s="4" t="inlineStr"/>
+      <c r="BJ16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr"/>
+      <c r="BL16" s="4" t="inlineStr"/>
+      <c r="BM16" s="11" t="inlineStr"/>
+      <c r="BN16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
-      <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="3" t="n"/>
-      <c r="U17" s="3" t="n"/>
-      <c r="V17" s="3" t="n"/>
-      <c r="W17" s="3" t="n"/>
-      <c r="X17" s="3" t="n"/>
-      <c r="Y17" s="3" t="n"/>
-      <c r="Z17" s="3" t="n"/>
-      <c r="AA17" s="3" t="n"/>
-      <c r="AB17" s="3" t="n"/>
-      <c r="AC17" s="3" t="n"/>
-      <c r="AD17" s="3" t="n"/>
-      <c r="AE17" s="3" t="n"/>
-      <c r="AF17" s="3" t="n"/>
-      <c r="AG17" s="3" t="n"/>
-      <c r="AH17" s="3" t="n"/>
-      <c r="AI17" s="3" t="n"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="inlineStr"/>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
-      <c r="AW17" s="3" t="inlineStr"/>
-      <c r="AX17" s="3" t="inlineStr"/>
-      <c r="AY17" s="3" t="inlineStr"/>
-      <c r="AZ17" s="3" t="inlineStr"/>
-      <c r="BA17" s="3" t="inlineStr"/>
-      <c r="BB17" s="3" t="inlineStr"/>
-      <c r="BC17" s="3" t="inlineStr"/>
-      <c r="BD17" s="3" t="inlineStr"/>
-      <c r="BE17" s="3" t="inlineStr"/>
-      <c r="BF17" s="3" t="inlineStr"/>
-      <c r="BG17" s="3" t="inlineStr"/>
-      <c r="BH17" s="3" t="inlineStr"/>
-      <c r="BI17" s="3" t="inlineStr"/>
-      <c r="BJ17" s="3" t="inlineStr"/>
-      <c r="BK17" s="3" t="inlineStr"/>
-      <c r="BL17" s="3" t="inlineStr"/>
-      <c r="BM17" s="3" t="inlineStr"/>
-      <c r="BN17" s="3" t="inlineStr"/>
-      <c r="BO17" s="3" t="inlineStr"/>
-      <c r="BP17" s="3" t="inlineStr"/>
-      <c r="BQ17" s="3" t="inlineStr"/>
+      <c r="C17" s="10" t="inlineStr"/>
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8" t="n"/>
+      <c r="AI17" s="8" t="n"/>
+      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK17" s="11" t="inlineStr"/>
+      <c r="AL17" s="11" t="inlineStr"/>
+      <c r="AM17" s="4" t="inlineStr"/>
+      <c r="AN17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr"/>
+      <c r="AP17" s="4" t="inlineStr"/>
+      <c r="AQ17" s="4" t="inlineStr"/>
+      <c r="AR17" s="11" t="inlineStr"/>
+      <c r="AS17" s="11" t="inlineStr"/>
+      <c r="AT17" s="4" t="inlineStr"/>
+      <c r="AU17" s="4" t="inlineStr"/>
+      <c r="AV17" s="4" t="inlineStr"/>
+      <c r="AW17" s="4" t="inlineStr"/>
+      <c r="AX17" s="4" t="inlineStr"/>
+      <c r="AY17" s="11" t="inlineStr"/>
+      <c r="AZ17" s="11" t="inlineStr"/>
+      <c r="BA17" s="4" t="inlineStr"/>
+      <c r="BB17" s="4" t="inlineStr"/>
+      <c r="BC17" s="4" t="inlineStr"/>
+      <c r="BD17" s="4" t="inlineStr"/>
+      <c r="BE17" s="4" t="inlineStr"/>
+      <c r="BF17" s="11" t="inlineStr"/>
+      <c r="BG17" s="11" t="inlineStr"/>
+      <c r="BH17" s="4" t="inlineStr"/>
+      <c r="BI17" s="4" t="inlineStr"/>
+      <c r="BJ17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr"/>
+      <c r="BL17" s="4" t="inlineStr"/>
+      <c r="BM17" s="11" t="inlineStr"/>
+      <c r="BN17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n"/>
-      <c r="R18" s="3" t="n"/>
-      <c r="S18" s="3" t="n"/>
-      <c r="T18" s="3" t="n"/>
-      <c r="U18" s="3" t="n"/>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="n"/>
-      <c r="X18" s="3" t="n"/>
-      <c r="Y18" s="3" t="n"/>
-      <c r="Z18" s="3" t="n"/>
-      <c r="AA18" s="3" t="n"/>
-      <c r="AB18" s="3" t="n"/>
-      <c r="AC18" s="3" t="n"/>
-      <c r="AD18" s="3" t="n"/>
-      <c r="AE18" s="3" t="n"/>
-      <c r="AF18" s="3" t="n"/>
-      <c r="AG18" s="3" t="n"/>
-      <c r="AH18" s="3" t="n"/>
-      <c r="AI18" s="3" t="n"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
-      <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr"/>
-      <c r="AX18" s="3" t="inlineStr"/>
-      <c r="AY18" s="3" t="inlineStr"/>
-      <c r="AZ18" s="3" t="inlineStr"/>
-      <c r="BA18" s="3" t="inlineStr"/>
-      <c r="BB18" s="3" t="inlineStr"/>
-      <c r="BC18" s="3" t="inlineStr"/>
-      <c r="BD18" s="3" t="inlineStr"/>
-      <c r="BE18" s="3" t="inlineStr"/>
-      <c r="BF18" s="3" t="inlineStr"/>
-      <c r="BG18" s="3" t="inlineStr"/>
-      <c r="BH18" s="3" t="inlineStr"/>
-      <c r="BI18" s="3" t="inlineStr"/>
-      <c r="BJ18" s="3" t="inlineStr"/>
-      <c r="BK18" s="3" t="inlineStr"/>
-      <c r="BL18" s="3" t="inlineStr"/>
-      <c r="BM18" s="3" t="inlineStr"/>
-      <c r="BN18" s="3" t="inlineStr"/>
-      <c r="BO18" s="3" t="inlineStr"/>
-      <c r="BP18" s="3" t="inlineStr"/>
-      <c r="BQ18" s="3" t="inlineStr"/>
+      <c r="C18" s="10" t="inlineStr"/>
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="8" t="n"/>
+      <c r="P18" s="8" t="n"/>
+      <c r="Q18" s="8" t="n"/>
+      <c r="R18" s="8" t="n"/>
+      <c r="S18" s="8" t="n"/>
+      <c r="T18" s="8" t="n"/>
+      <c r="U18" s="8" t="n"/>
+      <c r="V18" s="8" t="n"/>
+      <c r="W18" s="8" t="n"/>
+      <c r="X18" s="8" t="n"/>
+      <c r="Y18" s="8" t="n"/>
+      <c r="Z18" s="8" t="n"/>
+      <c r="AA18" s="8" t="n"/>
+      <c r="AB18" s="8" t="n"/>
+      <c r="AC18" s="8" t="n"/>
+      <c r="AD18" s="8" t="n"/>
+      <c r="AE18" s="8" t="n"/>
+      <c r="AF18" s="8" t="n"/>
+      <c r="AG18" s="8" t="n"/>
+      <c r="AH18" s="8" t="n"/>
+      <c r="AI18" s="8" t="n"/>
+      <c r="AJ18" s="4" t="inlineStr"/>
+      <c r="AK18" s="11" t="inlineStr"/>
+      <c r="AL18" s="11" t="inlineStr"/>
+      <c r="AM18" s="4" t="inlineStr"/>
+      <c r="AN18" s="4" t="inlineStr"/>
+      <c r="AO18" s="4" t="inlineStr"/>
+      <c r="AP18" s="4" t="inlineStr"/>
+      <c r="AQ18" s="4" t="inlineStr"/>
+      <c r="AR18" s="11" t="inlineStr"/>
+      <c r="AS18" s="11" t="inlineStr"/>
+      <c r="AT18" s="4" t="inlineStr"/>
+      <c r="AU18" s="4" t="inlineStr"/>
+      <c r="AV18" s="4" t="inlineStr"/>
+      <c r="AW18" s="4" t="inlineStr"/>
+      <c r="AX18" s="4" t="inlineStr"/>
+      <c r="AY18" s="11" t="inlineStr"/>
+      <c r="AZ18" s="11" t="inlineStr"/>
+      <c r="BA18" s="4" t="inlineStr"/>
+      <c r="BB18" s="4" t="inlineStr"/>
+      <c r="BC18" s="4" t="inlineStr"/>
+      <c r="BD18" s="4" t="inlineStr"/>
+      <c r="BE18" s="4" t="inlineStr"/>
+      <c r="BF18" s="11" t="inlineStr"/>
+      <c r="BG18" s="11" t="inlineStr"/>
+      <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BJ18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr"/>
+      <c r="BL18" s="4" t="inlineStr"/>
+      <c r="BM18" s="11" t="inlineStr"/>
+      <c r="BN18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>默认考勤组</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
-      <c r="R19" s="3" t="n"/>
-      <c r="S19" s="3" t="n"/>
-      <c r="T19" s="3" t="n"/>
-      <c r="U19" s="3" t="n"/>
-      <c r="V19" s="3" t="n"/>
-      <c r="W19" s="3" t="n"/>
-      <c r="X19" s="3" t="n"/>
-      <c r="Y19" s="3" t="n"/>
-      <c r="Z19" s="3" t="n"/>
-      <c r="AA19" s="3" t="n"/>
-      <c r="AB19" s="3" t="n"/>
-      <c r="AC19" s="3" t="n"/>
-      <c r="AD19" s="3" t="n"/>
-      <c r="AE19" s="3" t="n"/>
-      <c r="AF19" s="3" t="n"/>
-      <c r="AG19" s="3" t="n"/>
-      <c r="AH19" s="3" t="n"/>
-      <c r="AI19" s="3" t="n"/>
-      <c r="AJ19" s="3" t="inlineStr"/>
-      <c r="AK19" s="3" t="inlineStr"/>
-      <c r="AL19" s="3" t="inlineStr"/>
-      <c r="AM19" s="3" t="inlineStr"/>
-      <c r="AN19" s="3" t="inlineStr"/>
-      <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr"/>
-      <c r="AQ19" s="3" t="inlineStr"/>
-      <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr"/>
-      <c r="AV19" s="3" t="inlineStr"/>
-      <c r="AW19" s="3" t="inlineStr"/>
-      <c r="AX19" s="3" t="inlineStr"/>
-      <c r="AY19" s="3" t="inlineStr"/>
-      <c r="AZ19" s="3" t="inlineStr"/>
-      <c r="BA19" s="3" t="inlineStr"/>
-      <c r="BB19" s="3" t="inlineStr"/>
-      <c r="BC19" s="3" t="inlineStr"/>
-      <c r="BD19" s="3" t="inlineStr"/>
-      <c r="BE19" s="3" t="inlineStr"/>
-      <c r="BF19" s="3" t="inlineStr"/>
-      <c r="BG19" s="3" t="inlineStr"/>
-      <c r="BH19" s="3" t="inlineStr"/>
-      <c r="BI19" s="3" t="inlineStr"/>
-      <c r="BJ19" s="3" t="inlineStr"/>
-      <c r="BK19" s="3" t="inlineStr"/>
-      <c r="BL19" s="3" t="inlineStr"/>
-      <c r="BM19" s="3" t="inlineStr"/>
-      <c r="BN19" s="3" t="inlineStr"/>
-      <c r="BO19" s="3" t="inlineStr"/>
-      <c r="BP19" s="3" t="inlineStr"/>
-      <c r="BQ19" s="3" t="inlineStr"/>
+      <c r="C19" s="10" t="inlineStr"/>
+      <c r="D19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8" t="n"/>
+      <c r="AI19" s="8" t="n"/>
+      <c r="AJ19" s="4" t="inlineStr"/>
+      <c r="AK19" s="11" t="inlineStr"/>
+      <c r="AL19" s="11" t="inlineStr"/>
+      <c r="AM19" s="4" t="inlineStr"/>
+      <c r="AN19" s="4" t="inlineStr"/>
+      <c r="AO19" s="4" t="inlineStr"/>
+      <c r="AP19" s="4" t="inlineStr"/>
+      <c r="AQ19" s="4" t="inlineStr"/>
+      <c r="AR19" s="11" t="inlineStr"/>
+      <c r="AS19" s="11" t="inlineStr"/>
+      <c r="AT19" s="4" t="inlineStr"/>
+      <c r="AU19" s="4" t="inlineStr"/>
+      <c r="AV19" s="4" t="inlineStr"/>
+      <c r="AW19" s="4" t="inlineStr"/>
+      <c r="AX19" s="4" t="inlineStr"/>
+      <c r="AY19" s="11" t="inlineStr"/>
+      <c r="AZ19" s="11" t="inlineStr"/>
+      <c r="BA19" s="4" t="inlineStr"/>
+      <c r="BB19" s="4" t="inlineStr"/>
+      <c r="BC19" s="4" t="inlineStr"/>
+      <c r="BD19" s="4" t="inlineStr"/>
+      <c r="BE19" s="4" t="inlineStr"/>
+      <c r="BF19" s="11" t="inlineStr"/>
+      <c r="BG19" s="11" t="inlineStr"/>
+      <c r="BH19" s="4" t="inlineStr"/>
+      <c r="BI19" s="4" t="inlineStr"/>
+      <c r="BJ19" s="4" t="inlineStr"/>
+      <c r="BK19" s="4" t="inlineStr"/>
+      <c r="BL19" s="4" t="inlineStr"/>
+      <c r="BM19" s="11" t="inlineStr"/>
+      <c r="BN19" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:AI2"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="AJ3:BN3"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
@@ -4763,7 +4975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP19"/>
+  <dimension ref="A1:AP186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4805,7 +5017,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>创崎新能源技术（上海）有限公司2026年5月加班结算及加班工资</t>
+          <t>2026年5月加班统计汇总表</t>
         </is>
       </c>
     </row>
@@ -4960,7 +5172,7 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -5091,7 +5303,7 @@
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -5222,7 +5434,7 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -5353,7 +5565,7 @@
       <c r="B8" s="3" t="inlineStr"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -5484,7 +5696,7 @@
       <c r="B9" s="3" t="inlineStr"/>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -5615,7 +5827,7 @@
       <c r="B10" s="3" t="inlineStr"/>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -5746,7 +5958,7 @@
       <c r="B11" s="3" t="inlineStr"/>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -5877,7 +6089,7 @@
       <c r="B12" s="3" t="inlineStr"/>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -6008,7 +6220,7 @@
       <c r="B13" s="3" t="inlineStr"/>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -6139,7 +6351,7 @@
       <c r="B14" s="3" t="inlineStr"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -6270,7 +6482,7 @@
       <c r="B15" s="3" t="inlineStr"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -6401,7 +6613,7 @@
       <c r="B16" s="3" t="inlineStr"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -6532,7 +6744,7 @@
       <c r="B17" s="3" t="inlineStr"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -6663,7 +6875,7 @@
       <c r="B18" s="3" t="inlineStr"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -6794,7 +7006,7 @@
       <c r="B19" s="3" t="inlineStr"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>加班费</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -6920,9 +7132,5360 @@
         <v/>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>加班兑换方式</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>过往
+加班</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O90" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S90" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="T90" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U90" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="V90" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W90" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="X90" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y90" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z90" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA90" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB90" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC90" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD90" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE90" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF90" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG90" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI90" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="AJ90" s="2" t="inlineStr">
+        <is>
+          <t>5月加班时长合计</t>
+        </is>
+      </c>
+      <c r="AK90" s="3" t="n"/>
+      <c r="AL90" s="3" t="n"/>
+      <c r="AM90" s="2" t="inlineStr">
+        <is>
+          <t>5月加班抵扣合计</t>
+        </is>
+      </c>
+      <c r="AN90" s="3" t="n"/>
+      <c r="AO90" s="3" t="n"/>
+      <c r="AP90" s="2" t="inlineStr">
+        <is>
+          <t>5月剩余</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n"/>
+      <c r="B91" s="3" t="n"/>
+      <c r="C91" s="3" t="n"/>
+      <c r="D91" s="3" t="n"/>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
+      <c r="I91" s="3" t="n"/>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="n"/>
+      <c r="L91" s="3" t="n"/>
+      <c r="M91" s="3" t="n"/>
+      <c r="N91" s="3" t="n"/>
+      <c r="O91" s="3" t="n"/>
+      <c r="P91" s="3" t="n"/>
+      <c r="Q91" s="3" t="n"/>
+      <c r="R91" s="3" t="n"/>
+      <c r="S91" s="3" t="n"/>
+      <c r="T91" s="3" t="n"/>
+      <c r="U91" s="3" t="n"/>
+      <c r="V91" s="3" t="n"/>
+      <c r="W91" s="3" t="n"/>
+      <c r="X91" s="3" t="n"/>
+      <c r="Y91" s="3" t="n"/>
+      <c r="Z91" s="3" t="n"/>
+      <c r="AA91" s="3" t="n"/>
+      <c r="AB91" s="3" t="n"/>
+      <c r="AC91" s="3" t="n"/>
+      <c r="AD91" s="3" t="n"/>
+      <c r="AE91" s="3" t="n"/>
+      <c r="AF91" s="3" t="n"/>
+      <c r="AG91" s="3" t="n"/>
+      <c r="AH91" s="3" t="n"/>
+      <c r="AI91" s="3" t="n"/>
+      <c r="AJ91" s="3" t="n"/>
+      <c r="AK91" s="3" t="n"/>
+      <c r="AL91" s="3" t="n"/>
+      <c r="AM91" s="3" t="n"/>
+      <c r="AN91" s="3" t="n"/>
+      <c r="AO91" s="3" t="n"/>
+      <c r="AP91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="3" t="n"/>
+      <c r="C92" s="3" t="n"/>
+      <c r="D92" s="3" t="n"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
+      <c r="L92" s="3" t="n"/>
+      <c r="M92" s="3" t="n"/>
+      <c r="N92" s="3" t="n"/>
+      <c r="O92" s="3" t="n"/>
+      <c r="P92" s="3" t="n"/>
+      <c r="Q92" s="3" t="n"/>
+      <c r="R92" s="3" t="n"/>
+      <c r="S92" s="3" t="n"/>
+      <c r="T92" s="3" t="n"/>
+      <c r="U92" s="3" t="n"/>
+      <c r="V92" s="3" t="n"/>
+      <c r="W92" s="3" t="n"/>
+      <c r="X92" s="3" t="n"/>
+      <c r="Y92" s="3" t="n"/>
+      <c r="Z92" s="3" t="n"/>
+      <c r="AA92" s="3" t="n"/>
+      <c r="AB92" s="3" t="n"/>
+      <c r="AC92" s="3" t="n"/>
+      <c r="AD92" s="3" t="n"/>
+      <c r="AE92" s="3" t="n"/>
+      <c r="AF92" s="3" t="n"/>
+      <c r="AG92" s="3" t="n"/>
+      <c r="AH92" s="3" t="n"/>
+      <c r="AI92" s="3" t="n"/>
+      <c r="AJ92" s="2" t="inlineStr">
+        <is>
+          <t>4月剩余</t>
+        </is>
+      </c>
+      <c r="AK92" s="2" t="inlineStr">
+        <is>
+          <t>1倍</t>
+        </is>
+      </c>
+      <c r="AL92" s="3" t="n"/>
+      <c r="AM92" s="2" t="inlineStr">
+        <is>
+          <t>1倍</t>
+        </is>
+      </c>
+      <c r="AN92" s="3" t="n"/>
+      <c r="AO92" s="3" t="n"/>
+      <c r="AP92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n"/>
+      <c r="B93" s="3" t="n"/>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n"/>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="I93" s="3" t="n"/>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
+      <c r="L93" s="3" t="n"/>
+      <c r="M93" s="3" t="n"/>
+      <c r="N93" s="3" t="n"/>
+      <c r="O93" s="3" t="n"/>
+      <c r="P93" s="3" t="n"/>
+      <c r="Q93" s="3" t="n"/>
+      <c r="R93" s="3" t="n"/>
+      <c r="S93" s="3" t="n"/>
+      <c r="T93" s="3" t="n"/>
+      <c r="U93" s="3" t="n"/>
+      <c r="V93" s="3" t="n"/>
+      <c r="W93" s="3" t="n"/>
+      <c r="X93" s="3" t="n"/>
+      <c r="Y93" s="3" t="n"/>
+      <c r="Z93" s="3" t="n"/>
+      <c r="AA93" s="3" t="n"/>
+      <c r="AB93" s="3" t="n"/>
+      <c r="AC93" s="3" t="n"/>
+      <c r="AD93" s="3" t="n"/>
+      <c r="AE93" s="3" t="n"/>
+      <c r="AF93" s="3" t="n"/>
+      <c r="AG93" s="3" t="n"/>
+      <c r="AH93" s="3" t="n"/>
+      <c r="AI93" s="3" t="n"/>
+      <c r="AJ93" s="3" t="n"/>
+      <c r="AK93" s="3">
+        <f>SUM(D93:AI93)</f>
+        <v/>
+      </c>
+      <c r="AL93" s="3" t="n"/>
+      <c r="AM93" s="3" t="n"/>
+      <c r="AN93" s="3" t="n"/>
+      <c r="AO93" s="3" t="n"/>
+      <c r="AP93" s="3">
+        <f>AJ93+AK93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n"/>
+      <c r="B94" s="3" t="n"/>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n"/>
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="n"/>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+      <c r="M94" s="3" t="n"/>
+      <c r="N94" s="3" t="n"/>
+      <c r="O94" s="3" t="n"/>
+      <c r="P94" s="3" t="n"/>
+      <c r="Q94" s="3" t="n"/>
+      <c r="R94" s="3" t="n"/>
+      <c r="S94" s="3" t="n"/>
+      <c r="T94" s="3" t="n"/>
+      <c r="U94" s="3" t="n"/>
+      <c r="V94" s="3" t="n"/>
+      <c r="W94" s="3" t="n"/>
+      <c r="X94" s="3" t="n"/>
+      <c r="Y94" s="3" t="n"/>
+      <c r="Z94" s="3" t="n"/>
+      <c r="AA94" s="3" t="n"/>
+      <c r="AB94" s="3" t="n"/>
+      <c r="AC94" s="3" t="n"/>
+      <c r="AD94" s="3" t="n"/>
+      <c r="AE94" s="3" t="n"/>
+      <c r="AF94" s="3" t="n"/>
+      <c r="AG94" s="3" t="n"/>
+      <c r="AH94" s="3" t="n"/>
+      <c r="AI94" s="3" t="n"/>
+      <c r="AJ94" s="3" t="n"/>
+      <c r="AK94" s="3">
+        <f>SUM(D94:AI94)</f>
+        <v/>
+      </c>
+      <c r="AL94" s="3" t="n"/>
+      <c r="AM94" s="3" t="n"/>
+      <c r="AN94" s="3" t="n"/>
+      <c r="AO94" s="3" t="n"/>
+      <c r="AP94" s="3">
+        <f>AJ94+AK94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n"/>
+      <c r="B95" s="3" t="n"/>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n"/>
+      <c r="E95" s="3" t="n"/>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
+      <c r="L95" s="3" t="n"/>
+      <c r="M95" s="3" t="n"/>
+      <c r="N95" s="3" t="n"/>
+      <c r="O95" s="3" t="n"/>
+      <c r="P95" s="3" t="n"/>
+      <c r="Q95" s="3" t="n"/>
+      <c r="R95" s="3" t="n"/>
+      <c r="S95" s="3" t="n"/>
+      <c r="T95" s="3" t="n"/>
+      <c r="U95" s="3" t="n"/>
+      <c r="V95" s="3" t="n"/>
+      <c r="W95" s="3" t="n"/>
+      <c r="X95" s="3" t="n"/>
+      <c r="Y95" s="3" t="n"/>
+      <c r="Z95" s="3" t="n"/>
+      <c r="AA95" s="3" t="n"/>
+      <c r="AB95" s="3" t="n"/>
+      <c r="AC95" s="3" t="n"/>
+      <c r="AD95" s="3" t="n"/>
+      <c r="AE95" s="3" t="n"/>
+      <c r="AF95" s="3" t="n"/>
+      <c r="AG95" s="3" t="n"/>
+      <c r="AH95" s="3" t="n"/>
+      <c r="AI95" s="3" t="n"/>
+      <c r="AJ95" s="3" t="n"/>
+      <c r="AK95" s="3">
+        <f>SUM(D95:AI95)</f>
+        <v/>
+      </c>
+      <c r="AL95" s="3" t="n"/>
+      <c r="AM95" s="3" t="n"/>
+      <c r="AN95" s="3" t="n"/>
+      <c r="AO95" s="3" t="n"/>
+      <c r="AP95" s="3">
+        <f>AJ95+AK95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n"/>
+      <c r="B96" s="3" t="n"/>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n"/>
+      <c r="E96" s="3" t="n"/>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="n"/>
+      <c r="L96" s="3" t="n"/>
+      <c r="M96" s="3" t="n"/>
+      <c r="N96" s="3" t="n"/>
+      <c r="O96" s="3" t="n"/>
+      <c r="P96" s="3" t="n"/>
+      <c r="Q96" s="3" t="n"/>
+      <c r="R96" s="3" t="n"/>
+      <c r="S96" s="3" t="n"/>
+      <c r="T96" s="3" t="n"/>
+      <c r="U96" s="3" t="n"/>
+      <c r="V96" s="3" t="n"/>
+      <c r="W96" s="3" t="n"/>
+      <c r="X96" s="3" t="n"/>
+      <c r="Y96" s="3" t="n"/>
+      <c r="Z96" s="3" t="n"/>
+      <c r="AA96" s="3" t="n"/>
+      <c r="AB96" s="3" t="n"/>
+      <c r="AC96" s="3" t="n"/>
+      <c r="AD96" s="3" t="n"/>
+      <c r="AE96" s="3" t="n"/>
+      <c r="AF96" s="3" t="n"/>
+      <c r="AG96" s="3" t="n"/>
+      <c r="AH96" s="3" t="n"/>
+      <c r="AI96" s="3" t="n"/>
+      <c r="AJ96" s="3" t="n"/>
+      <c r="AK96" s="3">
+        <f>SUM(D96:AI96)</f>
+        <v/>
+      </c>
+      <c r="AL96" s="3" t="n"/>
+      <c r="AM96" s="3" t="n"/>
+      <c r="AN96" s="3" t="n"/>
+      <c r="AO96" s="3" t="n"/>
+      <c r="AP96" s="3">
+        <f>AJ96+AK96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n"/>
+      <c r="B97" s="3" t="n"/>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n"/>
+      <c r="E97" s="3" t="n"/>
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="3" t="n"/>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="n"/>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="n"/>
+      <c r="L97" s="3" t="n"/>
+      <c r="M97" s="3" t="n"/>
+      <c r="N97" s="3" t="n"/>
+      <c r="O97" s="3" t="n"/>
+      <c r="P97" s="3" t="n"/>
+      <c r="Q97" s="3" t="n"/>
+      <c r="R97" s="3" t="n"/>
+      <c r="S97" s="3" t="n"/>
+      <c r="T97" s="3" t="n"/>
+      <c r="U97" s="3" t="n"/>
+      <c r="V97" s="3" t="n"/>
+      <c r="W97" s="3" t="n"/>
+      <c r="X97" s="3" t="n"/>
+      <c r="Y97" s="3" t="n"/>
+      <c r="Z97" s="3" t="n"/>
+      <c r="AA97" s="3" t="n"/>
+      <c r="AB97" s="3" t="n"/>
+      <c r="AC97" s="3" t="n"/>
+      <c r="AD97" s="3" t="n"/>
+      <c r="AE97" s="3" t="n"/>
+      <c r="AF97" s="3" t="n"/>
+      <c r="AG97" s="3" t="n"/>
+      <c r="AH97" s="3" t="n"/>
+      <c r="AI97" s="3" t="n"/>
+      <c r="AJ97" s="3" t="n"/>
+      <c r="AK97" s="3">
+        <f>SUM(D97:AI97)</f>
+        <v/>
+      </c>
+      <c r="AL97" s="3" t="n"/>
+      <c r="AM97" s="3" t="n"/>
+      <c r="AN97" s="3" t="n"/>
+      <c r="AO97" s="3" t="n"/>
+      <c r="AP97" s="3">
+        <f>AJ97+AK97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n"/>
+      <c r="B98" s="3" t="n"/>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n"/>
+      <c r="E98" s="3" t="n"/>
+      <c r="F98" s="3" t="n"/>
+      <c r="G98" s="3" t="n"/>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
+      <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="n"/>
+      <c r="L98" s="3" t="n"/>
+      <c r="M98" s="3" t="n"/>
+      <c r="N98" s="3" t="n"/>
+      <c r="O98" s="3" t="n"/>
+      <c r="P98" s="3" t="n"/>
+      <c r="Q98" s="3" t="n"/>
+      <c r="R98" s="3" t="n"/>
+      <c r="S98" s="3" t="n"/>
+      <c r="T98" s="3" t="n"/>
+      <c r="U98" s="3" t="n"/>
+      <c r="V98" s="3" t="n"/>
+      <c r="W98" s="3" t="n"/>
+      <c r="X98" s="3" t="n"/>
+      <c r="Y98" s="3" t="n"/>
+      <c r="Z98" s="3" t="n"/>
+      <c r="AA98" s="3" t="n"/>
+      <c r="AB98" s="3" t="n"/>
+      <c r="AC98" s="3" t="n"/>
+      <c r="AD98" s="3" t="n"/>
+      <c r="AE98" s="3" t="n"/>
+      <c r="AF98" s="3" t="n"/>
+      <c r="AG98" s="3" t="n"/>
+      <c r="AH98" s="3" t="n"/>
+      <c r="AI98" s="3" t="n"/>
+      <c r="AJ98" s="3" t="n"/>
+      <c r="AK98" s="3">
+        <f>SUM(D98:AI98)</f>
+        <v/>
+      </c>
+      <c r="AL98" s="3" t="n"/>
+      <c r="AM98" s="3" t="n"/>
+      <c r="AN98" s="3" t="n"/>
+      <c r="AO98" s="3" t="n"/>
+      <c r="AP98" s="3">
+        <f>AJ98+AK98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n"/>
+      <c r="B99" s="3" t="n"/>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n"/>
+      <c r="E99" s="3" t="n"/>
+      <c r="F99" s="3" t="n"/>
+      <c r="G99" s="3" t="n"/>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="n"/>
+      <c r="L99" s="3" t="n"/>
+      <c r="M99" s="3" t="n"/>
+      <c r="N99" s="3" t="n"/>
+      <c r="O99" s="3" t="n"/>
+      <c r="P99" s="3" t="n"/>
+      <c r="Q99" s="3" t="n"/>
+      <c r="R99" s="3" t="n"/>
+      <c r="S99" s="3" t="n"/>
+      <c r="T99" s="3" t="n"/>
+      <c r="U99" s="3" t="n"/>
+      <c r="V99" s="3" t="n"/>
+      <c r="W99" s="3" t="n"/>
+      <c r="X99" s="3" t="n"/>
+      <c r="Y99" s="3" t="n"/>
+      <c r="Z99" s="3" t="n"/>
+      <c r="AA99" s="3" t="n"/>
+      <c r="AB99" s="3" t="n"/>
+      <c r="AC99" s="3" t="n"/>
+      <c r="AD99" s="3" t="n"/>
+      <c r="AE99" s="3" t="n"/>
+      <c r="AF99" s="3" t="n"/>
+      <c r="AG99" s="3" t="n"/>
+      <c r="AH99" s="3" t="n"/>
+      <c r="AI99" s="3" t="n"/>
+      <c r="AJ99" s="3" t="n"/>
+      <c r="AK99" s="3">
+        <f>SUM(D99:AI99)</f>
+        <v/>
+      </c>
+      <c r="AL99" s="3" t="n"/>
+      <c r="AM99" s="3" t="n"/>
+      <c r="AN99" s="3" t="n"/>
+      <c r="AO99" s="3" t="n"/>
+      <c r="AP99" s="3">
+        <f>AJ99+AK99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n"/>
+      <c r="B100" s="3" t="n"/>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n"/>
+      <c r="E100" s="3" t="n"/>
+      <c r="F100" s="3" t="n"/>
+      <c r="G100" s="3" t="n"/>
+      <c r="H100" s="3" t="n"/>
+      <c r="I100" s="3" t="n"/>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="n"/>
+      <c r="L100" s="3" t="n"/>
+      <c r="M100" s="3" t="n"/>
+      <c r="N100" s="3" t="n"/>
+      <c r="O100" s="3" t="n"/>
+      <c r="P100" s="3" t="n"/>
+      <c r="Q100" s="3" t="n"/>
+      <c r="R100" s="3" t="n"/>
+      <c r="S100" s="3" t="n"/>
+      <c r="T100" s="3" t="n"/>
+      <c r="U100" s="3" t="n"/>
+      <c r="V100" s="3" t="n"/>
+      <c r="W100" s="3" t="n"/>
+      <c r="X100" s="3" t="n"/>
+      <c r="Y100" s="3" t="n"/>
+      <c r="Z100" s="3" t="n"/>
+      <c r="AA100" s="3" t="n"/>
+      <c r="AB100" s="3" t="n"/>
+      <c r="AC100" s="3" t="n"/>
+      <c r="AD100" s="3" t="n"/>
+      <c r="AE100" s="3" t="n"/>
+      <c r="AF100" s="3" t="n"/>
+      <c r="AG100" s="3" t="n"/>
+      <c r="AH100" s="3" t="n"/>
+      <c r="AI100" s="3" t="n"/>
+      <c r="AJ100" s="3" t="n"/>
+      <c r="AK100" s="3">
+        <f>SUM(D100:AI100)</f>
+        <v/>
+      </c>
+      <c r="AL100" s="3" t="n"/>
+      <c r="AM100" s="3" t="n"/>
+      <c r="AN100" s="3" t="n"/>
+      <c r="AO100" s="3" t="n"/>
+      <c r="AP100" s="3">
+        <f>AJ100+AK100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n"/>
+      <c r="B101" s="3" t="n"/>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n"/>
+      <c r="E101" s="3" t="n"/>
+      <c r="F101" s="3" t="n"/>
+      <c r="G101" s="3" t="n"/>
+      <c r="H101" s="3" t="n"/>
+      <c r="I101" s="3" t="n"/>
+      <c r="J101" s="3" t="n"/>
+      <c r="K101" s="3" t="n"/>
+      <c r="L101" s="3" t="n"/>
+      <c r="M101" s="3" t="n"/>
+      <c r="N101" s="3" t="n"/>
+      <c r="O101" s="3" t="n"/>
+      <c r="P101" s="3" t="n"/>
+      <c r="Q101" s="3" t="n"/>
+      <c r="R101" s="3" t="n"/>
+      <c r="S101" s="3" t="n"/>
+      <c r="T101" s="3" t="n"/>
+      <c r="U101" s="3" t="n"/>
+      <c r="V101" s="3" t="n"/>
+      <c r="W101" s="3" t="n"/>
+      <c r="X101" s="3" t="n"/>
+      <c r="Y101" s="3" t="n"/>
+      <c r="Z101" s="3" t="n"/>
+      <c r="AA101" s="3" t="n"/>
+      <c r="AB101" s="3" t="n"/>
+      <c r="AC101" s="3" t="n"/>
+      <c r="AD101" s="3" t="n"/>
+      <c r="AE101" s="3" t="n"/>
+      <c r="AF101" s="3" t="n"/>
+      <c r="AG101" s="3" t="n"/>
+      <c r="AH101" s="3" t="n"/>
+      <c r="AI101" s="3" t="n"/>
+      <c r="AJ101" s="3" t="n"/>
+      <c r="AK101" s="3">
+        <f>SUM(D101:AI101)</f>
+        <v/>
+      </c>
+      <c r="AL101" s="3" t="n"/>
+      <c r="AM101" s="3" t="n"/>
+      <c r="AN101" s="3" t="n"/>
+      <c r="AO101" s="3" t="n"/>
+      <c r="AP101" s="3">
+        <f>AJ101+AK101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n"/>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="3" t="n"/>
+      <c r="H102" s="3" t="n"/>
+      <c r="I102" s="3" t="n"/>
+      <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="n"/>
+      <c r="L102" s="3" t="n"/>
+      <c r="M102" s="3" t="n"/>
+      <c r="N102" s="3" t="n"/>
+      <c r="O102" s="3" t="n"/>
+      <c r="P102" s="3" t="n"/>
+      <c r="Q102" s="3" t="n"/>
+      <c r="R102" s="3" t="n"/>
+      <c r="S102" s="3" t="n"/>
+      <c r="T102" s="3" t="n"/>
+      <c r="U102" s="3" t="n"/>
+      <c r="V102" s="3" t="n"/>
+      <c r="W102" s="3" t="n"/>
+      <c r="X102" s="3" t="n"/>
+      <c r="Y102" s="3" t="n"/>
+      <c r="Z102" s="3" t="n"/>
+      <c r="AA102" s="3" t="n"/>
+      <c r="AB102" s="3" t="n"/>
+      <c r="AC102" s="3" t="n"/>
+      <c r="AD102" s="3" t="n"/>
+      <c r="AE102" s="3" t="n"/>
+      <c r="AF102" s="3" t="n"/>
+      <c r="AG102" s="3" t="n"/>
+      <c r="AH102" s="3" t="n"/>
+      <c r="AI102" s="3" t="n"/>
+      <c r="AJ102" s="3" t="n"/>
+      <c r="AK102" s="3">
+        <f>SUM(D102:AI102)</f>
+        <v/>
+      </c>
+      <c r="AL102" s="3" t="n"/>
+      <c r="AM102" s="3" t="n"/>
+      <c r="AN102" s="3" t="n"/>
+      <c r="AO102" s="3" t="n"/>
+      <c r="AP102" s="3">
+        <f>AJ102+AK102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n"/>
+      <c r="B103" s="3" t="n"/>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n"/>
+      <c r="E103" s="3" t="n"/>
+      <c r="F103" s="3" t="n"/>
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="3" t="n"/>
+      <c r="I103" s="3" t="n"/>
+      <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="n"/>
+      <c r="L103" s="3" t="n"/>
+      <c r="M103" s="3" t="n"/>
+      <c r="N103" s="3" t="n"/>
+      <c r="O103" s="3" t="n"/>
+      <c r="P103" s="3" t="n"/>
+      <c r="Q103" s="3" t="n"/>
+      <c r="R103" s="3" t="n"/>
+      <c r="S103" s="3" t="n"/>
+      <c r="T103" s="3" t="n"/>
+      <c r="U103" s="3" t="n"/>
+      <c r="V103" s="3" t="n"/>
+      <c r="W103" s="3" t="n"/>
+      <c r="X103" s="3" t="n"/>
+      <c r="Y103" s="3" t="n"/>
+      <c r="Z103" s="3" t="n"/>
+      <c r="AA103" s="3" t="n"/>
+      <c r="AB103" s="3" t="n"/>
+      <c r="AC103" s="3" t="n"/>
+      <c r="AD103" s="3" t="n"/>
+      <c r="AE103" s="3" t="n"/>
+      <c r="AF103" s="3" t="n"/>
+      <c r="AG103" s="3" t="n"/>
+      <c r="AH103" s="3" t="n"/>
+      <c r="AI103" s="3" t="n"/>
+      <c r="AJ103" s="3" t="n"/>
+      <c r="AK103" s="3">
+        <f>SUM(D103:AI103)</f>
+        <v/>
+      </c>
+      <c r="AL103" s="3" t="n"/>
+      <c r="AM103" s="3" t="n"/>
+      <c r="AN103" s="3" t="n"/>
+      <c r="AO103" s="3" t="n"/>
+      <c r="AP103" s="3">
+        <f>AJ103+AK103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n"/>
+      <c r="B104" s="3" t="n"/>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n"/>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="n"/>
+      <c r="G104" s="3" t="n"/>
+      <c r="H104" s="3" t="n"/>
+      <c r="I104" s="3" t="n"/>
+      <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="n"/>
+      <c r="L104" s="3" t="n"/>
+      <c r="M104" s="3" t="n"/>
+      <c r="N104" s="3" t="n"/>
+      <c r="O104" s="3" t="n"/>
+      <c r="P104" s="3" t="n"/>
+      <c r="Q104" s="3" t="n"/>
+      <c r="R104" s="3" t="n"/>
+      <c r="S104" s="3" t="n"/>
+      <c r="T104" s="3" t="n"/>
+      <c r="U104" s="3" t="n"/>
+      <c r="V104" s="3" t="n"/>
+      <c r="W104" s="3" t="n"/>
+      <c r="X104" s="3" t="n"/>
+      <c r="Y104" s="3" t="n"/>
+      <c r="Z104" s="3" t="n"/>
+      <c r="AA104" s="3" t="n"/>
+      <c r="AB104" s="3" t="n"/>
+      <c r="AC104" s="3" t="n"/>
+      <c r="AD104" s="3" t="n"/>
+      <c r="AE104" s="3" t="n"/>
+      <c r="AF104" s="3" t="n"/>
+      <c r="AG104" s="3" t="n"/>
+      <c r="AH104" s="3" t="n"/>
+      <c r="AI104" s="3" t="n"/>
+      <c r="AJ104" s="3" t="n"/>
+      <c r="AK104" s="3">
+        <f>SUM(D104:AI104)</f>
+        <v/>
+      </c>
+      <c r="AL104" s="3" t="n"/>
+      <c r="AM104" s="3" t="n"/>
+      <c r="AN104" s="3" t="n"/>
+      <c r="AO104" s="3" t="n"/>
+      <c r="AP104" s="3">
+        <f>AJ104+AK104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n"/>
+      <c r="B105" s="3" t="n"/>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n"/>
+      <c r="E105" s="3" t="n"/>
+      <c r="F105" s="3" t="n"/>
+      <c r="G105" s="3" t="n"/>
+      <c r="H105" s="3" t="n"/>
+      <c r="I105" s="3" t="n"/>
+      <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="n"/>
+      <c r="L105" s="3" t="n"/>
+      <c r="M105" s="3" t="n"/>
+      <c r="N105" s="3" t="n"/>
+      <c r="O105" s="3" t="n"/>
+      <c r="P105" s="3" t="n"/>
+      <c r="Q105" s="3" t="n"/>
+      <c r="R105" s="3" t="n"/>
+      <c r="S105" s="3" t="n"/>
+      <c r="T105" s="3" t="n"/>
+      <c r="U105" s="3" t="n"/>
+      <c r="V105" s="3" t="n"/>
+      <c r="W105" s="3" t="n"/>
+      <c r="X105" s="3" t="n"/>
+      <c r="Y105" s="3" t="n"/>
+      <c r="Z105" s="3" t="n"/>
+      <c r="AA105" s="3" t="n"/>
+      <c r="AB105" s="3" t="n"/>
+      <c r="AC105" s="3" t="n"/>
+      <c r="AD105" s="3" t="n"/>
+      <c r="AE105" s="3" t="n"/>
+      <c r="AF105" s="3" t="n"/>
+      <c r="AG105" s="3" t="n"/>
+      <c r="AH105" s="3" t="n"/>
+      <c r="AI105" s="3" t="n"/>
+      <c r="AJ105" s="3" t="n"/>
+      <c r="AK105" s="3">
+        <f>SUM(D105:AI105)</f>
+        <v/>
+      </c>
+      <c r="AL105" s="3" t="n"/>
+      <c r="AM105" s="3" t="n"/>
+      <c r="AN105" s="3" t="n"/>
+      <c r="AO105" s="3" t="n"/>
+      <c r="AP105" s="3">
+        <f>AJ105+AK105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n"/>
+      <c r="B106" s="3" t="n"/>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n"/>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="3" t="n"/>
+      <c r="G106" s="3" t="n"/>
+      <c r="H106" s="3" t="n"/>
+      <c r="I106" s="3" t="n"/>
+      <c r="J106" s="3" t="n"/>
+      <c r="K106" s="3" t="n"/>
+      <c r="L106" s="3" t="n"/>
+      <c r="M106" s="3" t="n"/>
+      <c r="N106" s="3" t="n"/>
+      <c r="O106" s="3" t="n"/>
+      <c r="P106" s="3" t="n"/>
+      <c r="Q106" s="3" t="n"/>
+      <c r="R106" s="3" t="n"/>
+      <c r="S106" s="3" t="n"/>
+      <c r="T106" s="3" t="n"/>
+      <c r="U106" s="3" t="n"/>
+      <c r="V106" s="3" t="n"/>
+      <c r="W106" s="3" t="n"/>
+      <c r="X106" s="3" t="n"/>
+      <c r="Y106" s="3" t="n"/>
+      <c r="Z106" s="3" t="n"/>
+      <c r="AA106" s="3" t="n"/>
+      <c r="AB106" s="3" t="n"/>
+      <c r="AC106" s="3" t="n"/>
+      <c r="AD106" s="3" t="n"/>
+      <c r="AE106" s="3" t="n"/>
+      <c r="AF106" s="3" t="n"/>
+      <c r="AG106" s="3" t="n"/>
+      <c r="AH106" s="3" t="n"/>
+      <c r="AI106" s="3" t="n"/>
+      <c r="AJ106" s="3" t="n"/>
+      <c r="AK106" s="3">
+        <f>SUM(D106:AI106)</f>
+        <v/>
+      </c>
+      <c r="AL106" s="3" t="n"/>
+      <c r="AM106" s="3" t="n"/>
+      <c r="AN106" s="3" t="n"/>
+      <c r="AO106" s="3" t="n"/>
+      <c r="AP106" s="3">
+        <f>AJ106+AK106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n"/>
+      <c r="B107" s="3" t="n"/>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n"/>
+      <c r="E107" s="3" t="n"/>
+      <c r="F107" s="3" t="n"/>
+      <c r="G107" s="3" t="n"/>
+      <c r="H107" s="3" t="n"/>
+      <c r="I107" s="3" t="n"/>
+      <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="n"/>
+      <c r="L107" s="3" t="n"/>
+      <c r="M107" s="3" t="n"/>
+      <c r="N107" s="3" t="n"/>
+      <c r="O107" s="3" t="n"/>
+      <c r="P107" s="3" t="n"/>
+      <c r="Q107" s="3" t="n"/>
+      <c r="R107" s="3" t="n"/>
+      <c r="S107" s="3" t="n"/>
+      <c r="T107" s="3" t="n"/>
+      <c r="U107" s="3" t="n"/>
+      <c r="V107" s="3" t="n"/>
+      <c r="W107" s="3" t="n"/>
+      <c r="X107" s="3" t="n"/>
+      <c r="Y107" s="3" t="n"/>
+      <c r="Z107" s="3" t="n"/>
+      <c r="AA107" s="3" t="n"/>
+      <c r="AB107" s="3" t="n"/>
+      <c r="AC107" s="3" t="n"/>
+      <c r="AD107" s="3" t="n"/>
+      <c r="AE107" s="3" t="n"/>
+      <c r="AF107" s="3" t="n"/>
+      <c r="AG107" s="3" t="n"/>
+      <c r="AH107" s="3" t="n"/>
+      <c r="AI107" s="3" t="n"/>
+      <c r="AJ107" s="3" t="n"/>
+      <c r="AK107" s="3">
+        <f>SUM(D107:AI107)</f>
+        <v/>
+      </c>
+      <c r="AL107" s="3" t="n"/>
+      <c r="AM107" s="3" t="n"/>
+      <c r="AN107" s="3" t="n"/>
+      <c r="AO107" s="3" t="n"/>
+      <c r="AP107" s="3">
+        <f>AJ107+AK107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n"/>
+      <c r="B108" s="3" t="n"/>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n"/>
+      <c r="E108" s="3" t="n"/>
+      <c r="F108" s="3" t="n"/>
+      <c r="G108" s="3" t="n"/>
+      <c r="H108" s="3" t="n"/>
+      <c r="I108" s="3" t="n"/>
+      <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="n"/>
+      <c r="L108" s="3" t="n"/>
+      <c r="M108" s="3" t="n"/>
+      <c r="N108" s="3" t="n"/>
+      <c r="O108" s="3" t="n"/>
+      <c r="P108" s="3" t="n"/>
+      <c r="Q108" s="3" t="n"/>
+      <c r="R108" s="3" t="n"/>
+      <c r="S108" s="3" t="n"/>
+      <c r="T108" s="3" t="n"/>
+      <c r="U108" s="3" t="n"/>
+      <c r="V108" s="3" t="n"/>
+      <c r="W108" s="3" t="n"/>
+      <c r="X108" s="3" t="n"/>
+      <c r="Y108" s="3" t="n"/>
+      <c r="Z108" s="3" t="n"/>
+      <c r="AA108" s="3" t="n"/>
+      <c r="AB108" s="3" t="n"/>
+      <c r="AC108" s="3" t="n"/>
+      <c r="AD108" s="3" t="n"/>
+      <c r="AE108" s="3" t="n"/>
+      <c r="AF108" s="3" t="n"/>
+      <c r="AG108" s="3" t="n"/>
+      <c r="AH108" s="3" t="n"/>
+      <c r="AI108" s="3" t="n"/>
+      <c r="AJ108" s="3" t="n"/>
+      <c r="AK108" s="3">
+        <f>SUM(D108:AI108)</f>
+        <v/>
+      </c>
+      <c r="AL108" s="3" t="n"/>
+      <c r="AM108" s="3" t="n"/>
+      <c r="AN108" s="3" t="n"/>
+      <c r="AO108" s="3" t="n"/>
+      <c r="AP108" s="3">
+        <f>AJ108+AK108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n"/>
+      <c r="B109" s="3" t="n"/>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n"/>
+      <c r="E109" s="3" t="n"/>
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="3" t="n"/>
+      <c r="H109" s="3" t="n"/>
+      <c r="I109" s="3" t="n"/>
+      <c r="J109" s="3" t="n"/>
+      <c r="K109" s="3" t="n"/>
+      <c r="L109" s="3" t="n"/>
+      <c r="M109" s="3" t="n"/>
+      <c r="N109" s="3" t="n"/>
+      <c r="O109" s="3" t="n"/>
+      <c r="P109" s="3" t="n"/>
+      <c r="Q109" s="3" t="n"/>
+      <c r="R109" s="3" t="n"/>
+      <c r="S109" s="3" t="n"/>
+      <c r="T109" s="3" t="n"/>
+      <c r="U109" s="3" t="n"/>
+      <c r="V109" s="3" t="n"/>
+      <c r="W109" s="3" t="n"/>
+      <c r="X109" s="3" t="n"/>
+      <c r="Y109" s="3" t="n"/>
+      <c r="Z109" s="3" t="n"/>
+      <c r="AA109" s="3" t="n"/>
+      <c r="AB109" s="3" t="n"/>
+      <c r="AC109" s="3" t="n"/>
+      <c r="AD109" s="3" t="n"/>
+      <c r="AE109" s="3" t="n"/>
+      <c r="AF109" s="3" t="n"/>
+      <c r="AG109" s="3" t="n"/>
+      <c r="AH109" s="3" t="n"/>
+      <c r="AI109" s="3" t="n"/>
+      <c r="AJ109" s="3" t="n"/>
+      <c r="AK109" s="3">
+        <f>SUM(D109:AI109)</f>
+        <v/>
+      </c>
+      <c r="AL109" s="3" t="n"/>
+      <c r="AM109" s="3" t="n"/>
+      <c r="AN109" s="3" t="n"/>
+      <c r="AO109" s="3" t="n"/>
+      <c r="AP109" s="3">
+        <f>AJ109+AK109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n"/>
+      <c r="B110" s="3" t="n"/>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n"/>
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="3" t="n"/>
+      <c r="G110" s="3" t="n"/>
+      <c r="H110" s="3" t="n"/>
+      <c r="I110" s="3" t="n"/>
+      <c r="J110" s="3" t="n"/>
+      <c r="K110" s="3" t="n"/>
+      <c r="L110" s="3" t="n"/>
+      <c r="M110" s="3" t="n"/>
+      <c r="N110" s="3" t="n"/>
+      <c r="O110" s="3" t="n"/>
+      <c r="P110" s="3" t="n"/>
+      <c r="Q110" s="3" t="n"/>
+      <c r="R110" s="3" t="n"/>
+      <c r="S110" s="3" t="n"/>
+      <c r="T110" s="3" t="n"/>
+      <c r="U110" s="3" t="n"/>
+      <c r="V110" s="3" t="n"/>
+      <c r="W110" s="3" t="n"/>
+      <c r="X110" s="3" t="n"/>
+      <c r="Y110" s="3" t="n"/>
+      <c r="Z110" s="3" t="n"/>
+      <c r="AA110" s="3" t="n"/>
+      <c r="AB110" s="3" t="n"/>
+      <c r="AC110" s="3" t="n"/>
+      <c r="AD110" s="3" t="n"/>
+      <c r="AE110" s="3" t="n"/>
+      <c r="AF110" s="3" t="n"/>
+      <c r="AG110" s="3" t="n"/>
+      <c r="AH110" s="3" t="n"/>
+      <c r="AI110" s="3" t="n"/>
+      <c r="AJ110" s="3" t="n"/>
+      <c r="AK110" s="3">
+        <f>SUM(D110:AI110)</f>
+        <v/>
+      </c>
+      <c r="AL110" s="3" t="n"/>
+      <c r="AM110" s="3" t="n"/>
+      <c r="AN110" s="3" t="n"/>
+      <c r="AO110" s="3" t="n"/>
+      <c r="AP110" s="3">
+        <f>AJ110+AK110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n"/>
+      <c r="B111" s="3" t="n"/>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n"/>
+      <c r="E111" s="3" t="n"/>
+      <c r="F111" s="3" t="n"/>
+      <c r="G111" s="3" t="n"/>
+      <c r="H111" s="3" t="n"/>
+      <c r="I111" s="3" t="n"/>
+      <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="n"/>
+      <c r="L111" s="3" t="n"/>
+      <c r="M111" s="3" t="n"/>
+      <c r="N111" s="3" t="n"/>
+      <c r="O111" s="3" t="n"/>
+      <c r="P111" s="3" t="n"/>
+      <c r="Q111" s="3" t="n"/>
+      <c r="R111" s="3" t="n"/>
+      <c r="S111" s="3" t="n"/>
+      <c r="T111" s="3" t="n"/>
+      <c r="U111" s="3" t="n"/>
+      <c r="V111" s="3" t="n"/>
+      <c r="W111" s="3" t="n"/>
+      <c r="X111" s="3" t="n"/>
+      <c r="Y111" s="3" t="n"/>
+      <c r="Z111" s="3" t="n"/>
+      <c r="AA111" s="3" t="n"/>
+      <c r="AB111" s="3" t="n"/>
+      <c r="AC111" s="3" t="n"/>
+      <c r="AD111" s="3" t="n"/>
+      <c r="AE111" s="3" t="n"/>
+      <c r="AF111" s="3" t="n"/>
+      <c r="AG111" s="3" t="n"/>
+      <c r="AH111" s="3" t="n"/>
+      <c r="AI111" s="3" t="n"/>
+      <c r="AJ111" s="3" t="n"/>
+      <c r="AK111" s="3">
+        <f>SUM(D111:AI111)</f>
+        <v/>
+      </c>
+      <c r="AL111" s="3" t="n"/>
+      <c r="AM111" s="3" t="n"/>
+      <c r="AN111" s="3" t="n"/>
+      <c r="AO111" s="3" t="n"/>
+      <c r="AP111" s="3">
+        <f>AJ111+AK111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n"/>
+      <c r="B112" s="3" t="n"/>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n"/>
+      <c r="E112" s="3" t="n"/>
+      <c r="F112" s="3" t="n"/>
+      <c r="G112" s="3" t="n"/>
+      <c r="H112" s="3" t="n"/>
+      <c r="I112" s="3" t="n"/>
+      <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="n"/>
+      <c r="L112" s="3" t="n"/>
+      <c r="M112" s="3" t="n"/>
+      <c r="N112" s="3" t="n"/>
+      <c r="O112" s="3" t="n"/>
+      <c r="P112" s="3" t="n"/>
+      <c r="Q112" s="3" t="n"/>
+      <c r="R112" s="3" t="n"/>
+      <c r="S112" s="3" t="n"/>
+      <c r="T112" s="3" t="n"/>
+      <c r="U112" s="3" t="n"/>
+      <c r="V112" s="3" t="n"/>
+      <c r="W112" s="3" t="n"/>
+      <c r="X112" s="3" t="n"/>
+      <c r="Y112" s="3" t="n"/>
+      <c r="Z112" s="3" t="n"/>
+      <c r="AA112" s="3" t="n"/>
+      <c r="AB112" s="3" t="n"/>
+      <c r="AC112" s="3" t="n"/>
+      <c r="AD112" s="3" t="n"/>
+      <c r="AE112" s="3" t="n"/>
+      <c r="AF112" s="3" t="n"/>
+      <c r="AG112" s="3" t="n"/>
+      <c r="AH112" s="3" t="n"/>
+      <c r="AI112" s="3" t="n"/>
+      <c r="AJ112" s="3" t="n"/>
+      <c r="AK112" s="3">
+        <f>SUM(D112:AI112)</f>
+        <v/>
+      </c>
+      <c r="AL112" s="3" t="n"/>
+      <c r="AM112" s="3" t="n"/>
+      <c r="AN112" s="3" t="n"/>
+      <c r="AO112" s="3" t="n"/>
+      <c r="AP112" s="3">
+        <f>AJ112+AK112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n"/>
+      <c r="B113" s="3" t="n"/>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n"/>
+      <c r="E113" s="3" t="n"/>
+      <c r="F113" s="3" t="n"/>
+      <c r="G113" s="3" t="n"/>
+      <c r="H113" s="3" t="n"/>
+      <c r="I113" s="3" t="n"/>
+      <c r="J113" s="3" t="n"/>
+      <c r="K113" s="3" t="n"/>
+      <c r="L113" s="3" t="n"/>
+      <c r="M113" s="3" t="n"/>
+      <c r="N113" s="3" t="n"/>
+      <c r="O113" s="3" t="n"/>
+      <c r="P113" s="3" t="n"/>
+      <c r="Q113" s="3" t="n"/>
+      <c r="R113" s="3" t="n"/>
+      <c r="S113" s="3" t="n"/>
+      <c r="T113" s="3" t="n"/>
+      <c r="U113" s="3" t="n"/>
+      <c r="V113" s="3" t="n"/>
+      <c r="W113" s="3" t="n"/>
+      <c r="X113" s="3" t="n"/>
+      <c r="Y113" s="3" t="n"/>
+      <c r="Z113" s="3" t="n"/>
+      <c r="AA113" s="3" t="n"/>
+      <c r="AB113" s="3" t="n"/>
+      <c r="AC113" s="3" t="n"/>
+      <c r="AD113" s="3" t="n"/>
+      <c r="AE113" s="3" t="n"/>
+      <c r="AF113" s="3" t="n"/>
+      <c r="AG113" s="3" t="n"/>
+      <c r="AH113" s="3" t="n"/>
+      <c r="AI113" s="3" t="n"/>
+      <c r="AJ113" s="3" t="n"/>
+      <c r="AK113" s="3">
+        <f>SUM(D113:AI113)</f>
+        <v/>
+      </c>
+      <c r="AL113" s="3" t="n"/>
+      <c r="AM113" s="3" t="n"/>
+      <c r="AN113" s="3" t="n"/>
+      <c r="AO113" s="3" t="n"/>
+      <c r="AP113" s="3">
+        <f>AJ113+AK113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n"/>
+      <c r="B114" s="3" t="n"/>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n"/>
+      <c r="E114" s="3" t="n"/>
+      <c r="F114" s="3" t="n"/>
+      <c r="G114" s="3" t="n"/>
+      <c r="H114" s="3" t="n"/>
+      <c r="I114" s="3" t="n"/>
+      <c r="J114" s="3" t="n"/>
+      <c r="K114" s="3" t="n"/>
+      <c r="L114" s="3" t="n"/>
+      <c r="M114" s="3" t="n"/>
+      <c r="N114" s="3" t="n"/>
+      <c r="O114" s="3" t="n"/>
+      <c r="P114" s="3" t="n"/>
+      <c r="Q114" s="3" t="n"/>
+      <c r="R114" s="3" t="n"/>
+      <c r="S114" s="3" t="n"/>
+      <c r="T114" s="3" t="n"/>
+      <c r="U114" s="3" t="n"/>
+      <c r="V114" s="3" t="n"/>
+      <c r="W114" s="3" t="n"/>
+      <c r="X114" s="3" t="n"/>
+      <c r="Y114" s="3" t="n"/>
+      <c r="Z114" s="3" t="n"/>
+      <c r="AA114" s="3" t="n"/>
+      <c r="AB114" s="3" t="n"/>
+      <c r="AC114" s="3" t="n"/>
+      <c r="AD114" s="3" t="n"/>
+      <c r="AE114" s="3" t="n"/>
+      <c r="AF114" s="3" t="n"/>
+      <c r="AG114" s="3" t="n"/>
+      <c r="AH114" s="3" t="n"/>
+      <c r="AI114" s="3" t="n"/>
+      <c r="AJ114" s="3" t="n"/>
+      <c r="AK114" s="3">
+        <f>SUM(D114:AI114)</f>
+        <v/>
+      </c>
+      <c r="AL114" s="3" t="n"/>
+      <c r="AM114" s="3" t="n"/>
+      <c r="AN114" s="3" t="n"/>
+      <c r="AO114" s="3" t="n"/>
+      <c r="AP114" s="3">
+        <f>AJ114+AK114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n"/>
+      <c r="B115" s="3" t="n"/>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n"/>
+      <c r="E115" s="3" t="n"/>
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="3" t="n"/>
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="n"/>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="n"/>
+      <c r="L115" s="3" t="n"/>
+      <c r="M115" s="3" t="n"/>
+      <c r="N115" s="3" t="n"/>
+      <c r="O115" s="3" t="n"/>
+      <c r="P115" s="3" t="n"/>
+      <c r="Q115" s="3" t="n"/>
+      <c r="R115" s="3" t="n"/>
+      <c r="S115" s="3" t="n"/>
+      <c r="T115" s="3" t="n"/>
+      <c r="U115" s="3" t="n"/>
+      <c r="V115" s="3" t="n"/>
+      <c r="W115" s="3" t="n"/>
+      <c r="X115" s="3" t="n"/>
+      <c r="Y115" s="3" t="n"/>
+      <c r="Z115" s="3" t="n"/>
+      <c r="AA115" s="3" t="n"/>
+      <c r="AB115" s="3" t="n"/>
+      <c r="AC115" s="3" t="n"/>
+      <c r="AD115" s="3" t="n"/>
+      <c r="AE115" s="3" t="n"/>
+      <c r="AF115" s="3" t="n"/>
+      <c r="AG115" s="3" t="n"/>
+      <c r="AH115" s="3" t="n"/>
+      <c r="AI115" s="3" t="n"/>
+      <c r="AJ115" s="3" t="n"/>
+      <c r="AK115" s="3">
+        <f>SUM(D115:AI115)</f>
+        <v/>
+      </c>
+      <c r="AL115" s="3" t="n"/>
+      <c r="AM115" s="3" t="n"/>
+      <c r="AN115" s="3" t="n"/>
+      <c r="AO115" s="3" t="n"/>
+      <c r="AP115" s="3">
+        <f>AJ115+AK115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n"/>
+      <c r="B116" s="3" t="n"/>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="3" t="n"/>
+      <c r="H116" s="3" t="n"/>
+      <c r="I116" s="3" t="n"/>
+      <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="n"/>
+      <c r="L116" s="3" t="n"/>
+      <c r="M116" s="3" t="n"/>
+      <c r="N116" s="3" t="n"/>
+      <c r="O116" s="3" t="n"/>
+      <c r="P116" s="3" t="n"/>
+      <c r="Q116" s="3" t="n"/>
+      <c r="R116" s="3" t="n"/>
+      <c r="S116" s="3" t="n"/>
+      <c r="T116" s="3" t="n"/>
+      <c r="U116" s="3" t="n"/>
+      <c r="V116" s="3" t="n"/>
+      <c r="W116" s="3" t="n"/>
+      <c r="X116" s="3" t="n"/>
+      <c r="Y116" s="3" t="n"/>
+      <c r="Z116" s="3" t="n"/>
+      <c r="AA116" s="3" t="n"/>
+      <c r="AB116" s="3" t="n"/>
+      <c r="AC116" s="3" t="n"/>
+      <c r="AD116" s="3" t="n"/>
+      <c r="AE116" s="3" t="n"/>
+      <c r="AF116" s="3" t="n"/>
+      <c r="AG116" s="3" t="n"/>
+      <c r="AH116" s="3" t="n"/>
+      <c r="AI116" s="3" t="n"/>
+      <c r="AJ116" s="3" t="n"/>
+      <c r="AK116" s="3">
+        <f>SUM(D116:AI116)</f>
+        <v/>
+      </c>
+      <c r="AL116" s="3" t="n"/>
+      <c r="AM116" s="3" t="n"/>
+      <c r="AN116" s="3" t="n"/>
+      <c r="AO116" s="3" t="n"/>
+      <c r="AP116" s="3">
+        <f>AJ116+AK116</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n"/>
+      <c r="B117" s="3" t="n"/>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n"/>
+      <c r="E117" s="3" t="n"/>
+      <c r="F117" s="3" t="n"/>
+      <c r="G117" s="3" t="n"/>
+      <c r="H117" s="3" t="n"/>
+      <c r="I117" s="3" t="n"/>
+      <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="n"/>
+      <c r="L117" s="3" t="n"/>
+      <c r="M117" s="3" t="n"/>
+      <c r="N117" s="3" t="n"/>
+      <c r="O117" s="3" t="n"/>
+      <c r="P117" s="3" t="n"/>
+      <c r="Q117" s="3" t="n"/>
+      <c r="R117" s="3" t="n"/>
+      <c r="S117" s="3" t="n"/>
+      <c r="T117" s="3" t="n"/>
+      <c r="U117" s="3" t="n"/>
+      <c r="V117" s="3" t="n"/>
+      <c r="W117" s="3" t="n"/>
+      <c r="X117" s="3" t="n"/>
+      <c r="Y117" s="3" t="n"/>
+      <c r="Z117" s="3" t="n"/>
+      <c r="AA117" s="3" t="n"/>
+      <c r="AB117" s="3" t="n"/>
+      <c r="AC117" s="3" t="n"/>
+      <c r="AD117" s="3" t="n"/>
+      <c r="AE117" s="3" t="n"/>
+      <c r="AF117" s="3" t="n"/>
+      <c r="AG117" s="3" t="n"/>
+      <c r="AH117" s="3" t="n"/>
+      <c r="AI117" s="3" t="n"/>
+      <c r="AJ117" s="3" t="n"/>
+      <c r="AK117" s="3">
+        <f>SUM(D117:AI117)</f>
+        <v/>
+      </c>
+      <c r="AL117" s="3" t="n"/>
+      <c r="AM117" s="3" t="n"/>
+      <c r="AN117" s="3" t="n"/>
+      <c r="AO117" s="3" t="n"/>
+      <c r="AP117" s="3">
+        <f>AJ117+AK117</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n"/>
+      <c r="B118" s="3" t="n"/>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n"/>
+      <c r="E118" s="3" t="n"/>
+      <c r="F118" s="3" t="n"/>
+      <c r="G118" s="3" t="n"/>
+      <c r="H118" s="3" t="n"/>
+      <c r="I118" s="3" t="n"/>
+      <c r="J118" s="3" t="n"/>
+      <c r="K118" s="3" t="n"/>
+      <c r="L118" s="3" t="n"/>
+      <c r="M118" s="3" t="n"/>
+      <c r="N118" s="3" t="n"/>
+      <c r="O118" s="3" t="n"/>
+      <c r="P118" s="3" t="n"/>
+      <c r="Q118" s="3" t="n"/>
+      <c r="R118" s="3" t="n"/>
+      <c r="S118" s="3" t="n"/>
+      <c r="T118" s="3" t="n"/>
+      <c r="U118" s="3" t="n"/>
+      <c r="V118" s="3" t="n"/>
+      <c r="W118" s="3" t="n"/>
+      <c r="X118" s="3" t="n"/>
+      <c r="Y118" s="3" t="n"/>
+      <c r="Z118" s="3" t="n"/>
+      <c r="AA118" s="3" t="n"/>
+      <c r="AB118" s="3" t="n"/>
+      <c r="AC118" s="3" t="n"/>
+      <c r="AD118" s="3" t="n"/>
+      <c r="AE118" s="3" t="n"/>
+      <c r="AF118" s="3" t="n"/>
+      <c r="AG118" s="3" t="n"/>
+      <c r="AH118" s="3" t="n"/>
+      <c r="AI118" s="3" t="n"/>
+      <c r="AJ118" s="3" t="n"/>
+      <c r="AK118" s="3">
+        <f>SUM(D118:AI118)</f>
+        <v/>
+      </c>
+      <c r="AL118" s="3" t="n"/>
+      <c r="AM118" s="3" t="n"/>
+      <c r="AN118" s="3" t="n"/>
+      <c r="AO118" s="3" t="n"/>
+      <c r="AP118" s="3">
+        <f>AJ118+AK118</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n"/>
+      <c r="B119" s="3" t="n"/>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n"/>
+      <c r="E119" s="3" t="n"/>
+      <c r="F119" s="3" t="n"/>
+      <c r="G119" s="3" t="n"/>
+      <c r="H119" s="3" t="n"/>
+      <c r="I119" s="3" t="n"/>
+      <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="n"/>
+      <c r="L119" s="3" t="n"/>
+      <c r="M119" s="3" t="n"/>
+      <c r="N119" s="3" t="n"/>
+      <c r="O119" s="3" t="n"/>
+      <c r="P119" s="3" t="n"/>
+      <c r="Q119" s="3" t="n"/>
+      <c r="R119" s="3" t="n"/>
+      <c r="S119" s="3" t="n"/>
+      <c r="T119" s="3" t="n"/>
+      <c r="U119" s="3" t="n"/>
+      <c r="V119" s="3" t="n"/>
+      <c r="W119" s="3" t="n"/>
+      <c r="X119" s="3" t="n"/>
+      <c r="Y119" s="3" t="n"/>
+      <c r="Z119" s="3" t="n"/>
+      <c r="AA119" s="3" t="n"/>
+      <c r="AB119" s="3" t="n"/>
+      <c r="AC119" s="3" t="n"/>
+      <c r="AD119" s="3" t="n"/>
+      <c r="AE119" s="3" t="n"/>
+      <c r="AF119" s="3" t="n"/>
+      <c r="AG119" s="3" t="n"/>
+      <c r="AH119" s="3" t="n"/>
+      <c r="AI119" s="3" t="n"/>
+      <c r="AJ119" s="3" t="n"/>
+      <c r="AK119" s="3">
+        <f>SUM(D119:AI119)</f>
+        <v/>
+      </c>
+      <c r="AL119" s="3" t="n"/>
+      <c r="AM119" s="3" t="n"/>
+      <c r="AN119" s="3" t="n"/>
+      <c r="AO119" s="3" t="n"/>
+      <c r="AP119" s="3">
+        <f>AJ119+AK119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n"/>
+      <c r="B120" s="3" t="n"/>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n"/>
+      <c r="E120" s="3" t="n"/>
+      <c r="F120" s="3" t="n"/>
+      <c r="G120" s="3" t="n"/>
+      <c r="H120" s="3" t="n"/>
+      <c r="I120" s="3" t="n"/>
+      <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="n"/>
+      <c r="L120" s="3" t="n"/>
+      <c r="M120" s="3" t="n"/>
+      <c r="N120" s="3" t="n"/>
+      <c r="O120" s="3" t="n"/>
+      <c r="P120" s="3" t="n"/>
+      <c r="Q120" s="3" t="n"/>
+      <c r="R120" s="3" t="n"/>
+      <c r="S120" s="3" t="n"/>
+      <c r="T120" s="3" t="n"/>
+      <c r="U120" s="3" t="n"/>
+      <c r="V120" s="3" t="n"/>
+      <c r="W120" s="3" t="n"/>
+      <c r="X120" s="3" t="n"/>
+      <c r="Y120" s="3" t="n"/>
+      <c r="Z120" s="3" t="n"/>
+      <c r="AA120" s="3" t="n"/>
+      <c r="AB120" s="3" t="n"/>
+      <c r="AC120" s="3" t="n"/>
+      <c r="AD120" s="3" t="n"/>
+      <c r="AE120" s="3" t="n"/>
+      <c r="AF120" s="3" t="n"/>
+      <c r="AG120" s="3" t="n"/>
+      <c r="AH120" s="3" t="n"/>
+      <c r="AI120" s="3" t="n"/>
+      <c r="AJ120" s="3" t="n"/>
+      <c r="AK120" s="3">
+        <f>SUM(D120:AI120)</f>
+        <v/>
+      </c>
+      <c r="AL120" s="3" t="n"/>
+      <c r="AM120" s="3" t="n"/>
+      <c r="AN120" s="3" t="n"/>
+      <c r="AO120" s="3" t="n"/>
+      <c r="AP120" s="3">
+        <f>AJ120+AK120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n"/>
+      <c r="B121" s="3" t="n"/>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n"/>
+      <c r="E121" s="3" t="n"/>
+      <c r="F121" s="3" t="n"/>
+      <c r="G121" s="3" t="n"/>
+      <c r="H121" s="3" t="n"/>
+      <c r="I121" s="3" t="n"/>
+      <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="n"/>
+      <c r="L121" s="3" t="n"/>
+      <c r="M121" s="3" t="n"/>
+      <c r="N121" s="3" t="n"/>
+      <c r="O121" s="3" t="n"/>
+      <c r="P121" s="3" t="n"/>
+      <c r="Q121" s="3" t="n"/>
+      <c r="R121" s="3" t="n"/>
+      <c r="S121" s="3" t="n"/>
+      <c r="T121" s="3" t="n"/>
+      <c r="U121" s="3" t="n"/>
+      <c r="V121" s="3" t="n"/>
+      <c r="W121" s="3" t="n"/>
+      <c r="X121" s="3" t="n"/>
+      <c r="Y121" s="3" t="n"/>
+      <c r="Z121" s="3" t="n"/>
+      <c r="AA121" s="3" t="n"/>
+      <c r="AB121" s="3" t="n"/>
+      <c r="AC121" s="3" t="n"/>
+      <c r="AD121" s="3" t="n"/>
+      <c r="AE121" s="3" t="n"/>
+      <c r="AF121" s="3" t="n"/>
+      <c r="AG121" s="3" t="n"/>
+      <c r="AH121" s="3" t="n"/>
+      <c r="AI121" s="3" t="n"/>
+      <c r="AJ121" s="3" t="n"/>
+      <c r="AK121" s="3">
+        <f>SUM(D121:AI121)</f>
+        <v/>
+      </c>
+      <c r="AL121" s="3" t="n"/>
+      <c r="AM121" s="3" t="n"/>
+      <c r="AN121" s="3" t="n"/>
+      <c r="AO121" s="3" t="n"/>
+      <c r="AP121" s="3">
+        <f>AJ121+AK121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n"/>
+      <c r="B122" s="3" t="n"/>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n"/>
+      <c r="E122" s="3" t="n"/>
+      <c r="F122" s="3" t="n"/>
+      <c r="G122" s="3" t="n"/>
+      <c r="H122" s="3" t="n"/>
+      <c r="I122" s="3" t="n"/>
+      <c r="J122" s="3" t="n"/>
+      <c r="K122" s="3" t="n"/>
+      <c r="L122" s="3" t="n"/>
+      <c r="M122" s="3" t="n"/>
+      <c r="N122" s="3" t="n"/>
+      <c r="O122" s="3" t="n"/>
+      <c r="P122" s="3" t="n"/>
+      <c r="Q122" s="3" t="n"/>
+      <c r="R122" s="3" t="n"/>
+      <c r="S122" s="3" t="n"/>
+      <c r="T122" s="3" t="n"/>
+      <c r="U122" s="3" t="n"/>
+      <c r="V122" s="3" t="n"/>
+      <c r="W122" s="3" t="n"/>
+      <c r="X122" s="3" t="n"/>
+      <c r="Y122" s="3" t="n"/>
+      <c r="Z122" s="3" t="n"/>
+      <c r="AA122" s="3" t="n"/>
+      <c r="AB122" s="3" t="n"/>
+      <c r="AC122" s="3" t="n"/>
+      <c r="AD122" s="3" t="n"/>
+      <c r="AE122" s="3" t="n"/>
+      <c r="AF122" s="3" t="n"/>
+      <c r="AG122" s="3" t="n"/>
+      <c r="AH122" s="3" t="n"/>
+      <c r="AI122" s="3" t="n"/>
+      <c r="AJ122" s="3" t="n"/>
+      <c r="AK122" s="3">
+        <f>SUM(D122:AI122)</f>
+        <v/>
+      </c>
+      <c r="AL122" s="3" t="n"/>
+      <c r="AM122" s="3" t="n"/>
+      <c r="AN122" s="3" t="n"/>
+      <c r="AO122" s="3" t="n"/>
+      <c r="AP122" s="3">
+        <f>AJ122+AK122</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n"/>
+      <c r="B123" s="3" t="n"/>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n"/>
+      <c r="E123" s="3" t="n"/>
+      <c r="F123" s="3" t="n"/>
+      <c r="G123" s="3" t="n"/>
+      <c r="H123" s="3" t="n"/>
+      <c r="I123" s="3" t="n"/>
+      <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="n"/>
+      <c r="L123" s="3" t="n"/>
+      <c r="M123" s="3" t="n"/>
+      <c r="N123" s="3" t="n"/>
+      <c r="O123" s="3" t="n"/>
+      <c r="P123" s="3" t="n"/>
+      <c r="Q123" s="3" t="n"/>
+      <c r="R123" s="3" t="n"/>
+      <c r="S123" s="3" t="n"/>
+      <c r="T123" s="3" t="n"/>
+      <c r="U123" s="3" t="n"/>
+      <c r="V123" s="3" t="n"/>
+      <c r="W123" s="3" t="n"/>
+      <c r="X123" s="3" t="n"/>
+      <c r="Y123" s="3" t="n"/>
+      <c r="Z123" s="3" t="n"/>
+      <c r="AA123" s="3" t="n"/>
+      <c r="AB123" s="3" t="n"/>
+      <c r="AC123" s="3" t="n"/>
+      <c r="AD123" s="3" t="n"/>
+      <c r="AE123" s="3" t="n"/>
+      <c r="AF123" s="3" t="n"/>
+      <c r="AG123" s="3" t="n"/>
+      <c r="AH123" s="3" t="n"/>
+      <c r="AI123" s="3" t="n"/>
+      <c r="AJ123" s="3" t="n"/>
+      <c r="AK123" s="3">
+        <f>SUM(D123:AI123)</f>
+        <v/>
+      </c>
+      <c r="AL123" s="3" t="n"/>
+      <c r="AM123" s="3" t="n"/>
+      <c r="AN123" s="3" t="n"/>
+      <c r="AO123" s="3" t="n"/>
+      <c r="AP123" s="3">
+        <f>AJ123+AK123</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n"/>
+      <c r="B124" s="3" t="n"/>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n"/>
+      <c r="E124" s="3" t="n"/>
+      <c r="F124" s="3" t="n"/>
+      <c r="G124" s="3" t="n"/>
+      <c r="H124" s="3" t="n"/>
+      <c r="I124" s="3" t="n"/>
+      <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="n"/>
+      <c r="L124" s="3" t="n"/>
+      <c r="M124" s="3" t="n"/>
+      <c r="N124" s="3" t="n"/>
+      <c r="O124" s="3" t="n"/>
+      <c r="P124" s="3" t="n"/>
+      <c r="Q124" s="3" t="n"/>
+      <c r="R124" s="3" t="n"/>
+      <c r="S124" s="3" t="n"/>
+      <c r="T124" s="3" t="n"/>
+      <c r="U124" s="3" t="n"/>
+      <c r="V124" s="3" t="n"/>
+      <c r="W124" s="3" t="n"/>
+      <c r="X124" s="3" t="n"/>
+      <c r="Y124" s="3" t="n"/>
+      <c r="Z124" s="3" t="n"/>
+      <c r="AA124" s="3" t="n"/>
+      <c r="AB124" s="3" t="n"/>
+      <c r="AC124" s="3" t="n"/>
+      <c r="AD124" s="3" t="n"/>
+      <c r="AE124" s="3" t="n"/>
+      <c r="AF124" s="3" t="n"/>
+      <c r="AG124" s="3" t="n"/>
+      <c r="AH124" s="3" t="n"/>
+      <c r="AI124" s="3" t="n"/>
+      <c r="AJ124" s="3" t="n"/>
+      <c r="AK124" s="3">
+        <f>SUM(D124:AI124)</f>
+        <v/>
+      </c>
+      <c r="AL124" s="3" t="n"/>
+      <c r="AM124" s="3" t="n"/>
+      <c r="AN124" s="3" t="n"/>
+      <c r="AO124" s="3" t="n"/>
+      <c r="AP124" s="3">
+        <f>AJ124+AK124</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n"/>
+      <c r="B125" s="3" t="n"/>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n"/>
+      <c r="E125" s="3" t="n"/>
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="3" t="n"/>
+      <c r="H125" s="3" t="n"/>
+      <c r="I125" s="3" t="n"/>
+      <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="n"/>
+      <c r="L125" s="3" t="n"/>
+      <c r="M125" s="3" t="n"/>
+      <c r="N125" s="3" t="n"/>
+      <c r="O125" s="3" t="n"/>
+      <c r="P125" s="3" t="n"/>
+      <c r="Q125" s="3" t="n"/>
+      <c r="R125" s="3" t="n"/>
+      <c r="S125" s="3" t="n"/>
+      <c r="T125" s="3" t="n"/>
+      <c r="U125" s="3" t="n"/>
+      <c r="V125" s="3" t="n"/>
+      <c r="W125" s="3" t="n"/>
+      <c r="X125" s="3" t="n"/>
+      <c r="Y125" s="3" t="n"/>
+      <c r="Z125" s="3" t="n"/>
+      <c r="AA125" s="3" t="n"/>
+      <c r="AB125" s="3" t="n"/>
+      <c r="AC125" s="3" t="n"/>
+      <c r="AD125" s="3" t="n"/>
+      <c r="AE125" s="3" t="n"/>
+      <c r="AF125" s="3" t="n"/>
+      <c r="AG125" s="3" t="n"/>
+      <c r="AH125" s="3" t="n"/>
+      <c r="AI125" s="3" t="n"/>
+      <c r="AJ125" s="3" t="n"/>
+      <c r="AK125" s="3">
+        <f>SUM(D125:AI125)</f>
+        <v/>
+      </c>
+      <c r="AL125" s="3" t="n"/>
+      <c r="AM125" s="3" t="n"/>
+      <c r="AN125" s="3" t="n"/>
+      <c r="AO125" s="3" t="n"/>
+      <c r="AP125" s="3">
+        <f>AJ125+AK125</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="n"/>
+      <c r="B126" s="3" t="n"/>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n"/>
+      <c r="E126" s="3" t="n"/>
+      <c r="F126" s="3" t="n"/>
+      <c r="G126" s="3" t="n"/>
+      <c r="H126" s="3" t="n"/>
+      <c r="I126" s="3" t="n"/>
+      <c r="J126" s="3" t="n"/>
+      <c r="K126" s="3" t="n"/>
+      <c r="L126" s="3" t="n"/>
+      <c r="M126" s="3" t="n"/>
+      <c r="N126" s="3" t="n"/>
+      <c r="O126" s="3" t="n"/>
+      <c r="P126" s="3" t="n"/>
+      <c r="Q126" s="3" t="n"/>
+      <c r="R126" s="3" t="n"/>
+      <c r="S126" s="3" t="n"/>
+      <c r="T126" s="3" t="n"/>
+      <c r="U126" s="3" t="n"/>
+      <c r="V126" s="3" t="n"/>
+      <c r="W126" s="3" t="n"/>
+      <c r="X126" s="3" t="n"/>
+      <c r="Y126" s="3" t="n"/>
+      <c r="Z126" s="3" t="n"/>
+      <c r="AA126" s="3" t="n"/>
+      <c r="AB126" s="3" t="n"/>
+      <c r="AC126" s="3" t="n"/>
+      <c r="AD126" s="3" t="n"/>
+      <c r="AE126" s="3" t="n"/>
+      <c r="AF126" s="3" t="n"/>
+      <c r="AG126" s="3" t="n"/>
+      <c r="AH126" s="3" t="n"/>
+      <c r="AI126" s="3" t="n"/>
+      <c r="AJ126" s="3" t="n"/>
+      <c r="AK126" s="3">
+        <f>SUM(D126:AI126)</f>
+        <v/>
+      </c>
+      <c r="AL126" s="3" t="n"/>
+      <c r="AM126" s="3" t="n"/>
+      <c r="AN126" s="3" t="n"/>
+      <c r="AO126" s="3" t="n"/>
+      <c r="AP126" s="3">
+        <f>AJ126+AK126</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n"/>
+      <c r="B127" s="3" t="n"/>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n"/>
+      <c r="E127" s="3" t="n"/>
+      <c r="F127" s="3" t="n"/>
+      <c r="G127" s="3" t="n"/>
+      <c r="H127" s="3" t="n"/>
+      <c r="I127" s="3" t="n"/>
+      <c r="J127" s="3" t="n"/>
+      <c r="K127" s="3" t="n"/>
+      <c r="L127" s="3" t="n"/>
+      <c r="M127" s="3" t="n"/>
+      <c r="N127" s="3" t="n"/>
+      <c r="O127" s="3" t="n"/>
+      <c r="P127" s="3" t="n"/>
+      <c r="Q127" s="3" t="n"/>
+      <c r="R127" s="3" t="n"/>
+      <c r="S127" s="3" t="n"/>
+      <c r="T127" s="3" t="n"/>
+      <c r="U127" s="3" t="n"/>
+      <c r="V127" s="3" t="n"/>
+      <c r="W127" s="3" t="n"/>
+      <c r="X127" s="3" t="n"/>
+      <c r="Y127" s="3" t="n"/>
+      <c r="Z127" s="3" t="n"/>
+      <c r="AA127" s="3" t="n"/>
+      <c r="AB127" s="3" t="n"/>
+      <c r="AC127" s="3" t="n"/>
+      <c r="AD127" s="3" t="n"/>
+      <c r="AE127" s="3" t="n"/>
+      <c r="AF127" s="3" t="n"/>
+      <c r="AG127" s="3" t="n"/>
+      <c r="AH127" s="3" t="n"/>
+      <c r="AI127" s="3" t="n"/>
+      <c r="AJ127" s="3" t="n"/>
+      <c r="AK127" s="3">
+        <f>SUM(D127:AI127)</f>
+        <v/>
+      </c>
+      <c r="AL127" s="3" t="n"/>
+      <c r="AM127" s="3" t="n"/>
+      <c r="AN127" s="3" t="n"/>
+      <c r="AO127" s="3" t="n"/>
+      <c r="AP127" s="3">
+        <f>AJ127+AK127</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n"/>
+      <c r="B128" s="3" t="n"/>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n"/>
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="3" t="n"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
+      <c r="I128" s="3" t="n"/>
+      <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="n"/>
+      <c r="L128" s="3" t="n"/>
+      <c r="M128" s="3" t="n"/>
+      <c r="N128" s="3" t="n"/>
+      <c r="O128" s="3" t="n"/>
+      <c r="P128" s="3" t="n"/>
+      <c r="Q128" s="3" t="n"/>
+      <c r="R128" s="3" t="n"/>
+      <c r="S128" s="3" t="n"/>
+      <c r="T128" s="3" t="n"/>
+      <c r="U128" s="3" t="n"/>
+      <c r="V128" s="3" t="n"/>
+      <c r="W128" s="3" t="n"/>
+      <c r="X128" s="3" t="n"/>
+      <c r="Y128" s="3" t="n"/>
+      <c r="Z128" s="3" t="n"/>
+      <c r="AA128" s="3" t="n"/>
+      <c r="AB128" s="3" t="n"/>
+      <c r="AC128" s="3" t="n"/>
+      <c r="AD128" s="3" t="n"/>
+      <c r="AE128" s="3" t="n"/>
+      <c r="AF128" s="3" t="n"/>
+      <c r="AG128" s="3" t="n"/>
+      <c r="AH128" s="3" t="n"/>
+      <c r="AI128" s="3" t="n"/>
+      <c r="AJ128" s="3" t="n"/>
+      <c r="AK128" s="3">
+        <f>SUM(D128:AI128)</f>
+        <v/>
+      </c>
+      <c r="AL128" s="3" t="n"/>
+      <c r="AM128" s="3" t="n"/>
+      <c r="AN128" s="3" t="n"/>
+      <c r="AO128" s="3" t="n"/>
+      <c r="AP128" s="3">
+        <f>AJ128+AK128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n"/>
+      <c r="B129" s="3" t="n"/>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n"/>
+      <c r="E129" s="3" t="n"/>
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="3" t="n"/>
+      <c r="H129" s="3" t="n"/>
+      <c r="I129" s="3" t="n"/>
+      <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="n"/>
+      <c r="L129" s="3" t="n"/>
+      <c r="M129" s="3" t="n"/>
+      <c r="N129" s="3" t="n"/>
+      <c r="O129" s="3" t="n"/>
+      <c r="P129" s="3" t="n"/>
+      <c r="Q129" s="3" t="n"/>
+      <c r="R129" s="3" t="n"/>
+      <c r="S129" s="3" t="n"/>
+      <c r="T129" s="3" t="n"/>
+      <c r="U129" s="3" t="n"/>
+      <c r="V129" s="3" t="n"/>
+      <c r="W129" s="3" t="n"/>
+      <c r="X129" s="3" t="n"/>
+      <c r="Y129" s="3" t="n"/>
+      <c r="Z129" s="3" t="n"/>
+      <c r="AA129" s="3" t="n"/>
+      <c r="AB129" s="3" t="n"/>
+      <c r="AC129" s="3" t="n"/>
+      <c r="AD129" s="3" t="n"/>
+      <c r="AE129" s="3" t="n"/>
+      <c r="AF129" s="3" t="n"/>
+      <c r="AG129" s="3" t="n"/>
+      <c r="AH129" s="3" t="n"/>
+      <c r="AI129" s="3" t="n"/>
+      <c r="AJ129" s="3" t="n"/>
+      <c r="AK129" s="3">
+        <f>SUM(D129:AI129)</f>
+        <v/>
+      </c>
+      <c r="AL129" s="3" t="n"/>
+      <c r="AM129" s="3" t="n"/>
+      <c r="AN129" s="3" t="n"/>
+      <c r="AO129" s="3" t="n"/>
+      <c r="AP129" s="3">
+        <f>AJ129+AK129</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="n"/>
+      <c r="B130" s="3" t="n"/>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
+      <c r="I130" s="3" t="n"/>
+      <c r="J130" s="3" t="n"/>
+      <c r="K130" s="3" t="n"/>
+      <c r="L130" s="3" t="n"/>
+      <c r="M130" s="3" t="n"/>
+      <c r="N130" s="3" t="n"/>
+      <c r="O130" s="3" t="n"/>
+      <c r="P130" s="3" t="n"/>
+      <c r="Q130" s="3" t="n"/>
+      <c r="R130" s="3" t="n"/>
+      <c r="S130" s="3" t="n"/>
+      <c r="T130" s="3" t="n"/>
+      <c r="U130" s="3" t="n"/>
+      <c r="V130" s="3" t="n"/>
+      <c r="W130" s="3" t="n"/>
+      <c r="X130" s="3" t="n"/>
+      <c r="Y130" s="3" t="n"/>
+      <c r="Z130" s="3" t="n"/>
+      <c r="AA130" s="3" t="n"/>
+      <c r="AB130" s="3" t="n"/>
+      <c r="AC130" s="3" t="n"/>
+      <c r="AD130" s="3" t="n"/>
+      <c r="AE130" s="3" t="n"/>
+      <c r="AF130" s="3" t="n"/>
+      <c r="AG130" s="3" t="n"/>
+      <c r="AH130" s="3" t="n"/>
+      <c r="AI130" s="3" t="n"/>
+      <c r="AJ130" s="3" t="n"/>
+      <c r="AK130" s="3">
+        <f>SUM(D130:AI130)</f>
+        <v/>
+      </c>
+      <c r="AL130" s="3" t="n"/>
+      <c r="AM130" s="3" t="n"/>
+      <c r="AN130" s="3" t="n"/>
+      <c r="AO130" s="3" t="n"/>
+      <c r="AP130" s="3">
+        <f>AJ130+AK130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n"/>
+      <c r="B131" s="3" t="n"/>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n"/>
+      <c r="E131" s="3" t="n"/>
+      <c r="F131" s="3" t="n"/>
+      <c r="G131" s="3" t="n"/>
+      <c r="H131" s="3" t="n"/>
+      <c r="I131" s="3" t="n"/>
+      <c r="J131" s="3" t="n"/>
+      <c r="K131" s="3" t="n"/>
+      <c r="L131" s="3" t="n"/>
+      <c r="M131" s="3" t="n"/>
+      <c r="N131" s="3" t="n"/>
+      <c r="O131" s="3" t="n"/>
+      <c r="P131" s="3" t="n"/>
+      <c r="Q131" s="3" t="n"/>
+      <c r="R131" s="3" t="n"/>
+      <c r="S131" s="3" t="n"/>
+      <c r="T131" s="3" t="n"/>
+      <c r="U131" s="3" t="n"/>
+      <c r="V131" s="3" t="n"/>
+      <c r="W131" s="3" t="n"/>
+      <c r="X131" s="3" t="n"/>
+      <c r="Y131" s="3" t="n"/>
+      <c r="Z131" s="3" t="n"/>
+      <c r="AA131" s="3" t="n"/>
+      <c r="AB131" s="3" t="n"/>
+      <c r="AC131" s="3" t="n"/>
+      <c r="AD131" s="3" t="n"/>
+      <c r="AE131" s="3" t="n"/>
+      <c r="AF131" s="3" t="n"/>
+      <c r="AG131" s="3" t="n"/>
+      <c r="AH131" s="3" t="n"/>
+      <c r="AI131" s="3" t="n"/>
+      <c r="AJ131" s="3" t="n"/>
+      <c r="AK131" s="3">
+        <f>SUM(D131:AI131)</f>
+        <v/>
+      </c>
+      <c r="AL131" s="3" t="n"/>
+      <c r="AM131" s="3" t="n"/>
+      <c r="AN131" s="3" t="n"/>
+      <c r="AO131" s="3" t="n"/>
+      <c r="AP131" s="3">
+        <f>AJ131+AK131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n"/>
+      <c r="B132" s="3" t="n"/>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n"/>
+      <c r="E132" s="3" t="n"/>
+      <c r="F132" s="3" t="n"/>
+      <c r="G132" s="3" t="n"/>
+      <c r="H132" s="3" t="n"/>
+      <c r="I132" s="3" t="n"/>
+      <c r="J132" s="3" t="n"/>
+      <c r="K132" s="3" t="n"/>
+      <c r="L132" s="3" t="n"/>
+      <c r="M132" s="3" t="n"/>
+      <c r="N132" s="3" t="n"/>
+      <c r="O132" s="3" t="n"/>
+      <c r="P132" s="3" t="n"/>
+      <c r="Q132" s="3" t="n"/>
+      <c r="R132" s="3" t="n"/>
+      <c r="S132" s="3" t="n"/>
+      <c r="T132" s="3" t="n"/>
+      <c r="U132" s="3" t="n"/>
+      <c r="V132" s="3" t="n"/>
+      <c r="W132" s="3" t="n"/>
+      <c r="X132" s="3" t="n"/>
+      <c r="Y132" s="3" t="n"/>
+      <c r="Z132" s="3" t="n"/>
+      <c r="AA132" s="3" t="n"/>
+      <c r="AB132" s="3" t="n"/>
+      <c r="AC132" s="3" t="n"/>
+      <c r="AD132" s="3" t="n"/>
+      <c r="AE132" s="3" t="n"/>
+      <c r="AF132" s="3" t="n"/>
+      <c r="AG132" s="3" t="n"/>
+      <c r="AH132" s="3" t="n"/>
+      <c r="AI132" s="3" t="n"/>
+      <c r="AJ132" s="3" t="n"/>
+      <c r="AK132" s="3">
+        <f>SUM(D132:AI132)</f>
+        <v/>
+      </c>
+      <c r="AL132" s="3" t="n"/>
+      <c r="AM132" s="3" t="n"/>
+      <c r="AN132" s="3" t="n"/>
+      <c r="AO132" s="3" t="n"/>
+      <c r="AP132" s="3">
+        <f>AJ132+AK132</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n"/>
+      <c r="B133" s="3" t="n"/>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n"/>
+      <c r="E133" s="3" t="n"/>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="3" t="n"/>
+      <c r="H133" s="3" t="n"/>
+      <c r="I133" s="3" t="n"/>
+      <c r="J133" s="3" t="n"/>
+      <c r="K133" s="3" t="n"/>
+      <c r="L133" s="3" t="n"/>
+      <c r="M133" s="3" t="n"/>
+      <c r="N133" s="3" t="n"/>
+      <c r="O133" s="3" t="n"/>
+      <c r="P133" s="3" t="n"/>
+      <c r="Q133" s="3" t="n"/>
+      <c r="R133" s="3" t="n"/>
+      <c r="S133" s="3" t="n"/>
+      <c r="T133" s="3" t="n"/>
+      <c r="U133" s="3" t="n"/>
+      <c r="V133" s="3" t="n"/>
+      <c r="W133" s="3" t="n"/>
+      <c r="X133" s="3" t="n"/>
+      <c r="Y133" s="3" t="n"/>
+      <c r="Z133" s="3" t="n"/>
+      <c r="AA133" s="3" t="n"/>
+      <c r="AB133" s="3" t="n"/>
+      <c r="AC133" s="3" t="n"/>
+      <c r="AD133" s="3" t="n"/>
+      <c r="AE133" s="3" t="n"/>
+      <c r="AF133" s="3" t="n"/>
+      <c r="AG133" s="3" t="n"/>
+      <c r="AH133" s="3" t="n"/>
+      <c r="AI133" s="3" t="n"/>
+      <c r="AJ133" s="3" t="n"/>
+      <c r="AK133" s="3">
+        <f>SUM(D133:AI133)</f>
+        <v/>
+      </c>
+      <c r="AL133" s="3" t="n"/>
+      <c r="AM133" s="3" t="n"/>
+      <c r="AN133" s="3" t="n"/>
+      <c r="AO133" s="3" t="n"/>
+      <c r="AP133" s="3">
+        <f>AJ133+AK133</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n"/>
+      <c r="B134" s="3" t="n"/>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n"/>
+      <c r="E134" s="3" t="n"/>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="n"/>
+      <c r="L134" s="3" t="n"/>
+      <c r="M134" s="3" t="n"/>
+      <c r="N134" s="3" t="n"/>
+      <c r="O134" s="3" t="n"/>
+      <c r="P134" s="3" t="n"/>
+      <c r="Q134" s="3" t="n"/>
+      <c r="R134" s="3" t="n"/>
+      <c r="S134" s="3" t="n"/>
+      <c r="T134" s="3" t="n"/>
+      <c r="U134" s="3" t="n"/>
+      <c r="V134" s="3" t="n"/>
+      <c r="W134" s="3" t="n"/>
+      <c r="X134" s="3" t="n"/>
+      <c r="Y134" s="3" t="n"/>
+      <c r="Z134" s="3" t="n"/>
+      <c r="AA134" s="3" t="n"/>
+      <c r="AB134" s="3" t="n"/>
+      <c r="AC134" s="3" t="n"/>
+      <c r="AD134" s="3" t="n"/>
+      <c r="AE134" s="3" t="n"/>
+      <c r="AF134" s="3" t="n"/>
+      <c r="AG134" s="3" t="n"/>
+      <c r="AH134" s="3" t="n"/>
+      <c r="AI134" s="3" t="n"/>
+      <c r="AJ134" s="3" t="n"/>
+      <c r="AK134" s="3">
+        <f>SUM(D134:AI134)</f>
+        <v/>
+      </c>
+      <c r="AL134" s="3" t="n"/>
+      <c r="AM134" s="3" t="n"/>
+      <c r="AN134" s="3" t="n"/>
+      <c r="AO134" s="3" t="n"/>
+      <c r="AP134" s="3">
+        <f>AJ134+AK134</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n"/>
+      <c r="B135" s="3" t="n"/>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n"/>
+      <c r="E135" s="3" t="n"/>
+      <c r="F135" s="3" t="n"/>
+      <c r="G135" s="3" t="n"/>
+      <c r="H135" s="3" t="n"/>
+      <c r="I135" s="3" t="n"/>
+      <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="n"/>
+      <c r="L135" s="3" t="n"/>
+      <c r="M135" s="3" t="n"/>
+      <c r="N135" s="3" t="n"/>
+      <c r="O135" s="3" t="n"/>
+      <c r="P135" s="3" t="n"/>
+      <c r="Q135" s="3" t="n"/>
+      <c r="R135" s="3" t="n"/>
+      <c r="S135" s="3" t="n"/>
+      <c r="T135" s="3" t="n"/>
+      <c r="U135" s="3" t="n"/>
+      <c r="V135" s="3" t="n"/>
+      <c r="W135" s="3" t="n"/>
+      <c r="X135" s="3" t="n"/>
+      <c r="Y135" s="3" t="n"/>
+      <c r="Z135" s="3" t="n"/>
+      <c r="AA135" s="3" t="n"/>
+      <c r="AB135" s="3" t="n"/>
+      <c r="AC135" s="3" t="n"/>
+      <c r="AD135" s="3" t="n"/>
+      <c r="AE135" s="3" t="n"/>
+      <c r="AF135" s="3" t="n"/>
+      <c r="AG135" s="3" t="n"/>
+      <c r="AH135" s="3" t="n"/>
+      <c r="AI135" s="3" t="n"/>
+      <c r="AJ135" s="3" t="n"/>
+      <c r="AK135" s="3">
+        <f>SUM(D135:AI135)</f>
+        <v/>
+      </c>
+      <c r="AL135" s="3" t="n"/>
+      <c r="AM135" s="3" t="n"/>
+      <c r="AN135" s="3" t="n"/>
+      <c r="AO135" s="3" t="n"/>
+      <c r="AP135" s="3">
+        <f>AJ135+AK135</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="n"/>
+      <c r="B136" s="3" t="n"/>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n"/>
+      <c r="E136" s="3" t="n"/>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
+      <c r="I136" s="3" t="n"/>
+      <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="n"/>
+      <c r="L136" s="3" t="n"/>
+      <c r="M136" s="3" t="n"/>
+      <c r="N136" s="3" t="n"/>
+      <c r="O136" s="3" t="n"/>
+      <c r="P136" s="3" t="n"/>
+      <c r="Q136" s="3" t="n"/>
+      <c r="R136" s="3" t="n"/>
+      <c r="S136" s="3" t="n"/>
+      <c r="T136" s="3" t="n"/>
+      <c r="U136" s="3" t="n"/>
+      <c r="V136" s="3" t="n"/>
+      <c r="W136" s="3" t="n"/>
+      <c r="X136" s="3" t="n"/>
+      <c r="Y136" s="3" t="n"/>
+      <c r="Z136" s="3" t="n"/>
+      <c r="AA136" s="3" t="n"/>
+      <c r="AB136" s="3" t="n"/>
+      <c r="AC136" s="3" t="n"/>
+      <c r="AD136" s="3" t="n"/>
+      <c r="AE136" s="3" t="n"/>
+      <c r="AF136" s="3" t="n"/>
+      <c r="AG136" s="3" t="n"/>
+      <c r="AH136" s="3" t="n"/>
+      <c r="AI136" s="3" t="n"/>
+      <c r="AJ136" s="3" t="n"/>
+      <c r="AK136" s="3">
+        <f>SUM(D136:AI136)</f>
+        <v/>
+      </c>
+      <c r="AL136" s="3" t="n"/>
+      <c r="AM136" s="3" t="n"/>
+      <c r="AN136" s="3" t="n"/>
+      <c r="AO136" s="3" t="n"/>
+      <c r="AP136" s="3">
+        <f>AJ136+AK136</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n"/>
+      <c r="B137" s="3" t="n"/>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n"/>
+      <c r="E137" s="3" t="n"/>
+      <c r="F137" s="3" t="n"/>
+      <c r="G137" s="3" t="n"/>
+      <c r="H137" s="3" t="n"/>
+      <c r="I137" s="3" t="n"/>
+      <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="n"/>
+      <c r="L137" s="3" t="n"/>
+      <c r="M137" s="3" t="n"/>
+      <c r="N137" s="3" t="n"/>
+      <c r="O137" s="3" t="n"/>
+      <c r="P137" s="3" t="n"/>
+      <c r="Q137" s="3" t="n"/>
+      <c r="R137" s="3" t="n"/>
+      <c r="S137" s="3" t="n"/>
+      <c r="T137" s="3" t="n"/>
+      <c r="U137" s="3" t="n"/>
+      <c r="V137" s="3" t="n"/>
+      <c r="W137" s="3" t="n"/>
+      <c r="X137" s="3" t="n"/>
+      <c r="Y137" s="3" t="n"/>
+      <c r="Z137" s="3" t="n"/>
+      <c r="AA137" s="3" t="n"/>
+      <c r="AB137" s="3" t="n"/>
+      <c r="AC137" s="3" t="n"/>
+      <c r="AD137" s="3" t="n"/>
+      <c r="AE137" s="3" t="n"/>
+      <c r="AF137" s="3" t="n"/>
+      <c r="AG137" s="3" t="n"/>
+      <c r="AH137" s="3" t="n"/>
+      <c r="AI137" s="3" t="n"/>
+      <c r="AJ137" s="3" t="n"/>
+      <c r="AK137" s="3">
+        <f>SUM(D137:AI137)</f>
+        <v/>
+      </c>
+      <c r="AL137" s="3" t="n"/>
+      <c r="AM137" s="3" t="n"/>
+      <c r="AN137" s="3" t="n"/>
+      <c r="AO137" s="3" t="n"/>
+      <c r="AP137" s="3">
+        <f>AJ137+AK137</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="n"/>
+      <c r="B138" s="3" t="n"/>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n"/>
+      <c r="E138" s="3" t="n"/>
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="3" t="n"/>
+      <c r="H138" s="3" t="n"/>
+      <c r="I138" s="3" t="n"/>
+      <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="n"/>
+      <c r="L138" s="3" t="n"/>
+      <c r="M138" s="3" t="n"/>
+      <c r="N138" s="3" t="n"/>
+      <c r="O138" s="3" t="n"/>
+      <c r="P138" s="3" t="n"/>
+      <c r="Q138" s="3" t="n"/>
+      <c r="R138" s="3" t="n"/>
+      <c r="S138" s="3" t="n"/>
+      <c r="T138" s="3" t="n"/>
+      <c r="U138" s="3" t="n"/>
+      <c r="V138" s="3" t="n"/>
+      <c r="W138" s="3" t="n"/>
+      <c r="X138" s="3" t="n"/>
+      <c r="Y138" s="3" t="n"/>
+      <c r="Z138" s="3" t="n"/>
+      <c r="AA138" s="3" t="n"/>
+      <c r="AB138" s="3" t="n"/>
+      <c r="AC138" s="3" t="n"/>
+      <c r="AD138" s="3" t="n"/>
+      <c r="AE138" s="3" t="n"/>
+      <c r="AF138" s="3" t="n"/>
+      <c r="AG138" s="3" t="n"/>
+      <c r="AH138" s="3" t="n"/>
+      <c r="AI138" s="3" t="n"/>
+      <c r="AJ138" s="3" t="n"/>
+      <c r="AK138" s="3">
+        <f>SUM(D138:AI138)</f>
+        <v/>
+      </c>
+      <c r="AL138" s="3" t="n"/>
+      <c r="AM138" s="3" t="n"/>
+      <c r="AN138" s="3" t="n"/>
+      <c r="AO138" s="3" t="n"/>
+      <c r="AP138" s="3">
+        <f>AJ138+AK138</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n"/>
+      <c r="B139" s="3" t="n"/>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n"/>
+      <c r="E139" s="3" t="n"/>
+      <c r="F139" s="3" t="n"/>
+      <c r="G139" s="3" t="n"/>
+      <c r="H139" s="3" t="n"/>
+      <c r="I139" s="3" t="n"/>
+      <c r="J139" s="3" t="n"/>
+      <c r="K139" s="3" t="n"/>
+      <c r="L139" s="3" t="n"/>
+      <c r="M139" s="3" t="n"/>
+      <c r="N139" s="3" t="n"/>
+      <c r="O139" s="3" t="n"/>
+      <c r="P139" s="3" t="n"/>
+      <c r="Q139" s="3" t="n"/>
+      <c r="R139" s="3" t="n"/>
+      <c r="S139" s="3" t="n"/>
+      <c r="T139" s="3" t="n"/>
+      <c r="U139" s="3" t="n"/>
+      <c r="V139" s="3" t="n"/>
+      <c r="W139" s="3" t="n"/>
+      <c r="X139" s="3" t="n"/>
+      <c r="Y139" s="3" t="n"/>
+      <c r="Z139" s="3" t="n"/>
+      <c r="AA139" s="3" t="n"/>
+      <c r="AB139" s="3" t="n"/>
+      <c r="AC139" s="3" t="n"/>
+      <c r="AD139" s="3" t="n"/>
+      <c r="AE139" s="3" t="n"/>
+      <c r="AF139" s="3" t="n"/>
+      <c r="AG139" s="3" t="n"/>
+      <c r="AH139" s="3" t="n"/>
+      <c r="AI139" s="3" t="n"/>
+      <c r="AJ139" s="3" t="n"/>
+      <c r="AK139" s="3">
+        <f>SUM(D139:AI139)</f>
+        <v/>
+      </c>
+      <c r="AL139" s="3" t="n"/>
+      <c r="AM139" s="3" t="n"/>
+      <c r="AN139" s="3" t="n"/>
+      <c r="AO139" s="3" t="n"/>
+      <c r="AP139" s="3">
+        <f>AJ139+AK139</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="n"/>
+      <c r="B140" s="3" t="n"/>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n"/>
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="3" t="n"/>
+      <c r="G140" s="3" t="n"/>
+      <c r="H140" s="3" t="n"/>
+      <c r="I140" s="3" t="n"/>
+      <c r="J140" s="3" t="n"/>
+      <c r="K140" s="3" t="n"/>
+      <c r="L140" s="3" t="n"/>
+      <c r="M140" s="3" t="n"/>
+      <c r="N140" s="3" t="n"/>
+      <c r="O140" s="3" t="n"/>
+      <c r="P140" s="3" t="n"/>
+      <c r="Q140" s="3" t="n"/>
+      <c r="R140" s="3" t="n"/>
+      <c r="S140" s="3" t="n"/>
+      <c r="T140" s="3" t="n"/>
+      <c r="U140" s="3" t="n"/>
+      <c r="V140" s="3" t="n"/>
+      <c r="W140" s="3" t="n"/>
+      <c r="X140" s="3" t="n"/>
+      <c r="Y140" s="3" t="n"/>
+      <c r="Z140" s="3" t="n"/>
+      <c r="AA140" s="3" t="n"/>
+      <c r="AB140" s="3" t="n"/>
+      <c r="AC140" s="3" t="n"/>
+      <c r="AD140" s="3" t="n"/>
+      <c r="AE140" s="3" t="n"/>
+      <c r="AF140" s="3" t="n"/>
+      <c r="AG140" s="3" t="n"/>
+      <c r="AH140" s="3" t="n"/>
+      <c r="AI140" s="3" t="n"/>
+      <c r="AJ140" s="3" t="n"/>
+      <c r="AK140" s="3">
+        <f>SUM(D140:AI140)</f>
+        <v/>
+      </c>
+      <c r="AL140" s="3" t="n"/>
+      <c r="AM140" s="3" t="n"/>
+      <c r="AN140" s="3" t="n"/>
+      <c r="AO140" s="3" t="n"/>
+      <c r="AP140" s="3">
+        <f>AJ140+AK140</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n"/>
+      <c r="B141" s="3" t="n"/>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n"/>
+      <c r="E141" s="3" t="n"/>
+      <c r="F141" s="3" t="n"/>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
+      <c r="I141" s="3" t="n"/>
+      <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="n"/>
+      <c r="L141" s="3" t="n"/>
+      <c r="M141" s="3" t="n"/>
+      <c r="N141" s="3" t="n"/>
+      <c r="O141" s="3" t="n"/>
+      <c r="P141" s="3" t="n"/>
+      <c r="Q141" s="3" t="n"/>
+      <c r="R141" s="3" t="n"/>
+      <c r="S141" s="3" t="n"/>
+      <c r="T141" s="3" t="n"/>
+      <c r="U141" s="3" t="n"/>
+      <c r="V141" s="3" t="n"/>
+      <c r="W141" s="3" t="n"/>
+      <c r="X141" s="3" t="n"/>
+      <c r="Y141" s="3" t="n"/>
+      <c r="Z141" s="3" t="n"/>
+      <c r="AA141" s="3" t="n"/>
+      <c r="AB141" s="3" t="n"/>
+      <c r="AC141" s="3" t="n"/>
+      <c r="AD141" s="3" t="n"/>
+      <c r="AE141" s="3" t="n"/>
+      <c r="AF141" s="3" t="n"/>
+      <c r="AG141" s="3" t="n"/>
+      <c r="AH141" s="3" t="n"/>
+      <c r="AI141" s="3" t="n"/>
+      <c r="AJ141" s="3" t="n"/>
+      <c r="AK141" s="3">
+        <f>SUM(D141:AI141)</f>
+        <v/>
+      </c>
+      <c r="AL141" s="3" t="n"/>
+      <c r="AM141" s="3" t="n"/>
+      <c r="AN141" s="3" t="n"/>
+      <c r="AO141" s="3" t="n"/>
+      <c r="AP141" s="3">
+        <f>AJ141+AK141</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n"/>
+      <c r="B142" s="3" t="n"/>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n"/>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
+      <c r="I142" s="3" t="n"/>
+      <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="n"/>
+      <c r="L142" s="3" t="n"/>
+      <c r="M142" s="3" t="n"/>
+      <c r="N142" s="3" t="n"/>
+      <c r="O142" s="3" t="n"/>
+      <c r="P142" s="3" t="n"/>
+      <c r="Q142" s="3" t="n"/>
+      <c r="R142" s="3" t="n"/>
+      <c r="S142" s="3" t="n"/>
+      <c r="T142" s="3" t="n"/>
+      <c r="U142" s="3" t="n"/>
+      <c r="V142" s="3" t="n"/>
+      <c r="W142" s="3" t="n"/>
+      <c r="X142" s="3" t="n"/>
+      <c r="Y142" s="3" t="n"/>
+      <c r="Z142" s="3" t="n"/>
+      <c r="AA142" s="3" t="n"/>
+      <c r="AB142" s="3" t="n"/>
+      <c r="AC142" s="3" t="n"/>
+      <c r="AD142" s="3" t="n"/>
+      <c r="AE142" s="3" t="n"/>
+      <c r="AF142" s="3" t="n"/>
+      <c r="AG142" s="3" t="n"/>
+      <c r="AH142" s="3" t="n"/>
+      <c r="AI142" s="3" t="n"/>
+      <c r="AJ142" s="3" t="n"/>
+      <c r="AK142" s="3">
+        <f>SUM(D142:AI142)</f>
+        <v/>
+      </c>
+      <c r="AL142" s="3" t="n"/>
+      <c r="AM142" s="3" t="n"/>
+      <c r="AN142" s="3" t="n"/>
+      <c r="AO142" s="3" t="n"/>
+      <c r="AP142" s="3">
+        <f>AJ142+AK142</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n"/>
+      <c r="B143" s="3" t="n"/>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n"/>
+      <c r="E143" s="3" t="n"/>
+      <c r="F143" s="3" t="n"/>
+      <c r="G143" s="3" t="n"/>
+      <c r="H143" s="3" t="n"/>
+      <c r="I143" s="3" t="n"/>
+      <c r="J143" s="3" t="n"/>
+      <c r="K143" s="3" t="n"/>
+      <c r="L143" s="3" t="n"/>
+      <c r="M143" s="3" t="n"/>
+      <c r="N143" s="3" t="n"/>
+      <c r="O143" s="3" t="n"/>
+      <c r="P143" s="3" t="n"/>
+      <c r="Q143" s="3" t="n"/>
+      <c r="R143" s="3" t="n"/>
+      <c r="S143" s="3" t="n"/>
+      <c r="T143" s="3" t="n"/>
+      <c r="U143" s="3" t="n"/>
+      <c r="V143" s="3" t="n"/>
+      <c r="W143" s="3" t="n"/>
+      <c r="X143" s="3" t="n"/>
+      <c r="Y143" s="3" t="n"/>
+      <c r="Z143" s="3" t="n"/>
+      <c r="AA143" s="3" t="n"/>
+      <c r="AB143" s="3" t="n"/>
+      <c r="AC143" s="3" t="n"/>
+      <c r="AD143" s="3" t="n"/>
+      <c r="AE143" s="3" t="n"/>
+      <c r="AF143" s="3" t="n"/>
+      <c r="AG143" s="3" t="n"/>
+      <c r="AH143" s="3" t="n"/>
+      <c r="AI143" s="3" t="n"/>
+      <c r="AJ143" s="3" t="n"/>
+      <c r="AK143" s="3">
+        <f>SUM(D143:AI143)</f>
+        <v/>
+      </c>
+      <c r="AL143" s="3" t="n"/>
+      <c r="AM143" s="3" t="n"/>
+      <c r="AN143" s="3" t="n"/>
+      <c r="AO143" s="3" t="n"/>
+      <c r="AP143" s="3">
+        <f>AJ143+AK143</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n"/>
+      <c r="B144" s="3" t="n"/>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n"/>
+      <c r="E144" s="3" t="n"/>
+      <c r="F144" s="3" t="n"/>
+      <c r="G144" s="3" t="n"/>
+      <c r="H144" s="3" t="n"/>
+      <c r="I144" s="3" t="n"/>
+      <c r="J144" s="3" t="n"/>
+      <c r="K144" s="3" t="n"/>
+      <c r="L144" s="3" t="n"/>
+      <c r="M144" s="3" t="n"/>
+      <c r="N144" s="3" t="n"/>
+      <c r="O144" s="3" t="n"/>
+      <c r="P144" s="3" t="n"/>
+      <c r="Q144" s="3" t="n"/>
+      <c r="R144" s="3" t="n"/>
+      <c r="S144" s="3" t="n"/>
+      <c r="T144" s="3" t="n"/>
+      <c r="U144" s="3" t="n"/>
+      <c r="V144" s="3" t="n"/>
+      <c r="W144" s="3" t="n"/>
+      <c r="X144" s="3" t="n"/>
+      <c r="Y144" s="3" t="n"/>
+      <c r="Z144" s="3" t="n"/>
+      <c r="AA144" s="3" t="n"/>
+      <c r="AB144" s="3" t="n"/>
+      <c r="AC144" s="3" t="n"/>
+      <c r="AD144" s="3" t="n"/>
+      <c r="AE144" s="3" t="n"/>
+      <c r="AF144" s="3" t="n"/>
+      <c r="AG144" s="3" t="n"/>
+      <c r="AH144" s="3" t="n"/>
+      <c r="AI144" s="3" t="n"/>
+      <c r="AJ144" s="3" t="n"/>
+      <c r="AK144" s="3">
+        <f>SUM(D144:AI144)</f>
+        <v/>
+      </c>
+      <c r="AL144" s="3" t="n"/>
+      <c r="AM144" s="3" t="n"/>
+      <c r="AN144" s="3" t="n"/>
+      <c r="AO144" s="3" t="n"/>
+      <c r="AP144" s="3">
+        <f>AJ144+AK144</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n"/>
+      <c r="B145" s="3" t="n"/>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n"/>
+      <c r="E145" s="3" t="n"/>
+      <c r="F145" s="3" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="3" t="n"/>
+      <c r="I145" s="3" t="n"/>
+      <c r="J145" s="3" t="n"/>
+      <c r="K145" s="3" t="n"/>
+      <c r="L145" s="3" t="n"/>
+      <c r="M145" s="3" t="n"/>
+      <c r="N145" s="3" t="n"/>
+      <c r="O145" s="3" t="n"/>
+      <c r="P145" s="3" t="n"/>
+      <c r="Q145" s="3" t="n"/>
+      <c r="R145" s="3" t="n"/>
+      <c r="S145" s="3" t="n"/>
+      <c r="T145" s="3" t="n"/>
+      <c r="U145" s="3" t="n"/>
+      <c r="V145" s="3" t="n"/>
+      <c r="W145" s="3" t="n"/>
+      <c r="X145" s="3" t="n"/>
+      <c r="Y145" s="3" t="n"/>
+      <c r="Z145" s="3" t="n"/>
+      <c r="AA145" s="3" t="n"/>
+      <c r="AB145" s="3" t="n"/>
+      <c r="AC145" s="3" t="n"/>
+      <c r="AD145" s="3" t="n"/>
+      <c r="AE145" s="3" t="n"/>
+      <c r="AF145" s="3" t="n"/>
+      <c r="AG145" s="3" t="n"/>
+      <c r="AH145" s="3" t="n"/>
+      <c r="AI145" s="3" t="n"/>
+      <c r="AJ145" s="3" t="n"/>
+      <c r="AK145" s="3">
+        <f>SUM(D145:AI145)</f>
+        <v/>
+      </c>
+      <c r="AL145" s="3" t="n"/>
+      <c r="AM145" s="3" t="n"/>
+      <c r="AN145" s="3" t="n"/>
+      <c r="AO145" s="3" t="n"/>
+      <c r="AP145" s="3">
+        <f>AJ145+AK145</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n"/>
+      <c r="B146" s="3" t="n"/>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n"/>
+      <c r="E146" s="3" t="n"/>
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="3" t="n"/>
+      <c r="H146" s="3" t="n"/>
+      <c r="I146" s="3" t="n"/>
+      <c r="J146" s="3" t="n"/>
+      <c r="K146" s="3" t="n"/>
+      <c r="L146" s="3" t="n"/>
+      <c r="M146" s="3" t="n"/>
+      <c r="N146" s="3" t="n"/>
+      <c r="O146" s="3" t="n"/>
+      <c r="P146" s="3" t="n"/>
+      <c r="Q146" s="3" t="n"/>
+      <c r="R146" s="3" t="n"/>
+      <c r="S146" s="3" t="n"/>
+      <c r="T146" s="3" t="n"/>
+      <c r="U146" s="3" t="n"/>
+      <c r="V146" s="3" t="n"/>
+      <c r="W146" s="3" t="n"/>
+      <c r="X146" s="3" t="n"/>
+      <c r="Y146" s="3" t="n"/>
+      <c r="Z146" s="3" t="n"/>
+      <c r="AA146" s="3" t="n"/>
+      <c r="AB146" s="3" t="n"/>
+      <c r="AC146" s="3" t="n"/>
+      <c r="AD146" s="3" t="n"/>
+      <c r="AE146" s="3" t="n"/>
+      <c r="AF146" s="3" t="n"/>
+      <c r="AG146" s="3" t="n"/>
+      <c r="AH146" s="3" t="n"/>
+      <c r="AI146" s="3" t="n"/>
+      <c r="AJ146" s="3" t="n"/>
+      <c r="AK146" s="3">
+        <f>SUM(D146:AI146)</f>
+        <v/>
+      </c>
+      <c r="AL146" s="3" t="n"/>
+      <c r="AM146" s="3" t="n"/>
+      <c r="AN146" s="3" t="n"/>
+      <c r="AO146" s="3" t="n"/>
+      <c r="AP146" s="3">
+        <f>AJ146+AK146</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n"/>
+      <c r="B147" s="3" t="n"/>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n"/>
+      <c r="E147" s="3" t="n"/>
+      <c r="F147" s="3" t="n"/>
+      <c r="G147" s="3" t="n"/>
+      <c r="H147" s="3" t="n"/>
+      <c r="I147" s="3" t="n"/>
+      <c r="J147" s="3" t="n"/>
+      <c r="K147" s="3" t="n"/>
+      <c r="L147" s="3" t="n"/>
+      <c r="M147" s="3" t="n"/>
+      <c r="N147" s="3" t="n"/>
+      <c r="O147" s="3" t="n"/>
+      <c r="P147" s="3" t="n"/>
+      <c r="Q147" s="3" t="n"/>
+      <c r="R147" s="3" t="n"/>
+      <c r="S147" s="3" t="n"/>
+      <c r="T147" s="3" t="n"/>
+      <c r="U147" s="3" t="n"/>
+      <c r="V147" s="3" t="n"/>
+      <c r="W147" s="3" t="n"/>
+      <c r="X147" s="3" t="n"/>
+      <c r="Y147" s="3" t="n"/>
+      <c r="Z147" s="3" t="n"/>
+      <c r="AA147" s="3" t="n"/>
+      <c r="AB147" s="3" t="n"/>
+      <c r="AC147" s="3" t="n"/>
+      <c r="AD147" s="3" t="n"/>
+      <c r="AE147" s="3" t="n"/>
+      <c r="AF147" s="3" t="n"/>
+      <c r="AG147" s="3" t="n"/>
+      <c r="AH147" s="3" t="n"/>
+      <c r="AI147" s="3" t="n"/>
+      <c r="AJ147" s="3" t="n"/>
+      <c r="AK147" s="3">
+        <f>SUM(D147:AI147)</f>
+        <v/>
+      </c>
+      <c r="AL147" s="3" t="n"/>
+      <c r="AM147" s="3" t="n"/>
+      <c r="AN147" s="3" t="n"/>
+      <c r="AO147" s="3" t="n"/>
+      <c r="AP147" s="3">
+        <f>AJ147+AK147</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n"/>
+      <c r="B148" s="3" t="n"/>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n"/>
+      <c r="E148" s="3" t="n"/>
+      <c r="F148" s="3" t="n"/>
+      <c r="G148" s="3" t="n"/>
+      <c r="H148" s="3" t="n"/>
+      <c r="I148" s="3" t="n"/>
+      <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="n"/>
+      <c r="L148" s="3" t="n"/>
+      <c r="M148" s="3" t="n"/>
+      <c r="N148" s="3" t="n"/>
+      <c r="O148" s="3" t="n"/>
+      <c r="P148" s="3" t="n"/>
+      <c r="Q148" s="3" t="n"/>
+      <c r="R148" s="3" t="n"/>
+      <c r="S148" s="3" t="n"/>
+      <c r="T148" s="3" t="n"/>
+      <c r="U148" s="3" t="n"/>
+      <c r="V148" s="3" t="n"/>
+      <c r="W148" s="3" t="n"/>
+      <c r="X148" s="3" t="n"/>
+      <c r="Y148" s="3" t="n"/>
+      <c r="Z148" s="3" t="n"/>
+      <c r="AA148" s="3" t="n"/>
+      <c r="AB148" s="3" t="n"/>
+      <c r="AC148" s="3" t="n"/>
+      <c r="AD148" s="3" t="n"/>
+      <c r="AE148" s="3" t="n"/>
+      <c r="AF148" s="3" t="n"/>
+      <c r="AG148" s="3" t="n"/>
+      <c r="AH148" s="3" t="n"/>
+      <c r="AI148" s="3" t="n"/>
+      <c r="AJ148" s="3" t="n"/>
+      <c r="AK148" s="3">
+        <f>SUM(D148:AI148)</f>
+        <v/>
+      </c>
+      <c r="AL148" s="3" t="n"/>
+      <c r="AM148" s="3" t="n"/>
+      <c r="AN148" s="3" t="n"/>
+      <c r="AO148" s="3" t="n"/>
+      <c r="AP148" s="3">
+        <f>AJ148+AK148</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n"/>
+      <c r="B149" s="3" t="n"/>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n"/>
+      <c r="E149" s="3" t="n"/>
+      <c r="F149" s="3" t="n"/>
+      <c r="G149" s="3" t="n"/>
+      <c r="H149" s="3" t="n"/>
+      <c r="I149" s="3" t="n"/>
+      <c r="J149" s="3" t="n"/>
+      <c r="K149" s="3" t="n"/>
+      <c r="L149" s="3" t="n"/>
+      <c r="M149" s="3" t="n"/>
+      <c r="N149" s="3" t="n"/>
+      <c r="O149" s="3" t="n"/>
+      <c r="P149" s="3" t="n"/>
+      <c r="Q149" s="3" t="n"/>
+      <c r="R149" s="3" t="n"/>
+      <c r="S149" s="3" t="n"/>
+      <c r="T149" s="3" t="n"/>
+      <c r="U149" s="3" t="n"/>
+      <c r="V149" s="3" t="n"/>
+      <c r="W149" s="3" t="n"/>
+      <c r="X149" s="3" t="n"/>
+      <c r="Y149" s="3" t="n"/>
+      <c r="Z149" s="3" t="n"/>
+      <c r="AA149" s="3" t="n"/>
+      <c r="AB149" s="3" t="n"/>
+      <c r="AC149" s="3" t="n"/>
+      <c r="AD149" s="3" t="n"/>
+      <c r="AE149" s="3" t="n"/>
+      <c r="AF149" s="3" t="n"/>
+      <c r="AG149" s="3" t="n"/>
+      <c r="AH149" s="3" t="n"/>
+      <c r="AI149" s="3" t="n"/>
+      <c r="AJ149" s="3" t="n"/>
+      <c r="AK149" s="3">
+        <f>SUM(D149:AI149)</f>
+        <v/>
+      </c>
+      <c r="AL149" s="3" t="n"/>
+      <c r="AM149" s="3" t="n"/>
+      <c r="AN149" s="3" t="n"/>
+      <c r="AO149" s="3" t="n"/>
+      <c r="AP149" s="3">
+        <f>AJ149+AK149</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n"/>
+      <c r="B150" s="3" t="n"/>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="3" t="n"/>
+      <c r="H150" s="3" t="n"/>
+      <c r="I150" s="3" t="n"/>
+      <c r="J150" s="3" t="n"/>
+      <c r="K150" s="3" t="n"/>
+      <c r="L150" s="3" t="n"/>
+      <c r="M150" s="3" t="n"/>
+      <c r="N150" s="3" t="n"/>
+      <c r="O150" s="3" t="n"/>
+      <c r="P150" s="3" t="n"/>
+      <c r="Q150" s="3" t="n"/>
+      <c r="R150" s="3" t="n"/>
+      <c r="S150" s="3" t="n"/>
+      <c r="T150" s="3" t="n"/>
+      <c r="U150" s="3" t="n"/>
+      <c r="V150" s="3" t="n"/>
+      <c r="W150" s="3" t="n"/>
+      <c r="X150" s="3" t="n"/>
+      <c r="Y150" s="3" t="n"/>
+      <c r="Z150" s="3" t="n"/>
+      <c r="AA150" s="3" t="n"/>
+      <c r="AB150" s="3" t="n"/>
+      <c r="AC150" s="3" t="n"/>
+      <c r="AD150" s="3" t="n"/>
+      <c r="AE150" s="3" t="n"/>
+      <c r="AF150" s="3" t="n"/>
+      <c r="AG150" s="3" t="n"/>
+      <c r="AH150" s="3" t="n"/>
+      <c r="AI150" s="3" t="n"/>
+      <c r="AJ150" s="3" t="n"/>
+      <c r="AK150" s="3">
+        <f>SUM(D150:AI150)</f>
+        <v/>
+      </c>
+      <c r="AL150" s="3" t="n"/>
+      <c r="AM150" s="3" t="n"/>
+      <c r="AN150" s="3" t="n"/>
+      <c r="AO150" s="3" t="n"/>
+      <c r="AP150" s="3">
+        <f>AJ150+AK150</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n"/>
+      <c r="B151" s="3" t="n"/>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n"/>
+      <c r="E151" s="3" t="n"/>
+      <c r="F151" s="3" t="n"/>
+      <c r="G151" s="3" t="n"/>
+      <c r="H151" s="3" t="n"/>
+      <c r="I151" s="3" t="n"/>
+      <c r="J151" s="3" t="n"/>
+      <c r="K151" s="3" t="n"/>
+      <c r="L151" s="3" t="n"/>
+      <c r="M151" s="3" t="n"/>
+      <c r="N151" s="3" t="n"/>
+      <c r="O151" s="3" t="n"/>
+      <c r="P151" s="3" t="n"/>
+      <c r="Q151" s="3" t="n"/>
+      <c r="R151" s="3" t="n"/>
+      <c r="S151" s="3" t="n"/>
+      <c r="T151" s="3" t="n"/>
+      <c r="U151" s="3" t="n"/>
+      <c r="V151" s="3" t="n"/>
+      <c r="W151" s="3" t="n"/>
+      <c r="X151" s="3" t="n"/>
+      <c r="Y151" s="3" t="n"/>
+      <c r="Z151" s="3" t="n"/>
+      <c r="AA151" s="3" t="n"/>
+      <c r="AB151" s="3" t="n"/>
+      <c r="AC151" s="3" t="n"/>
+      <c r="AD151" s="3" t="n"/>
+      <c r="AE151" s="3" t="n"/>
+      <c r="AF151" s="3" t="n"/>
+      <c r="AG151" s="3" t="n"/>
+      <c r="AH151" s="3" t="n"/>
+      <c r="AI151" s="3" t="n"/>
+      <c r="AJ151" s="3" t="n"/>
+      <c r="AK151" s="3">
+        <f>SUM(D151:AI151)</f>
+        <v/>
+      </c>
+      <c r="AL151" s="3" t="n"/>
+      <c r="AM151" s="3" t="n"/>
+      <c r="AN151" s="3" t="n"/>
+      <c r="AO151" s="3" t="n"/>
+      <c r="AP151" s="3">
+        <f>AJ151+AK151</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n"/>
+      <c r="B152" s="3" t="n"/>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n"/>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="3" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="3" t="n"/>
+      <c r="I152" s="3" t="n"/>
+      <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="n"/>
+      <c r="L152" s="3" t="n"/>
+      <c r="M152" s="3" t="n"/>
+      <c r="N152" s="3" t="n"/>
+      <c r="O152" s="3" t="n"/>
+      <c r="P152" s="3" t="n"/>
+      <c r="Q152" s="3" t="n"/>
+      <c r="R152" s="3" t="n"/>
+      <c r="S152" s="3" t="n"/>
+      <c r="T152" s="3" t="n"/>
+      <c r="U152" s="3" t="n"/>
+      <c r="V152" s="3" t="n"/>
+      <c r="W152" s="3" t="n"/>
+      <c r="X152" s="3" t="n"/>
+      <c r="Y152" s="3" t="n"/>
+      <c r="Z152" s="3" t="n"/>
+      <c r="AA152" s="3" t="n"/>
+      <c r="AB152" s="3" t="n"/>
+      <c r="AC152" s="3" t="n"/>
+      <c r="AD152" s="3" t="n"/>
+      <c r="AE152" s="3" t="n"/>
+      <c r="AF152" s="3" t="n"/>
+      <c r="AG152" s="3" t="n"/>
+      <c r="AH152" s="3" t="n"/>
+      <c r="AI152" s="3" t="n"/>
+      <c r="AJ152" s="3" t="n"/>
+      <c r="AK152" s="3">
+        <f>SUM(D152:AI152)</f>
+        <v/>
+      </c>
+      <c r="AL152" s="3" t="n"/>
+      <c r="AM152" s="3" t="n"/>
+      <c r="AN152" s="3" t="n"/>
+      <c r="AO152" s="3" t="n"/>
+      <c r="AP152" s="3">
+        <f>AJ152+AK152</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n"/>
+      <c r="B153" s="3" t="n"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n"/>
+      <c r="E153" s="3" t="n"/>
+      <c r="F153" s="3" t="n"/>
+      <c r="G153" s="3" t="n"/>
+      <c r="H153" s="3" t="n"/>
+      <c r="I153" s="3" t="n"/>
+      <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="n"/>
+      <c r="L153" s="3" t="n"/>
+      <c r="M153" s="3" t="n"/>
+      <c r="N153" s="3" t="n"/>
+      <c r="O153" s="3" t="n"/>
+      <c r="P153" s="3" t="n"/>
+      <c r="Q153" s="3" t="n"/>
+      <c r="R153" s="3" t="n"/>
+      <c r="S153" s="3" t="n"/>
+      <c r="T153" s="3" t="n"/>
+      <c r="U153" s="3" t="n"/>
+      <c r="V153" s="3" t="n"/>
+      <c r="W153" s="3" t="n"/>
+      <c r="X153" s="3" t="n"/>
+      <c r="Y153" s="3" t="n"/>
+      <c r="Z153" s="3" t="n"/>
+      <c r="AA153" s="3" t="n"/>
+      <c r="AB153" s="3" t="n"/>
+      <c r="AC153" s="3" t="n"/>
+      <c r="AD153" s="3" t="n"/>
+      <c r="AE153" s="3" t="n"/>
+      <c r="AF153" s="3" t="n"/>
+      <c r="AG153" s="3" t="n"/>
+      <c r="AH153" s="3" t="n"/>
+      <c r="AI153" s="3" t="n"/>
+      <c r="AJ153" s="3" t="n"/>
+      <c r="AK153" s="3">
+        <f>SUM(D153:AI153)</f>
+        <v/>
+      </c>
+      <c r="AL153" s="3" t="n"/>
+      <c r="AM153" s="3" t="n"/>
+      <c r="AN153" s="3" t="n"/>
+      <c r="AO153" s="3" t="n"/>
+      <c r="AP153" s="3">
+        <f>AJ153+AK153</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n"/>
+      <c r="B154" s="3" t="n"/>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n"/>
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
+      <c r="I154" s="3" t="n"/>
+      <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="n"/>
+      <c r="L154" s="3" t="n"/>
+      <c r="M154" s="3" t="n"/>
+      <c r="N154" s="3" t="n"/>
+      <c r="O154" s="3" t="n"/>
+      <c r="P154" s="3" t="n"/>
+      <c r="Q154" s="3" t="n"/>
+      <c r="R154" s="3" t="n"/>
+      <c r="S154" s="3" t="n"/>
+      <c r="T154" s="3" t="n"/>
+      <c r="U154" s="3" t="n"/>
+      <c r="V154" s="3" t="n"/>
+      <c r="W154" s="3" t="n"/>
+      <c r="X154" s="3" t="n"/>
+      <c r="Y154" s="3" t="n"/>
+      <c r="Z154" s="3" t="n"/>
+      <c r="AA154" s="3" t="n"/>
+      <c r="AB154" s="3" t="n"/>
+      <c r="AC154" s="3" t="n"/>
+      <c r="AD154" s="3" t="n"/>
+      <c r="AE154" s="3" t="n"/>
+      <c r="AF154" s="3" t="n"/>
+      <c r="AG154" s="3" t="n"/>
+      <c r="AH154" s="3" t="n"/>
+      <c r="AI154" s="3" t="n"/>
+      <c r="AJ154" s="3" t="n"/>
+      <c r="AK154" s="3">
+        <f>SUM(D154:AI154)</f>
+        <v/>
+      </c>
+      <c r="AL154" s="3" t="n"/>
+      <c r="AM154" s="3" t="n"/>
+      <c r="AN154" s="3" t="n"/>
+      <c r="AO154" s="3" t="n"/>
+      <c r="AP154" s="3">
+        <f>AJ154+AK154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n"/>
+      <c r="B155" s="3" t="n"/>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n"/>
+      <c r="E155" s="3" t="n"/>
+      <c r="F155" s="3" t="n"/>
+      <c r="G155" s="3" t="n"/>
+      <c r="H155" s="3" t="n"/>
+      <c r="I155" s="3" t="n"/>
+      <c r="J155" s="3" t="n"/>
+      <c r="K155" s="3" t="n"/>
+      <c r="L155" s="3" t="n"/>
+      <c r="M155" s="3" t="n"/>
+      <c r="N155" s="3" t="n"/>
+      <c r="O155" s="3" t="n"/>
+      <c r="P155" s="3" t="n"/>
+      <c r="Q155" s="3" t="n"/>
+      <c r="R155" s="3" t="n"/>
+      <c r="S155" s="3" t="n"/>
+      <c r="T155" s="3" t="n"/>
+      <c r="U155" s="3" t="n"/>
+      <c r="V155" s="3" t="n"/>
+      <c r="W155" s="3" t="n"/>
+      <c r="X155" s="3" t="n"/>
+      <c r="Y155" s="3" t="n"/>
+      <c r="Z155" s="3" t="n"/>
+      <c r="AA155" s="3" t="n"/>
+      <c r="AB155" s="3" t="n"/>
+      <c r="AC155" s="3" t="n"/>
+      <c r="AD155" s="3" t="n"/>
+      <c r="AE155" s="3" t="n"/>
+      <c r="AF155" s="3" t="n"/>
+      <c r="AG155" s="3" t="n"/>
+      <c r="AH155" s="3" t="n"/>
+      <c r="AI155" s="3" t="n"/>
+      <c r="AJ155" s="3" t="n"/>
+      <c r="AK155" s="3">
+        <f>SUM(D155:AI155)</f>
+        <v/>
+      </c>
+      <c r="AL155" s="3" t="n"/>
+      <c r="AM155" s="3" t="n"/>
+      <c r="AN155" s="3" t="n"/>
+      <c r="AO155" s="3" t="n"/>
+      <c r="AP155" s="3">
+        <f>AJ155+AK155</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n"/>
+      <c r="B156" s="3" t="n"/>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n"/>
+      <c r="E156" s="3" t="n"/>
+      <c r="F156" s="3" t="n"/>
+      <c r="G156" s="3" t="n"/>
+      <c r="H156" s="3" t="n"/>
+      <c r="I156" s="3" t="n"/>
+      <c r="J156" s="3" t="n"/>
+      <c r="K156" s="3" t="n"/>
+      <c r="L156" s="3" t="n"/>
+      <c r="M156" s="3" t="n"/>
+      <c r="N156" s="3" t="n"/>
+      <c r="O156" s="3" t="n"/>
+      <c r="P156" s="3" t="n"/>
+      <c r="Q156" s="3" t="n"/>
+      <c r="R156" s="3" t="n"/>
+      <c r="S156" s="3" t="n"/>
+      <c r="T156" s="3" t="n"/>
+      <c r="U156" s="3" t="n"/>
+      <c r="V156" s="3" t="n"/>
+      <c r="W156" s="3" t="n"/>
+      <c r="X156" s="3" t="n"/>
+      <c r="Y156" s="3" t="n"/>
+      <c r="Z156" s="3" t="n"/>
+      <c r="AA156" s="3" t="n"/>
+      <c r="AB156" s="3" t="n"/>
+      <c r="AC156" s="3" t="n"/>
+      <c r="AD156" s="3" t="n"/>
+      <c r="AE156" s="3" t="n"/>
+      <c r="AF156" s="3" t="n"/>
+      <c r="AG156" s="3" t="n"/>
+      <c r="AH156" s="3" t="n"/>
+      <c r="AI156" s="3" t="n"/>
+      <c r="AJ156" s="3" t="n"/>
+      <c r="AK156" s="3">
+        <f>SUM(D156:AI156)</f>
+        <v/>
+      </c>
+      <c r="AL156" s="3" t="n"/>
+      <c r="AM156" s="3" t="n"/>
+      <c r="AN156" s="3" t="n"/>
+      <c r="AO156" s="3" t="n"/>
+      <c r="AP156" s="3">
+        <f>AJ156+AK156</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n"/>
+      <c r="B157" s="3" t="n"/>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n"/>
+      <c r="E157" s="3" t="n"/>
+      <c r="F157" s="3" t="n"/>
+      <c r="G157" s="3" t="n"/>
+      <c r="H157" s="3" t="n"/>
+      <c r="I157" s="3" t="n"/>
+      <c r="J157" s="3" t="n"/>
+      <c r="K157" s="3" t="n"/>
+      <c r="L157" s="3" t="n"/>
+      <c r="M157" s="3" t="n"/>
+      <c r="N157" s="3" t="n"/>
+      <c r="O157" s="3" t="n"/>
+      <c r="P157" s="3" t="n"/>
+      <c r="Q157" s="3" t="n"/>
+      <c r="R157" s="3" t="n"/>
+      <c r="S157" s="3" t="n"/>
+      <c r="T157" s="3" t="n"/>
+      <c r="U157" s="3" t="n"/>
+      <c r="V157" s="3" t="n"/>
+      <c r="W157" s="3" t="n"/>
+      <c r="X157" s="3" t="n"/>
+      <c r="Y157" s="3" t="n"/>
+      <c r="Z157" s="3" t="n"/>
+      <c r="AA157" s="3" t="n"/>
+      <c r="AB157" s="3" t="n"/>
+      <c r="AC157" s="3" t="n"/>
+      <c r="AD157" s="3" t="n"/>
+      <c r="AE157" s="3" t="n"/>
+      <c r="AF157" s="3" t="n"/>
+      <c r="AG157" s="3" t="n"/>
+      <c r="AH157" s="3" t="n"/>
+      <c r="AI157" s="3" t="n"/>
+      <c r="AJ157" s="3" t="n"/>
+      <c r="AK157" s="3">
+        <f>SUM(D157:AI157)</f>
+        <v/>
+      </c>
+      <c r="AL157" s="3" t="n"/>
+      <c r="AM157" s="3" t="n"/>
+      <c r="AN157" s="3" t="n"/>
+      <c r="AO157" s="3" t="n"/>
+      <c r="AP157" s="3">
+        <f>AJ157+AK157</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n"/>
+      <c r="B158" s="3" t="n"/>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n"/>
+      <c r="E158" s="3" t="n"/>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
+      <c r="I158" s="3" t="n"/>
+      <c r="J158" s="3" t="n"/>
+      <c r="K158" s="3" t="n"/>
+      <c r="L158" s="3" t="n"/>
+      <c r="M158" s="3" t="n"/>
+      <c r="N158" s="3" t="n"/>
+      <c r="O158" s="3" t="n"/>
+      <c r="P158" s="3" t="n"/>
+      <c r="Q158" s="3" t="n"/>
+      <c r="R158" s="3" t="n"/>
+      <c r="S158" s="3" t="n"/>
+      <c r="T158" s="3" t="n"/>
+      <c r="U158" s="3" t="n"/>
+      <c r="V158" s="3" t="n"/>
+      <c r="W158" s="3" t="n"/>
+      <c r="X158" s="3" t="n"/>
+      <c r="Y158" s="3" t="n"/>
+      <c r="Z158" s="3" t="n"/>
+      <c r="AA158" s="3" t="n"/>
+      <c r="AB158" s="3" t="n"/>
+      <c r="AC158" s="3" t="n"/>
+      <c r="AD158" s="3" t="n"/>
+      <c r="AE158" s="3" t="n"/>
+      <c r="AF158" s="3" t="n"/>
+      <c r="AG158" s="3" t="n"/>
+      <c r="AH158" s="3" t="n"/>
+      <c r="AI158" s="3" t="n"/>
+      <c r="AJ158" s="3" t="n"/>
+      <c r="AK158" s="3">
+        <f>SUM(D158:AI158)</f>
+        <v/>
+      </c>
+      <c r="AL158" s="3" t="n"/>
+      <c r="AM158" s="3" t="n"/>
+      <c r="AN158" s="3" t="n"/>
+      <c r="AO158" s="3" t="n"/>
+      <c r="AP158" s="3">
+        <f>AJ158+AK158</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n"/>
+      <c r="B159" s="3" t="n"/>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n"/>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="3" t="n"/>
+      <c r="G159" s="3" t="n"/>
+      <c r="H159" s="3" t="n"/>
+      <c r="I159" s="3" t="n"/>
+      <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="n"/>
+      <c r="L159" s="3" t="n"/>
+      <c r="M159" s="3" t="n"/>
+      <c r="N159" s="3" t="n"/>
+      <c r="O159" s="3" t="n"/>
+      <c r="P159" s="3" t="n"/>
+      <c r="Q159" s="3" t="n"/>
+      <c r="R159" s="3" t="n"/>
+      <c r="S159" s="3" t="n"/>
+      <c r="T159" s="3" t="n"/>
+      <c r="U159" s="3" t="n"/>
+      <c r="V159" s="3" t="n"/>
+      <c r="W159" s="3" t="n"/>
+      <c r="X159" s="3" t="n"/>
+      <c r="Y159" s="3" t="n"/>
+      <c r="Z159" s="3" t="n"/>
+      <c r="AA159" s="3" t="n"/>
+      <c r="AB159" s="3" t="n"/>
+      <c r="AC159" s="3" t="n"/>
+      <c r="AD159" s="3" t="n"/>
+      <c r="AE159" s="3" t="n"/>
+      <c r="AF159" s="3" t="n"/>
+      <c r="AG159" s="3" t="n"/>
+      <c r="AH159" s="3" t="n"/>
+      <c r="AI159" s="3" t="n"/>
+      <c r="AJ159" s="3" t="n"/>
+      <c r="AK159" s="3">
+        <f>SUM(D159:AI159)</f>
+        <v/>
+      </c>
+      <c r="AL159" s="3" t="n"/>
+      <c r="AM159" s="3" t="n"/>
+      <c r="AN159" s="3" t="n"/>
+      <c r="AO159" s="3" t="n"/>
+      <c r="AP159" s="3">
+        <f>AJ159+AK159</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n"/>
+      <c r="B160" s="3" t="n"/>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n"/>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
+      <c r="I160" s="3" t="n"/>
+      <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="n"/>
+      <c r="L160" s="3" t="n"/>
+      <c r="M160" s="3" t="n"/>
+      <c r="N160" s="3" t="n"/>
+      <c r="O160" s="3" t="n"/>
+      <c r="P160" s="3" t="n"/>
+      <c r="Q160" s="3" t="n"/>
+      <c r="R160" s="3" t="n"/>
+      <c r="S160" s="3" t="n"/>
+      <c r="T160" s="3" t="n"/>
+      <c r="U160" s="3" t="n"/>
+      <c r="V160" s="3" t="n"/>
+      <c r="W160" s="3" t="n"/>
+      <c r="X160" s="3" t="n"/>
+      <c r="Y160" s="3" t="n"/>
+      <c r="Z160" s="3" t="n"/>
+      <c r="AA160" s="3" t="n"/>
+      <c r="AB160" s="3" t="n"/>
+      <c r="AC160" s="3" t="n"/>
+      <c r="AD160" s="3" t="n"/>
+      <c r="AE160" s="3" t="n"/>
+      <c r="AF160" s="3" t="n"/>
+      <c r="AG160" s="3" t="n"/>
+      <c r="AH160" s="3" t="n"/>
+      <c r="AI160" s="3" t="n"/>
+      <c r="AJ160" s="3" t="n"/>
+      <c r="AK160" s="3">
+        <f>SUM(D160:AI160)</f>
+        <v/>
+      </c>
+      <c r="AL160" s="3" t="n"/>
+      <c r="AM160" s="3" t="n"/>
+      <c r="AN160" s="3" t="n"/>
+      <c r="AO160" s="3" t="n"/>
+      <c r="AP160" s="3">
+        <f>AJ160+AK160</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n"/>
+      <c r="B161" s="3" t="n"/>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n"/>
+      <c r="E161" s="3" t="n"/>
+      <c r="F161" s="3" t="n"/>
+      <c r="G161" s="3" t="n"/>
+      <c r="H161" s="3" t="n"/>
+      <c r="I161" s="3" t="n"/>
+      <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="n"/>
+      <c r="L161" s="3" t="n"/>
+      <c r="M161" s="3" t="n"/>
+      <c r="N161" s="3" t="n"/>
+      <c r="O161" s="3" t="n"/>
+      <c r="P161" s="3" t="n"/>
+      <c r="Q161" s="3" t="n"/>
+      <c r="R161" s="3" t="n"/>
+      <c r="S161" s="3" t="n"/>
+      <c r="T161" s="3" t="n"/>
+      <c r="U161" s="3" t="n"/>
+      <c r="V161" s="3" t="n"/>
+      <c r="W161" s="3" t="n"/>
+      <c r="X161" s="3" t="n"/>
+      <c r="Y161" s="3" t="n"/>
+      <c r="Z161" s="3" t="n"/>
+      <c r="AA161" s="3" t="n"/>
+      <c r="AB161" s="3" t="n"/>
+      <c r="AC161" s="3" t="n"/>
+      <c r="AD161" s="3" t="n"/>
+      <c r="AE161" s="3" t="n"/>
+      <c r="AF161" s="3" t="n"/>
+      <c r="AG161" s="3" t="n"/>
+      <c r="AH161" s="3" t="n"/>
+      <c r="AI161" s="3" t="n"/>
+      <c r="AJ161" s="3" t="n"/>
+      <c r="AK161" s="3">
+        <f>SUM(D161:AI161)</f>
+        <v/>
+      </c>
+      <c r="AL161" s="3" t="n"/>
+      <c r="AM161" s="3" t="n"/>
+      <c r="AN161" s="3" t="n"/>
+      <c r="AO161" s="3" t="n"/>
+      <c r="AP161" s="3">
+        <f>AJ161+AK161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n"/>
+      <c r="B162" s="3" t="n"/>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n"/>
+      <c r="E162" s="3" t="n"/>
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
+      <c r="I162" s="3" t="n"/>
+      <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="n"/>
+      <c r="L162" s="3" t="n"/>
+      <c r="M162" s="3" t="n"/>
+      <c r="N162" s="3" t="n"/>
+      <c r="O162" s="3" t="n"/>
+      <c r="P162" s="3" t="n"/>
+      <c r="Q162" s="3" t="n"/>
+      <c r="R162" s="3" t="n"/>
+      <c r="S162" s="3" t="n"/>
+      <c r="T162" s="3" t="n"/>
+      <c r="U162" s="3" t="n"/>
+      <c r="V162" s="3" t="n"/>
+      <c r="W162" s="3" t="n"/>
+      <c r="X162" s="3" t="n"/>
+      <c r="Y162" s="3" t="n"/>
+      <c r="Z162" s="3" t="n"/>
+      <c r="AA162" s="3" t="n"/>
+      <c r="AB162" s="3" t="n"/>
+      <c r="AC162" s="3" t="n"/>
+      <c r="AD162" s="3" t="n"/>
+      <c r="AE162" s="3" t="n"/>
+      <c r="AF162" s="3" t="n"/>
+      <c r="AG162" s="3" t="n"/>
+      <c r="AH162" s="3" t="n"/>
+      <c r="AI162" s="3" t="n"/>
+      <c r="AJ162" s="3" t="n"/>
+      <c r="AK162" s="3">
+        <f>SUM(D162:AI162)</f>
+        <v/>
+      </c>
+      <c r="AL162" s="3" t="n"/>
+      <c r="AM162" s="3" t="n"/>
+      <c r="AN162" s="3" t="n"/>
+      <c r="AO162" s="3" t="n"/>
+      <c r="AP162" s="3">
+        <f>AJ162+AK162</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n"/>
+      <c r="B163" s="3" t="n"/>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n"/>
+      <c r="E163" s="3" t="n"/>
+      <c r="F163" s="3" t="n"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="3" t="n"/>
+      <c r="I163" s="3" t="n"/>
+      <c r="J163" s="3" t="n"/>
+      <c r="K163" s="3" t="n"/>
+      <c r="L163" s="3" t="n"/>
+      <c r="M163" s="3" t="n"/>
+      <c r="N163" s="3" t="n"/>
+      <c r="O163" s="3" t="n"/>
+      <c r="P163" s="3" t="n"/>
+      <c r="Q163" s="3" t="n"/>
+      <c r="R163" s="3" t="n"/>
+      <c r="S163" s="3" t="n"/>
+      <c r="T163" s="3" t="n"/>
+      <c r="U163" s="3" t="n"/>
+      <c r="V163" s="3" t="n"/>
+      <c r="W163" s="3" t="n"/>
+      <c r="X163" s="3" t="n"/>
+      <c r="Y163" s="3" t="n"/>
+      <c r="Z163" s="3" t="n"/>
+      <c r="AA163" s="3" t="n"/>
+      <c r="AB163" s="3" t="n"/>
+      <c r="AC163" s="3" t="n"/>
+      <c r="AD163" s="3" t="n"/>
+      <c r="AE163" s="3" t="n"/>
+      <c r="AF163" s="3" t="n"/>
+      <c r="AG163" s="3" t="n"/>
+      <c r="AH163" s="3" t="n"/>
+      <c r="AI163" s="3" t="n"/>
+      <c r="AJ163" s="3" t="n"/>
+      <c r="AK163" s="3">
+        <f>SUM(D163:AI163)</f>
+        <v/>
+      </c>
+      <c r="AL163" s="3" t="n"/>
+      <c r="AM163" s="3" t="n"/>
+      <c r="AN163" s="3" t="n"/>
+      <c r="AO163" s="3" t="n"/>
+      <c r="AP163" s="3">
+        <f>AJ163+AK163</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n"/>
+      <c r="B164" s="3" t="n"/>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n"/>
+      <c r="E164" s="3" t="n"/>
+      <c r="F164" s="3" t="n"/>
+      <c r="G164" s="3" t="n"/>
+      <c r="H164" s="3" t="n"/>
+      <c r="I164" s="3" t="n"/>
+      <c r="J164" s="3" t="n"/>
+      <c r="K164" s="3" t="n"/>
+      <c r="L164" s="3" t="n"/>
+      <c r="M164" s="3" t="n"/>
+      <c r="N164" s="3" t="n"/>
+      <c r="O164" s="3" t="n"/>
+      <c r="P164" s="3" t="n"/>
+      <c r="Q164" s="3" t="n"/>
+      <c r="R164" s="3" t="n"/>
+      <c r="S164" s="3" t="n"/>
+      <c r="T164" s="3" t="n"/>
+      <c r="U164" s="3" t="n"/>
+      <c r="V164" s="3" t="n"/>
+      <c r="W164" s="3" t="n"/>
+      <c r="X164" s="3" t="n"/>
+      <c r="Y164" s="3" t="n"/>
+      <c r="Z164" s="3" t="n"/>
+      <c r="AA164" s="3" t="n"/>
+      <c r="AB164" s="3" t="n"/>
+      <c r="AC164" s="3" t="n"/>
+      <c r="AD164" s="3" t="n"/>
+      <c r="AE164" s="3" t="n"/>
+      <c r="AF164" s="3" t="n"/>
+      <c r="AG164" s="3" t="n"/>
+      <c r="AH164" s="3" t="n"/>
+      <c r="AI164" s="3" t="n"/>
+      <c r="AJ164" s="3" t="n"/>
+      <c r="AK164" s="3">
+        <f>SUM(D164:AI164)</f>
+        <v/>
+      </c>
+      <c r="AL164" s="3" t="n"/>
+      <c r="AM164" s="3" t="n"/>
+      <c r="AN164" s="3" t="n"/>
+      <c r="AO164" s="3" t="n"/>
+      <c r="AP164" s="3">
+        <f>AJ164+AK164</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n"/>
+      <c r="B165" s="3" t="n"/>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n"/>
+      <c r="E165" s="3" t="n"/>
+      <c r="F165" s="3" t="n"/>
+      <c r="G165" s="3" t="n"/>
+      <c r="H165" s="3" t="n"/>
+      <c r="I165" s="3" t="n"/>
+      <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="n"/>
+      <c r="L165" s="3" t="n"/>
+      <c r="M165" s="3" t="n"/>
+      <c r="N165" s="3" t="n"/>
+      <c r="O165" s="3" t="n"/>
+      <c r="P165" s="3" t="n"/>
+      <c r="Q165" s="3" t="n"/>
+      <c r="R165" s="3" t="n"/>
+      <c r="S165" s="3" t="n"/>
+      <c r="T165" s="3" t="n"/>
+      <c r="U165" s="3" t="n"/>
+      <c r="V165" s="3" t="n"/>
+      <c r="W165" s="3" t="n"/>
+      <c r="X165" s="3" t="n"/>
+      <c r="Y165" s="3" t="n"/>
+      <c r="Z165" s="3" t="n"/>
+      <c r="AA165" s="3" t="n"/>
+      <c r="AB165" s="3" t="n"/>
+      <c r="AC165" s="3" t="n"/>
+      <c r="AD165" s="3" t="n"/>
+      <c r="AE165" s="3" t="n"/>
+      <c r="AF165" s="3" t="n"/>
+      <c r="AG165" s="3" t="n"/>
+      <c r="AH165" s="3" t="n"/>
+      <c r="AI165" s="3" t="n"/>
+      <c r="AJ165" s="3" t="n"/>
+      <c r="AK165" s="3">
+        <f>SUM(D165:AI165)</f>
+        <v/>
+      </c>
+      <c r="AL165" s="3" t="n"/>
+      <c r="AM165" s="3" t="n"/>
+      <c r="AN165" s="3" t="n"/>
+      <c r="AO165" s="3" t="n"/>
+      <c r="AP165" s="3">
+        <f>AJ165+AK165</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n"/>
+      <c r="B166" s="3" t="n"/>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n"/>
+      <c r="E166" s="3" t="n"/>
+      <c r="F166" s="3" t="n"/>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="3" t="n"/>
+      <c r="I166" s="3" t="n"/>
+      <c r="J166" s="3" t="n"/>
+      <c r="K166" s="3" t="n"/>
+      <c r="L166" s="3" t="n"/>
+      <c r="M166" s="3" t="n"/>
+      <c r="N166" s="3" t="n"/>
+      <c r="O166" s="3" t="n"/>
+      <c r="P166" s="3" t="n"/>
+      <c r="Q166" s="3" t="n"/>
+      <c r="R166" s="3" t="n"/>
+      <c r="S166" s="3" t="n"/>
+      <c r="T166" s="3" t="n"/>
+      <c r="U166" s="3" t="n"/>
+      <c r="V166" s="3" t="n"/>
+      <c r="W166" s="3" t="n"/>
+      <c r="X166" s="3" t="n"/>
+      <c r="Y166" s="3" t="n"/>
+      <c r="Z166" s="3" t="n"/>
+      <c r="AA166" s="3" t="n"/>
+      <c r="AB166" s="3" t="n"/>
+      <c r="AC166" s="3" t="n"/>
+      <c r="AD166" s="3" t="n"/>
+      <c r="AE166" s="3" t="n"/>
+      <c r="AF166" s="3" t="n"/>
+      <c r="AG166" s="3" t="n"/>
+      <c r="AH166" s="3" t="n"/>
+      <c r="AI166" s="3" t="n"/>
+      <c r="AJ166" s="3" t="n"/>
+      <c r="AK166" s="3">
+        <f>SUM(D166:AI166)</f>
+        <v/>
+      </c>
+      <c r="AL166" s="3" t="n"/>
+      <c r="AM166" s="3" t="n"/>
+      <c r="AN166" s="3" t="n"/>
+      <c r="AO166" s="3" t="n"/>
+      <c r="AP166" s="3">
+        <f>AJ166+AK166</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n"/>
+      <c r="B167" s="3" t="n"/>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n"/>
+      <c r="E167" s="3" t="n"/>
+      <c r="F167" s="3" t="n"/>
+      <c r="G167" s="3" t="n"/>
+      <c r="H167" s="3" t="n"/>
+      <c r="I167" s="3" t="n"/>
+      <c r="J167" s="3" t="n"/>
+      <c r="K167" s="3" t="n"/>
+      <c r="L167" s="3" t="n"/>
+      <c r="M167" s="3" t="n"/>
+      <c r="N167" s="3" t="n"/>
+      <c r="O167" s="3" t="n"/>
+      <c r="P167" s="3" t="n"/>
+      <c r="Q167" s="3" t="n"/>
+      <c r="R167" s="3" t="n"/>
+      <c r="S167" s="3" t="n"/>
+      <c r="T167" s="3" t="n"/>
+      <c r="U167" s="3" t="n"/>
+      <c r="V167" s="3" t="n"/>
+      <c r="W167" s="3" t="n"/>
+      <c r="X167" s="3" t="n"/>
+      <c r="Y167" s="3" t="n"/>
+      <c r="Z167" s="3" t="n"/>
+      <c r="AA167" s="3" t="n"/>
+      <c r="AB167" s="3" t="n"/>
+      <c r="AC167" s="3" t="n"/>
+      <c r="AD167" s="3" t="n"/>
+      <c r="AE167" s="3" t="n"/>
+      <c r="AF167" s="3" t="n"/>
+      <c r="AG167" s="3" t="n"/>
+      <c r="AH167" s="3" t="n"/>
+      <c r="AI167" s="3" t="n"/>
+      <c r="AJ167" s="3" t="n"/>
+      <c r="AK167" s="3">
+        <f>SUM(D167:AI167)</f>
+        <v/>
+      </c>
+      <c r="AL167" s="3" t="n"/>
+      <c r="AM167" s="3" t="n"/>
+      <c r="AN167" s="3" t="n"/>
+      <c r="AO167" s="3" t="n"/>
+      <c r="AP167" s="3">
+        <f>AJ167+AK167</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n"/>
+      <c r="B168" s="3" t="n"/>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n"/>
+      <c r="E168" s="3" t="n"/>
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="3" t="n"/>
+      <c r="H168" s="3" t="n"/>
+      <c r="I168" s="3" t="n"/>
+      <c r="J168" s="3" t="n"/>
+      <c r="K168" s="3" t="n"/>
+      <c r="L168" s="3" t="n"/>
+      <c r="M168" s="3" t="n"/>
+      <c r="N168" s="3" t="n"/>
+      <c r="O168" s="3" t="n"/>
+      <c r="P168" s="3" t="n"/>
+      <c r="Q168" s="3" t="n"/>
+      <c r="R168" s="3" t="n"/>
+      <c r="S168" s="3" t="n"/>
+      <c r="T168" s="3" t="n"/>
+      <c r="U168" s="3" t="n"/>
+      <c r="V168" s="3" t="n"/>
+      <c r="W168" s="3" t="n"/>
+      <c r="X168" s="3" t="n"/>
+      <c r="Y168" s="3" t="n"/>
+      <c r="Z168" s="3" t="n"/>
+      <c r="AA168" s="3" t="n"/>
+      <c r="AB168" s="3" t="n"/>
+      <c r="AC168" s="3" t="n"/>
+      <c r="AD168" s="3" t="n"/>
+      <c r="AE168" s="3" t="n"/>
+      <c r="AF168" s="3" t="n"/>
+      <c r="AG168" s="3" t="n"/>
+      <c r="AH168" s="3" t="n"/>
+      <c r="AI168" s="3" t="n"/>
+      <c r="AJ168" s="3" t="n"/>
+      <c r="AK168" s="3">
+        <f>SUM(D168:AI168)</f>
+        <v/>
+      </c>
+      <c r="AL168" s="3" t="n"/>
+      <c r="AM168" s="3" t="n"/>
+      <c r="AN168" s="3" t="n"/>
+      <c r="AO168" s="3" t="n"/>
+      <c r="AP168" s="3">
+        <f>AJ168+AK168</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n"/>
+      <c r="B169" s="3" t="n"/>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n"/>
+      <c r="E169" s="3" t="n"/>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="3" t="n"/>
+      <c r="K169" s="3" t="n"/>
+      <c r="L169" s="3" t="n"/>
+      <c r="M169" s="3" t="n"/>
+      <c r="N169" s="3" t="n"/>
+      <c r="O169" s="3" t="n"/>
+      <c r="P169" s="3" t="n"/>
+      <c r="Q169" s="3" t="n"/>
+      <c r="R169" s="3" t="n"/>
+      <c r="S169" s="3" t="n"/>
+      <c r="T169" s="3" t="n"/>
+      <c r="U169" s="3" t="n"/>
+      <c r="V169" s="3" t="n"/>
+      <c r="W169" s="3" t="n"/>
+      <c r="X169" s="3" t="n"/>
+      <c r="Y169" s="3" t="n"/>
+      <c r="Z169" s="3" t="n"/>
+      <c r="AA169" s="3" t="n"/>
+      <c r="AB169" s="3" t="n"/>
+      <c r="AC169" s="3" t="n"/>
+      <c r="AD169" s="3" t="n"/>
+      <c r="AE169" s="3" t="n"/>
+      <c r="AF169" s="3" t="n"/>
+      <c r="AG169" s="3" t="n"/>
+      <c r="AH169" s="3" t="n"/>
+      <c r="AI169" s="3" t="n"/>
+      <c r="AJ169" s="3" t="n"/>
+      <c r="AK169" s="3">
+        <f>SUM(D169:AI169)</f>
+        <v/>
+      </c>
+      <c r="AL169" s="3" t="n"/>
+      <c r="AM169" s="3" t="n"/>
+      <c r="AN169" s="3" t="n"/>
+      <c r="AO169" s="3" t="n"/>
+      <c r="AP169" s="3">
+        <f>AJ169+AK169</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n"/>
+      <c r="B170" s="3" t="n"/>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n"/>
+      <c r="E170" s="3" t="n"/>
+      <c r="F170" s="3" t="n"/>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="3" t="n"/>
+      <c r="I170" s="3" t="n"/>
+      <c r="J170" s="3" t="n"/>
+      <c r="K170" s="3" t="n"/>
+      <c r="L170" s="3" t="n"/>
+      <c r="M170" s="3" t="n"/>
+      <c r="N170" s="3" t="n"/>
+      <c r="O170" s="3" t="n"/>
+      <c r="P170" s="3" t="n"/>
+      <c r="Q170" s="3" t="n"/>
+      <c r="R170" s="3" t="n"/>
+      <c r="S170" s="3" t="n"/>
+      <c r="T170" s="3" t="n"/>
+      <c r="U170" s="3" t="n"/>
+      <c r="V170" s="3" t="n"/>
+      <c r="W170" s="3" t="n"/>
+      <c r="X170" s="3" t="n"/>
+      <c r="Y170" s="3" t="n"/>
+      <c r="Z170" s="3" t="n"/>
+      <c r="AA170" s="3" t="n"/>
+      <c r="AB170" s="3" t="n"/>
+      <c r="AC170" s="3" t="n"/>
+      <c r="AD170" s="3" t="n"/>
+      <c r="AE170" s="3" t="n"/>
+      <c r="AF170" s="3" t="n"/>
+      <c r="AG170" s="3" t="n"/>
+      <c r="AH170" s="3" t="n"/>
+      <c r="AI170" s="3" t="n"/>
+      <c r="AJ170" s="3" t="n"/>
+      <c r="AK170" s="3">
+        <f>SUM(D170:AI170)</f>
+        <v/>
+      </c>
+      <c r="AL170" s="3" t="n"/>
+      <c r="AM170" s="3" t="n"/>
+      <c r="AN170" s="3" t="n"/>
+      <c r="AO170" s="3" t="n"/>
+      <c r="AP170" s="3">
+        <f>AJ170+AK170</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n"/>
+      <c r="B171" s="3" t="n"/>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n"/>
+      <c r="E171" s="3" t="n"/>
+      <c r="F171" s="3" t="n"/>
+      <c r="G171" s="3" t="n"/>
+      <c r="H171" s="3" t="n"/>
+      <c r="I171" s="3" t="n"/>
+      <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="n"/>
+      <c r="L171" s="3" t="n"/>
+      <c r="M171" s="3" t="n"/>
+      <c r="N171" s="3" t="n"/>
+      <c r="O171" s="3" t="n"/>
+      <c r="P171" s="3" t="n"/>
+      <c r="Q171" s="3" t="n"/>
+      <c r="R171" s="3" t="n"/>
+      <c r="S171" s="3" t="n"/>
+      <c r="T171" s="3" t="n"/>
+      <c r="U171" s="3" t="n"/>
+      <c r="V171" s="3" t="n"/>
+      <c r="W171" s="3" t="n"/>
+      <c r="X171" s="3" t="n"/>
+      <c r="Y171" s="3" t="n"/>
+      <c r="Z171" s="3" t="n"/>
+      <c r="AA171" s="3" t="n"/>
+      <c r="AB171" s="3" t="n"/>
+      <c r="AC171" s="3" t="n"/>
+      <c r="AD171" s="3" t="n"/>
+      <c r="AE171" s="3" t="n"/>
+      <c r="AF171" s="3" t="n"/>
+      <c r="AG171" s="3" t="n"/>
+      <c r="AH171" s="3" t="n"/>
+      <c r="AI171" s="3" t="n"/>
+      <c r="AJ171" s="3" t="n"/>
+      <c r="AK171" s="3">
+        <f>SUM(D171:AI171)</f>
+        <v/>
+      </c>
+      <c r="AL171" s="3" t="n"/>
+      <c r="AM171" s="3" t="n"/>
+      <c r="AN171" s="3" t="n"/>
+      <c r="AO171" s="3" t="n"/>
+      <c r="AP171" s="3">
+        <f>AJ171+AK171</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n"/>
+      <c r="B172" s="3" t="n"/>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n"/>
+      <c r="E172" s="3" t="n"/>
+      <c r="F172" s="3" t="n"/>
+      <c r="G172" s="3" t="n"/>
+      <c r="H172" s="3" t="n"/>
+      <c r="I172" s="3" t="n"/>
+      <c r="J172" s="3" t="n"/>
+      <c r="K172" s="3" t="n"/>
+      <c r="L172" s="3" t="n"/>
+      <c r="M172" s="3" t="n"/>
+      <c r="N172" s="3" t="n"/>
+      <c r="O172" s="3" t="n"/>
+      <c r="P172" s="3" t="n"/>
+      <c r="Q172" s="3" t="n"/>
+      <c r="R172" s="3" t="n"/>
+      <c r="S172" s="3" t="n"/>
+      <c r="T172" s="3" t="n"/>
+      <c r="U172" s="3" t="n"/>
+      <c r="V172" s="3" t="n"/>
+      <c r="W172" s="3" t="n"/>
+      <c r="X172" s="3" t="n"/>
+      <c r="Y172" s="3" t="n"/>
+      <c r="Z172" s="3" t="n"/>
+      <c r="AA172" s="3" t="n"/>
+      <c r="AB172" s="3" t="n"/>
+      <c r="AC172" s="3" t="n"/>
+      <c r="AD172" s="3" t="n"/>
+      <c r="AE172" s="3" t="n"/>
+      <c r="AF172" s="3" t="n"/>
+      <c r="AG172" s="3" t="n"/>
+      <c r="AH172" s="3" t="n"/>
+      <c r="AI172" s="3" t="n"/>
+      <c r="AJ172" s="3" t="n"/>
+      <c r="AK172" s="3">
+        <f>SUM(D172:AI172)</f>
+        <v/>
+      </c>
+      <c r="AL172" s="3" t="n"/>
+      <c r="AM172" s="3" t="n"/>
+      <c r="AN172" s="3" t="n"/>
+      <c r="AO172" s="3" t="n"/>
+      <c r="AP172" s="3">
+        <f>AJ172+AK172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n"/>
+      <c r="B173" s="3" t="n"/>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n"/>
+      <c r="E173" s="3" t="n"/>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="3" t="n"/>
+      <c r="I173" s="3" t="n"/>
+      <c r="J173" s="3" t="n"/>
+      <c r="K173" s="3" t="n"/>
+      <c r="L173" s="3" t="n"/>
+      <c r="M173" s="3" t="n"/>
+      <c r="N173" s="3" t="n"/>
+      <c r="O173" s="3" t="n"/>
+      <c r="P173" s="3" t="n"/>
+      <c r="Q173" s="3" t="n"/>
+      <c r="R173" s="3" t="n"/>
+      <c r="S173" s="3" t="n"/>
+      <c r="T173" s="3" t="n"/>
+      <c r="U173" s="3" t="n"/>
+      <c r="V173" s="3" t="n"/>
+      <c r="W173" s="3" t="n"/>
+      <c r="X173" s="3" t="n"/>
+      <c r="Y173" s="3" t="n"/>
+      <c r="Z173" s="3" t="n"/>
+      <c r="AA173" s="3" t="n"/>
+      <c r="AB173" s="3" t="n"/>
+      <c r="AC173" s="3" t="n"/>
+      <c r="AD173" s="3" t="n"/>
+      <c r="AE173" s="3" t="n"/>
+      <c r="AF173" s="3" t="n"/>
+      <c r="AG173" s="3" t="n"/>
+      <c r="AH173" s="3" t="n"/>
+      <c r="AI173" s="3" t="n"/>
+      <c r="AJ173" s="3" t="n"/>
+      <c r="AK173" s="3">
+        <f>SUM(D173:AI173)</f>
+        <v/>
+      </c>
+      <c r="AL173" s="3" t="n"/>
+      <c r="AM173" s="3" t="n"/>
+      <c r="AN173" s="3" t="n"/>
+      <c r="AO173" s="3" t="n"/>
+      <c r="AP173" s="3">
+        <f>AJ173+AK173</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n"/>
+      <c r="B174" s="3" t="n"/>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="n"/>
+      <c r="E174" s="3" t="n"/>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="3" t="n"/>
+      <c r="H174" s="3" t="n"/>
+      <c r="I174" s="3" t="n"/>
+      <c r="J174" s="3" t="n"/>
+      <c r="K174" s="3" t="n"/>
+      <c r="L174" s="3" t="n"/>
+      <c r="M174" s="3" t="n"/>
+      <c r="N174" s="3" t="n"/>
+      <c r="O174" s="3" t="n"/>
+      <c r="P174" s="3" t="n"/>
+      <c r="Q174" s="3" t="n"/>
+      <c r="R174" s="3" t="n"/>
+      <c r="S174" s="3" t="n"/>
+      <c r="T174" s="3" t="n"/>
+      <c r="U174" s="3" t="n"/>
+      <c r="V174" s="3" t="n"/>
+      <c r="W174" s="3" t="n"/>
+      <c r="X174" s="3" t="n"/>
+      <c r="Y174" s="3" t="n"/>
+      <c r="Z174" s="3" t="n"/>
+      <c r="AA174" s="3" t="n"/>
+      <c r="AB174" s="3" t="n"/>
+      <c r="AC174" s="3" t="n"/>
+      <c r="AD174" s="3" t="n"/>
+      <c r="AE174" s="3" t="n"/>
+      <c r="AF174" s="3" t="n"/>
+      <c r="AG174" s="3" t="n"/>
+      <c r="AH174" s="3" t="n"/>
+      <c r="AI174" s="3" t="n"/>
+      <c r="AJ174" s="3" t="n"/>
+      <c r="AK174" s="3">
+        <f>SUM(D174:AI174)</f>
+        <v/>
+      </c>
+      <c r="AL174" s="3" t="n"/>
+      <c r="AM174" s="3" t="n"/>
+      <c r="AN174" s="3" t="n"/>
+      <c r="AO174" s="3" t="n"/>
+      <c r="AP174" s="3">
+        <f>AJ174+AK174</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n"/>
+      <c r="B175" s="3" t="n"/>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n"/>
+      <c r="E175" s="3" t="n"/>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="3" t="n"/>
+      <c r="H175" s="3" t="n"/>
+      <c r="I175" s="3" t="n"/>
+      <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="n"/>
+      <c r="L175" s="3" t="n"/>
+      <c r="M175" s="3" t="n"/>
+      <c r="N175" s="3" t="n"/>
+      <c r="O175" s="3" t="n"/>
+      <c r="P175" s="3" t="n"/>
+      <c r="Q175" s="3" t="n"/>
+      <c r="R175" s="3" t="n"/>
+      <c r="S175" s="3" t="n"/>
+      <c r="T175" s="3" t="n"/>
+      <c r="U175" s="3" t="n"/>
+      <c r="V175" s="3" t="n"/>
+      <c r="W175" s="3" t="n"/>
+      <c r="X175" s="3" t="n"/>
+      <c r="Y175" s="3" t="n"/>
+      <c r="Z175" s="3" t="n"/>
+      <c r="AA175" s="3" t="n"/>
+      <c r="AB175" s="3" t="n"/>
+      <c r="AC175" s="3" t="n"/>
+      <c r="AD175" s="3" t="n"/>
+      <c r="AE175" s="3" t="n"/>
+      <c r="AF175" s="3" t="n"/>
+      <c r="AG175" s="3" t="n"/>
+      <c r="AH175" s="3" t="n"/>
+      <c r="AI175" s="3" t="n"/>
+      <c r="AJ175" s="3" t="n"/>
+      <c r="AK175" s="3">
+        <f>SUM(D175:AI175)</f>
+        <v/>
+      </c>
+      <c r="AL175" s="3" t="n"/>
+      <c r="AM175" s="3" t="n"/>
+      <c r="AN175" s="3" t="n"/>
+      <c r="AO175" s="3" t="n"/>
+      <c r="AP175" s="3">
+        <f>AJ175+AK175</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n"/>
+      <c r="B176" s="3" t="n"/>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n"/>
+      <c r="E176" s="3" t="n"/>
+      <c r="F176" s="3" t="n"/>
+      <c r="G176" s="3" t="n"/>
+      <c r="H176" s="3" t="n"/>
+      <c r="I176" s="3" t="n"/>
+      <c r="J176" s="3" t="n"/>
+      <c r="K176" s="3" t="n"/>
+      <c r="L176" s="3" t="n"/>
+      <c r="M176" s="3" t="n"/>
+      <c r="N176" s="3" t="n"/>
+      <c r="O176" s="3" t="n"/>
+      <c r="P176" s="3" t="n"/>
+      <c r="Q176" s="3" t="n"/>
+      <c r="R176" s="3" t="n"/>
+      <c r="S176" s="3" t="n"/>
+      <c r="T176" s="3" t="n"/>
+      <c r="U176" s="3" t="n"/>
+      <c r="V176" s="3" t="n"/>
+      <c r="W176" s="3" t="n"/>
+      <c r="X176" s="3" t="n"/>
+      <c r="Y176" s="3" t="n"/>
+      <c r="Z176" s="3" t="n"/>
+      <c r="AA176" s="3" t="n"/>
+      <c r="AB176" s="3" t="n"/>
+      <c r="AC176" s="3" t="n"/>
+      <c r="AD176" s="3" t="n"/>
+      <c r="AE176" s="3" t="n"/>
+      <c r="AF176" s="3" t="n"/>
+      <c r="AG176" s="3" t="n"/>
+      <c r="AH176" s="3" t="n"/>
+      <c r="AI176" s="3" t="n"/>
+      <c r="AJ176" s="3" t="n"/>
+      <c r="AK176" s="3">
+        <f>SUM(D176:AI176)</f>
+        <v/>
+      </c>
+      <c r="AL176" s="3" t="n"/>
+      <c r="AM176" s="3" t="n"/>
+      <c r="AN176" s="3" t="n"/>
+      <c r="AO176" s="3" t="n"/>
+      <c r="AP176" s="3">
+        <f>AJ176+AK176</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n"/>
+      <c r="B177" s="3" t="n"/>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n"/>
+      <c r="E177" s="3" t="n"/>
+      <c r="F177" s="3" t="n"/>
+      <c r="G177" s="3" t="n"/>
+      <c r="H177" s="3" t="n"/>
+      <c r="I177" s="3" t="n"/>
+      <c r="J177" s="3" t="n"/>
+      <c r="K177" s="3" t="n"/>
+      <c r="L177" s="3" t="n"/>
+      <c r="M177" s="3" t="n"/>
+      <c r="N177" s="3" t="n"/>
+      <c r="O177" s="3" t="n"/>
+      <c r="P177" s="3" t="n"/>
+      <c r="Q177" s="3" t="n"/>
+      <c r="R177" s="3" t="n"/>
+      <c r="S177" s="3" t="n"/>
+      <c r="T177" s="3" t="n"/>
+      <c r="U177" s="3" t="n"/>
+      <c r="V177" s="3" t="n"/>
+      <c r="W177" s="3" t="n"/>
+      <c r="X177" s="3" t="n"/>
+      <c r="Y177" s="3" t="n"/>
+      <c r="Z177" s="3" t="n"/>
+      <c r="AA177" s="3" t="n"/>
+      <c r="AB177" s="3" t="n"/>
+      <c r="AC177" s="3" t="n"/>
+      <c r="AD177" s="3" t="n"/>
+      <c r="AE177" s="3" t="n"/>
+      <c r="AF177" s="3" t="n"/>
+      <c r="AG177" s="3" t="n"/>
+      <c r="AH177" s="3" t="n"/>
+      <c r="AI177" s="3" t="n"/>
+      <c r="AJ177" s="3" t="n"/>
+      <c r="AK177" s="3">
+        <f>SUM(D177:AI177)</f>
+        <v/>
+      </c>
+      <c r="AL177" s="3" t="n"/>
+      <c r="AM177" s="3" t="n"/>
+      <c r="AN177" s="3" t="n"/>
+      <c r="AO177" s="3" t="n"/>
+      <c r="AP177" s="3">
+        <f>AJ177+AK177</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n"/>
+      <c r="B178" s="3" t="n"/>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n"/>
+      <c r="E178" s="3" t="n"/>
+      <c r="F178" s="3" t="n"/>
+      <c r="G178" s="3" t="n"/>
+      <c r="H178" s="3" t="n"/>
+      <c r="I178" s="3" t="n"/>
+      <c r="J178" s="3" t="n"/>
+      <c r="K178" s="3" t="n"/>
+      <c r="L178" s="3" t="n"/>
+      <c r="M178" s="3" t="n"/>
+      <c r="N178" s="3" t="n"/>
+      <c r="O178" s="3" t="n"/>
+      <c r="P178" s="3" t="n"/>
+      <c r="Q178" s="3" t="n"/>
+      <c r="R178" s="3" t="n"/>
+      <c r="S178" s="3" t="n"/>
+      <c r="T178" s="3" t="n"/>
+      <c r="U178" s="3" t="n"/>
+      <c r="V178" s="3" t="n"/>
+      <c r="W178" s="3" t="n"/>
+      <c r="X178" s="3" t="n"/>
+      <c r="Y178" s="3" t="n"/>
+      <c r="Z178" s="3" t="n"/>
+      <c r="AA178" s="3" t="n"/>
+      <c r="AB178" s="3" t="n"/>
+      <c r="AC178" s="3" t="n"/>
+      <c r="AD178" s="3" t="n"/>
+      <c r="AE178" s="3" t="n"/>
+      <c r="AF178" s="3" t="n"/>
+      <c r="AG178" s="3" t="n"/>
+      <c r="AH178" s="3" t="n"/>
+      <c r="AI178" s="3" t="n"/>
+      <c r="AJ178" s="3" t="n"/>
+      <c r="AK178" s="3">
+        <f>SUM(D178:AI178)</f>
+        <v/>
+      </c>
+      <c r="AL178" s="3" t="n"/>
+      <c r="AM178" s="3" t="n"/>
+      <c r="AN178" s="3" t="n"/>
+      <c r="AO178" s="3" t="n"/>
+      <c r="AP178" s="3">
+        <f>AJ178+AK178</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n"/>
+      <c r="B179" s="3" t="n"/>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n"/>
+      <c r="E179" s="3" t="n"/>
+      <c r="F179" s="3" t="n"/>
+      <c r="G179" s="3" t="n"/>
+      <c r="H179" s="3" t="n"/>
+      <c r="I179" s="3" t="n"/>
+      <c r="J179" s="3" t="n"/>
+      <c r="K179" s="3" t="n"/>
+      <c r="L179" s="3" t="n"/>
+      <c r="M179" s="3" t="n"/>
+      <c r="N179" s="3" t="n"/>
+      <c r="O179" s="3" t="n"/>
+      <c r="P179" s="3" t="n"/>
+      <c r="Q179" s="3" t="n"/>
+      <c r="R179" s="3" t="n"/>
+      <c r="S179" s="3" t="n"/>
+      <c r="T179" s="3" t="n"/>
+      <c r="U179" s="3" t="n"/>
+      <c r="V179" s="3" t="n"/>
+      <c r="W179" s="3" t="n"/>
+      <c r="X179" s="3" t="n"/>
+      <c r="Y179" s="3" t="n"/>
+      <c r="Z179" s="3" t="n"/>
+      <c r="AA179" s="3" t="n"/>
+      <c r="AB179" s="3" t="n"/>
+      <c r="AC179" s="3" t="n"/>
+      <c r="AD179" s="3" t="n"/>
+      <c r="AE179" s="3" t="n"/>
+      <c r="AF179" s="3" t="n"/>
+      <c r="AG179" s="3" t="n"/>
+      <c r="AH179" s="3" t="n"/>
+      <c r="AI179" s="3" t="n"/>
+      <c r="AJ179" s="3" t="n"/>
+      <c r="AK179" s="3">
+        <f>SUM(D179:AI179)</f>
+        <v/>
+      </c>
+      <c r="AL179" s="3" t="n"/>
+      <c r="AM179" s="3" t="n"/>
+      <c r="AN179" s="3" t="n"/>
+      <c r="AO179" s="3" t="n"/>
+      <c r="AP179" s="3">
+        <f>AJ179+AK179</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n"/>
+      <c r="B180" s="3" t="n"/>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="3" t="n"/>
+      <c r="G180" s="3" t="n"/>
+      <c r="H180" s="3" t="n"/>
+      <c r="I180" s="3" t="n"/>
+      <c r="J180" s="3" t="n"/>
+      <c r="K180" s="3" t="n"/>
+      <c r="L180" s="3" t="n"/>
+      <c r="M180" s="3" t="n"/>
+      <c r="N180" s="3" t="n"/>
+      <c r="O180" s="3" t="n"/>
+      <c r="P180" s="3" t="n"/>
+      <c r="Q180" s="3" t="n"/>
+      <c r="R180" s="3" t="n"/>
+      <c r="S180" s="3" t="n"/>
+      <c r="T180" s="3" t="n"/>
+      <c r="U180" s="3" t="n"/>
+      <c r="V180" s="3" t="n"/>
+      <c r="W180" s="3" t="n"/>
+      <c r="X180" s="3" t="n"/>
+      <c r="Y180" s="3" t="n"/>
+      <c r="Z180" s="3" t="n"/>
+      <c r="AA180" s="3" t="n"/>
+      <c r="AB180" s="3" t="n"/>
+      <c r="AC180" s="3" t="n"/>
+      <c r="AD180" s="3" t="n"/>
+      <c r="AE180" s="3" t="n"/>
+      <c r="AF180" s="3" t="n"/>
+      <c r="AG180" s="3" t="n"/>
+      <c r="AH180" s="3" t="n"/>
+      <c r="AI180" s="3" t="n"/>
+      <c r="AJ180" s="3" t="n"/>
+      <c r="AK180" s="3">
+        <f>SUM(D180:AI180)</f>
+        <v/>
+      </c>
+      <c r="AL180" s="3" t="n"/>
+      <c r="AM180" s="3" t="n"/>
+      <c r="AN180" s="3" t="n"/>
+      <c r="AO180" s="3" t="n"/>
+      <c r="AP180" s="3">
+        <f>AJ180+AK180</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n"/>
+      <c r="B181" s="3" t="n"/>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n"/>
+      <c r="E181" s="3" t="n"/>
+      <c r="F181" s="3" t="n"/>
+      <c r="G181" s="3" t="n"/>
+      <c r="H181" s="3" t="n"/>
+      <c r="I181" s="3" t="n"/>
+      <c r="J181" s="3" t="n"/>
+      <c r="K181" s="3" t="n"/>
+      <c r="L181" s="3" t="n"/>
+      <c r="M181" s="3" t="n"/>
+      <c r="N181" s="3" t="n"/>
+      <c r="O181" s="3" t="n"/>
+      <c r="P181" s="3" t="n"/>
+      <c r="Q181" s="3" t="n"/>
+      <c r="R181" s="3" t="n"/>
+      <c r="S181" s="3" t="n"/>
+      <c r="T181" s="3" t="n"/>
+      <c r="U181" s="3" t="n"/>
+      <c r="V181" s="3" t="n"/>
+      <c r="W181" s="3" t="n"/>
+      <c r="X181" s="3" t="n"/>
+      <c r="Y181" s="3" t="n"/>
+      <c r="Z181" s="3" t="n"/>
+      <c r="AA181" s="3" t="n"/>
+      <c r="AB181" s="3" t="n"/>
+      <c r="AC181" s="3" t="n"/>
+      <c r="AD181" s="3" t="n"/>
+      <c r="AE181" s="3" t="n"/>
+      <c r="AF181" s="3" t="n"/>
+      <c r="AG181" s="3" t="n"/>
+      <c r="AH181" s="3" t="n"/>
+      <c r="AI181" s="3" t="n"/>
+      <c r="AJ181" s="3" t="n"/>
+      <c r="AK181" s="3">
+        <f>SUM(D181:AI181)</f>
+        <v/>
+      </c>
+      <c r="AL181" s="3" t="n"/>
+      <c r="AM181" s="3" t="n"/>
+      <c r="AN181" s="3" t="n"/>
+      <c r="AO181" s="3" t="n"/>
+      <c r="AP181" s="3">
+        <f>AJ181+AK181</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n"/>
+      <c r="B182" s="3" t="n"/>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n"/>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="3" t="n"/>
+      <c r="G182" s="3" t="n"/>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="n"/>
+      <c r="J182" s="3" t="n"/>
+      <c r="K182" s="3" t="n"/>
+      <c r="L182" s="3" t="n"/>
+      <c r="M182" s="3" t="n"/>
+      <c r="N182" s="3" t="n"/>
+      <c r="O182" s="3" t="n"/>
+      <c r="P182" s="3" t="n"/>
+      <c r="Q182" s="3" t="n"/>
+      <c r="R182" s="3" t="n"/>
+      <c r="S182" s="3" t="n"/>
+      <c r="T182" s="3" t="n"/>
+      <c r="U182" s="3" t="n"/>
+      <c r="V182" s="3" t="n"/>
+      <c r="W182" s="3" t="n"/>
+      <c r="X182" s="3" t="n"/>
+      <c r="Y182" s="3" t="n"/>
+      <c r="Z182" s="3" t="n"/>
+      <c r="AA182" s="3" t="n"/>
+      <c r="AB182" s="3" t="n"/>
+      <c r="AC182" s="3" t="n"/>
+      <c r="AD182" s="3" t="n"/>
+      <c r="AE182" s="3" t="n"/>
+      <c r="AF182" s="3" t="n"/>
+      <c r="AG182" s="3" t="n"/>
+      <c r="AH182" s="3" t="n"/>
+      <c r="AI182" s="3" t="n"/>
+      <c r="AJ182" s="3" t="n"/>
+      <c r="AK182" s="3">
+        <f>SUM(D182:AI182)</f>
+        <v/>
+      </c>
+      <c r="AL182" s="3" t="n"/>
+      <c r="AM182" s="3" t="n"/>
+      <c r="AN182" s="3" t="n"/>
+      <c r="AO182" s="3" t="n"/>
+      <c r="AP182" s="3">
+        <f>AJ182+AK182</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n"/>
+      <c r="B183" s="3" t="n"/>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="n"/>
+      <c r="E183" s="3" t="n"/>
+      <c r="F183" s="3" t="n"/>
+      <c r="G183" s="3" t="n"/>
+      <c r="H183" s="3" t="n"/>
+      <c r="I183" s="3" t="n"/>
+      <c r="J183" s="3" t="n"/>
+      <c r="K183" s="3" t="n"/>
+      <c r="L183" s="3" t="n"/>
+      <c r="M183" s="3" t="n"/>
+      <c r="N183" s="3" t="n"/>
+      <c r="O183" s="3" t="n"/>
+      <c r="P183" s="3" t="n"/>
+      <c r="Q183" s="3" t="n"/>
+      <c r="R183" s="3" t="n"/>
+      <c r="S183" s="3" t="n"/>
+      <c r="T183" s="3" t="n"/>
+      <c r="U183" s="3" t="n"/>
+      <c r="V183" s="3" t="n"/>
+      <c r="W183" s="3" t="n"/>
+      <c r="X183" s="3" t="n"/>
+      <c r="Y183" s="3" t="n"/>
+      <c r="Z183" s="3" t="n"/>
+      <c r="AA183" s="3" t="n"/>
+      <c r="AB183" s="3" t="n"/>
+      <c r="AC183" s="3" t="n"/>
+      <c r="AD183" s="3" t="n"/>
+      <c r="AE183" s="3" t="n"/>
+      <c r="AF183" s="3" t="n"/>
+      <c r="AG183" s="3" t="n"/>
+      <c r="AH183" s="3" t="n"/>
+      <c r="AI183" s="3" t="n"/>
+      <c r="AJ183" s="3" t="n"/>
+      <c r="AK183" s="3">
+        <f>SUM(D183:AI183)</f>
+        <v/>
+      </c>
+      <c r="AL183" s="3" t="n"/>
+      <c r="AM183" s="3" t="n"/>
+      <c r="AN183" s="3" t="n"/>
+      <c r="AO183" s="3" t="n"/>
+      <c r="AP183" s="3">
+        <f>AJ183+AK183</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n"/>
+      <c r="B184" s="3" t="n"/>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n"/>
+      <c r="E184" s="3" t="n"/>
+      <c r="F184" s="3" t="n"/>
+      <c r="G184" s="3" t="n"/>
+      <c r="H184" s="3" t="n"/>
+      <c r="I184" s="3" t="n"/>
+      <c r="J184" s="3" t="n"/>
+      <c r="K184" s="3" t="n"/>
+      <c r="L184" s="3" t="n"/>
+      <c r="M184" s="3" t="n"/>
+      <c r="N184" s="3" t="n"/>
+      <c r="O184" s="3" t="n"/>
+      <c r="P184" s="3" t="n"/>
+      <c r="Q184" s="3" t="n"/>
+      <c r="R184" s="3" t="n"/>
+      <c r="S184" s="3" t="n"/>
+      <c r="T184" s="3" t="n"/>
+      <c r="U184" s="3" t="n"/>
+      <c r="V184" s="3" t="n"/>
+      <c r="W184" s="3" t="n"/>
+      <c r="X184" s="3" t="n"/>
+      <c r="Y184" s="3" t="n"/>
+      <c r="Z184" s="3" t="n"/>
+      <c r="AA184" s="3" t="n"/>
+      <c r="AB184" s="3" t="n"/>
+      <c r="AC184" s="3" t="n"/>
+      <c r="AD184" s="3" t="n"/>
+      <c r="AE184" s="3" t="n"/>
+      <c r="AF184" s="3" t="n"/>
+      <c r="AG184" s="3" t="n"/>
+      <c r="AH184" s="3" t="n"/>
+      <c r="AI184" s="3" t="n"/>
+      <c r="AJ184" s="3" t="n"/>
+      <c r="AK184" s="3">
+        <f>SUM(D184:AI184)</f>
+        <v/>
+      </c>
+      <c r="AL184" s="3" t="n"/>
+      <c r="AM184" s="3" t="n"/>
+      <c r="AN184" s="3" t="n"/>
+      <c r="AO184" s="3" t="n"/>
+      <c r="AP184" s="3">
+        <f>AJ184+AK184</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n"/>
+      <c r="B185" s="3" t="n"/>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n"/>
+      <c r="E185" s="3" t="n"/>
+      <c r="F185" s="3" t="n"/>
+      <c r="G185" s="3" t="n"/>
+      <c r="H185" s="3" t="n"/>
+      <c r="I185" s="3" t="n"/>
+      <c r="J185" s="3" t="n"/>
+      <c r="K185" s="3" t="n"/>
+      <c r="L185" s="3" t="n"/>
+      <c r="M185" s="3" t="n"/>
+      <c r="N185" s="3" t="n"/>
+      <c r="O185" s="3" t="n"/>
+      <c r="P185" s="3" t="n"/>
+      <c r="Q185" s="3" t="n"/>
+      <c r="R185" s="3" t="n"/>
+      <c r="S185" s="3" t="n"/>
+      <c r="T185" s="3" t="n"/>
+      <c r="U185" s="3" t="n"/>
+      <c r="V185" s="3" t="n"/>
+      <c r="W185" s="3" t="n"/>
+      <c r="X185" s="3" t="n"/>
+      <c r="Y185" s="3" t="n"/>
+      <c r="Z185" s="3" t="n"/>
+      <c r="AA185" s="3" t="n"/>
+      <c r="AB185" s="3" t="n"/>
+      <c r="AC185" s="3" t="n"/>
+      <c r="AD185" s="3" t="n"/>
+      <c r="AE185" s="3" t="n"/>
+      <c r="AF185" s="3" t="n"/>
+      <c r="AG185" s="3" t="n"/>
+      <c r="AH185" s="3" t="n"/>
+      <c r="AI185" s="3" t="n"/>
+      <c r="AJ185" s="3" t="n"/>
+      <c r="AK185" s="3">
+        <f>SUM(D185:AI185)</f>
+        <v/>
+      </c>
+      <c r="AL185" s="3" t="n"/>
+      <c r="AM185" s="3" t="n"/>
+      <c r="AN185" s="3" t="n"/>
+      <c r="AO185" s="3" t="n"/>
+      <c r="AP185" s="3">
+        <f>AJ185+AK185</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n"/>
+      <c r="B186" s="3" t="n"/>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n"/>
+      <c r="E186" s="3" t="n"/>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="3" t="n"/>
+      <c r="H186" s="3" t="n"/>
+      <c r="I186" s="3" t="n"/>
+      <c r="J186" s="3" t="n"/>
+      <c r="K186" s="3" t="n"/>
+      <c r="L186" s="3" t="n"/>
+      <c r="M186" s="3" t="n"/>
+      <c r="N186" s="3" t="n"/>
+      <c r="O186" s="3" t="n"/>
+      <c r="P186" s="3" t="n"/>
+      <c r="Q186" s="3" t="n"/>
+      <c r="R186" s="3" t="n"/>
+      <c r="S186" s="3" t="n"/>
+      <c r="T186" s="3" t="n"/>
+      <c r="U186" s="3" t="n"/>
+      <c r="V186" s="3" t="n"/>
+      <c r="W186" s="3" t="n"/>
+      <c r="X186" s="3" t="n"/>
+      <c r="Y186" s="3" t="n"/>
+      <c r="Z186" s="3" t="n"/>
+      <c r="AA186" s="3" t="n"/>
+      <c r="AB186" s="3" t="n"/>
+      <c r="AC186" s="3" t="n"/>
+      <c r="AD186" s="3" t="n"/>
+      <c r="AE186" s="3" t="n"/>
+      <c r="AF186" s="3" t="n"/>
+      <c r="AG186" s="3" t="n"/>
+      <c r="AH186" s="3" t="n"/>
+      <c r="AI186" s="3" t="n"/>
+      <c r="AJ186" s="3" t="n"/>
+      <c r="AK186" s="3">
+        <f>SUM(D186:AI186)</f>
+        <v/>
+      </c>
+      <c r="AL186" s="3" t="n"/>
+      <c r="AM186" s="3" t="n"/>
+      <c r="AN186" s="3" t="n"/>
+      <c r="AO186" s="3" t="n"/>
+      <c r="AP186" s="3">
+        <f>AJ186+AK186</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="41">
+    <mergeCell ref="AM92:AO92"/>
     <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="Q90:Q92"/>
+    <mergeCell ref="F90:F92"/>
+    <mergeCell ref="H90:H92"/>
+    <mergeCell ref="J90:J92"/>
+    <mergeCell ref="T90:T92"/>
+    <mergeCell ref="L90:L92"/>
+    <mergeCell ref="V90:V92"/>
+    <mergeCell ref="AC90:AC92"/>
+    <mergeCell ref="N90:N92"/>
+    <mergeCell ref="AJ90:AL91"/>
+    <mergeCell ref="AK92:AL92"/>
+    <mergeCell ref="O90:O92"/>
+    <mergeCell ref="AF90:AF92"/>
+    <mergeCell ref="G90:G92"/>
+    <mergeCell ref="X90:X92"/>
+    <mergeCell ref="S90:S92"/>
+    <mergeCell ref="I90:I92"/>
+    <mergeCell ref="Z90:Z92"/>
+    <mergeCell ref="U90:U92"/>
+    <mergeCell ref="AA90:AA92"/>
+    <mergeCell ref="AH90:AH92"/>
+    <mergeCell ref="AP90:AP92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="AE90:AE92"/>
+    <mergeCell ref="D90:D92"/>
+    <mergeCell ref="AG90:AG92"/>
+    <mergeCell ref="AI90:AI92"/>
+    <mergeCell ref="P90:P92"/>
+    <mergeCell ref="R90:R92"/>
+    <mergeCell ref="AB90:AB92"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="AM90:AO91"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="AD90:AD92"/>
+    <mergeCell ref="E90:E92"/>
+    <mergeCell ref="K90:K92"/>
+    <mergeCell ref="W90:W92"/>
+    <mergeCell ref="M90:M92"/>
+    <mergeCell ref="Y90:Y92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/templates/master_template.xlsx
+++ b/backend/templates/master_template.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,14 @@
       <name val="宋体"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,8 +66,13 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090EE90"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,12 +86,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,10 +108,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -114,6 +120,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -921,17 +932,47 @@
       <c r="AG7" s="3" t="inlineStr"/>
       <c r="AH7" s="3" t="inlineStr"/>
       <c r="AI7" s="3" t="n"/>
-      <c r="AJ7" s="3" t="n"/>
-      <c r="AK7" s="3" t="n"/>
-      <c r="AL7" s="3" t="n"/>
-      <c r="AM7" s="3" t="n"/>
-      <c r="AN7" s="3" t="n"/>
-      <c r="AO7" s="3" t="n"/>
-      <c r="AP7" s="3" t="n"/>
-      <c r="AQ7" s="3" t="n"/>
-      <c r="AR7" s="3" t="n"/>
+      <c r="AJ7" s="4">
+        <f>COUNTIF(D7:AH7,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK7" s="4">
+        <f>COUNTIF(D7:AH7,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL7" s="4">
+        <f>COUNTIF(D7:AH7,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM7" s="4">
+        <f>COUNTIF(D7:AH7,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN7" s="4">
+        <f>COUNTIF(D7:AH7,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO7" s="4">
+        <f>COUNTIF(D7:AH7,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP7" s="4">
+        <f>COUNTIF(D7:AH7,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ7" s="4">
+        <f>COUNTIF(D7:AH7,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR7" s="4">
+        <f>COUNTIF(D7:AH7,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS7" s="3" t="n"/>
-      <c r="AT7" s="3" t="n"/>
+      <c r="AT7" s="4">
+        <f>21-AJ7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n"/>
@@ -1055,17 +1096,47 @@
       <c r="AG9" s="3" t="inlineStr"/>
       <c r="AH9" s="3" t="inlineStr"/>
       <c r="AI9" s="3" t="n"/>
-      <c r="AJ9" s="3" t="n"/>
-      <c r="AK9" s="3" t="n"/>
-      <c r="AL9" s="3" t="n"/>
-      <c r="AM9" s="3" t="n"/>
-      <c r="AN9" s="3" t="n"/>
-      <c r="AO9" s="3" t="n"/>
-      <c r="AP9" s="3" t="n"/>
-      <c r="AQ9" s="3" t="n"/>
-      <c r="AR9" s="3" t="n"/>
+      <c r="AJ9" s="4">
+        <f>COUNTIF(D9:AH9,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK9" s="4">
+        <f>COUNTIF(D9:AH9,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL9" s="4">
+        <f>COUNTIF(D9:AH9,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM9" s="4">
+        <f>COUNTIF(D9:AH9,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN9" s="4">
+        <f>COUNTIF(D9:AH9,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO9" s="4">
+        <f>COUNTIF(D9:AH9,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP9" s="4">
+        <f>COUNTIF(D9:AH9,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ9" s="4">
+        <f>COUNTIF(D9:AH9,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR9" s="4">
+        <f>COUNTIF(D9:AH9,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS9" s="3" t="n"/>
-      <c r="AT9" s="3" t="n"/>
+      <c r="AT9" s="4">
+        <f>21-AJ9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
@@ -1189,17 +1260,47 @@
       <c r="AG11" s="3" t="inlineStr"/>
       <c r="AH11" s="3" t="inlineStr"/>
       <c r="AI11" s="3" t="n"/>
-      <c r="AJ11" s="3" t="n"/>
-      <c r="AK11" s="3" t="n"/>
-      <c r="AL11" s="3" t="n"/>
-      <c r="AM11" s="3" t="n"/>
-      <c r="AN11" s="3" t="n"/>
-      <c r="AO11" s="3" t="n"/>
-      <c r="AP11" s="3" t="n"/>
-      <c r="AQ11" s="3" t="n"/>
-      <c r="AR11" s="3" t="n"/>
+      <c r="AJ11" s="4">
+        <f>COUNTIF(D11:AH11,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK11" s="4">
+        <f>COUNTIF(D11:AH11,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL11" s="4">
+        <f>COUNTIF(D11:AH11,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="4">
+        <f>COUNTIF(D11:AH11,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN11" s="4">
+        <f>COUNTIF(D11:AH11,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO11" s="4">
+        <f>COUNTIF(D11:AH11,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP11" s="4">
+        <f>COUNTIF(D11:AH11,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ11" s="4">
+        <f>COUNTIF(D11:AH11,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR11" s="4">
+        <f>COUNTIF(D11:AH11,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS11" s="3" t="n"/>
-      <c r="AT11" s="3" t="n"/>
+      <c r="AT11" s="4">
+        <f>21-AJ11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
@@ -1323,17 +1424,47 @@
       <c r="AG13" s="3" t="inlineStr"/>
       <c r="AH13" s="3" t="inlineStr"/>
       <c r="AI13" s="3" t="n"/>
-      <c r="AJ13" s="3" t="n"/>
-      <c r="AK13" s="3" t="n"/>
-      <c r="AL13" s="3" t="n"/>
-      <c r="AM13" s="3" t="n"/>
-      <c r="AN13" s="3" t="n"/>
-      <c r="AO13" s="3" t="n"/>
-      <c r="AP13" s="3" t="n"/>
-      <c r="AQ13" s="3" t="n"/>
-      <c r="AR13" s="3" t="n"/>
+      <c r="AJ13" s="4">
+        <f>COUNTIF(D13:AH13,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK13" s="4">
+        <f>COUNTIF(D13:AH13,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL13" s="4">
+        <f>COUNTIF(D13:AH13,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM13" s="4">
+        <f>COUNTIF(D13:AH13,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN13" s="4">
+        <f>COUNTIF(D13:AH13,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO13" s="4">
+        <f>COUNTIF(D13:AH13,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP13" s="4">
+        <f>COUNTIF(D13:AH13,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ13" s="4">
+        <f>COUNTIF(D13:AH13,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR13" s="4">
+        <f>COUNTIF(D13:AH13,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS13" s="3" t="n"/>
-      <c r="AT13" s="3" t="n"/>
+      <c r="AT13" s="4">
+        <f>21-AJ13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
@@ -1457,17 +1588,47 @@
       <c r="AG15" s="3" t="inlineStr"/>
       <c r="AH15" s="3" t="inlineStr"/>
       <c r="AI15" s="3" t="n"/>
-      <c r="AJ15" s="3" t="n"/>
-      <c r="AK15" s="3" t="n"/>
-      <c r="AL15" s="3" t="n"/>
-      <c r="AM15" s="3" t="n"/>
-      <c r="AN15" s="3" t="n"/>
-      <c r="AO15" s="3" t="n"/>
-      <c r="AP15" s="3" t="n"/>
-      <c r="AQ15" s="3" t="n"/>
-      <c r="AR15" s="3" t="n"/>
+      <c r="AJ15" s="4">
+        <f>COUNTIF(D15:AH15,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK15" s="4">
+        <f>COUNTIF(D15:AH15,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="4">
+        <f>COUNTIF(D15:AH15,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="4">
+        <f>COUNTIF(D15:AH15,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN15" s="4">
+        <f>COUNTIF(D15:AH15,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO15" s="4">
+        <f>COUNTIF(D15:AH15,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP15" s="4">
+        <f>COUNTIF(D15:AH15,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ15" s="4">
+        <f>COUNTIF(D15:AH15,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR15" s="4">
+        <f>COUNTIF(D15:AH15,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS15" s="3" t="n"/>
-      <c r="AT15" s="3" t="n"/>
+      <c r="AT15" s="4">
+        <f>21-AJ15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -1591,17 +1752,47 @@
       <c r="AG17" s="3" t="inlineStr"/>
       <c r="AH17" s="3" t="inlineStr"/>
       <c r="AI17" s="3" t="n"/>
-      <c r="AJ17" s="3" t="n"/>
-      <c r="AK17" s="3" t="n"/>
-      <c r="AL17" s="3" t="n"/>
-      <c r="AM17" s="3" t="n"/>
-      <c r="AN17" s="3" t="n"/>
-      <c r="AO17" s="3" t="n"/>
-      <c r="AP17" s="3" t="n"/>
-      <c r="AQ17" s="3" t="n"/>
-      <c r="AR17" s="3" t="n"/>
+      <c r="AJ17" s="4">
+        <f>COUNTIF(D17:AH17,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK17" s="4">
+        <f>COUNTIF(D17:AH17,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL17" s="4">
+        <f>COUNTIF(D17:AH17,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM17" s="4">
+        <f>COUNTIF(D17:AH17,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN17" s="4">
+        <f>COUNTIF(D17:AH17,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO17" s="4">
+        <f>COUNTIF(D17:AH17,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP17" s="4">
+        <f>COUNTIF(D17:AH17,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ17" s="4">
+        <f>COUNTIF(D17:AH17,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR17" s="4">
+        <f>COUNTIF(D17:AH17,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS17" s="3" t="n"/>
-      <c r="AT17" s="3" t="n"/>
+      <c r="AT17" s="4">
+        <f>21-AJ17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
@@ -1725,17 +1916,47 @@
       <c r="AG19" s="3" t="inlineStr"/>
       <c r="AH19" s="3" t="inlineStr"/>
       <c r="AI19" s="3" t="n"/>
-      <c r="AJ19" s="3" t="n"/>
-      <c r="AK19" s="3" t="n"/>
-      <c r="AL19" s="3" t="n"/>
-      <c r="AM19" s="3" t="n"/>
-      <c r="AN19" s="3" t="n"/>
-      <c r="AO19" s="3" t="n"/>
-      <c r="AP19" s="3" t="n"/>
-      <c r="AQ19" s="3" t="n"/>
-      <c r="AR19" s="3" t="n"/>
+      <c r="AJ19" s="4">
+        <f>COUNTIF(D19:AH19,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK19" s="4">
+        <f>COUNTIF(D19:AH19,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="4">
+        <f>COUNTIF(D19:AH19,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="4">
+        <f>COUNTIF(D19:AH19,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN19" s="4">
+        <f>COUNTIF(D19:AH19,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO19" s="4">
+        <f>COUNTIF(D19:AH19,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP19" s="4">
+        <f>COUNTIF(D19:AH19,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="4">
+        <f>COUNTIF(D19:AH19,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR19" s="4">
+        <f>COUNTIF(D19:AH19,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS19" s="3" t="n"/>
-      <c r="AT19" s="3" t="n"/>
+      <c r="AT19" s="4">
+        <f>21-AJ19</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
@@ -1859,17 +2080,47 @@
       <c r="AG21" s="3" t="inlineStr"/>
       <c r="AH21" s="3" t="inlineStr"/>
       <c r="AI21" s="3" t="n"/>
-      <c r="AJ21" s="3" t="n"/>
-      <c r="AK21" s="3" t="n"/>
-      <c r="AL21" s="3" t="n"/>
-      <c r="AM21" s="3" t="n"/>
-      <c r="AN21" s="3" t="n"/>
-      <c r="AO21" s="3" t="n"/>
-      <c r="AP21" s="3" t="n"/>
-      <c r="AQ21" s="3" t="n"/>
-      <c r="AR21" s="3" t="n"/>
+      <c r="AJ21" s="4">
+        <f>COUNTIF(D21:AH21,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK21" s="4">
+        <f>COUNTIF(D21:AH21,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="4">
+        <f>COUNTIF(D21:AH21,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="4">
+        <f>COUNTIF(D21:AH21,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN21" s="4">
+        <f>COUNTIF(D21:AH21,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO21" s="4">
+        <f>COUNTIF(D21:AH21,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP21" s="4">
+        <f>COUNTIF(D21:AH21,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ21" s="4">
+        <f>COUNTIF(D21:AH21,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR21" s="4">
+        <f>COUNTIF(D21:AH21,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS21" s="3" t="n"/>
-      <c r="AT21" s="3" t="n"/>
+      <c r="AT21" s="4">
+        <f>21-AJ21</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -1993,17 +2244,47 @@
       <c r="AG23" s="3" t="inlineStr"/>
       <c r="AH23" s="3" t="inlineStr"/>
       <c r="AI23" s="3" t="n"/>
-      <c r="AJ23" s="3" t="n"/>
-      <c r="AK23" s="3" t="n"/>
-      <c r="AL23" s="3" t="n"/>
-      <c r="AM23" s="3" t="n"/>
-      <c r="AN23" s="3" t="n"/>
-      <c r="AO23" s="3" t="n"/>
-      <c r="AP23" s="3" t="n"/>
-      <c r="AQ23" s="3" t="n"/>
-      <c r="AR23" s="3" t="n"/>
+      <c r="AJ23" s="4">
+        <f>COUNTIF(D23:AH23,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK23" s="4">
+        <f>COUNTIF(D23:AH23,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL23" s="4">
+        <f>COUNTIF(D23:AH23,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM23" s="4">
+        <f>COUNTIF(D23:AH23,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN23" s="4">
+        <f>COUNTIF(D23:AH23,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO23" s="4">
+        <f>COUNTIF(D23:AH23,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP23" s="4">
+        <f>COUNTIF(D23:AH23,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ23" s="4">
+        <f>COUNTIF(D23:AH23,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR23" s="4">
+        <f>COUNTIF(D23:AH23,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS23" s="3" t="n"/>
-      <c r="AT23" s="3" t="n"/>
+      <c r="AT23" s="4">
+        <f>21-AJ23</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -2127,17 +2408,47 @@
       <c r="AG25" s="3" t="inlineStr"/>
       <c r="AH25" s="3" t="inlineStr"/>
       <c r="AI25" s="3" t="n"/>
-      <c r="AJ25" s="3" t="n"/>
-      <c r="AK25" s="3" t="n"/>
-      <c r="AL25" s="3" t="n"/>
-      <c r="AM25" s="3" t="n"/>
-      <c r="AN25" s="3" t="n"/>
-      <c r="AO25" s="3" t="n"/>
-      <c r="AP25" s="3" t="n"/>
-      <c r="AQ25" s="3" t="n"/>
-      <c r="AR25" s="3" t="n"/>
+      <c r="AJ25" s="4">
+        <f>COUNTIF(D25:AH25,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK25" s="4">
+        <f>COUNTIF(D25:AH25,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL25" s="4">
+        <f>COUNTIF(D25:AH25,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM25" s="4">
+        <f>COUNTIF(D25:AH25,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN25" s="4">
+        <f>COUNTIF(D25:AH25,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO25" s="4">
+        <f>COUNTIF(D25:AH25,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP25" s="4">
+        <f>COUNTIF(D25:AH25,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ25" s="4">
+        <f>COUNTIF(D25:AH25,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR25" s="4">
+        <f>COUNTIF(D25:AH25,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS25" s="3" t="n"/>
-      <c r="AT25" s="3" t="n"/>
+      <c r="AT25" s="4">
+        <f>21-AJ25</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
@@ -2261,17 +2572,47 @@
       <c r="AG27" s="3" t="inlineStr"/>
       <c r="AH27" s="3" t="inlineStr"/>
       <c r="AI27" s="3" t="n"/>
-      <c r="AJ27" s="3" t="n"/>
-      <c r="AK27" s="3" t="n"/>
-      <c r="AL27" s="3" t="n"/>
-      <c r="AM27" s="3" t="n"/>
-      <c r="AN27" s="3" t="n"/>
-      <c r="AO27" s="3" t="n"/>
-      <c r="AP27" s="3" t="n"/>
-      <c r="AQ27" s="3" t="n"/>
-      <c r="AR27" s="3" t="n"/>
+      <c r="AJ27" s="4">
+        <f>COUNTIF(D27:AH27,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK27" s="4">
+        <f>COUNTIF(D27:AH27,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL27" s="4">
+        <f>COUNTIF(D27:AH27,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM27" s="4">
+        <f>COUNTIF(D27:AH27,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN27" s="4">
+        <f>COUNTIF(D27:AH27,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO27" s="4">
+        <f>COUNTIF(D27:AH27,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP27" s="4">
+        <f>COUNTIF(D27:AH27,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ27" s="4">
+        <f>COUNTIF(D27:AH27,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR27" s="4">
+        <f>COUNTIF(D27:AH27,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS27" s="3" t="n"/>
-      <c r="AT27" s="3" t="n"/>
+      <c r="AT27" s="4">
+        <f>21-AJ27</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
@@ -2395,17 +2736,47 @@
       <c r="AG29" s="3" t="inlineStr"/>
       <c r="AH29" s="3" t="inlineStr"/>
       <c r="AI29" s="3" t="n"/>
-      <c r="AJ29" s="3" t="n"/>
-      <c r="AK29" s="3" t="n"/>
-      <c r="AL29" s="3" t="n"/>
-      <c r="AM29" s="3" t="n"/>
-      <c r="AN29" s="3" t="n"/>
-      <c r="AO29" s="3" t="n"/>
-      <c r="AP29" s="3" t="n"/>
-      <c r="AQ29" s="3" t="n"/>
-      <c r="AR29" s="3" t="n"/>
+      <c r="AJ29" s="4">
+        <f>COUNTIF(D29:AH29,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK29" s="4">
+        <f>COUNTIF(D29:AH29,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL29" s="4">
+        <f>COUNTIF(D29:AH29,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM29" s="4">
+        <f>COUNTIF(D29:AH29,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN29" s="4">
+        <f>COUNTIF(D29:AH29,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO29" s="4">
+        <f>COUNTIF(D29:AH29,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP29" s="4">
+        <f>COUNTIF(D29:AH29,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ29" s="4">
+        <f>COUNTIF(D29:AH29,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR29" s="4">
+        <f>COUNTIF(D29:AH29,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS29" s="3" t="n"/>
-      <c r="AT29" s="3" t="n"/>
+      <c r="AT29" s="4">
+        <f>21-AJ29</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
@@ -2529,17 +2900,47 @@
       <c r="AG31" s="3" t="inlineStr"/>
       <c r="AH31" s="3" t="inlineStr"/>
       <c r="AI31" s="3" t="n"/>
-      <c r="AJ31" s="3" t="n"/>
-      <c r="AK31" s="3" t="n"/>
-      <c r="AL31" s="3" t="n"/>
-      <c r="AM31" s="3" t="n"/>
-      <c r="AN31" s="3" t="n"/>
-      <c r="AO31" s="3" t="n"/>
-      <c r="AP31" s="3" t="n"/>
-      <c r="AQ31" s="3" t="n"/>
-      <c r="AR31" s="3" t="n"/>
+      <c r="AJ31" s="4">
+        <f>COUNTIF(D31:AH31,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK31" s="4">
+        <f>COUNTIF(D31:AH31,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL31" s="4">
+        <f>COUNTIF(D31:AH31,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM31" s="4">
+        <f>COUNTIF(D31:AH31,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN31" s="4">
+        <f>COUNTIF(D31:AH31,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO31" s="4">
+        <f>COUNTIF(D31:AH31,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP31" s="4">
+        <f>COUNTIF(D31:AH31,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ31" s="4">
+        <f>COUNTIF(D31:AH31,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR31" s="4">
+        <f>COUNTIF(D31:AH31,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS31" s="3" t="n"/>
-      <c r="AT31" s="3" t="n"/>
+      <c r="AT31" s="4">
+        <f>21-AJ31</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
@@ -2663,17 +3064,47 @@
       <c r="AG33" s="3" t="inlineStr"/>
       <c r="AH33" s="3" t="inlineStr"/>
       <c r="AI33" s="3" t="n"/>
-      <c r="AJ33" s="3" t="n"/>
-      <c r="AK33" s="3" t="n"/>
-      <c r="AL33" s="3" t="n"/>
-      <c r="AM33" s="3" t="n"/>
-      <c r="AN33" s="3" t="n"/>
-      <c r="AO33" s="3" t="n"/>
-      <c r="AP33" s="3" t="n"/>
-      <c r="AQ33" s="3" t="n"/>
-      <c r="AR33" s="3" t="n"/>
+      <c r="AJ33" s="4">
+        <f>COUNTIF(D33:AH33,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK33" s="4">
+        <f>COUNTIF(D33:AH33,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL33" s="4">
+        <f>COUNTIF(D33:AH33,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM33" s="4">
+        <f>COUNTIF(D33:AH33,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN33" s="4">
+        <f>COUNTIF(D33:AH33,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO33" s="4">
+        <f>COUNTIF(D33:AH33,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP33" s="4">
+        <f>COUNTIF(D33:AH33,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ33" s="4">
+        <f>COUNTIF(D33:AH33,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR33" s="4">
+        <f>COUNTIF(D33:AH33,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS33" s="3" t="n"/>
-      <c r="AT33" s="3" t="n"/>
+      <c r="AT33" s="4">
+        <f>21-AJ33</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -2797,17 +3228,47 @@
       <c r="AG35" s="3" t="inlineStr"/>
       <c r="AH35" s="3" t="inlineStr"/>
       <c r="AI35" s="3" t="n"/>
-      <c r="AJ35" s="3" t="n"/>
-      <c r="AK35" s="3" t="n"/>
-      <c r="AL35" s="3" t="n"/>
-      <c r="AM35" s="3" t="n"/>
-      <c r="AN35" s="3" t="n"/>
-      <c r="AO35" s="3" t="n"/>
-      <c r="AP35" s="3" t="n"/>
-      <c r="AQ35" s="3" t="n"/>
-      <c r="AR35" s="3" t="n"/>
+      <c r="AJ35" s="4">
+        <f>COUNTIF(D35:AH35,$AJ$5)</f>
+        <v/>
+      </c>
+      <c r="AK35" s="4">
+        <f>COUNTIF(D35:AH35,$AK$5)</f>
+        <v/>
+      </c>
+      <c r="AL35" s="4">
+        <f>COUNTIF(D35:AH35,$AL$5)</f>
+        <v/>
+      </c>
+      <c r="AM35" s="4">
+        <f>COUNTIF(D35:AH35,$AM$5)</f>
+        <v/>
+      </c>
+      <c r="AN35" s="4">
+        <f>COUNTIF(D35:AH35,$AN$5)</f>
+        <v/>
+      </c>
+      <c r="AO35" s="4">
+        <f>COUNTIF(D35:AH35,$AO$5)</f>
+        <v/>
+      </c>
+      <c r="AP35" s="4">
+        <f>COUNTIF(D35:AH35,$AP$5)</f>
+        <v/>
+      </c>
+      <c r="AQ35" s="4">
+        <f>COUNTIF(D35:AH35,$AQ$5)</f>
+        <v/>
+      </c>
+      <c r="AR35" s="4">
+        <f>COUNTIF(D35:AH35,$AR$5)</f>
+        <v/>
+      </c>
       <c r="AS35" s="3" t="n"/>
-      <c r="AT35" s="3" t="n"/>
+      <c r="AT35" s="4">
+        <f>21-AJ35</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -3251,75 +3712,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN19"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
-    <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="3" customWidth="1" min="9" max="9"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
-    <col width="3" customWidth="1" min="11" max="11"/>
-    <col width="3" customWidth="1" min="12" max="12"/>
-    <col width="3" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
-    <col width="3" customWidth="1" min="16" max="16"/>
-    <col width="3" customWidth="1" min="17" max="17"/>
-    <col width="3" customWidth="1" min="18" max="18"/>
-    <col width="3" customWidth="1" min="19" max="19"/>
-    <col width="3" customWidth="1" min="20" max="20"/>
-    <col width="3" customWidth="1" min="21" max="21"/>
-    <col width="3" customWidth="1" min="22" max="22"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
-    <col width="3" customWidth="1" min="25" max="25"/>
-    <col width="3" customWidth="1" min="26" max="26"/>
-    <col width="3" customWidth="1" min="27" max="27"/>
-    <col width="3" customWidth="1" min="28" max="28"/>
-    <col width="3" customWidth="1" min="29" max="29"/>
-    <col width="3" customWidth="1" min="30" max="30"/>
-    <col width="3" customWidth="1" min="31" max="31"/>
-    <col width="3" customWidth="1" min="32" max="32"/>
-    <col width="3" customWidth="1" min="33" max="33"/>
-    <col width="3" customWidth="1" min="34" max="34"/>
-    <col width="3" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-    <col width="10" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
-    <col width="10" customWidth="1" min="44" max="44"/>
-    <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="10" customWidth="1" min="46" max="46"/>
-    <col width="10" customWidth="1" min="47" max="47"/>
-    <col width="10" customWidth="1" min="48" max="48"/>
-    <col width="10" customWidth="1" min="49" max="49"/>
-    <col width="10" customWidth="1" min="50" max="50"/>
-    <col width="10" customWidth="1" min="51" max="51"/>
-    <col width="10" customWidth="1" min="52" max="52"/>
-    <col width="10" customWidth="1" min="53" max="53"/>
-    <col width="10" customWidth="1" min="54" max="54"/>
-    <col width="10" customWidth="1" min="55" max="55"/>
-    <col width="10" customWidth="1" min="56" max="56"/>
-    <col width="10" customWidth="1" min="57" max="57"/>
-    <col width="10" customWidth="1" min="58" max="58"/>
-    <col width="10" customWidth="1" min="59" max="59"/>
-    <col width="10" customWidth="1" min="60" max="60"/>
-    <col width="10" customWidth="1" min="61" max="61"/>
-    <col width="10" customWidth="1" min="62" max="62"/>
-    <col width="10" customWidth="1" min="63" max="63"/>
-    <col width="10" customWidth="1" min="64" max="64"/>
-    <col width="10" customWidth="1" min="65" max="65"/>
-    <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3328,1642 +3755,919 @@
           <t>月度汇总 统计日期：2026-05-01 至 2026-05-31</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n"/>
-      <c r="C1" s="7" t="n"/>
-      <c r="D1" s="7" t="n"/>
-      <c r="E1" s="7" t="n"/>
-      <c r="F1" s="8" t="n"/>
-      <c r="G1" s="8" t="n"/>
-      <c r="H1" s="8" t="n"/>
-      <c r="I1" s="8" t="n"/>
-      <c r="J1" s="8" t="n"/>
-      <c r="K1" s="8" t="n"/>
-      <c r="L1" s="8" t="n"/>
-      <c r="M1" s="8" t="n"/>
-      <c r="N1" s="8" t="n"/>
-      <c r="O1" s="8" t="n"/>
-      <c r="P1" s="8" t="n"/>
-      <c r="Q1" s="8" t="n"/>
-      <c r="R1" s="8" t="n"/>
-      <c r="S1" s="8" t="n"/>
-      <c r="T1" s="8" t="n"/>
-      <c r="U1" s="8" t="n"/>
-      <c r="V1" s="8" t="n"/>
-      <c r="W1" s="8" t="n"/>
-      <c r="X1" s="8" t="n"/>
-      <c r="Y1" s="8" t="n"/>
-      <c r="Z1" s="8" t="n"/>
-      <c r="AA1" s="8" t="n"/>
-      <c r="AB1" s="8" t="n"/>
-      <c r="AC1" s="8" t="n"/>
-      <c r="AD1" s="8" t="n"/>
-      <c r="AE1" s="8" t="n"/>
-      <c r="AF1" s="8" t="n"/>
-      <c r="AG1" s="8" t="n"/>
-      <c r="AH1" s="8" t="n"/>
-      <c r="AI1" s="8" t="n"/>
-      <c r="AJ1" s="2" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AK1" s="9" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="AL1" s="9" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="AM1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AN1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AO1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AQ1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AR1" s="9" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="AS1" s="9" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="AT1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AU1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AV1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AW1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AX1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AY1" s="9" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="AZ1" s="9" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="BA1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="BB1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="BC1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="BD1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="BE1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="BF1" s="9" t="inlineStr">
+      <c r="X1" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="BG1" s="9" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="BH1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="BI1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="BJ1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="BK1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="BL1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="BM1" s="9" t="inlineStr">
+      <c r="AE1" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="BN1" s="9" t="inlineStr">
+      <c r="AF1" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>报表生成时间：2026-06-16 08:12</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="n"/>
-      <c r="N2" s="8" t="n"/>
-      <c r="O2" s="8" t="n"/>
-      <c r="P2" s="8" t="n"/>
-      <c r="Q2" s="8" t="n"/>
-      <c r="R2" s="8" t="n"/>
-      <c r="S2" s="8" t="n"/>
-      <c r="T2" s="8" t="n"/>
-      <c r="U2" s="8" t="n"/>
-      <c r="V2" s="8" t="n"/>
-      <c r="W2" s="8" t="n"/>
-      <c r="X2" s="8" t="n"/>
-      <c r="Y2" s="8" t="n"/>
-      <c r="Z2" s="8" t="n"/>
-      <c r="AA2" s="8" t="n"/>
-      <c r="AB2" s="8" t="n"/>
-      <c r="AC2" s="8" t="n"/>
-      <c r="AD2" s="8" t="n"/>
-      <c r="AE2" s="8" t="n"/>
-      <c r="AF2" s="8" t="n"/>
-      <c r="AG2" s="8" t="n"/>
-      <c r="AH2" s="8" t="n"/>
-      <c r="AI2" s="8" t="n"/>
-      <c r="AJ2" s="4" t="n"/>
-      <c r="AK2" s="11" t="n"/>
-      <c r="AL2" s="11" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n"/>
-      <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="11" t="n"/>
-      <c r="AS2" s="11" t="n"/>
-      <c r="AT2" s="4" t="n"/>
-      <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="n"/>
-      <c r="AW2" s="4" t="n"/>
-      <c r="AX2" s="4" t="n"/>
-      <c r="AY2" s="11" t="n"/>
-      <c r="AZ2" s="11" t="n"/>
-      <c r="BA2" s="4" t="n"/>
-      <c r="BB2" s="4" t="n"/>
-      <c r="BC2" s="4" t="n"/>
-      <c r="BD2" s="4" t="n"/>
-      <c r="BE2" s="4" t="n"/>
-      <c r="BF2" s="11" t="n"/>
-      <c r="BG2" s="11" t="n"/>
-      <c r="BH2" s="4" t="n"/>
-      <c r="BI2" s="4" t="n"/>
-      <c r="BJ2" s="4" t="n"/>
-      <c r="BK2" s="4" t="n"/>
-      <c r="BL2" s="4" t="n"/>
-      <c r="BM2" s="11" t="n"/>
-      <c r="BN2" s="11" t="n"/>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>报表生成时间：2026-06-17 03:25</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="9" t="n"/>
+      <c r="K2" s="9" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="9" t="n"/>
+      <c r="R2" s="9" t="n"/>
+      <c r="S2" s="4" t="n"/>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
+      <c r="W2" s="4" t="n"/>
+      <c r="X2" s="9" t="n"/>
+      <c r="Y2" s="9" t="n"/>
+      <c r="Z2" s="4" t="n"/>
+      <c r="AA2" s="4" t="n"/>
+      <c r="AB2" s="4" t="n"/>
+      <c r="AC2" s="4" t="n"/>
+      <c r="AD2" s="4" t="n"/>
+      <c r="AE2" s="9" t="n"/>
+      <c r="AF2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>员工信息</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>每日考勤状态</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
       <c r="E3" s="4" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="8" t="n"/>
-      <c r="I3" s="8" t="n"/>
-      <c r="J3" s="8" t="n"/>
-      <c r="K3" s="8" t="n"/>
-      <c r="L3" s="8" t="n"/>
-      <c r="M3" s="8" t="n"/>
-      <c r="N3" s="8" t="n"/>
-      <c r="O3" s="8" t="n"/>
-      <c r="P3" s="8" t="n"/>
-      <c r="Q3" s="8" t="n"/>
-      <c r="R3" s="8" t="n"/>
-      <c r="S3" s="8" t="n"/>
-      <c r="T3" s="8" t="n"/>
-      <c r="U3" s="8" t="n"/>
-      <c r="V3" s="8" t="n"/>
-      <c r="W3" s="8" t="n"/>
-      <c r="X3" s="8" t="n"/>
-      <c r="Y3" s="8" t="n"/>
-      <c r="Z3" s="8" t="n"/>
-      <c r="AA3" s="8" t="n"/>
-      <c r="AB3" s="8" t="n"/>
-      <c r="AC3" s="8" t="n"/>
-      <c r="AD3" s="8" t="n"/>
-      <c r="AE3" s="8" t="n"/>
-      <c r="AF3" s="8" t="n"/>
-      <c r="AG3" s="8" t="n"/>
-      <c r="AH3" s="8" t="n"/>
-      <c r="AI3" s="8" t="n"/>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>每日考勤状态</t>
-        </is>
-      </c>
-      <c r="AK3" s="11" t="n"/>
-      <c r="AL3" s="11" t="n"/>
-      <c r="AM3" s="4" t="n"/>
-      <c r="AN3" s="4" t="n"/>
-      <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="4" t="n"/>
-      <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="11" t="n"/>
-      <c r="AS3" s="11" t="n"/>
-      <c r="AT3" s="4" t="n"/>
-      <c r="AU3" s="4" t="n"/>
-      <c r="AV3" s="4" t="n"/>
-      <c r="AW3" s="4" t="n"/>
-      <c r="AX3" s="4" t="n"/>
-      <c r="AY3" s="11" t="n"/>
-      <c r="AZ3" s="11" t="n"/>
-      <c r="BA3" s="4" t="n"/>
-      <c r="BB3" s="4" t="n"/>
-      <c r="BC3" s="4" t="n"/>
-      <c r="BD3" s="4" t="n"/>
-      <c r="BE3" s="4" t="n"/>
-      <c r="BF3" s="11" t="n"/>
-      <c r="BG3" s="11" t="n"/>
-      <c r="BH3" s="4" t="n"/>
-      <c r="BI3" s="4" t="n"/>
-      <c r="BJ3" s="4" t="n"/>
-      <c r="BK3" s="4" t="n"/>
-      <c r="BL3" s="4" t="n"/>
-      <c r="BM3" s="11" t="n"/>
-      <c r="BN3" s="11" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="9" t="n"/>
+      <c r="R3" s="9" t="n"/>
+      <c r="S3" s="4" t="n"/>
+      <c r="T3" s="4" t="n"/>
+      <c r="U3" s="4" t="n"/>
+      <c r="V3" s="4" t="n"/>
+      <c r="W3" s="4" t="n"/>
+      <c r="X3" s="9" t="n"/>
+      <c r="Y3" s="9" t="n"/>
+      <c r="Z3" s="4" t="n"/>
+      <c r="AA3" s="4" t="n"/>
+      <c r="AB3" s="4" t="n"/>
+      <c r="AC3" s="4" t="n"/>
+      <c r="AD3" s="4" t="n"/>
+      <c r="AE3" s="9" t="n"/>
+      <c r="AF3" s="9" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>考勤组</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>工号</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>职位</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="8" t="n"/>
-      <c r="H4" s="8" t="n"/>
-      <c r="I4" s="8" t="n"/>
-      <c r="J4" s="8" t="n"/>
-      <c r="K4" s="8" t="n"/>
-      <c r="L4" s="8" t="n"/>
-      <c r="M4" s="8" t="n"/>
-      <c r="N4" s="8" t="n"/>
-      <c r="O4" s="8" t="n"/>
-      <c r="P4" s="8" t="n"/>
-      <c r="Q4" s="8" t="n"/>
-      <c r="R4" s="8" t="n"/>
-      <c r="S4" s="8" t="n"/>
-      <c r="T4" s="8" t="n"/>
-      <c r="U4" s="8" t="n"/>
-      <c r="V4" s="8" t="n"/>
-      <c r="W4" s="8" t="n"/>
-      <c r="X4" s="8" t="n"/>
-      <c r="Y4" s="8" t="n"/>
-      <c r="Z4" s="8" t="n"/>
-      <c r="AA4" s="8" t="n"/>
-      <c r="AB4" s="8" t="n"/>
-      <c r="AC4" s="8" t="n"/>
-      <c r="AD4" s="8" t="n"/>
-      <c r="AE4" s="8" t="n"/>
-      <c r="AF4" s="8" t="n"/>
-      <c r="AG4" s="8" t="n"/>
-      <c r="AH4" s="8" t="n"/>
-      <c r="AI4" s="8" t="n"/>
-      <c r="AJ4" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AK4" s="9" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="AL4" s="9" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="AM4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AN4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AO4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AQ4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AR4" s="9" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="AS4" s="9" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="AT4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AU4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AV4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AY4" s="9" t="inlineStr">
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="AZ4" s="9" t="inlineStr">
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="BA4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="BB4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="BF4" s="9" t="inlineStr">
+      <c r="X4" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="BG4" s="9" t="inlineStr">
+      <c r="Y4" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="BI4" s="2" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="BJ4" s="2" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="BK4" s="2" t="inlineStr">
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="BL4" s="2" t="inlineStr">
+      <c r="AD4" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="BM4" s="9" t="inlineStr">
+      <c r="AE4" s="7" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="BN4" s="9" t="inlineStr">
+      <c r="AF4" s="7" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n"/>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr"/>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="10" t="inlineStr"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n"/>
-      <c r="M5" s="8" t="n"/>
-      <c r="N5" s="8" t="n"/>
-      <c r="O5" s="8" t="n"/>
-      <c r="P5" s="8" t="n"/>
-      <c r="Q5" s="8" t="n"/>
-      <c r="R5" s="8" t="n"/>
-      <c r="S5" s="8" t="n"/>
-      <c r="T5" s="8" t="n"/>
-      <c r="U5" s="8" t="n"/>
-      <c r="V5" s="8" t="n"/>
-      <c r="W5" s="8" t="n"/>
-      <c r="X5" s="8" t="n"/>
-      <c r="Y5" s="8" t="n"/>
-      <c r="Z5" s="8" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="8" t="n"/>
-      <c r="AC5" s="8" t="n"/>
-      <c r="AD5" s="8" t="n"/>
-      <c r="AE5" s="8" t="n"/>
-      <c r="AF5" s="8" t="n"/>
-      <c r="AG5" s="8" t="n"/>
-      <c r="AH5" s="8" t="n"/>
-      <c r="AI5" s="8" t="n"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="11" t="inlineStr"/>
-      <c r="AL5" s="11" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="11" t="inlineStr"/>
-      <c r="AS5" s="11" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="11" t="inlineStr"/>
-      <c r="AZ5" s="11" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr"/>
-      <c r="BC5" s="4" t="inlineStr"/>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr"/>
-      <c r="BF5" s="11" t="inlineStr"/>
-      <c r="BG5" s="11" t="inlineStr"/>
-      <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
-      <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
-      <c r="BM5" s="11" t="inlineStr"/>
-      <c r="BN5" s="11" t="inlineStr"/>
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="9" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="9" t="inlineStr"/>
+      <c r="R5" s="9" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="9" t="inlineStr"/>
+      <c r="Y5" s="9" t="inlineStr"/>
+      <c r="Z5" s="4" t="inlineStr"/>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="inlineStr"/>
+      <c r="AE5" s="9" t="inlineStr"/>
+      <c r="AF5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n"/>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n"/>
-      <c r="O6" s="8" t="n"/>
-      <c r="P6" s="8" t="n"/>
-      <c r="Q6" s="8" t="n"/>
-      <c r="R6" s="8" t="n"/>
-      <c r="S6" s="8" t="n"/>
-      <c r="T6" s="8" t="n"/>
-      <c r="U6" s="8" t="n"/>
-      <c r="V6" s="8" t="n"/>
-      <c r="W6" s="8" t="n"/>
-      <c r="X6" s="8" t="n"/>
-      <c r="Y6" s="8" t="n"/>
-      <c r="Z6" s="8" t="n"/>
-      <c r="AA6" s="8" t="n"/>
-      <c r="AB6" s="8" t="n"/>
-      <c r="AC6" s="8" t="n"/>
-      <c r="AD6" s="8" t="n"/>
-      <c r="AE6" s="8" t="n"/>
-      <c r="AF6" s="8" t="n"/>
-      <c r="AG6" s="8" t="n"/>
-      <c r="AH6" s="8" t="n"/>
-      <c r="AI6" s="8" t="n"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="11" t="inlineStr"/>
-      <c r="AL6" s="11" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="11" t="inlineStr"/>
-      <c r="AS6" s="11" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="11" t="inlineStr"/>
-      <c r="AZ6" s="11" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr"/>
-      <c r="BC6" s="4" t="inlineStr"/>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr"/>
-      <c r="BF6" s="11" t="inlineStr"/>
-      <c r="BG6" s="11" t="inlineStr"/>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
-      <c r="BM6" s="11" t="inlineStr"/>
-      <c r="BN6" s="11" t="inlineStr"/>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="9" t="inlineStr"/>
+      <c r="R6" s="9" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="9" t="inlineStr"/>
+      <c r="Y6" s="9" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="inlineStr"/>
+      <c r="AE6" s="9" t="inlineStr"/>
+      <c r="AF6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n"/>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr"/>
-      <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n"/>
-      <c r="O7" s="8" t="n"/>
-      <c r="P7" s="8" t="n"/>
-      <c r="Q7" s="8" t="n"/>
-      <c r="R7" s="8" t="n"/>
-      <c r="S7" s="8" t="n"/>
-      <c r="T7" s="8" t="n"/>
-      <c r="U7" s="8" t="n"/>
-      <c r="V7" s="8" t="n"/>
-      <c r="W7" s="8" t="n"/>
-      <c r="X7" s="8" t="n"/>
-      <c r="Y7" s="8" t="n"/>
-      <c r="Z7" s="8" t="n"/>
-      <c r="AA7" s="8" t="n"/>
-      <c r="AB7" s="8" t="n"/>
-      <c r="AC7" s="8" t="n"/>
-      <c r="AD7" s="8" t="n"/>
-      <c r="AE7" s="8" t="n"/>
-      <c r="AF7" s="8" t="n"/>
-      <c r="AG7" s="8" t="n"/>
-      <c r="AH7" s="8" t="n"/>
-      <c r="AI7" s="8" t="n"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="11" t="inlineStr"/>
-      <c r="AL7" s="11" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="11" t="inlineStr"/>
-      <c r="AS7" s="11" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr"/>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="11" t="inlineStr"/>
-      <c r="AZ7" s="11" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr"/>
-      <c r="BC7" s="4" t="inlineStr"/>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr"/>
-      <c r="BF7" s="11" t="inlineStr"/>
-      <c r="BG7" s="11" t="inlineStr"/>
-      <c r="BH7" s="4" t="inlineStr"/>
-      <c r="BI7" s="4" t="inlineStr"/>
-      <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr"/>
-      <c r="BL7" s="4" t="inlineStr"/>
-      <c r="BM7" s="11" t="inlineStr"/>
-      <c r="BN7" s="11" t="inlineStr"/>
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="9" t="inlineStr"/>
+      <c r="R7" s="9" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="9" t="inlineStr"/>
+      <c r="Y7" s="9" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="inlineStr"/>
+      <c r="AE7" s="9" t="inlineStr"/>
+      <c r="AF7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr"/>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-      <c r="O8" s="8" t="n"/>
-      <c r="P8" s="8" t="n"/>
-      <c r="Q8" s="8" t="n"/>
-      <c r="R8" s="8" t="n"/>
-      <c r="S8" s="8" t="n"/>
-      <c r="T8" s="8" t="n"/>
-      <c r="U8" s="8" t="n"/>
-      <c r="V8" s="8" t="n"/>
-      <c r="W8" s="8" t="n"/>
-      <c r="X8" s="8" t="n"/>
-      <c r="Y8" s="8" t="n"/>
-      <c r="Z8" s="8" t="n"/>
-      <c r="AA8" s="8" t="n"/>
-      <c r="AB8" s="8" t="n"/>
-      <c r="AC8" s="8" t="n"/>
-      <c r="AD8" s="8" t="n"/>
-      <c r="AE8" s="8" t="n"/>
-      <c r="AF8" s="8" t="n"/>
-      <c r="AG8" s="8" t="n"/>
-      <c r="AH8" s="8" t="n"/>
-      <c r="AI8" s="8" t="n"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="11" t="inlineStr"/>
-      <c r="AL8" s="11" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="11" t="inlineStr"/>
-      <c r="AS8" s="11" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr"/>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="11" t="inlineStr"/>
-      <c r="AZ8" s="11" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr"/>
-      <c r="BC8" s="4" t="inlineStr"/>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr"/>
-      <c r="BF8" s="11" t="inlineStr"/>
-      <c r="BG8" s="11" t="inlineStr"/>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr"/>
-      <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr"/>
-      <c r="BL8" s="4" t="inlineStr"/>
-      <c r="BM8" s="11" t="inlineStr"/>
-      <c r="BN8" s="11" t="inlineStr"/>
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="9" t="inlineStr"/>
+      <c r="R8" s="9" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr"/>
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="9" t="inlineStr"/>
+      <c r="Y8" s="9" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="inlineStr"/>
+      <c r="AE8" s="9" t="inlineStr"/>
+      <c r="AF8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr"/>
-      <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
-      <c r="M9" s="8" t="n"/>
-      <c r="N9" s="8" t="n"/>
-      <c r="O9" s="8" t="n"/>
-      <c r="P9" s="8" t="n"/>
-      <c r="Q9" s="8" t="n"/>
-      <c r="R9" s="8" t="n"/>
-      <c r="S9" s="8" t="n"/>
-      <c r="T9" s="8" t="n"/>
-      <c r="U9" s="8" t="n"/>
-      <c r="V9" s="8" t="n"/>
-      <c r="W9" s="8" t="n"/>
-      <c r="X9" s="8" t="n"/>
-      <c r="Y9" s="8" t="n"/>
-      <c r="Z9" s="8" t="n"/>
-      <c r="AA9" s="8" t="n"/>
-      <c r="AB9" s="8" t="n"/>
-      <c r="AC9" s="8" t="n"/>
-      <c r="AD9" s="8" t="n"/>
-      <c r="AE9" s="8" t="n"/>
-      <c r="AF9" s="8" t="n"/>
-      <c r="AG9" s="8" t="n"/>
-      <c r="AH9" s="8" t="n"/>
-      <c r="AI9" s="8" t="n"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="11" t="inlineStr"/>
-      <c r="AL9" s="11" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="11" t="inlineStr"/>
-      <c r="AS9" s="11" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr"/>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="11" t="inlineStr"/>
-      <c r="AZ9" s="11" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr"/>
-      <c r="BC9" s="4" t="inlineStr"/>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr"/>
-      <c r="BF9" s="11" t="inlineStr"/>
-      <c r="BG9" s="11" t="inlineStr"/>
-      <c r="BH9" s="4" t="inlineStr"/>
-      <c r="BI9" s="4" t="inlineStr"/>
-      <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr"/>
-      <c r="BL9" s="4" t="inlineStr"/>
-      <c r="BM9" s="11" t="inlineStr"/>
-      <c r="BN9" s="11" t="inlineStr"/>
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="9" t="inlineStr"/>
+      <c r="R9" s="9" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="9" t="inlineStr"/>
+      <c r="Y9" s="9" t="inlineStr"/>
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="inlineStr"/>
+      <c r="AE9" s="9" t="inlineStr"/>
+      <c r="AF9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr"/>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
-      <c r="O10" s="8" t="n"/>
-      <c r="P10" s="8" t="n"/>
-      <c r="Q10" s="8" t="n"/>
-      <c r="R10" s="8" t="n"/>
-      <c r="S10" s="8" t="n"/>
-      <c r="T10" s="8" t="n"/>
-      <c r="U10" s="8" t="n"/>
-      <c r="V10" s="8" t="n"/>
-      <c r="W10" s="8" t="n"/>
-      <c r="X10" s="8" t="n"/>
-      <c r="Y10" s="8" t="n"/>
-      <c r="Z10" s="8" t="n"/>
-      <c r="AA10" s="8" t="n"/>
-      <c r="AB10" s="8" t="n"/>
-      <c r="AC10" s="8" t="n"/>
-      <c r="AD10" s="8" t="n"/>
-      <c r="AE10" s="8" t="n"/>
-      <c r="AF10" s="8" t="n"/>
-      <c r="AG10" s="8" t="n"/>
-      <c r="AH10" s="8" t="n"/>
-      <c r="AI10" s="8" t="n"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="11" t="inlineStr"/>
-      <c r="AL10" s="11" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="11" t="inlineStr"/>
-      <c r="AS10" s="11" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr"/>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="11" t="inlineStr"/>
-      <c r="AZ10" s="11" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr"/>
-      <c r="BC10" s="4" t="inlineStr"/>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr"/>
-      <c r="BF10" s="11" t="inlineStr"/>
-      <c r="BG10" s="11" t="inlineStr"/>
-      <c r="BH10" s="4" t="inlineStr"/>
-      <c r="BI10" s="4" t="inlineStr"/>
-      <c r="BJ10" s="4" t="inlineStr"/>
-      <c r="BK10" s="4" t="inlineStr"/>
-      <c r="BL10" s="4" t="inlineStr"/>
-      <c r="BM10" s="11" t="inlineStr"/>
-      <c r="BN10" s="11" t="inlineStr"/>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="9" t="inlineStr"/>
+      <c r="R10" s="9" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr"/>
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="9" t="inlineStr"/>
+      <c r="Y10" s="9" t="inlineStr"/>
+      <c r="Z10" s="4" t="inlineStr"/>
+      <c r="AA10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AD10" s="4" t="inlineStr"/>
+      <c r="AE10" s="9" t="inlineStr"/>
+      <c r="AF10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr"/>
-      <c r="D11" s="10" t="inlineStr"/>
-      <c r="E11" s="10" t="inlineStr"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="8" t="n"/>
-      <c r="N11" s="8" t="n"/>
-      <c r="O11" s="8" t="n"/>
-      <c r="P11" s="8" t="n"/>
-      <c r="Q11" s="8" t="n"/>
-      <c r="R11" s="8" t="n"/>
-      <c r="S11" s="8" t="n"/>
-      <c r="T11" s="8" t="n"/>
-      <c r="U11" s="8" t="n"/>
-      <c r="V11" s="8" t="n"/>
-      <c r="W11" s="8" t="n"/>
-      <c r="X11" s="8" t="n"/>
-      <c r="Y11" s="8" t="n"/>
-      <c r="Z11" s="8" t="n"/>
-      <c r="AA11" s="8" t="n"/>
-      <c r="AB11" s="8" t="n"/>
-      <c r="AC11" s="8" t="n"/>
-      <c r="AD11" s="8" t="n"/>
-      <c r="AE11" s="8" t="n"/>
-      <c r="AF11" s="8" t="n"/>
-      <c r="AG11" s="8" t="n"/>
-      <c r="AH11" s="8" t="n"/>
-      <c r="AI11" s="8" t="n"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="11" t="inlineStr"/>
-      <c r="AL11" s="11" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="11" t="inlineStr"/>
-      <c r="AS11" s="11" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr"/>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="11" t="inlineStr"/>
-      <c r="AZ11" s="11" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr"/>
-      <c r="BC11" s="4" t="inlineStr"/>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr"/>
-      <c r="BF11" s="11" t="inlineStr"/>
-      <c r="BG11" s="11" t="inlineStr"/>
-      <c r="BH11" s="4" t="inlineStr"/>
-      <c r="BI11" s="4" t="inlineStr"/>
-      <c r="BJ11" s="4" t="inlineStr"/>
-      <c r="BK11" s="4" t="inlineStr"/>
-      <c r="BL11" s="4" t="inlineStr"/>
-      <c r="BM11" s="11" t="inlineStr"/>
-      <c r="BN11" s="11" t="inlineStr"/>
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr"/>
+      <c r="K11" s="9" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="9" t="inlineStr"/>
+      <c r="R11" s="9" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="9" t="inlineStr"/>
+      <c r="Y11" s="9" t="inlineStr"/>
+      <c r="Z11" s="4" t="inlineStr"/>
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AD11" s="4" t="inlineStr"/>
+      <c r="AE11" s="9" t="inlineStr"/>
+      <c r="AF11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr"/>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
-      <c r="O12" s="8" t="n"/>
-      <c r="P12" s="8" t="n"/>
-      <c r="Q12" s="8" t="n"/>
-      <c r="R12" s="8" t="n"/>
-      <c r="S12" s="8" t="n"/>
-      <c r="T12" s="8" t="n"/>
-      <c r="U12" s="8" t="n"/>
-      <c r="V12" s="8" t="n"/>
-      <c r="W12" s="8" t="n"/>
-      <c r="X12" s="8" t="n"/>
-      <c r="Y12" s="8" t="n"/>
-      <c r="Z12" s="8" t="n"/>
-      <c r="AA12" s="8" t="n"/>
-      <c r="AB12" s="8" t="n"/>
-      <c r="AC12" s="8" t="n"/>
-      <c r="AD12" s="8" t="n"/>
-      <c r="AE12" s="8" t="n"/>
-      <c r="AF12" s="8" t="n"/>
-      <c r="AG12" s="8" t="n"/>
-      <c r="AH12" s="8" t="n"/>
-      <c r="AI12" s="8" t="n"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="11" t="inlineStr"/>
-      <c r="AL12" s="11" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="11" t="inlineStr"/>
-      <c r="AS12" s="11" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr"/>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="11" t="inlineStr"/>
-      <c r="AZ12" s="11" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr"/>
-      <c r="BC12" s="4" t="inlineStr"/>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr"/>
-      <c r="BF12" s="11" t="inlineStr"/>
-      <c r="BG12" s="11" t="inlineStr"/>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr"/>
-      <c r="BL12" s="4" t="inlineStr"/>
-      <c r="BM12" s="11" t="inlineStr"/>
-      <c r="BN12" s="11" t="inlineStr"/>
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="9" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="9" t="inlineStr"/>
+      <c r="R12" s="9" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr"/>
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="9" t="inlineStr"/>
+      <c r="Y12" s="9" t="inlineStr"/>
+      <c r="Z12" s="4" t="inlineStr"/>
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="inlineStr"/>
+      <c r="AE12" s="9" t="inlineStr"/>
+      <c r="AF12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n"/>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr"/>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="10" t="inlineStr"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
-      <c r="M13" s="8" t="n"/>
-      <c r="N13" s="8" t="n"/>
-      <c r="O13" s="8" t="n"/>
-      <c r="P13" s="8" t="n"/>
-      <c r="Q13" s="8" t="n"/>
-      <c r="R13" s="8" t="n"/>
-      <c r="S13" s="8" t="n"/>
-      <c r="T13" s="8" t="n"/>
-      <c r="U13" s="8" t="n"/>
-      <c r="V13" s="8" t="n"/>
-      <c r="W13" s="8" t="n"/>
-      <c r="X13" s="8" t="n"/>
-      <c r="Y13" s="8" t="n"/>
-      <c r="Z13" s="8" t="n"/>
-      <c r="AA13" s="8" t="n"/>
-      <c r="AB13" s="8" t="n"/>
-      <c r="AC13" s="8" t="n"/>
-      <c r="AD13" s="8" t="n"/>
-      <c r="AE13" s="8" t="n"/>
-      <c r="AF13" s="8" t="n"/>
-      <c r="AG13" s="8" t="n"/>
-      <c r="AH13" s="8" t="n"/>
-      <c r="AI13" s="8" t="n"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="11" t="inlineStr"/>
-      <c r="AL13" s="11" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="11" t="inlineStr"/>
-      <c r="AS13" s="11" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="11" t="inlineStr"/>
-      <c r="AZ13" s="11" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr"/>
-      <c r="BC13" s="4" t="inlineStr"/>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr"/>
-      <c r="BF13" s="11" t="inlineStr"/>
-      <c r="BG13" s="11" t="inlineStr"/>
-      <c r="BH13" s="4" t="inlineStr"/>
-      <c r="BI13" s="4" t="inlineStr"/>
-      <c r="BJ13" s="4" t="inlineStr"/>
-      <c r="BK13" s="4" t="inlineStr"/>
-      <c r="BL13" s="4" t="inlineStr"/>
-      <c r="BM13" s="11" t="inlineStr"/>
-      <c r="BN13" s="11" t="inlineStr"/>
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="9" t="inlineStr"/>
+      <c r="K13" s="9" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="9" t="inlineStr"/>
+      <c r="R13" s="9" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr"/>
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" s="4" t="inlineStr"/>
+      <c r="X13" s="9" t="inlineStr"/>
+      <c r="Y13" s="9" t="inlineStr"/>
+      <c r="Z13" s="4" t="inlineStr"/>
+      <c r="AA13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="inlineStr"/>
+      <c r="AE13" s="9" t="inlineStr"/>
+      <c r="AF13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
-      <c r="P14" s="8" t="n"/>
-      <c r="Q14" s="8" t="n"/>
-      <c r="R14" s="8" t="n"/>
-      <c r="S14" s="8" t="n"/>
-      <c r="T14" s="8" t="n"/>
-      <c r="U14" s="8" t="n"/>
-      <c r="V14" s="8" t="n"/>
-      <c r="W14" s="8" t="n"/>
-      <c r="X14" s="8" t="n"/>
-      <c r="Y14" s="8" t="n"/>
-      <c r="Z14" s="8" t="n"/>
-      <c r="AA14" s="8" t="n"/>
-      <c r="AB14" s="8" t="n"/>
-      <c r="AC14" s="8" t="n"/>
-      <c r="AD14" s="8" t="n"/>
-      <c r="AE14" s="8" t="n"/>
-      <c r="AF14" s="8" t="n"/>
-      <c r="AG14" s="8" t="n"/>
-      <c r="AH14" s="8" t="n"/>
-      <c r="AI14" s="8" t="n"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="11" t="inlineStr"/>
-      <c r="AL14" s="11" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="11" t="inlineStr"/>
-      <c r="AS14" s="11" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr"/>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="11" t="inlineStr"/>
-      <c r="AZ14" s="11" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr"/>
-      <c r="BC14" s="4" t="inlineStr"/>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr"/>
-      <c r="BF14" s="11" t="inlineStr"/>
-      <c r="BG14" s="11" t="inlineStr"/>
-      <c r="BH14" s="4" t="inlineStr"/>
-      <c r="BI14" s="4" t="inlineStr"/>
-      <c r="BJ14" s="4" t="inlineStr"/>
-      <c r="BK14" s="4" t="inlineStr"/>
-      <c r="BL14" s="4" t="inlineStr"/>
-      <c r="BM14" s="11" t="inlineStr"/>
-      <c r="BN14" s="11" t="inlineStr"/>
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="9" t="inlineStr"/>
+      <c r="R14" s="9" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr"/>
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="9" t="inlineStr"/>
+      <c r="Y14" s="9" t="inlineStr"/>
+      <c r="Z14" s="4" t="inlineStr"/>
+      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="inlineStr"/>
+      <c r="AE14" s="9" t="inlineStr"/>
+      <c r="AF14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
-      <c r="N15" s="8" t="n"/>
-      <c r="O15" s="8" t="n"/>
-      <c r="P15" s="8" t="n"/>
-      <c r="Q15" s="8" t="n"/>
-      <c r="R15" s="8" t="n"/>
-      <c r="S15" s="8" t="n"/>
-      <c r="T15" s="8" t="n"/>
-      <c r="U15" s="8" t="n"/>
-      <c r="V15" s="8" t="n"/>
-      <c r="W15" s="8" t="n"/>
-      <c r="X15" s="8" t="n"/>
-      <c r="Y15" s="8" t="n"/>
-      <c r="Z15" s="8" t="n"/>
-      <c r="AA15" s="8" t="n"/>
-      <c r="AB15" s="8" t="n"/>
-      <c r="AC15" s="8" t="n"/>
-      <c r="AD15" s="8" t="n"/>
-      <c r="AE15" s="8" t="n"/>
-      <c r="AF15" s="8" t="n"/>
-      <c r="AG15" s="8" t="n"/>
-      <c r="AH15" s="8" t="n"/>
-      <c r="AI15" s="8" t="n"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="11" t="inlineStr"/>
-      <c r="AL15" s="11" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr"/>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="11" t="inlineStr"/>
-      <c r="AS15" s="11" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr"/>
-      <c r="AX15" s="4" t="inlineStr"/>
-      <c r="AY15" s="11" t="inlineStr"/>
-      <c r="AZ15" s="11" t="inlineStr"/>
-      <c r="BA15" s="4" t="inlineStr"/>
-      <c r="BB15" s="4" t="inlineStr"/>
-      <c r="BC15" s="4" t="inlineStr"/>
-      <c r="BD15" s="4" t="inlineStr"/>
-      <c r="BE15" s="4" t="inlineStr"/>
-      <c r="BF15" s="11" t="inlineStr"/>
-      <c r="BG15" s="11" t="inlineStr"/>
-      <c r="BH15" s="4" t="inlineStr"/>
-      <c r="BI15" s="4" t="inlineStr"/>
-      <c r="BJ15" s="4" t="inlineStr"/>
-      <c r="BK15" s="4" t="inlineStr"/>
-      <c r="BL15" s="4" t="inlineStr"/>
-      <c r="BM15" s="11" t="inlineStr"/>
-      <c r="BN15" s="11" t="inlineStr"/>
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="9" t="inlineStr"/>
+      <c r="R15" s="9" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr"/>
+      <c r="U15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="inlineStr"/>
+      <c r="W15" s="4" t="inlineStr"/>
+      <c r="X15" s="9" t="inlineStr"/>
+      <c r="Y15" s="9" t="inlineStr"/>
+      <c r="Z15" s="4" t="inlineStr"/>
+      <c r="AA15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AD15" s="4" t="inlineStr"/>
+      <c r="AE15" s="9" t="inlineStr"/>
+      <c r="AF15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr"/>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
-      <c r="P16" s="8" t="n"/>
-      <c r="Q16" s="8" t="n"/>
-      <c r="R16" s="8" t="n"/>
-      <c r="S16" s="8" t="n"/>
-      <c r="T16" s="8" t="n"/>
-      <c r="U16" s="8" t="n"/>
-      <c r="V16" s="8" t="n"/>
-      <c r="W16" s="8" t="n"/>
-      <c r="X16" s="8" t="n"/>
-      <c r="Y16" s="8" t="n"/>
-      <c r="Z16" s="8" t="n"/>
-      <c r="AA16" s="8" t="n"/>
-      <c r="AB16" s="8" t="n"/>
-      <c r="AC16" s="8" t="n"/>
-      <c r="AD16" s="8" t="n"/>
-      <c r="AE16" s="8" t="n"/>
-      <c r="AF16" s="8" t="n"/>
-      <c r="AG16" s="8" t="n"/>
-      <c r="AH16" s="8" t="n"/>
-      <c r="AI16" s="8" t="n"/>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="11" t="inlineStr"/>
-      <c r="AL16" s="11" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr"/>
-      <c r="AQ16" s="4" t="inlineStr"/>
-      <c r="AR16" s="11" t="inlineStr"/>
-      <c r="AS16" s="11" t="inlineStr"/>
-      <c r="AT16" s="4" t="inlineStr"/>
-      <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr"/>
-      <c r="AW16" s="4" t="inlineStr"/>
-      <c r="AX16" s="4" t="inlineStr"/>
-      <c r="AY16" s="11" t="inlineStr"/>
-      <c r="AZ16" s="11" t="inlineStr"/>
-      <c r="BA16" s="4" t="inlineStr"/>
-      <c r="BB16" s="4" t="inlineStr"/>
-      <c r="BC16" s="4" t="inlineStr"/>
-      <c r="BD16" s="4" t="inlineStr"/>
-      <c r="BE16" s="4" t="inlineStr"/>
-      <c r="BF16" s="11" t="inlineStr"/>
-      <c r="BG16" s="11" t="inlineStr"/>
-      <c r="BH16" s="4" t="inlineStr"/>
-      <c r="BI16" s="4" t="inlineStr"/>
-      <c r="BJ16" s="4" t="inlineStr"/>
-      <c r="BK16" s="4" t="inlineStr"/>
-      <c r="BL16" s="4" t="inlineStr"/>
-      <c r="BM16" s="11" t="inlineStr"/>
-      <c r="BN16" s="11" t="inlineStr"/>
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="9" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr"/>
+      <c r="Q16" s="9" t="inlineStr"/>
+      <c r="R16" s="9" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr"/>
+      <c r="T16" s="4" t="inlineStr"/>
+      <c r="U16" s="4" t="inlineStr"/>
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="4" t="inlineStr"/>
+      <c r="X16" s="9" t="inlineStr"/>
+      <c r="Y16" s="9" t="inlineStr"/>
+      <c r="Z16" s="4" t="inlineStr"/>
+      <c r="AA16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AD16" s="4" t="inlineStr"/>
+      <c r="AE16" s="9" t="inlineStr"/>
+      <c r="AF16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr"/>
-      <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="10" t="inlineStr"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
-      <c r="P17" s="8" t="n"/>
-      <c r="Q17" s="8" t="n"/>
-      <c r="R17" s="8" t="n"/>
-      <c r="S17" s="8" t="n"/>
-      <c r="T17" s="8" t="n"/>
-      <c r="U17" s="8" t="n"/>
-      <c r="V17" s="8" t="n"/>
-      <c r="W17" s="8" t="n"/>
-      <c r="X17" s="8" t="n"/>
-      <c r="Y17" s="8" t="n"/>
-      <c r="Z17" s="8" t="n"/>
-      <c r="AA17" s="8" t="n"/>
-      <c r="AB17" s="8" t="n"/>
-      <c r="AC17" s="8" t="n"/>
-      <c r="AD17" s="8" t="n"/>
-      <c r="AE17" s="8" t="n"/>
-      <c r="AF17" s="8" t="n"/>
-      <c r="AG17" s="8" t="n"/>
-      <c r="AH17" s="8" t="n"/>
-      <c r="AI17" s="8" t="n"/>
-      <c r="AJ17" s="4" t="inlineStr"/>
-      <c r="AK17" s="11" t="inlineStr"/>
-      <c r="AL17" s="11" t="inlineStr"/>
-      <c r="AM17" s="4" t="inlineStr"/>
-      <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
-      <c r="AP17" s="4" t="inlineStr"/>
-      <c r="AQ17" s="4" t="inlineStr"/>
-      <c r="AR17" s="11" t="inlineStr"/>
-      <c r="AS17" s="11" t="inlineStr"/>
-      <c r="AT17" s="4" t="inlineStr"/>
-      <c r="AU17" s="4" t="inlineStr"/>
-      <c r="AV17" s="4" t="inlineStr"/>
-      <c r="AW17" s="4" t="inlineStr"/>
-      <c r="AX17" s="4" t="inlineStr"/>
-      <c r="AY17" s="11" t="inlineStr"/>
-      <c r="AZ17" s="11" t="inlineStr"/>
-      <c r="BA17" s="4" t="inlineStr"/>
-      <c r="BB17" s="4" t="inlineStr"/>
-      <c r="BC17" s="4" t="inlineStr"/>
-      <c r="BD17" s="4" t="inlineStr"/>
-      <c r="BE17" s="4" t="inlineStr"/>
-      <c r="BF17" s="11" t="inlineStr"/>
-      <c r="BG17" s="11" t="inlineStr"/>
-      <c r="BH17" s="4" t="inlineStr"/>
-      <c r="BI17" s="4" t="inlineStr"/>
-      <c r="BJ17" s="4" t="inlineStr"/>
-      <c r="BK17" s="4" t="inlineStr"/>
-      <c r="BL17" s="4" t="inlineStr"/>
-      <c r="BM17" s="11" t="inlineStr"/>
-      <c r="BN17" s="11" t="inlineStr"/>
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="9" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="9" t="inlineStr"/>
+      <c r="R17" s="9" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr"/>
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="inlineStr"/>
+      <c r="X17" s="9" t="inlineStr"/>
+      <c r="Y17" s="9" t="inlineStr"/>
+      <c r="Z17" s="4" t="inlineStr"/>
+      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="inlineStr"/>
+      <c r="AE17" s="9" t="inlineStr"/>
+      <c r="AF17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr"/>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
-      <c r="O18" s="8" t="n"/>
-      <c r="P18" s="8" t="n"/>
-      <c r="Q18" s="8" t="n"/>
-      <c r="R18" s="8" t="n"/>
-      <c r="S18" s="8" t="n"/>
-      <c r="T18" s="8" t="n"/>
-      <c r="U18" s="8" t="n"/>
-      <c r="V18" s="8" t="n"/>
-      <c r="W18" s="8" t="n"/>
-      <c r="X18" s="8" t="n"/>
-      <c r="Y18" s="8" t="n"/>
-      <c r="Z18" s="8" t="n"/>
-      <c r="AA18" s="8" t="n"/>
-      <c r="AB18" s="8" t="n"/>
-      <c r="AC18" s="8" t="n"/>
-      <c r="AD18" s="8" t="n"/>
-      <c r="AE18" s="8" t="n"/>
-      <c r="AF18" s="8" t="n"/>
-      <c r="AG18" s="8" t="n"/>
-      <c r="AH18" s="8" t="n"/>
-      <c r="AI18" s="8" t="n"/>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="11" t="inlineStr"/>
-      <c r="AL18" s="11" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr"/>
-      <c r="AQ18" s="4" t="inlineStr"/>
-      <c r="AR18" s="11" t="inlineStr"/>
-      <c r="AS18" s="11" t="inlineStr"/>
-      <c r="AT18" s="4" t="inlineStr"/>
-      <c r="AU18" s="4" t="inlineStr"/>
-      <c r="AV18" s="4" t="inlineStr"/>
-      <c r="AW18" s="4" t="inlineStr"/>
-      <c r="AX18" s="4" t="inlineStr"/>
-      <c r="AY18" s="11" t="inlineStr"/>
-      <c r="AZ18" s="11" t="inlineStr"/>
-      <c r="BA18" s="4" t="inlineStr"/>
-      <c r="BB18" s="4" t="inlineStr"/>
-      <c r="BC18" s="4" t="inlineStr"/>
-      <c r="BD18" s="4" t="inlineStr"/>
-      <c r="BE18" s="4" t="inlineStr"/>
-      <c r="BF18" s="11" t="inlineStr"/>
-      <c r="BG18" s="11" t="inlineStr"/>
-      <c r="BH18" s="4" t="inlineStr"/>
-      <c r="BI18" s="4" t="inlineStr"/>
-      <c r="BJ18" s="4" t="inlineStr"/>
-      <c r="BK18" s="4" t="inlineStr"/>
-      <c r="BL18" s="4" t="inlineStr"/>
-      <c r="BM18" s="11" t="inlineStr"/>
-      <c r="BN18" s="11" t="inlineStr"/>
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="9" t="inlineStr"/>
+      <c r="R18" s="9" t="inlineStr"/>
+      <c r="S18" s="4" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr"/>
+      <c r="U18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="4" t="inlineStr"/>
+      <c r="X18" s="9" t="inlineStr"/>
+      <c r="Y18" s="9" t="inlineStr"/>
+      <c r="Z18" s="4" t="inlineStr"/>
+      <c r="AA18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AD18" s="4" t="inlineStr"/>
+      <c r="AE18" s="9" t="inlineStr"/>
+      <c r="AF18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>默认考勤组</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr"/>
-      <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="10" t="inlineStr"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
-      <c r="O19" s="8" t="n"/>
-      <c r="P19" s="8" t="n"/>
-      <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="8" t="n"/>
-      <c r="S19" s="8" t="n"/>
-      <c r="T19" s="8" t="n"/>
-      <c r="U19" s="8" t="n"/>
-      <c r="V19" s="8" t="n"/>
-      <c r="W19" s="8" t="n"/>
-      <c r="X19" s="8" t="n"/>
-      <c r="Y19" s="8" t="n"/>
-      <c r="Z19" s="8" t="n"/>
-      <c r="AA19" s="8" t="n"/>
-      <c r="AB19" s="8" t="n"/>
-      <c r="AC19" s="8" t="n"/>
-      <c r="AD19" s="8" t="n"/>
-      <c r="AE19" s="8" t="n"/>
-      <c r="AF19" s="8" t="n"/>
-      <c r="AG19" s="8" t="n"/>
-      <c r="AH19" s="8" t="n"/>
-      <c r="AI19" s="8" t="n"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="11" t="inlineStr"/>
-      <c r="AL19" s="11" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="11" t="inlineStr"/>
-      <c r="AS19" s="11" t="inlineStr"/>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr"/>
-      <c r="AV19" s="4" t="inlineStr"/>
-      <c r="AW19" s="4" t="inlineStr"/>
-      <c r="AX19" s="4" t="inlineStr"/>
-      <c r="AY19" s="11" t="inlineStr"/>
-      <c r="AZ19" s="11" t="inlineStr"/>
-      <c r="BA19" s="4" t="inlineStr"/>
-      <c r="BB19" s="4" t="inlineStr"/>
-      <c r="BC19" s="4" t="inlineStr"/>
-      <c r="BD19" s="4" t="inlineStr"/>
-      <c r="BE19" s="4" t="inlineStr"/>
-      <c r="BF19" s="11" t="inlineStr"/>
-      <c r="BG19" s="11" t="inlineStr"/>
-      <c r="BH19" s="4" t="inlineStr"/>
-      <c r="BI19" s="4" t="inlineStr"/>
-      <c r="BJ19" s="4" t="inlineStr"/>
-      <c r="BK19" s="4" t="inlineStr"/>
-      <c r="BL19" s="4" t="inlineStr"/>
-      <c r="BM19" s="11" t="inlineStr"/>
-      <c r="BN19" s="11" t="inlineStr"/>
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="9" t="inlineStr"/>
+      <c r="R19" s="9" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr"/>
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="inlineStr"/>
+      <c r="X19" s="9" t="inlineStr"/>
+      <c r="Y19" s="9" t="inlineStr"/>
+      <c r="Z19" s="4" t="inlineStr"/>
+      <c r="AA19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="inlineStr"/>
+      <c r="AE19" s="9" t="inlineStr"/>
+      <c r="AF19" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="AJ3:BN3"/>
-    <mergeCell ref="A3:E3"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2"/>
+    <mergeCell ref="B3:AF3"/>
+    <mergeCell ref="A1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5021,151 +4725,247 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>加班兑换方式</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE2" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH2" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="AI2" s="3" t="n"/>
+      <c r="AJ2" s="11" t="inlineStr">
+        <is>
+          <t>5月加班时长合计</t>
+        </is>
+      </c>
+      <c r="AK2" s="3" t="n"/>
+      <c r="AL2" s="3" t="n"/>
+      <c r="AM2" s="11" t="inlineStr">
+        <is>
+          <t>5月加班倍数合计</t>
+        </is>
+      </c>
+      <c r="AN2" s="3" t="n"/>
+      <c r="AO2" s="3" t="n"/>
+      <c r="AP2" s="11" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" s="3" t="n"/>
+      <c r="X3" s="3" t="n"/>
+      <c r="Y3" s="3" t="n"/>
+      <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
+      <c r="AB3" s="3" t="n"/>
+      <c r="AC3" s="3" t="n"/>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="3" t="n"/>
+      <c r="AF3" s="3" t="n"/>
+      <c r="AG3" s="3" t="n"/>
+      <c r="AH3" s="3" t="n"/>
+      <c r="AI3" s="3" t="n"/>
+      <c r="AJ3" s="3" t="n"/>
+      <c r="AK3" s="3" t="n"/>
+      <c r="AL3" s="3" t="n"/>
+      <c r="AM3" s="3" t="n"/>
+      <c r="AN3" s="3" t="n"/>
+      <c r="AO3" s="3" t="n"/>
+      <c r="AP3" s="3" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>加班兑换方式</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="W4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="X4" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC4" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD4" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE4" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH4" s="2" t="n">
-        <v>31</v>
-      </c>
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
+      <c r="AE4" s="3" t="n"/>
+      <c r="AF4" s="3" t="n"/>
+      <c r="AG4" s="3" t="n"/>
+      <c r="AH4" s="3" t="n"/>
       <c r="AI4" s="3" t="n"/>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>1.5倍工时</t>
+          <t>1.5倍</t>
         </is>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>2倍工时</t>
+          <t>2倍</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>3倍工时</t>
+          <t>3倍</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>1.5倍合计</t>
+          <t>1.5倍</t>
         </is>
       </c>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2倍合计</t>
+          <t>2倍</t>
         </is>
       </c>
       <c r="AO4" s="2" t="inlineStr">
         <is>
-          <t>3倍合计</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr">
-        <is>
-          <t>加班工资合计</t>
-        </is>
-      </c>
+          <t>3倍</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -5269,31 +5069,31 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n"/>
-      <c r="AJ5" s="3">
+      <c r="AJ5" s="12">
         <f>SUM(J5:M5,O5:S5,V5:Z5,AC5:AG5)</f>
         <v/>
       </c>
-      <c r="AK5" s="3">
+      <c r="AK5" s="12">
         <f>SUM(G5:I5,N5,T5:U5,AA5:AB5,AH5:AI5)</f>
         <v/>
       </c>
-      <c r="AL5" s="3">
+      <c r="AL5" s="12">
         <f>SUM(E5:F5)</f>
         <v/>
       </c>
-      <c r="AM5" s="3">
+      <c r="AM5" s="12">
         <f>AJ5*1.5</f>
         <v/>
       </c>
-      <c r="AN5" s="3">
+      <c r="AN5" s="12">
         <f>AK5*2</f>
         <v/>
       </c>
-      <c r="AO5" s="3">
+      <c r="AO5" s="12">
         <f>AL5*3</f>
         <v/>
       </c>
-      <c r="AP5" s="3">
+      <c r="AP5" s="12">
         <f>SUM(AM5:AO5)</f>
         <v/>
       </c>
@@ -5400,31 +5200,31 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n"/>
-      <c r="AJ6" s="3">
+      <c r="AJ6" s="12">
         <f>SUM(J6:M6,O6:S6,V6:Z6,AC6:AG6)</f>
         <v/>
       </c>
-      <c r="AK6" s="3">
+      <c r="AK6" s="12">
         <f>SUM(G6:I6,N6,T6:U6,AA6:AB6,AH6:AI6)</f>
         <v/>
       </c>
-      <c r="AL6" s="3">
+      <c r="AL6" s="12">
         <f>SUM(E6:F6)</f>
         <v/>
       </c>
-      <c r="AM6" s="3">
+      <c r="AM6" s="12">
         <f>AJ6*1.5</f>
         <v/>
       </c>
-      <c r="AN6" s="3">
+      <c r="AN6" s="12">
         <f>AK6*2</f>
         <v/>
       </c>
-      <c r="AO6" s="3">
+      <c r="AO6" s="12">
         <f>AL6*3</f>
         <v/>
       </c>
-      <c r="AP6" s="3">
+      <c r="AP6" s="12">
         <f>SUM(AM6:AO6)</f>
         <v/>
       </c>
@@ -5531,31 +5331,31 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n"/>
-      <c r="AJ7" s="3">
+      <c r="AJ7" s="12">
         <f>SUM(J7:M7,O7:S7,V7:Z7,AC7:AG7)</f>
         <v/>
       </c>
-      <c r="AK7" s="3">
+      <c r="AK7" s="12">
         <f>SUM(G7:I7,N7,T7:U7,AA7:AB7,AH7:AI7)</f>
         <v/>
       </c>
-      <c r="AL7" s="3">
+      <c r="AL7" s="12">
         <f>SUM(E7:F7)</f>
         <v/>
       </c>
-      <c r="AM7" s="3">
+      <c r="AM7" s="12">
         <f>AJ7*1.5</f>
         <v/>
       </c>
-      <c r="AN7" s="3">
+      <c r="AN7" s="12">
         <f>AK7*2</f>
         <v/>
       </c>
-      <c r="AO7" s="3">
+      <c r="AO7" s="12">
         <f>AL7*3</f>
         <v/>
       </c>
-      <c r="AP7" s="3">
+      <c r="AP7" s="12">
         <f>SUM(AM7:AO7)</f>
         <v/>
       </c>
@@ -5662,31 +5462,31 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n"/>
-      <c r="AJ8" s="3">
+      <c r="AJ8" s="12">
         <f>SUM(J8:M8,O8:S8,V8:Z8,AC8:AG8)</f>
         <v/>
       </c>
-      <c r="AK8" s="3">
+      <c r="AK8" s="12">
         <f>SUM(G8:I8,N8,T8:U8,AA8:AB8,AH8:AI8)</f>
         <v/>
       </c>
-      <c r="AL8" s="3">
+      <c r="AL8" s="12">
         <f>SUM(E8:F8)</f>
         <v/>
       </c>
-      <c r="AM8" s="3">
+      <c r="AM8" s="12">
         <f>AJ8*1.5</f>
         <v/>
       </c>
-      <c r="AN8" s="3">
+      <c r="AN8" s="12">
         <f>AK8*2</f>
         <v/>
       </c>
-      <c r="AO8" s="3">
+      <c r="AO8" s="12">
         <f>AL8*3</f>
         <v/>
       </c>
-      <c r="AP8" s="3">
+      <c r="AP8" s="12">
         <f>SUM(AM8:AO8)</f>
         <v/>
       </c>
@@ -5793,31 +5593,31 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n"/>
-      <c r="AJ9" s="3">
+      <c r="AJ9" s="12">
         <f>SUM(J9:M9,O9:S9,V9:Z9,AC9:AG9)</f>
         <v/>
       </c>
-      <c r="AK9" s="3">
+      <c r="AK9" s="12">
         <f>SUM(G9:I9,N9,T9:U9,AA9:AB9,AH9:AI9)</f>
         <v/>
       </c>
-      <c r="AL9" s="3">
+      <c r="AL9" s="12">
         <f>SUM(E9:F9)</f>
         <v/>
       </c>
-      <c r="AM9" s="3">
+      <c r="AM9" s="12">
         <f>AJ9*1.5</f>
         <v/>
       </c>
-      <c r="AN9" s="3">
+      <c r="AN9" s="12">
         <f>AK9*2</f>
         <v/>
       </c>
-      <c r="AO9" s="3">
+      <c r="AO9" s="12">
         <f>AL9*3</f>
         <v/>
       </c>
-      <c r="AP9" s="3">
+      <c r="AP9" s="12">
         <f>SUM(AM9:AO9)</f>
         <v/>
       </c>
@@ -5924,31 +5724,31 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n"/>
-      <c r="AJ10" s="3">
+      <c r="AJ10" s="12">
         <f>SUM(J10:M10,O10:S10,V10:Z10,AC10:AG10)</f>
         <v/>
       </c>
-      <c r="AK10" s="3">
+      <c r="AK10" s="12">
         <f>SUM(G10:I10,N10,T10:U10,AA10:AB10,AH10:AI10)</f>
         <v/>
       </c>
-      <c r="AL10" s="3">
+      <c r="AL10" s="12">
         <f>SUM(E10:F10)</f>
         <v/>
       </c>
-      <c r="AM10" s="3">
+      <c r="AM10" s="12">
         <f>AJ10*1.5</f>
         <v/>
       </c>
-      <c r="AN10" s="3">
+      <c r="AN10" s="12">
         <f>AK10*2</f>
         <v/>
       </c>
-      <c r="AO10" s="3">
+      <c r="AO10" s="12">
         <f>AL10*3</f>
         <v/>
       </c>
-      <c r="AP10" s="3">
+      <c r="AP10" s="12">
         <f>SUM(AM10:AO10)</f>
         <v/>
       </c>
@@ -6055,31 +5855,31 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n"/>
-      <c r="AJ11" s="3">
+      <c r="AJ11" s="12">
         <f>SUM(J11:M11,O11:S11,V11:Z11,AC11:AG11)</f>
         <v/>
       </c>
-      <c r="AK11" s="3">
+      <c r="AK11" s="12">
         <f>SUM(G11:I11,N11,T11:U11,AA11:AB11,AH11:AI11)</f>
         <v/>
       </c>
-      <c r="AL11" s="3">
+      <c r="AL11" s="12">
         <f>SUM(E11:F11)</f>
         <v/>
       </c>
-      <c r="AM11" s="3">
+      <c r="AM11" s="12">
         <f>AJ11*1.5</f>
         <v/>
       </c>
-      <c r="AN11" s="3">
+      <c r="AN11" s="12">
         <f>AK11*2</f>
         <v/>
       </c>
-      <c r="AO11" s="3">
+      <c r="AO11" s="12">
         <f>AL11*3</f>
         <v/>
       </c>
-      <c r="AP11" s="3">
+      <c r="AP11" s="12">
         <f>SUM(AM11:AO11)</f>
         <v/>
       </c>
@@ -6186,31 +5986,31 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n"/>
-      <c r="AJ12" s="3">
+      <c r="AJ12" s="12">
         <f>SUM(J12:M12,O12:S12,V12:Z12,AC12:AG12)</f>
         <v/>
       </c>
-      <c r="AK12" s="3">
+      <c r="AK12" s="12">
         <f>SUM(G12:I12,N12,T12:U12,AA12:AB12,AH12:AI12)</f>
         <v/>
       </c>
-      <c r="AL12" s="3">
+      <c r="AL12" s="12">
         <f>SUM(E12:F12)</f>
         <v/>
       </c>
-      <c r="AM12" s="3">
+      <c r="AM12" s="12">
         <f>AJ12*1.5</f>
         <v/>
       </c>
-      <c r="AN12" s="3">
+      <c r="AN12" s="12">
         <f>AK12*2</f>
         <v/>
       </c>
-      <c r="AO12" s="3">
+      <c r="AO12" s="12">
         <f>AL12*3</f>
         <v/>
       </c>
-      <c r="AP12" s="3">
+      <c r="AP12" s="12">
         <f>SUM(AM12:AO12)</f>
         <v/>
       </c>
@@ -6317,31 +6117,31 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n"/>
-      <c r="AJ13" s="3">
+      <c r="AJ13" s="12">
         <f>SUM(J13:M13,O13:S13,V13:Z13,AC13:AG13)</f>
         <v/>
       </c>
-      <c r="AK13" s="3">
+      <c r="AK13" s="12">
         <f>SUM(G13:I13,N13,T13:U13,AA13:AB13,AH13:AI13)</f>
         <v/>
       </c>
-      <c r="AL13" s="3">
+      <c r="AL13" s="12">
         <f>SUM(E13:F13)</f>
         <v/>
       </c>
-      <c r="AM13" s="3">
+      <c r="AM13" s="12">
         <f>AJ13*1.5</f>
         <v/>
       </c>
-      <c r="AN13" s="3">
+      <c r="AN13" s="12">
         <f>AK13*2</f>
         <v/>
       </c>
-      <c r="AO13" s="3">
+      <c r="AO13" s="12">
         <f>AL13*3</f>
         <v/>
       </c>
-      <c r="AP13" s="3">
+      <c r="AP13" s="12">
         <f>SUM(AM13:AO13)</f>
         <v/>
       </c>
@@ -6448,31 +6248,31 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n"/>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="12">
         <f>SUM(J14:M14,O14:S14,V14:Z14,AC14:AG14)</f>
         <v/>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="12">
         <f>SUM(G14:I14,N14,T14:U14,AA14:AB14,AH14:AI14)</f>
         <v/>
       </c>
-      <c r="AL14" s="3">
+      <c r="AL14" s="12">
         <f>SUM(E14:F14)</f>
         <v/>
       </c>
-      <c r="AM14" s="3">
+      <c r="AM14" s="12">
         <f>AJ14*1.5</f>
         <v/>
       </c>
-      <c r="AN14" s="3">
+      <c r="AN14" s="12">
         <f>AK14*2</f>
         <v/>
       </c>
-      <c r="AO14" s="3">
+      <c r="AO14" s="12">
         <f>AL14*3</f>
         <v/>
       </c>
-      <c r="AP14" s="3">
+      <c r="AP14" s="12">
         <f>SUM(AM14:AO14)</f>
         <v/>
       </c>
@@ -6579,31 +6379,31 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n"/>
-      <c r="AJ15" s="3">
+      <c r="AJ15" s="12">
         <f>SUM(J15:M15,O15:S15,V15:Z15,AC15:AG15)</f>
         <v/>
       </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="12">
         <f>SUM(G15:I15,N15,T15:U15,AA15:AB15,AH15:AI15)</f>
         <v/>
       </c>
-      <c r="AL15" s="3">
+      <c r="AL15" s="12">
         <f>SUM(E15:F15)</f>
         <v/>
       </c>
-      <c r="AM15" s="3">
+      <c r="AM15" s="12">
         <f>AJ15*1.5</f>
         <v/>
       </c>
-      <c r="AN15" s="3">
+      <c r="AN15" s="12">
         <f>AK15*2</f>
         <v/>
       </c>
-      <c r="AO15" s="3">
+      <c r="AO15" s="12">
         <f>AL15*3</f>
         <v/>
       </c>
-      <c r="AP15" s="3">
+      <c r="AP15" s="12">
         <f>SUM(AM15:AO15)</f>
         <v/>
       </c>
@@ -6710,31 +6510,31 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n"/>
-      <c r="AJ16" s="3">
+      <c r="AJ16" s="12">
         <f>SUM(J16:M16,O16:S16,V16:Z16,AC16:AG16)</f>
         <v/>
       </c>
-      <c r="AK16" s="3">
+      <c r="AK16" s="12">
         <f>SUM(G16:I16,N16,T16:U16,AA16:AB16,AH16:AI16)</f>
         <v/>
       </c>
-      <c r="AL16" s="3">
+      <c r="AL16" s="12">
         <f>SUM(E16:F16)</f>
         <v/>
       </c>
-      <c r="AM16" s="3">
+      <c r="AM16" s="12">
         <f>AJ16*1.5</f>
         <v/>
       </c>
-      <c r="AN16" s="3">
+      <c r="AN16" s="12">
         <f>AK16*2</f>
         <v/>
       </c>
-      <c r="AO16" s="3">
+      <c r="AO16" s="12">
         <f>AL16*3</f>
         <v/>
       </c>
-      <c r="AP16" s="3">
+      <c r="AP16" s="12">
         <f>SUM(AM16:AO16)</f>
         <v/>
       </c>
@@ -6841,31 +6641,31 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n"/>
-      <c r="AJ17" s="3">
+      <c r="AJ17" s="12">
         <f>SUM(J17:M17,O17:S17,V17:Z17,AC17:AG17)</f>
         <v/>
       </c>
-      <c r="AK17" s="3">
+      <c r="AK17" s="12">
         <f>SUM(G17:I17,N17,T17:U17,AA17:AB17,AH17:AI17)</f>
         <v/>
       </c>
-      <c r="AL17" s="3">
+      <c r="AL17" s="12">
         <f>SUM(E17:F17)</f>
         <v/>
       </c>
-      <c r="AM17" s="3">
+      <c r="AM17" s="12">
         <f>AJ17*1.5</f>
         <v/>
       </c>
-      <c r="AN17" s="3">
+      <c r="AN17" s="12">
         <f>AK17*2</f>
         <v/>
       </c>
-      <c r="AO17" s="3">
+      <c r="AO17" s="12">
         <f>AL17*3</f>
         <v/>
       </c>
-      <c r="AP17" s="3">
+      <c r="AP17" s="12">
         <f>SUM(AM17:AO17)</f>
         <v/>
       </c>
@@ -6972,31 +6772,31 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n"/>
-      <c r="AJ18" s="3">
+      <c r="AJ18" s="12">
         <f>SUM(J18:M18,O18:S18,V18:Z18,AC18:AG18)</f>
         <v/>
       </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="12">
         <f>SUM(G18:I18,N18,T18:U18,AA18:AB18,AH18:AI18)</f>
         <v/>
       </c>
-      <c r="AL18" s="3">
+      <c r="AL18" s="12">
         <f>SUM(E18:F18)</f>
         <v/>
       </c>
-      <c r="AM18" s="3">
+      <c r="AM18" s="12">
         <f>AJ18*1.5</f>
         <v/>
       </c>
-      <c r="AN18" s="3">
+      <c r="AN18" s="12">
         <f>AK18*2</f>
         <v/>
       </c>
-      <c r="AO18" s="3">
+      <c r="AO18" s="12">
         <f>AL18*3</f>
         <v/>
       </c>
-      <c r="AP18" s="3">
+      <c r="AP18" s="12">
         <f>SUM(AM18:AO18)</f>
         <v/>
       </c>
@@ -7103,31 +6903,31 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n"/>
-      <c r="AJ19" s="3">
+      <c r="AJ19" s="12">
         <f>SUM(J19:M19,O19:S19,V19:Z19,AC19:AG19)</f>
         <v/>
       </c>
-      <c r="AK19" s="3">
+      <c r="AK19" s="12">
         <f>SUM(G19:I19,N19,T19:U19,AA19:AB19,AH19:AI19)</f>
         <v/>
       </c>
-      <c r="AL19" s="3">
+      <c r="AL19" s="12">
         <f>SUM(E19:F19)</f>
         <v/>
       </c>
-      <c r="AM19" s="3">
+      <c r="AM19" s="12">
         <f>AJ19*1.5</f>
         <v/>
       </c>
-      <c r="AN19" s="3">
+      <c r="AN19" s="12">
         <f>AK19*2</f>
         <v/>
       </c>
-      <c r="AO19" s="3">
+      <c r="AO19" s="12">
         <f>AL19*3</f>
         <v/>
       </c>
-      <c r="AP19" s="3">
+      <c r="AP19" s="12">
         <f>SUM(AM19:AO19)</f>
         <v/>
       </c>
@@ -7247,21 +7047,21 @@
       <c r="AI90" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="AJ90" s="2" t="inlineStr">
+      <c r="AJ90" s="11" t="inlineStr">
         <is>
           <t>5月加班时长合计</t>
         </is>
       </c>
       <c r="AK90" s="3" t="n"/>
       <c r="AL90" s="3" t="n"/>
-      <c r="AM90" s="2" t="inlineStr">
+      <c r="AM90" s="11" t="inlineStr">
         <is>
           <t>5月加班抵扣合计</t>
         </is>
       </c>
       <c r="AN90" s="3" t="n"/>
       <c r="AO90" s="3" t="n"/>
-      <c r="AP90" s="2" t="inlineStr">
+      <c r="AP90" s="11" t="inlineStr">
         <is>
           <t>5月剩余</t>
         </is>
@@ -7407,16 +7207,16 @@
       <c r="AG93" s="3" t="n"/>
       <c r="AH93" s="3" t="n"/>
       <c r="AI93" s="3" t="n"/>
-      <c r="AJ93" s="3" t="n"/>
-      <c r="AK93" s="3">
+      <c r="AJ93" s="13" t="n"/>
+      <c r="AK93" s="12">
         <f>SUM(D93:AI93)</f>
         <v/>
       </c>
-      <c r="AL93" s="3" t="n"/>
-      <c r="AM93" s="3" t="n"/>
-      <c r="AN93" s="3" t="n"/>
-      <c r="AO93" s="3" t="n"/>
-      <c r="AP93" s="3">
+      <c r="AL93" s="13" t="n"/>
+      <c r="AM93" s="13" t="n"/>
+      <c r="AN93" s="13" t="n"/>
+      <c r="AO93" s="13" t="n"/>
+      <c r="AP93" s="12">
         <f>AJ93+AK93</f>
         <v/>
       </c>
@@ -7461,16 +7261,16 @@
       <c r="AG94" s="3" t="n"/>
       <c r="AH94" s="3" t="n"/>
       <c r="AI94" s="3" t="n"/>
-      <c r="AJ94" s="3" t="n"/>
-      <c r="AK94" s="3">
+      <c r="AJ94" s="13" t="n"/>
+      <c r="AK94" s="12">
         <f>SUM(D94:AI94)</f>
         <v/>
       </c>
-      <c r="AL94" s="3" t="n"/>
-      <c r="AM94" s="3" t="n"/>
-      <c r="AN94" s="3" t="n"/>
-      <c r="AO94" s="3" t="n"/>
-      <c r="AP94" s="3">
+      <c r="AL94" s="13" t="n"/>
+      <c r="AM94" s="13" t="n"/>
+      <c r="AN94" s="13" t="n"/>
+      <c r="AO94" s="13" t="n"/>
+      <c r="AP94" s="12">
         <f>AJ94+AK94</f>
         <v/>
       </c>
@@ -7515,16 +7315,16 @@
       <c r="AG95" s="3" t="n"/>
       <c r="AH95" s="3" t="n"/>
       <c r="AI95" s="3" t="n"/>
-      <c r="AJ95" s="3" t="n"/>
-      <c r="AK95" s="3">
+      <c r="AJ95" s="13" t="n"/>
+      <c r="AK95" s="12">
         <f>SUM(D95:AI95)</f>
         <v/>
       </c>
-      <c r="AL95" s="3" t="n"/>
-      <c r="AM95" s="3" t="n"/>
-      <c r="AN95" s="3" t="n"/>
-      <c r="AO95" s="3" t="n"/>
-      <c r="AP95" s="3">
+      <c r="AL95" s="13" t="n"/>
+      <c r="AM95" s="13" t="n"/>
+      <c r="AN95" s="13" t="n"/>
+      <c r="AO95" s="13" t="n"/>
+      <c r="AP95" s="12">
         <f>AJ95+AK95</f>
         <v/>
       </c>
@@ -7569,16 +7369,16 @@
       <c r="AG96" s="3" t="n"/>
       <c r="AH96" s="3" t="n"/>
       <c r="AI96" s="3" t="n"/>
-      <c r="AJ96" s="3" t="n"/>
-      <c r="AK96" s="3">
+      <c r="AJ96" s="13" t="n"/>
+      <c r="AK96" s="12">
         <f>SUM(D96:AI96)</f>
         <v/>
       </c>
-      <c r="AL96" s="3" t="n"/>
-      <c r="AM96" s="3" t="n"/>
-      <c r="AN96" s="3" t="n"/>
-      <c r="AO96" s="3" t="n"/>
-      <c r="AP96" s="3">
+      <c r="AL96" s="13" t="n"/>
+      <c r="AM96" s="13" t="n"/>
+      <c r="AN96" s="13" t="n"/>
+      <c r="AO96" s="13" t="n"/>
+      <c r="AP96" s="12">
         <f>AJ96+AK96</f>
         <v/>
       </c>
@@ -7623,16 +7423,16 @@
       <c r="AG97" s="3" t="n"/>
       <c r="AH97" s="3" t="n"/>
       <c r="AI97" s="3" t="n"/>
-      <c r="AJ97" s="3" t="n"/>
-      <c r="AK97" s="3">
+      <c r="AJ97" s="13" t="n"/>
+      <c r="AK97" s="12">
         <f>SUM(D97:AI97)</f>
         <v/>
       </c>
-      <c r="AL97" s="3" t="n"/>
-      <c r="AM97" s="3" t="n"/>
-      <c r="AN97" s="3" t="n"/>
-      <c r="AO97" s="3" t="n"/>
-      <c r="AP97" s="3">
+      <c r="AL97" s="13" t="n"/>
+      <c r="AM97" s="13" t="n"/>
+      <c r="AN97" s="13" t="n"/>
+      <c r="AO97" s="13" t="n"/>
+      <c r="AP97" s="12">
         <f>AJ97+AK97</f>
         <v/>
       </c>
@@ -7677,16 +7477,16 @@
       <c r="AG98" s="3" t="n"/>
       <c r="AH98" s="3" t="n"/>
       <c r="AI98" s="3" t="n"/>
-      <c r="AJ98" s="3" t="n"/>
-      <c r="AK98" s="3">
+      <c r="AJ98" s="13" t="n"/>
+      <c r="AK98" s="12">
         <f>SUM(D98:AI98)</f>
         <v/>
       </c>
-      <c r="AL98" s="3" t="n"/>
-      <c r="AM98" s="3" t="n"/>
-      <c r="AN98" s="3" t="n"/>
-      <c r="AO98" s="3" t="n"/>
-      <c r="AP98" s="3">
+      <c r="AL98" s="13" t="n"/>
+      <c r="AM98" s="13" t="n"/>
+      <c r="AN98" s="13" t="n"/>
+      <c r="AO98" s="13" t="n"/>
+      <c r="AP98" s="12">
         <f>AJ98+AK98</f>
         <v/>
       </c>
@@ -7731,16 +7531,16 @@
       <c r="AG99" s="3" t="n"/>
       <c r="AH99" s="3" t="n"/>
       <c r="AI99" s="3" t="n"/>
-      <c r="AJ99" s="3" t="n"/>
-      <c r="AK99" s="3">
+      <c r="AJ99" s="13" t="n"/>
+      <c r="AK99" s="12">
         <f>SUM(D99:AI99)</f>
         <v/>
       </c>
-      <c r="AL99" s="3" t="n"/>
-      <c r="AM99" s="3" t="n"/>
-      <c r="AN99" s="3" t="n"/>
-      <c r="AO99" s="3" t="n"/>
-      <c r="AP99" s="3">
+      <c r="AL99" s="13" t="n"/>
+      <c r="AM99" s="13" t="n"/>
+      <c r="AN99" s="13" t="n"/>
+      <c r="AO99" s="13" t="n"/>
+      <c r="AP99" s="12">
         <f>AJ99+AK99</f>
         <v/>
       </c>
@@ -7785,16 +7585,16 @@
       <c r="AG100" s="3" t="n"/>
       <c r="AH100" s="3" t="n"/>
       <c r="AI100" s="3" t="n"/>
-      <c r="AJ100" s="3" t="n"/>
-      <c r="AK100" s="3">
+      <c r="AJ100" s="13" t="n"/>
+      <c r="AK100" s="12">
         <f>SUM(D100:AI100)</f>
         <v/>
       </c>
-      <c r="AL100" s="3" t="n"/>
-      <c r="AM100" s="3" t="n"/>
-      <c r="AN100" s="3" t="n"/>
-      <c r="AO100" s="3" t="n"/>
-      <c r="AP100" s="3">
+      <c r="AL100" s="13" t="n"/>
+      <c r="AM100" s="13" t="n"/>
+      <c r="AN100" s="13" t="n"/>
+      <c r="AO100" s="13" t="n"/>
+      <c r="AP100" s="12">
         <f>AJ100+AK100</f>
         <v/>
       </c>
@@ -7839,16 +7639,16 @@
       <c r="AG101" s="3" t="n"/>
       <c r="AH101" s="3" t="n"/>
       <c r="AI101" s="3" t="n"/>
-      <c r="AJ101" s="3" t="n"/>
-      <c r="AK101" s="3">
+      <c r="AJ101" s="13" t="n"/>
+      <c r="AK101" s="12">
         <f>SUM(D101:AI101)</f>
         <v/>
       </c>
-      <c r="AL101" s="3" t="n"/>
-      <c r="AM101" s="3" t="n"/>
-      <c r="AN101" s="3" t="n"/>
-      <c r="AO101" s="3" t="n"/>
-      <c r="AP101" s="3">
+      <c r="AL101" s="13" t="n"/>
+      <c r="AM101" s="13" t="n"/>
+      <c r="AN101" s="13" t="n"/>
+      <c r="AO101" s="13" t="n"/>
+      <c r="AP101" s="12">
         <f>AJ101+AK101</f>
         <v/>
       </c>
@@ -7893,16 +7693,16 @@
       <c r="AG102" s="3" t="n"/>
       <c r="AH102" s="3" t="n"/>
       <c r="AI102" s="3" t="n"/>
-      <c r="AJ102" s="3" t="n"/>
-      <c r="AK102" s="3">
+      <c r="AJ102" s="13" t="n"/>
+      <c r="AK102" s="12">
         <f>SUM(D102:AI102)</f>
         <v/>
       </c>
-      <c r="AL102" s="3" t="n"/>
-      <c r="AM102" s="3" t="n"/>
-      <c r="AN102" s="3" t="n"/>
-      <c r="AO102" s="3" t="n"/>
-      <c r="AP102" s="3">
+      <c r="AL102" s="13" t="n"/>
+      <c r="AM102" s="13" t="n"/>
+      <c r="AN102" s="13" t="n"/>
+      <c r="AO102" s="13" t="n"/>
+      <c r="AP102" s="12">
         <f>AJ102+AK102</f>
         <v/>
       </c>
@@ -7947,16 +7747,16 @@
       <c r="AG103" s="3" t="n"/>
       <c r="AH103" s="3" t="n"/>
       <c r="AI103" s="3" t="n"/>
-      <c r="AJ103" s="3" t="n"/>
-      <c r="AK103" s="3">
+      <c r="AJ103" s="13" t="n"/>
+      <c r="AK103" s="12">
         <f>SUM(D103:AI103)</f>
         <v/>
       </c>
-      <c r="AL103" s="3" t="n"/>
-      <c r="AM103" s="3" t="n"/>
-      <c r="AN103" s="3" t="n"/>
-      <c r="AO103" s="3" t="n"/>
-      <c r="AP103" s="3">
+      <c r="AL103" s="13" t="n"/>
+      <c r="AM103" s="13" t="n"/>
+      <c r="AN103" s="13" t="n"/>
+      <c r="AO103" s="13" t="n"/>
+      <c r="AP103" s="12">
         <f>AJ103+AK103</f>
         <v/>
       </c>
@@ -8001,16 +7801,16 @@
       <c r="AG104" s="3" t="n"/>
       <c r="AH104" s="3" t="n"/>
       <c r="AI104" s="3" t="n"/>
-      <c r="AJ104" s="3" t="n"/>
-      <c r="AK104" s="3">
+      <c r="AJ104" s="13" t="n"/>
+      <c r="AK104" s="12">
         <f>SUM(D104:AI104)</f>
         <v/>
       </c>
-      <c r="AL104" s="3" t="n"/>
-      <c r="AM104" s="3" t="n"/>
-      <c r="AN104" s="3" t="n"/>
-      <c r="AO104" s="3" t="n"/>
-      <c r="AP104" s="3">
+      <c r="AL104" s="13" t="n"/>
+      <c r="AM104" s="13" t="n"/>
+      <c r="AN104" s="13" t="n"/>
+      <c r="AO104" s="13" t="n"/>
+      <c r="AP104" s="12">
         <f>AJ104+AK104</f>
         <v/>
       </c>
@@ -8055,16 +7855,16 @@
       <c r="AG105" s="3" t="n"/>
       <c r="AH105" s="3" t="n"/>
       <c r="AI105" s="3" t="n"/>
-      <c r="AJ105" s="3" t="n"/>
-      <c r="AK105" s="3">
+      <c r="AJ105" s="13" t="n"/>
+      <c r="AK105" s="12">
         <f>SUM(D105:AI105)</f>
         <v/>
       </c>
-      <c r="AL105" s="3" t="n"/>
-      <c r="AM105" s="3" t="n"/>
-      <c r="AN105" s="3" t="n"/>
-      <c r="AO105" s="3" t="n"/>
-      <c r="AP105" s="3">
+      <c r="AL105" s="13" t="n"/>
+      <c r="AM105" s="13" t="n"/>
+      <c r="AN105" s="13" t="n"/>
+      <c r="AO105" s="13" t="n"/>
+      <c r="AP105" s="12">
         <f>AJ105+AK105</f>
         <v/>
       </c>
@@ -8109,16 +7909,16 @@
       <c r="AG106" s="3" t="n"/>
       <c r="AH106" s="3" t="n"/>
       <c r="AI106" s="3" t="n"/>
-      <c r="AJ106" s="3" t="n"/>
-      <c r="AK106" s="3">
+      <c r="AJ106" s="13" t="n"/>
+      <c r="AK106" s="12">
         <f>SUM(D106:AI106)</f>
         <v/>
       </c>
-      <c r="AL106" s="3" t="n"/>
-      <c r="AM106" s="3" t="n"/>
-      <c r="AN106" s="3" t="n"/>
-      <c r="AO106" s="3" t="n"/>
-      <c r="AP106" s="3">
+      <c r="AL106" s="13" t="n"/>
+      <c r="AM106" s="13" t="n"/>
+      <c r="AN106" s="13" t="n"/>
+      <c r="AO106" s="13" t="n"/>
+      <c r="AP106" s="12">
         <f>AJ106+AK106</f>
         <v/>
       </c>
@@ -8163,16 +7963,16 @@
       <c r="AG107" s="3" t="n"/>
       <c r="AH107" s="3" t="n"/>
       <c r="AI107" s="3" t="n"/>
-      <c r="AJ107" s="3" t="n"/>
-      <c r="AK107" s="3">
+      <c r="AJ107" s="13" t="n"/>
+      <c r="AK107" s="12">
         <f>SUM(D107:AI107)</f>
         <v/>
       </c>
-      <c r="AL107" s="3" t="n"/>
-      <c r="AM107" s="3" t="n"/>
-      <c r="AN107" s="3" t="n"/>
-      <c r="AO107" s="3" t="n"/>
-      <c r="AP107" s="3">
+      <c r="AL107" s="13" t="n"/>
+      <c r="AM107" s="13" t="n"/>
+      <c r="AN107" s="13" t="n"/>
+      <c r="AO107" s="13" t="n"/>
+      <c r="AP107" s="12">
         <f>AJ107+AK107</f>
         <v/>
       </c>
@@ -8217,16 +8017,16 @@
       <c r="AG108" s="3" t="n"/>
       <c r="AH108" s="3" t="n"/>
       <c r="AI108" s="3" t="n"/>
-      <c r="AJ108" s="3" t="n"/>
-      <c r="AK108" s="3">
+      <c r="AJ108" s="13" t="n"/>
+      <c r="AK108" s="12">
         <f>SUM(D108:AI108)</f>
         <v/>
       </c>
-      <c r="AL108" s="3" t="n"/>
-      <c r="AM108" s="3" t="n"/>
-      <c r="AN108" s="3" t="n"/>
-      <c r="AO108" s="3" t="n"/>
-      <c r="AP108" s="3">
+      <c r="AL108" s="13" t="n"/>
+      <c r="AM108" s="13" t="n"/>
+      <c r="AN108" s="13" t="n"/>
+      <c r="AO108" s="13" t="n"/>
+      <c r="AP108" s="12">
         <f>AJ108+AK108</f>
         <v/>
       </c>
@@ -8271,16 +8071,16 @@
       <c r="AG109" s="3" t="n"/>
       <c r="AH109" s="3" t="n"/>
       <c r="AI109" s="3" t="n"/>
-      <c r="AJ109" s="3" t="n"/>
-      <c r="AK109" s="3">
+      <c r="AJ109" s="13" t="n"/>
+      <c r="AK109" s="12">
         <f>SUM(D109:AI109)</f>
         <v/>
       </c>
-      <c r="AL109" s="3" t="n"/>
-      <c r="AM109" s="3" t="n"/>
-      <c r="AN109" s="3" t="n"/>
-      <c r="AO109" s="3" t="n"/>
-      <c r="AP109" s="3">
+      <c r="AL109" s="13" t="n"/>
+      <c r="AM109" s="13" t="n"/>
+      <c r="AN109" s="13" t="n"/>
+      <c r="AO109" s="13" t="n"/>
+      <c r="AP109" s="12">
         <f>AJ109+AK109</f>
         <v/>
       </c>
@@ -8325,16 +8125,16 @@
       <c r="AG110" s="3" t="n"/>
       <c r="AH110" s="3" t="n"/>
       <c r="AI110" s="3" t="n"/>
-      <c r="AJ110" s="3" t="n"/>
-      <c r="AK110" s="3">
+      <c r="AJ110" s="13" t="n"/>
+      <c r="AK110" s="12">
         <f>SUM(D110:AI110)</f>
         <v/>
       </c>
-      <c r="AL110" s="3" t="n"/>
-      <c r="AM110" s="3" t="n"/>
-      <c r="AN110" s="3" t="n"/>
-      <c r="AO110" s="3" t="n"/>
-      <c r="AP110" s="3">
+      <c r="AL110" s="13" t="n"/>
+      <c r="AM110" s="13" t="n"/>
+      <c r="AN110" s="13" t="n"/>
+      <c r="AO110" s="13" t="n"/>
+      <c r="AP110" s="12">
         <f>AJ110+AK110</f>
         <v/>
       </c>
@@ -8379,16 +8179,16 @@
       <c r="AG111" s="3" t="n"/>
       <c r="AH111" s="3" t="n"/>
       <c r="AI111" s="3" t="n"/>
-      <c r="AJ111" s="3" t="n"/>
-      <c r="AK111" s="3">
+      <c r="AJ111" s="13" t="n"/>
+      <c r="AK111" s="12">
         <f>SUM(D111:AI111)</f>
         <v/>
       </c>
-      <c r="AL111" s="3" t="n"/>
-      <c r="AM111" s="3" t="n"/>
-      <c r="AN111" s="3" t="n"/>
-      <c r="AO111" s="3" t="n"/>
-      <c r="AP111" s="3">
+      <c r="AL111" s="13" t="n"/>
+      <c r="AM111" s="13" t="n"/>
+      <c r="AN111" s="13" t="n"/>
+      <c r="AO111" s="13" t="n"/>
+      <c r="AP111" s="12">
         <f>AJ111+AK111</f>
         <v/>
       </c>
@@ -8433,16 +8233,16 @@
       <c r="AG112" s="3" t="n"/>
       <c r="AH112" s="3" t="n"/>
       <c r="AI112" s="3" t="n"/>
-      <c r="AJ112" s="3" t="n"/>
-      <c r="AK112" s="3">
+      <c r="AJ112" s="13" t="n"/>
+      <c r="AK112" s="12">
         <f>SUM(D112:AI112)</f>
         <v/>
       </c>
-      <c r="AL112" s="3" t="n"/>
-      <c r="AM112" s="3" t="n"/>
-      <c r="AN112" s="3" t="n"/>
-      <c r="AO112" s="3" t="n"/>
-      <c r="AP112" s="3">
+      <c r="AL112" s="13" t="n"/>
+      <c r="AM112" s="13" t="n"/>
+      <c r="AN112" s="13" t="n"/>
+      <c r="AO112" s="13" t="n"/>
+      <c r="AP112" s="12">
         <f>AJ112+AK112</f>
         <v/>
       </c>
@@ -8487,16 +8287,16 @@
       <c r="AG113" s="3" t="n"/>
       <c r="AH113" s="3" t="n"/>
       <c r="AI113" s="3" t="n"/>
-      <c r="AJ113" s="3" t="n"/>
-      <c r="AK113" s="3">
+      <c r="AJ113" s="13" t="n"/>
+      <c r="AK113" s="12">
         <f>SUM(D113:AI113)</f>
         <v/>
       </c>
-      <c r="AL113" s="3" t="n"/>
-      <c r="AM113" s="3" t="n"/>
-      <c r="AN113" s="3" t="n"/>
-      <c r="AO113" s="3" t="n"/>
-      <c r="AP113" s="3">
+      <c r="AL113" s="13" t="n"/>
+      <c r="AM113" s="13" t="n"/>
+      <c r="AN113" s="13" t="n"/>
+      <c r="AO113" s="13" t="n"/>
+      <c r="AP113" s="12">
         <f>AJ113+AK113</f>
         <v/>
       </c>
@@ -8541,16 +8341,16 @@
       <c r="AG114" s="3" t="n"/>
       <c r="AH114" s="3" t="n"/>
       <c r="AI114" s="3" t="n"/>
-      <c r="AJ114" s="3" t="n"/>
-      <c r="AK114" s="3">
+      <c r="AJ114" s="13" t="n"/>
+      <c r="AK114" s="12">
         <f>SUM(D114:AI114)</f>
         <v/>
       </c>
-      <c r="AL114" s="3" t="n"/>
-      <c r="AM114" s="3" t="n"/>
-      <c r="AN114" s="3" t="n"/>
-      <c r="AO114" s="3" t="n"/>
-      <c r="AP114" s="3">
+      <c r="AL114" s="13" t="n"/>
+      <c r="AM114" s="13" t="n"/>
+      <c r="AN114" s="13" t="n"/>
+      <c r="AO114" s="13" t="n"/>
+      <c r="AP114" s="12">
         <f>AJ114+AK114</f>
         <v/>
       </c>
@@ -8595,16 +8395,16 @@
       <c r="AG115" s="3" t="n"/>
       <c r="AH115" s="3" t="n"/>
       <c r="AI115" s="3" t="n"/>
-      <c r="AJ115" s="3" t="n"/>
-      <c r="AK115" s="3">
+      <c r="AJ115" s="13" t="n"/>
+      <c r="AK115" s="12">
         <f>SUM(D115:AI115)</f>
         <v/>
       </c>
-      <c r="AL115" s="3" t="n"/>
-      <c r="AM115" s="3" t="n"/>
-      <c r="AN115" s="3" t="n"/>
-      <c r="AO115" s="3" t="n"/>
-      <c r="AP115" s="3">
+      <c r="AL115" s="13" t="n"/>
+      <c r="AM115" s="13" t="n"/>
+      <c r="AN115" s="13" t="n"/>
+      <c r="AO115" s="13" t="n"/>
+      <c r="AP115" s="12">
         <f>AJ115+AK115</f>
         <v/>
       </c>
@@ -8649,16 +8449,16 @@
       <c r="AG116" s="3" t="n"/>
       <c r="AH116" s="3" t="n"/>
       <c r="AI116" s="3" t="n"/>
-      <c r="AJ116" s="3" t="n"/>
-      <c r="AK116" s="3">
+      <c r="AJ116" s="13" t="n"/>
+      <c r="AK116" s="12">
         <f>SUM(D116:AI116)</f>
         <v/>
       </c>
-      <c r="AL116" s="3" t="n"/>
-      <c r="AM116" s="3" t="n"/>
-      <c r="AN116" s="3" t="n"/>
-      <c r="AO116" s="3" t="n"/>
-      <c r="AP116" s="3">
+      <c r="AL116" s="13" t="n"/>
+      <c r="AM116" s="13" t="n"/>
+      <c r="AN116" s="13" t="n"/>
+      <c r="AO116" s="13" t="n"/>
+      <c r="AP116" s="12">
         <f>AJ116+AK116</f>
         <v/>
       </c>
@@ -8703,16 +8503,16 @@
       <c r="AG117" s="3" t="n"/>
       <c r="AH117" s="3" t="n"/>
       <c r="AI117" s="3" t="n"/>
-      <c r="AJ117" s="3" t="n"/>
-      <c r="AK117" s="3">
+      <c r="AJ117" s="13" t="n"/>
+      <c r="AK117" s="12">
         <f>SUM(D117:AI117)</f>
         <v/>
       </c>
-      <c r="AL117" s="3" t="n"/>
-      <c r="AM117" s="3" t="n"/>
-      <c r="AN117" s="3" t="n"/>
-      <c r="AO117" s="3" t="n"/>
-      <c r="AP117" s="3">
+      <c r="AL117" s="13" t="n"/>
+      <c r="AM117" s="13" t="n"/>
+      <c r="AN117" s="13" t="n"/>
+      <c r="AO117" s="13" t="n"/>
+      <c r="AP117" s="12">
         <f>AJ117+AK117</f>
         <v/>
       </c>
@@ -8757,16 +8557,16 @@
       <c r="AG118" s="3" t="n"/>
       <c r="AH118" s="3" t="n"/>
       <c r="AI118" s="3" t="n"/>
-      <c r="AJ118" s="3" t="n"/>
-      <c r="AK118" s="3">
+      <c r="AJ118" s="13" t="n"/>
+      <c r="AK118" s="12">
         <f>SUM(D118:AI118)</f>
         <v/>
       </c>
-      <c r="AL118" s="3" t="n"/>
-      <c r="AM118" s="3" t="n"/>
-      <c r="AN118" s="3" t="n"/>
-      <c r="AO118" s="3" t="n"/>
-      <c r="AP118" s="3">
+      <c r="AL118" s="13" t="n"/>
+      <c r="AM118" s="13" t="n"/>
+      <c r="AN118" s="13" t="n"/>
+      <c r="AO118" s="13" t="n"/>
+      <c r="AP118" s="12">
         <f>AJ118+AK118</f>
         <v/>
       </c>
@@ -8811,16 +8611,16 @@
       <c r="AG119" s="3" t="n"/>
       <c r="AH119" s="3" t="n"/>
       <c r="AI119" s="3" t="n"/>
-      <c r="AJ119" s="3" t="n"/>
-      <c r="AK119" s="3">
+      <c r="AJ119" s="13" t="n"/>
+      <c r="AK119" s="12">
         <f>SUM(D119:AI119)</f>
         <v/>
       </c>
-      <c r="AL119" s="3" t="n"/>
-      <c r="AM119" s="3" t="n"/>
-      <c r="AN119" s="3" t="n"/>
-      <c r="AO119" s="3" t="n"/>
-      <c r="AP119" s="3">
+      <c r="AL119" s="13" t="n"/>
+      <c r="AM119" s="13" t="n"/>
+      <c r="AN119" s="13" t="n"/>
+      <c r="AO119" s="13" t="n"/>
+      <c r="AP119" s="12">
         <f>AJ119+AK119</f>
         <v/>
       </c>
@@ -8865,16 +8665,16 @@
       <c r="AG120" s="3" t="n"/>
       <c r="AH120" s="3" t="n"/>
       <c r="AI120" s="3" t="n"/>
-      <c r="AJ120" s="3" t="n"/>
-      <c r="AK120" s="3">
+      <c r="AJ120" s="13" t="n"/>
+      <c r="AK120" s="12">
         <f>SUM(D120:AI120)</f>
         <v/>
       </c>
-      <c r="AL120" s="3" t="n"/>
-      <c r="AM120" s="3" t="n"/>
-      <c r="AN120" s="3" t="n"/>
-      <c r="AO120" s="3" t="n"/>
-      <c r="AP120" s="3">
+      <c r="AL120" s="13" t="n"/>
+      <c r="AM120" s="13" t="n"/>
+      <c r="AN120" s="13" t="n"/>
+      <c r="AO120" s="13" t="n"/>
+      <c r="AP120" s="12">
         <f>AJ120+AK120</f>
         <v/>
       </c>
@@ -8919,16 +8719,16 @@
       <c r="AG121" s="3" t="n"/>
       <c r="AH121" s="3" t="n"/>
       <c r="AI121" s="3" t="n"/>
-      <c r="AJ121" s="3" t="n"/>
-      <c r="AK121" s="3">
+      <c r="AJ121" s="13" t="n"/>
+      <c r="AK121" s="12">
         <f>SUM(D121:AI121)</f>
         <v/>
       </c>
-      <c r="AL121" s="3" t="n"/>
-      <c r="AM121" s="3" t="n"/>
-      <c r="AN121" s="3" t="n"/>
-      <c r="AO121" s="3" t="n"/>
-      <c r="AP121" s="3">
+      <c r="AL121" s="13" t="n"/>
+      <c r="AM121" s="13" t="n"/>
+      <c r="AN121" s="13" t="n"/>
+      <c r="AO121" s="13" t="n"/>
+      <c r="AP121" s="12">
         <f>AJ121+AK121</f>
         <v/>
       </c>
@@ -8973,16 +8773,16 @@
       <c r="AG122" s="3" t="n"/>
       <c r="AH122" s="3" t="n"/>
       <c r="AI122" s="3" t="n"/>
-      <c r="AJ122" s="3" t="n"/>
-      <c r="AK122" s="3">
+      <c r="AJ122" s="13" t="n"/>
+      <c r="AK122" s="12">
         <f>SUM(D122:AI122)</f>
         <v/>
       </c>
-      <c r="AL122" s="3" t="n"/>
-      <c r="AM122" s="3" t="n"/>
-      <c r="AN122" s="3" t="n"/>
-      <c r="AO122" s="3" t="n"/>
-      <c r="AP122" s="3">
+      <c r="AL122" s="13" t="n"/>
+      <c r="AM122" s="13" t="n"/>
+      <c r="AN122" s="13" t="n"/>
+      <c r="AO122" s="13" t="n"/>
+      <c r="AP122" s="12">
         <f>AJ122+AK122</f>
         <v/>
       </c>
@@ -9027,16 +8827,16 @@
       <c r="AG123" s="3" t="n"/>
       <c r="AH123" s="3" t="n"/>
       <c r="AI123" s="3" t="n"/>
-      <c r="AJ123" s="3" t="n"/>
-      <c r="AK123" s="3">
+      <c r="AJ123" s="13" t="n"/>
+      <c r="AK123" s="12">
         <f>SUM(D123:AI123)</f>
         <v/>
       </c>
-      <c r="AL123" s="3" t="n"/>
-      <c r="AM123" s="3" t="n"/>
-      <c r="AN123" s="3" t="n"/>
-      <c r="AO123" s="3" t="n"/>
-      <c r="AP123" s="3">
+      <c r="AL123" s="13" t="n"/>
+      <c r="AM123" s="13" t="n"/>
+      <c r="AN123" s="13" t="n"/>
+      <c r="AO123" s="13" t="n"/>
+      <c r="AP123" s="12">
         <f>AJ123+AK123</f>
         <v/>
       </c>
@@ -9081,16 +8881,16 @@
       <c r="AG124" s="3" t="n"/>
       <c r="AH124" s="3" t="n"/>
       <c r="AI124" s="3" t="n"/>
-      <c r="AJ124" s="3" t="n"/>
-      <c r="AK124" s="3">
+      <c r="AJ124" s="13" t="n"/>
+      <c r="AK124" s="12">
         <f>SUM(D124:AI124)</f>
         <v/>
       </c>
-      <c r="AL124" s="3" t="n"/>
-      <c r="AM124" s="3" t="n"/>
-      <c r="AN124" s="3" t="n"/>
-      <c r="AO124" s="3" t="n"/>
-      <c r="AP124" s="3">
+      <c r="AL124" s="13" t="n"/>
+      <c r="AM124" s="13" t="n"/>
+      <c r="AN124" s="13" t="n"/>
+      <c r="AO124" s="13" t="n"/>
+      <c r="AP124" s="12">
         <f>AJ124+AK124</f>
         <v/>
       </c>
@@ -9135,16 +8935,16 @@
       <c r="AG125" s="3" t="n"/>
       <c r="AH125" s="3" t="n"/>
       <c r="AI125" s="3" t="n"/>
-      <c r="AJ125" s="3" t="n"/>
-      <c r="AK125" s="3">
+      <c r="AJ125" s="13" t="n"/>
+      <c r="AK125" s="12">
         <f>SUM(D125:AI125)</f>
         <v/>
       </c>
-      <c r="AL125" s="3" t="n"/>
-      <c r="AM125" s="3" t="n"/>
-      <c r="AN125" s="3" t="n"/>
-      <c r="AO125" s="3" t="n"/>
-      <c r="AP125" s="3">
+      <c r="AL125" s="13" t="n"/>
+      <c r="AM125" s="13" t="n"/>
+      <c r="AN125" s="13" t="n"/>
+      <c r="AO125" s="13" t="n"/>
+      <c r="AP125" s="12">
         <f>AJ125+AK125</f>
         <v/>
       </c>
@@ -9189,16 +8989,16 @@
       <c r="AG126" s="3" t="n"/>
       <c r="AH126" s="3" t="n"/>
       <c r="AI126" s="3" t="n"/>
-      <c r="AJ126" s="3" t="n"/>
-      <c r="AK126" s="3">
+      <c r="AJ126" s="13" t="n"/>
+      <c r="AK126" s="12">
         <f>SUM(D126:AI126)</f>
         <v/>
       </c>
-      <c r="AL126" s="3" t="n"/>
-      <c r="AM126" s="3" t="n"/>
-      <c r="AN126" s="3" t="n"/>
-      <c r="AO126" s="3" t="n"/>
-      <c r="AP126" s="3">
+      <c r="AL126" s="13" t="n"/>
+      <c r="AM126" s="13" t="n"/>
+      <c r="AN126" s="13" t="n"/>
+      <c r="AO126" s="13" t="n"/>
+      <c r="AP126" s="12">
         <f>AJ126+AK126</f>
         <v/>
       </c>
@@ -9243,16 +9043,16 @@
       <c r="AG127" s="3" t="n"/>
       <c r="AH127" s="3" t="n"/>
       <c r="AI127" s="3" t="n"/>
-      <c r="AJ127" s="3" t="n"/>
-      <c r="AK127" s="3">
+      <c r="AJ127" s="13" t="n"/>
+      <c r="AK127" s="12">
         <f>SUM(D127:AI127)</f>
         <v/>
       </c>
-      <c r="AL127" s="3" t="n"/>
-      <c r="AM127" s="3" t="n"/>
-      <c r="AN127" s="3" t="n"/>
-      <c r="AO127" s="3" t="n"/>
-      <c r="AP127" s="3">
+      <c r="AL127" s="13" t="n"/>
+      <c r="AM127" s="13" t="n"/>
+      <c r="AN127" s="13" t="n"/>
+      <c r="AO127" s="13" t="n"/>
+      <c r="AP127" s="12">
         <f>AJ127+AK127</f>
         <v/>
       </c>
@@ -9297,16 +9097,16 @@
       <c r="AG128" s="3" t="n"/>
       <c r="AH128" s="3" t="n"/>
       <c r="AI128" s="3" t="n"/>
-      <c r="AJ128" s="3" t="n"/>
-      <c r="AK128" s="3">
+      <c r="AJ128" s="13" t="n"/>
+      <c r="AK128" s="12">
         <f>SUM(D128:AI128)</f>
         <v/>
       </c>
-      <c r="AL128" s="3" t="n"/>
-      <c r="AM128" s="3" t="n"/>
-      <c r="AN128" s="3" t="n"/>
-      <c r="AO128" s="3" t="n"/>
-      <c r="AP128" s="3">
+      <c r="AL128" s="13" t="n"/>
+      <c r="AM128" s="13" t="n"/>
+      <c r="AN128" s="13" t="n"/>
+      <c r="AO128" s="13" t="n"/>
+      <c r="AP128" s="12">
         <f>AJ128+AK128</f>
         <v/>
       </c>
@@ -9351,16 +9151,16 @@
       <c r="AG129" s="3" t="n"/>
       <c r="AH129" s="3" t="n"/>
       <c r="AI129" s="3" t="n"/>
-      <c r="AJ129" s="3" t="n"/>
-      <c r="AK129" s="3">
+      <c r="AJ129" s="13" t="n"/>
+      <c r="AK129" s="12">
         <f>SUM(D129:AI129)</f>
         <v/>
       </c>
-      <c r="AL129" s="3" t="n"/>
-      <c r="AM129" s="3" t="n"/>
-      <c r="AN129" s="3" t="n"/>
-      <c r="AO129" s="3" t="n"/>
-      <c r="AP129" s="3">
+      <c r="AL129" s="13" t="n"/>
+      <c r="AM129" s="13" t="n"/>
+      <c r="AN129" s="13" t="n"/>
+      <c r="AO129" s="13" t="n"/>
+      <c r="AP129" s="12">
         <f>AJ129+AK129</f>
         <v/>
       </c>
@@ -9405,16 +9205,16 @@
       <c r="AG130" s="3" t="n"/>
       <c r="AH130" s="3" t="n"/>
       <c r="AI130" s="3" t="n"/>
-      <c r="AJ130" s="3" t="n"/>
-      <c r="AK130" s="3">
+      <c r="AJ130" s="13" t="n"/>
+      <c r="AK130" s="12">
         <f>SUM(D130:AI130)</f>
         <v/>
       </c>
-      <c r="AL130" s="3" t="n"/>
-      <c r="AM130" s="3" t="n"/>
-      <c r="AN130" s="3" t="n"/>
-      <c r="AO130" s="3" t="n"/>
-      <c r="AP130" s="3">
+      <c r="AL130" s="13" t="n"/>
+      <c r="AM130" s="13" t="n"/>
+      <c r="AN130" s="13" t="n"/>
+      <c r="AO130" s="13" t="n"/>
+      <c r="AP130" s="12">
         <f>AJ130+AK130</f>
         <v/>
       </c>
@@ -9459,16 +9259,16 @@
       <c r="AG131" s="3" t="n"/>
       <c r="AH131" s="3" t="n"/>
       <c r="AI131" s="3" t="n"/>
-      <c r="AJ131" s="3" t="n"/>
-      <c r="AK131" s="3">
+      <c r="AJ131" s="13" t="n"/>
+      <c r="AK131" s="12">
         <f>SUM(D131:AI131)</f>
         <v/>
       </c>
-      <c r="AL131" s="3" t="n"/>
-      <c r="AM131" s="3" t="n"/>
-      <c r="AN131" s="3" t="n"/>
-      <c r="AO131" s="3" t="n"/>
-      <c r="AP131" s="3">
+      <c r="AL131" s="13" t="n"/>
+      <c r="AM131" s="13" t="n"/>
+      <c r="AN131" s="13" t="n"/>
+      <c r="AO131" s="13" t="n"/>
+      <c r="AP131" s="12">
         <f>AJ131+AK131</f>
         <v/>
       </c>
@@ -9513,16 +9313,16 @@
       <c r="AG132" s="3" t="n"/>
       <c r="AH132" s="3" t="n"/>
       <c r="AI132" s="3" t="n"/>
-      <c r="AJ132" s="3" t="n"/>
-      <c r="AK132" s="3">
+      <c r="AJ132" s="13" t="n"/>
+      <c r="AK132" s="12">
         <f>SUM(D132:AI132)</f>
         <v/>
       </c>
-      <c r="AL132" s="3" t="n"/>
-      <c r="AM132" s="3" t="n"/>
-      <c r="AN132" s="3" t="n"/>
-      <c r="AO132" s="3" t="n"/>
-      <c r="AP132" s="3">
+      <c r="AL132" s="13" t="n"/>
+      <c r="AM132" s="13" t="n"/>
+      <c r="AN132" s="13" t="n"/>
+      <c r="AO132" s="13" t="n"/>
+      <c r="AP132" s="12">
         <f>AJ132+AK132</f>
         <v/>
       </c>
@@ -9567,16 +9367,16 @@
       <c r="AG133" s="3" t="n"/>
       <c r="AH133" s="3" t="n"/>
       <c r="AI133" s="3" t="n"/>
-      <c r="AJ133" s="3" t="n"/>
-      <c r="AK133" s="3">
+      <c r="AJ133" s="13" t="n"/>
+      <c r="AK133" s="12">
         <f>SUM(D133:AI133)</f>
         <v/>
       </c>
-      <c r="AL133" s="3" t="n"/>
-      <c r="AM133" s="3" t="n"/>
-      <c r="AN133" s="3" t="n"/>
-      <c r="AO133" s="3" t="n"/>
-      <c r="AP133" s="3">
+      <c r="AL133" s="13" t="n"/>
+      <c r="AM133" s="13" t="n"/>
+      <c r="AN133" s="13" t="n"/>
+      <c r="AO133" s="13" t="n"/>
+      <c r="AP133" s="12">
         <f>AJ133+AK133</f>
         <v/>
       </c>
@@ -9621,16 +9421,16 @@
       <c r="AG134" s="3" t="n"/>
       <c r="AH134" s="3" t="n"/>
       <c r="AI134" s="3" t="n"/>
-      <c r="AJ134" s="3" t="n"/>
-      <c r="AK134" s="3">
+      <c r="AJ134" s="13" t="n"/>
+      <c r="AK134" s="12">
         <f>SUM(D134:AI134)</f>
         <v/>
       </c>
-      <c r="AL134" s="3" t="n"/>
-      <c r="AM134" s="3" t="n"/>
-      <c r="AN134" s="3" t="n"/>
-      <c r="AO134" s="3" t="n"/>
-      <c r="AP134" s="3">
+      <c r="AL134" s="13" t="n"/>
+      <c r="AM134" s="13" t="n"/>
+      <c r="AN134" s="13" t="n"/>
+      <c r="AO134" s="13" t="n"/>
+      <c r="AP134" s="12">
         <f>AJ134+AK134</f>
         <v/>
       </c>
@@ -9675,16 +9475,16 @@
       <c r="AG135" s="3" t="n"/>
       <c r="AH135" s="3" t="n"/>
       <c r="AI135" s="3" t="n"/>
-      <c r="AJ135" s="3" t="n"/>
-      <c r="AK135" s="3">
+      <c r="AJ135" s="13" t="n"/>
+      <c r="AK135" s="12">
         <f>SUM(D135:AI135)</f>
         <v/>
       </c>
-      <c r="AL135" s="3" t="n"/>
-      <c r="AM135" s="3" t="n"/>
-      <c r="AN135" s="3" t="n"/>
-      <c r="AO135" s="3" t="n"/>
-      <c r="AP135" s="3">
+      <c r="AL135" s="13" t="n"/>
+      <c r="AM135" s="13" t="n"/>
+      <c r="AN135" s="13" t="n"/>
+      <c r="AO135" s="13" t="n"/>
+      <c r="AP135" s="12">
         <f>AJ135+AK135</f>
         <v/>
       </c>
@@ -9729,16 +9529,16 @@
       <c r="AG136" s="3" t="n"/>
       <c r="AH136" s="3" t="n"/>
       <c r="AI136" s="3" t="n"/>
-      <c r="AJ136" s="3" t="n"/>
-      <c r="AK136" s="3">
+      <c r="AJ136" s="13" t="n"/>
+      <c r="AK136" s="12">
         <f>SUM(D136:AI136)</f>
         <v/>
       </c>
-      <c r="AL136" s="3" t="n"/>
-      <c r="AM136" s="3" t="n"/>
-      <c r="AN136" s="3" t="n"/>
-      <c r="AO136" s="3" t="n"/>
-      <c r="AP136" s="3">
+      <c r="AL136" s="13" t="n"/>
+      <c r="AM136" s="13" t="n"/>
+      <c r="AN136" s="13" t="n"/>
+      <c r="AO136" s="13" t="n"/>
+      <c r="AP136" s="12">
         <f>AJ136+AK136</f>
         <v/>
       </c>
@@ -9783,16 +9583,16 @@
       <c r="AG137" s="3" t="n"/>
       <c r="AH137" s="3" t="n"/>
       <c r="AI137" s="3" t="n"/>
-      <c r="AJ137" s="3" t="n"/>
-      <c r="AK137" s="3">
+      <c r="AJ137" s="13" t="n"/>
+      <c r="AK137" s="12">
         <f>SUM(D137:AI137)</f>
         <v/>
       </c>
-      <c r="AL137" s="3" t="n"/>
-      <c r="AM137" s="3" t="n"/>
-      <c r="AN137" s="3" t="n"/>
-      <c r="AO137" s="3" t="n"/>
-      <c r="AP137" s="3">
+      <c r="AL137" s="13" t="n"/>
+      <c r="AM137" s="13" t="n"/>
+      <c r="AN137" s="13" t="n"/>
+      <c r="AO137" s="13" t="n"/>
+      <c r="AP137" s="12">
         <f>AJ137+AK137</f>
         <v/>
       </c>
@@ -9837,16 +9637,16 @@
       <c r="AG138" s="3" t="n"/>
       <c r="AH138" s="3" t="n"/>
       <c r="AI138" s="3" t="n"/>
-      <c r="AJ138" s="3" t="n"/>
-      <c r="AK138" s="3">
+      <c r="AJ138" s="13" t="n"/>
+      <c r="AK138" s="12">
         <f>SUM(D138:AI138)</f>
         <v/>
       </c>
-      <c r="AL138" s="3" t="n"/>
-      <c r="AM138" s="3" t="n"/>
-      <c r="AN138" s="3" t="n"/>
-      <c r="AO138" s="3" t="n"/>
-      <c r="AP138" s="3">
+      <c r="AL138" s="13" t="n"/>
+      <c r="AM138" s="13" t="n"/>
+      <c r="AN138" s="13" t="n"/>
+      <c r="AO138" s="13" t="n"/>
+      <c r="AP138" s="12">
         <f>AJ138+AK138</f>
         <v/>
       </c>
@@ -9891,16 +9691,16 @@
       <c r="AG139" s="3" t="n"/>
       <c r="AH139" s="3" t="n"/>
       <c r="AI139" s="3" t="n"/>
-      <c r="AJ139" s="3" t="n"/>
-      <c r="AK139" s="3">
+      <c r="AJ139" s="13" t="n"/>
+      <c r="AK139" s="12">
         <f>SUM(D139:AI139)</f>
         <v/>
       </c>
-      <c r="AL139" s="3" t="n"/>
-      <c r="AM139" s="3" t="n"/>
-      <c r="AN139" s="3" t="n"/>
-      <c r="AO139" s="3" t="n"/>
-      <c r="AP139" s="3">
+      <c r="AL139" s="13" t="n"/>
+      <c r="AM139" s="13" t="n"/>
+      <c r="AN139" s="13" t="n"/>
+      <c r="AO139" s="13" t="n"/>
+      <c r="AP139" s="12">
         <f>AJ139+AK139</f>
         <v/>
       </c>
@@ -9945,16 +9745,16 @@
       <c r="AG140" s="3" t="n"/>
       <c r="AH140" s="3" t="n"/>
       <c r="AI140" s="3" t="n"/>
-      <c r="AJ140" s="3" t="n"/>
-      <c r="AK140" s="3">
+      <c r="AJ140" s="13" t="n"/>
+      <c r="AK140" s="12">
         <f>SUM(D140:AI140)</f>
         <v/>
       </c>
-      <c r="AL140" s="3" t="n"/>
-      <c r="AM140" s="3" t="n"/>
-      <c r="AN140" s="3" t="n"/>
-      <c r="AO140" s="3" t="n"/>
-      <c r="AP140" s="3">
+      <c r="AL140" s="13" t="n"/>
+      <c r="AM140" s="13" t="n"/>
+      <c r="AN140" s="13" t="n"/>
+      <c r="AO140" s="13" t="n"/>
+      <c r="AP140" s="12">
         <f>AJ140+AK140</f>
         <v/>
       </c>
@@ -9999,16 +9799,16 @@
       <c r="AG141" s="3" t="n"/>
       <c r="AH141" s="3" t="n"/>
       <c r="AI141" s="3" t="n"/>
-      <c r="AJ141" s="3" t="n"/>
-      <c r="AK141" s="3">
+      <c r="AJ141" s="13" t="n"/>
+      <c r="AK141" s="12">
         <f>SUM(D141:AI141)</f>
         <v/>
       </c>
-      <c r="AL141" s="3" t="n"/>
-      <c r="AM141" s="3" t="n"/>
-      <c r="AN141" s="3" t="n"/>
-      <c r="AO141" s="3" t="n"/>
-      <c r="AP141" s="3">
+      <c r="AL141" s="13" t="n"/>
+      <c r="AM141" s="13" t="n"/>
+      <c r="AN141" s="13" t="n"/>
+      <c r="AO141" s="13" t="n"/>
+      <c r="AP141" s="12">
         <f>AJ141+AK141</f>
         <v/>
       </c>
@@ -10053,16 +9853,16 @@
       <c r="AG142" s="3" t="n"/>
       <c r="AH142" s="3" t="n"/>
       <c r="AI142" s="3" t="n"/>
-      <c r="AJ142" s="3" t="n"/>
-      <c r="AK142" s="3">
+      <c r="AJ142" s="13" t="n"/>
+      <c r="AK142" s="12">
         <f>SUM(D142:AI142)</f>
         <v/>
       </c>
-      <c r="AL142" s="3" t="n"/>
-      <c r="AM142" s="3" t="n"/>
-      <c r="AN142" s="3" t="n"/>
-      <c r="AO142" s="3" t="n"/>
-      <c r="AP142" s="3">
+      <c r="AL142" s="13" t="n"/>
+      <c r="AM142" s="13" t="n"/>
+      <c r="AN142" s="13" t="n"/>
+      <c r="AO142" s="13" t="n"/>
+      <c r="AP142" s="12">
         <f>AJ142+AK142</f>
         <v/>
       </c>
@@ -10107,16 +9907,16 @@
       <c r="AG143" s="3" t="n"/>
       <c r="AH143" s="3" t="n"/>
       <c r="AI143" s="3" t="n"/>
-      <c r="AJ143" s="3" t="n"/>
-      <c r="AK143" s="3">
+      <c r="AJ143" s="13" t="n"/>
+      <c r="AK143" s="12">
         <f>SUM(D143:AI143)</f>
         <v/>
       </c>
-      <c r="AL143" s="3" t="n"/>
-      <c r="AM143" s="3" t="n"/>
-      <c r="AN143" s="3" t="n"/>
-      <c r="AO143" s="3" t="n"/>
-      <c r="AP143" s="3">
+      <c r="AL143" s="13" t="n"/>
+      <c r="AM143" s="13" t="n"/>
+      <c r="AN143" s="13" t="n"/>
+      <c r="AO143" s="13" t="n"/>
+      <c r="AP143" s="12">
         <f>AJ143+AK143</f>
         <v/>
       </c>
@@ -10161,16 +9961,16 @@
       <c r="AG144" s="3" t="n"/>
       <c r="AH144" s="3" t="n"/>
       <c r="AI144" s="3" t="n"/>
-      <c r="AJ144" s="3" t="n"/>
-      <c r="AK144" s="3">
+      <c r="AJ144" s="13" t="n"/>
+      <c r="AK144" s="12">
         <f>SUM(D144:AI144)</f>
         <v/>
       </c>
-      <c r="AL144" s="3" t="n"/>
-      <c r="AM144" s="3" t="n"/>
-      <c r="AN144" s="3" t="n"/>
-      <c r="AO144" s="3" t="n"/>
-      <c r="AP144" s="3">
+      <c r="AL144" s="13" t="n"/>
+      <c r="AM144" s="13" t="n"/>
+      <c r="AN144" s="13" t="n"/>
+      <c r="AO144" s="13" t="n"/>
+      <c r="AP144" s="12">
         <f>AJ144+AK144</f>
         <v/>
       </c>
@@ -10215,16 +10015,16 @@
       <c r="AG145" s="3" t="n"/>
       <c r="AH145" s="3" t="n"/>
       <c r="AI145" s="3" t="n"/>
-      <c r="AJ145" s="3" t="n"/>
-      <c r="AK145" s="3">
+      <c r="AJ145" s="13" t="n"/>
+      <c r="AK145" s="12">
         <f>SUM(D145:AI145)</f>
         <v/>
       </c>
-      <c r="AL145" s="3" t="n"/>
-      <c r="AM145" s="3" t="n"/>
-      <c r="AN145" s="3" t="n"/>
-      <c r="AO145" s="3" t="n"/>
-      <c r="AP145" s="3">
+      <c r="AL145" s="13" t="n"/>
+      <c r="AM145" s="13" t="n"/>
+      <c r="AN145" s="13" t="n"/>
+      <c r="AO145" s="13" t="n"/>
+      <c r="AP145" s="12">
         <f>AJ145+AK145</f>
         <v/>
       </c>
@@ -10269,16 +10069,16 @@
       <c r="AG146" s="3" t="n"/>
       <c r="AH146" s="3" t="n"/>
       <c r="AI146" s="3" t="n"/>
-      <c r="AJ146" s="3" t="n"/>
-      <c r="AK146" s="3">
+      <c r="AJ146" s="13" t="n"/>
+      <c r="AK146" s="12">
         <f>SUM(D146:AI146)</f>
         <v/>
       </c>
-      <c r="AL146" s="3" t="n"/>
-      <c r="AM146" s="3" t="n"/>
-      <c r="AN146" s="3" t="n"/>
-      <c r="AO146" s="3" t="n"/>
-      <c r="AP146" s="3">
+      <c r="AL146" s="13" t="n"/>
+      <c r="AM146" s="13" t="n"/>
+      <c r="AN146" s="13" t="n"/>
+      <c r="AO146" s="13" t="n"/>
+      <c r="AP146" s="12">
         <f>AJ146+AK146</f>
         <v/>
       </c>
@@ -10323,16 +10123,16 @@
       <c r="AG147" s="3" t="n"/>
       <c r="AH147" s="3" t="n"/>
       <c r="AI147" s="3" t="n"/>
-      <c r="AJ147" s="3" t="n"/>
-      <c r="AK147" s="3">
+      <c r="AJ147" s="13" t="n"/>
+      <c r="AK147" s="12">
         <f>SUM(D147:AI147)</f>
         <v/>
       </c>
-      <c r="AL147" s="3" t="n"/>
-      <c r="AM147" s="3" t="n"/>
-      <c r="AN147" s="3" t="n"/>
-      <c r="AO147" s="3" t="n"/>
-      <c r="AP147" s="3">
+      <c r="AL147" s="13" t="n"/>
+      <c r="AM147" s="13" t="n"/>
+      <c r="AN147" s="13" t="n"/>
+      <c r="AO147" s="13" t="n"/>
+      <c r="AP147" s="12">
         <f>AJ147+AK147</f>
         <v/>
       </c>
@@ -10377,16 +10177,16 @@
       <c r="AG148" s="3" t="n"/>
       <c r="AH148" s="3" t="n"/>
       <c r="AI148" s="3" t="n"/>
-      <c r="AJ148" s="3" t="n"/>
-      <c r="AK148" s="3">
+      <c r="AJ148" s="13" t="n"/>
+      <c r="AK148" s="12">
         <f>SUM(D148:AI148)</f>
         <v/>
       </c>
-      <c r="AL148" s="3" t="n"/>
-      <c r="AM148" s="3" t="n"/>
-      <c r="AN148" s="3" t="n"/>
-      <c r="AO148" s="3" t="n"/>
-      <c r="AP148" s="3">
+      <c r="AL148" s="13" t="n"/>
+      <c r="AM148" s="13" t="n"/>
+      <c r="AN148" s="13" t="n"/>
+      <c r="AO148" s="13" t="n"/>
+      <c r="AP148" s="12">
         <f>AJ148+AK148</f>
         <v/>
       </c>
@@ -10431,16 +10231,16 @@
       <c r="AG149" s="3" t="n"/>
       <c r="AH149" s="3" t="n"/>
       <c r="AI149" s="3" t="n"/>
-      <c r="AJ149" s="3" t="n"/>
-      <c r="AK149" s="3">
+      <c r="AJ149" s="13" t="n"/>
+      <c r="AK149" s="12">
         <f>SUM(D149:AI149)</f>
         <v/>
       </c>
-      <c r="AL149" s="3" t="n"/>
-      <c r="AM149" s="3" t="n"/>
-      <c r="AN149" s="3" t="n"/>
-      <c r="AO149" s="3" t="n"/>
-      <c r="AP149" s="3">
+      <c r="AL149" s="13" t="n"/>
+      <c r="AM149" s="13" t="n"/>
+      <c r="AN149" s="13" t="n"/>
+      <c r="AO149" s="13" t="n"/>
+      <c r="AP149" s="12">
         <f>AJ149+AK149</f>
         <v/>
       </c>
@@ -10485,16 +10285,16 @@
       <c r="AG150" s="3" t="n"/>
       <c r="AH150" s="3" t="n"/>
       <c r="AI150" s="3" t="n"/>
-      <c r="AJ150" s="3" t="n"/>
-      <c r="AK150" s="3">
+      <c r="AJ150" s="13" t="n"/>
+      <c r="AK150" s="12">
         <f>SUM(D150:AI150)</f>
         <v/>
       </c>
-      <c r="AL150" s="3" t="n"/>
-      <c r="AM150" s="3" t="n"/>
-      <c r="AN150" s="3" t="n"/>
-      <c r="AO150" s="3" t="n"/>
-      <c r="AP150" s="3">
+      <c r="AL150" s="13" t="n"/>
+      <c r="AM150" s="13" t="n"/>
+      <c r="AN150" s="13" t="n"/>
+      <c r="AO150" s="13" t="n"/>
+      <c r="AP150" s="12">
         <f>AJ150+AK150</f>
         <v/>
       </c>
@@ -10539,16 +10339,16 @@
       <c r="AG151" s="3" t="n"/>
       <c r="AH151" s="3" t="n"/>
       <c r="AI151" s="3" t="n"/>
-      <c r="AJ151" s="3" t="n"/>
-      <c r="AK151" s="3">
+      <c r="AJ151" s="13" t="n"/>
+      <c r="AK151" s="12">
         <f>SUM(D151:AI151)</f>
         <v/>
       </c>
-      <c r="AL151" s="3" t="n"/>
-      <c r="AM151" s="3" t="n"/>
-      <c r="AN151" s="3" t="n"/>
-      <c r="AO151" s="3" t="n"/>
-      <c r="AP151" s="3">
+      <c r="AL151" s="13" t="n"/>
+      <c r="AM151" s="13" t="n"/>
+      <c r="AN151" s="13" t="n"/>
+      <c r="AO151" s="13" t="n"/>
+      <c r="AP151" s="12">
         <f>AJ151+AK151</f>
         <v/>
       </c>
@@ -10593,16 +10393,16 @@
       <c r="AG152" s="3" t="n"/>
       <c r="AH152" s="3" t="n"/>
       <c r="AI152" s="3" t="n"/>
-      <c r="AJ152" s="3" t="n"/>
-      <c r="AK152" s="3">
+      <c r="AJ152" s="13" t="n"/>
+      <c r="AK152" s="12">
         <f>SUM(D152:AI152)</f>
         <v/>
       </c>
-      <c r="AL152" s="3" t="n"/>
-      <c r="AM152" s="3" t="n"/>
-      <c r="AN152" s="3" t="n"/>
-      <c r="AO152" s="3" t="n"/>
-      <c r="AP152" s="3">
+      <c r="AL152" s="13" t="n"/>
+      <c r="AM152" s="13" t="n"/>
+      <c r="AN152" s="13" t="n"/>
+      <c r="AO152" s="13" t="n"/>
+      <c r="AP152" s="12">
         <f>AJ152+AK152</f>
         <v/>
       </c>
@@ -10647,16 +10447,16 @@
       <c r="AG153" s="3" t="n"/>
       <c r="AH153" s="3" t="n"/>
       <c r="AI153" s="3" t="n"/>
-      <c r="AJ153" s="3" t="n"/>
-      <c r="AK153" s="3">
+      <c r="AJ153" s="13" t="n"/>
+      <c r="AK153" s="12">
         <f>SUM(D153:AI153)</f>
         <v/>
       </c>
-      <c r="AL153" s="3" t="n"/>
-      <c r="AM153" s="3" t="n"/>
-      <c r="AN153" s="3" t="n"/>
-      <c r="AO153" s="3" t="n"/>
-      <c r="AP153" s="3">
+      <c r="AL153" s="13" t="n"/>
+      <c r="AM153" s="13" t="n"/>
+      <c r="AN153" s="13" t="n"/>
+      <c r="AO153" s="13" t="n"/>
+      <c r="AP153" s="12">
         <f>AJ153+AK153</f>
         <v/>
       </c>
@@ -10701,16 +10501,16 @@
       <c r="AG154" s="3" t="n"/>
       <c r="AH154" s="3" t="n"/>
       <c r="AI154" s="3" t="n"/>
-      <c r="AJ154" s="3" t="n"/>
-      <c r="AK154" s="3">
+      <c r="AJ154" s="13" t="n"/>
+      <c r="AK154" s="12">
         <f>SUM(D154:AI154)</f>
         <v/>
       </c>
-      <c r="AL154" s="3" t="n"/>
-      <c r="AM154" s="3" t="n"/>
-      <c r="AN154" s="3" t="n"/>
-      <c r="AO154" s="3" t="n"/>
-      <c r="AP154" s="3">
+      <c r="AL154" s="13" t="n"/>
+      <c r="AM154" s="13" t="n"/>
+      <c r="AN154" s="13" t="n"/>
+      <c r="AO154" s="13" t="n"/>
+      <c r="AP154" s="12">
         <f>AJ154+AK154</f>
         <v/>
       </c>
@@ -10755,16 +10555,16 @@
       <c r="AG155" s="3" t="n"/>
       <c r="AH155" s="3" t="n"/>
       <c r="AI155" s="3" t="n"/>
-      <c r="AJ155" s="3" t="n"/>
-      <c r="AK155" s="3">
+      <c r="AJ155" s="13" t="n"/>
+      <c r="AK155" s="12">
         <f>SUM(D155:AI155)</f>
         <v/>
       </c>
-      <c r="AL155" s="3" t="n"/>
-      <c r="AM155" s="3" t="n"/>
-      <c r="AN155" s="3" t="n"/>
-      <c r="AO155" s="3" t="n"/>
-      <c r="AP155" s="3">
+      <c r="AL155" s="13" t="n"/>
+      <c r="AM155" s="13" t="n"/>
+      <c r="AN155" s="13" t="n"/>
+      <c r="AO155" s="13" t="n"/>
+      <c r="AP155" s="12">
         <f>AJ155+AK155</f>
         <v/>
       </c>
@@ -10809,16 +10609,16 @@
       <c r="AG156" s="3" t="n"/>
       <c r="AH156" s="3" t="n"/>
       <c r="AI156" s="3" t="n"/>
-      <c r="AJ156" s="3" t="n"/>
-      <c r="AK156" s="3">
+      <c r="AJ156" s="13" t="n"/>
+      <c r="AK156" s="12">
         <f>SUM(D156:AI156)</f>
         <v/>
       </c>
-      <c r="AL156" s="3" t="n"/>
-      <c r="AM156" s="3" t="n"/>
-      <c r="AN156" s="3" t="n"/>
-      <c r="AO156" s="3" t="n"/>
-      <c r="AP156" s="3">
+      <c r="AL156" s="13" t="n"/>
+      <c r="AM156" s="13" t="n"/>
+      <c r="AN156" s="13" t="n"/>
+      <c r="AO156" s="13" t="n"/>
+      <c r="AP156" s="12">
         <f>AJ156+AK156</f>
         <v/>
       </c>
@@ -10863,16 +10663,16 @@
       <c r="AG157" s="3" t="n"/>
       <c r="AH157" s="3" t="n"/>
       <c r="AI157" s="3" t="n"/>
-      <c r="AJ157" s="3" t="n"/>
-      <c r="AK157" s="3">
+      <c r="AJ157" s="13" t="n"/>
+      <c r="AK157" s="12">
         <f>SUM(D157:AI157)</f>
         <v/>
       </c>
-      <c r="AL157" s="3" t="n"/>
-      <c r="AM157" s="3" t="n"/>
-      <c r="AN157" s="3" t="n"/>
-      <c r="AO157" s="3" t="n"/>
-      <c r="AP157" s="3">
+      <c r="AL157" s="13" t="n"/>
+      <c r="AM157" s="13" t="n"/>
+      <c r="AN157" s="13" t="n"/>
+      <c r="AO157" s="13" t="n"/>
+      <c r="AP157" s="12">
         <f>AJ157+AK157</f>
         <v/>
       </c>
@@ -10917,16 +10717,16 @@
       <c r="AG158" s="3" t="n"/>
       <c r="AH158" s="3" t="n"/>
       <c r="AI158" s="3" t="n"/>
-      <c r="AJ158" s="3" t="n"/>
-      <c r="AK158" s="3">
+      <c r="AJ158" s="13" t="n"/>
+      <c r="AK158" s="12">
         <f>SUM(D158:AI158)</f>
         <v/>
       </c>
-      <c r="AL158" s="3" t="n"/>
-      <c r="AM158" s="3" t="n"/>
-      <c r="AN158" s="3" t="n"/>
-      <c r="AO158" s="3" t="n"/>
-      <c r="AP158" s="3">
+      <c r="AL158" s="13" t="n"/>
+      <c r="AM158" s="13" t="n"/>
+      <c r="AN158" s="13" t="n"/>
+      <c r="AO158" s="13" t="n"/>
+      <c r="AP158" s="12">
         <f>AJ158+AK158</f>
         <v/>
       </c>
@@ -10971,16 +10771,16 @@
       <c r="AG159" s="3" t="n"/>
       <c r="AH159" s="3" t="n"/>
       <c r="AI159" s="3" t="n"/>
-      <c r="AJ159" s="3" t="n"/>
-      <c r="AK159" s="3">
+      <c r="AJ159" s="13" t="n"/>
+      <c r="AK159" s="12">
         <f>SUM(D159:AI159)</f>
         <v/>
       </c>
-      <c r="AL159" s="3" t="n"/>
-      <c r="AM159" s="3" t="n"/>
-      <c r="AN159" s="3" t="n"/>
-      <c r="AO159" s="3" t="n"/>
-      <c r="AP159" s="3">
+      <c r="AL159" s="13" t="n"/>
+      <c r="AM159" s="13" t="n"/>
+      <c r="AN159" s="13" t="n"/>
+      <c r="AO159" s="13" t="n"/>
+      <c r="AP159" s="12">
         <f>AJ159+AK159</f>
         <v/>
       </c>
@@ -11025,16 +10825,16 @@
       <c r="AG160" s="3" t="n"/>
       <c r="AH160" s="3" t="n"/>
       <c r="AI160" s="3" t="n"/>
-      <c r="AJ160" s="3" t="n"/>
-      <c r="AK160" s="3">
+      <c r="AJ160" s="13" t="n"/>
+      <c r="AK160" s="12">
         <f>SUM(D160:AI160)</f>
         <v/>
       </c>
-      <c r="AL160" s="3" t="n"/>
-      <c r="AM160" s="3" t="n"/>
-      <c r="AN160" s="3" t="n"/>
-      <c r="AO160" s="3" t="n"/>
-      <c r="AP160" s="3">
+      <c r="AL160" s="13" t="n"/>
+      <c r="AM160" s="13" t="n"/>
+      <c r="AN160" s="13" t="n"/>
+      <c r="AO160" s="13" t="n"/>
+      <c r="AP160" s="12">
         <f>AJ160+AK160</f>
         <v/>
       </c>
@@ -11079,16 +10879,16 @@
       <c r="AG161" s="3" t="n"/>
       <c r="AH161" s="3" t="n"/>
       <c r="AI161" s="3" t="n"/>
-      <c r="AJ161" s="3" t="n"/>
-      <c r="AK161" s="3">
+      <c r="AJ161" s="13" t="n"/>
+      <c r="AK161" s="12">
         <f>SUM(D161:AI161)</f>
         <v/>
       </c>
-      <c r="AL161" s="3" t="n"/>
-      <c r="AM161" s="3" t="n"/>
-      <c r="AN161" s="3" t="n"/>
-      <c r="AO161" s="3" t="n"/>
-      <c r="AP161" s="3">
+      <c r="AL161" s="13" t="n"/>
+      <c r="AM161" s="13" t="n"/>
+      <c r="AN161" s="13" t="n"/>
+      <c r="AO161" s="13" t="n"/>
+      <c r="AP161" s="12">
         <f>AJ161+AK161</f>
         <v/>
       </c>
@@ -11133,16 +10933,16 @@
       <c r="AG162" s="3" t="n"/>
       <c r="AH162" s="3" t="n"/>
       <c r="AI162" s="3" t="n"/>
-      <c r="AJ162" s="3" t="n"/>
-      <c r="AK162" s="3">
+      <c r="AJ162" s="13" t="n"/>
+      <c r="AK162" s="12">
         <f>SUM(D162:AI162)</f>
         <v/>
       </c>
-      <c r="AL162" s="3" t="n"/>
-      <c r="AM162" s="3" t="n"/>
-      <c r="AN162" s="3" t="n"/>
-      <c r="AO162" s="3" t="n"/>
-      <c r="AP162" s="3">
+      <c r="AL162" s="13" t="n"/>
+      <c r="AM162" s="13" t="n"/>
+      <c r="AN162" s="13" t="n"/>
+      <c r="AO162" s="13" t="n"/>
+      <c r="AP162" s="12">
         <f>AJ162+AK162</f>
         <v/>
       </c>
@@ -11187,16 +10987,16 @@
       <c r="AG163" s="3" t="n"/>
       <c r="AH163" s="3" t="n"/>
       <c r="AI163" s="3" t="n"/>
-      <c r="AJ163" s="3" t="n"/>
-      <c r="AK163" s="3">
+      <c r="AJ163" s="13" t="n"/>
+      <c r="AK163" s="12">
         <f>SUM(D163:AI163)</f>
         <v/>
       </c>
-      <c r="AL163" s="3" t="n"/>
-      <c r="AM163" s="3" t="n"/>
-      <c r="AN163" s="3" t="n"/>
-      <c r="AO163" s="3" t="n"/>
-      <c r="AP163" s="3">
+      <c r="AL163" s="13" t="n"/>
+      <c r="AM163" s="13" t="n"/>
+      <c r="AN163" s="13" t="n"/>
+      <c r="AO163" s="13" t="n"/>
+      <c r="AP163" s="12">
         <f>AJ163+AK163</f>
         <v/>
       </c>
@@ -11241,16 +11041,16 @@
       <c r="AG164" s="3" t="n"/>
       <c r="AH164" s="3" t="n"/>
       <c r="AI164" s="3" t="n"/>
-      <c r="AJ164" s="3" t="n"/>
-      <c r="AK164" s="3">
+      <c r="AJ164" s="13" t="n"/>
+      <c r="AK164" s="12">
         <f>SUM(D164:AI164)</f>
         <v/>
       </c>
-      <c r="AL164" s="3" t="n"/>
-      <c r="AM164" s="3" t="n"/>
-      <c r="AN164" s="3" t="n"/>
-      <c r="AO164" s="3" t="n"/>
-      <c r="AP164" s="3">
+      <c r="AL164" s="13" t="n"/>
+      <c r="AM164" s="13" t="n"/>
+      <c r="AN164" s="13" t="n"/>
+      <c r="AO164" s="13" t="n"/>
+      <c r="AP164" s="12">
         <f>AJ164+AK164</f>
         <v/>
       </c>
@@ -11295,16 +11095,16 @@
       <c r="AG165" s="3" t="n"/>
       <c r="AH165" s="3" t="n"/>
       <c r="AI165" s="3" t="n"/>
-      <c r="AJ165" s="3" t="n"/>
-      <c r="AK165" s="3">
+      <c r="AJ165" s="13" t="n"/>
+      <c r="AK165" s="12">
         <f>SUM(D165:AI165)</f>
         <v/>
       </c>
-      <c r="AL165" s="3" t="n"/>
-      <c r="AM165" s="3" t="n"/>
-      <c r="AN165" s="3" t="n"/>
-      <c r="AO165" s="3" t="n"/>
-      <c r="AP165" s="3">
+      <c r="AL165" s="13" t="n"/>
+      <c r="AM165" s="13" t="n"/>
+      <c r="AN165" s="13" t="n"/>
+      <c r="AO165" s="13" t="n"/>
+      <c r="AP165" s="12">
         <f>AJ165+AK165</f>
         <v/>
       </c>
@@ -11349,16 +11149,16 @@
       <c r="AG166" s="3" t="n"/>
       <c r="AH166" s="3" t="n"/>
       <c r="AI166" s="3" t="n"/>
-      <c r="AJ166" s="3" t="n"/>
-      <c r="AK166" s="3">
+      <c r="AJ166" s="13" t="n"/>
+      <c r="AK166" s="12">
         <f>SUM(D166:AI166)</f>
         <v/>
       </c>
-      <c r="AL166" s="3" t="n"/>
-      <c r="AM166" s="3" t="n"/>
-      <c r="AN166" s="3" t="n"/>
-      <c r="AO166" s="3" t="n"/>
-      <c r="AP166" s="3">
+      <c r="AL166" s="13" t="n"/>
+      <c r="AM166" s="13" t="n"/>
+      <c r="AN166" s="13" t="n"/>
+      <c r="AO166" s="13" t="n"/>
+      <c r="AP166" s="12">
         <f>AJ166+AK166</f>
         <v/>
       </c>
@@ -11403,16 +11203,16 @@
       <c r="AG167" s="3" t="n"/>
       <c r="AH167" s="3" t="n"/>
       <c r="AI167" s="3" t="n"/>
-      <c r="AJ167" s="3" t="n"/>
-      <c r="AK167" s="3">
+      <c r="AJ167" s="13" t="n"/>
+      <c r="AK167" s="12">
         <f>SUM(D167:AI167)</f>
         <v/>
       </c>
-      <c r="AL167" s="3" t="n"/>
-      <c r="AM167" s="3" t="n"/>
-      <c r="AN167" s="3" t="n"/>
-      <c r="AO167" s="3" t="n"/>
-      <c r="AP167" s="3">
+      <c r="AL167" s="13" t="n"/>
+      <c r="AM167" s="13" t="n"/>
+      <c r="AN167" s="13" t="n"/>
+      <c r="AO167" s="13" t="n"/>
+      <c r="AP167" s="12">
         <f>AJ167+AK167</f>
         <v/>
       </c>
@@ -11457,16 +11257,16 @@
       <c r="AG168" s="3" t="n"/>
       <c r="AH168" s="3" t="n"/>
       <c r="AI168" s="3" t="n"/>
-      <c r="AJ168" s="3" t="n"/>
-      <c r="AK168" s="3">
+      <c r="AJ168" s="13" t="n"/>
+      <c r="AK168" s="12">
         <f>SUM(D168:AI168)</f>
         <v/>
       </c>
-      <c r="AL168" s="3" t="n"/>
-      <c r="AM168" s="3" t="n"/>
-      <c r="AN168" s="3" t="n"/>
-      <c r="AO168" s="3" t="n"/>
-      <c r="AP168" s="3">
+      <c r="AL168" s="13" t="n"/>
+      <c r="AM168" s="13" t="n"/>
+      <c r="AN168" s="13" t="n"/>
+      <c r="AO168" s="13" t="n"/>
+      <c r="AP168" s="12">
         <f>AJ168+AK168</f>
         <v/>
       </c>
@@ -11511,16 +11311,16 @@
       <c r="AG169" s="3" t="n"/>
       <c r="AH169" s="3" t="n"/>
       <c r="AI169" s="3" t="n"/>
-      <c r="AJ169" s="3" t="n"/>
-      <c r="AK169" s="3">
+      <c r="AJ169" s="13" t="n"/>
+      <c r="AK169" s="12">
         <f>SUM(D169:AI169)</f>
         <v/>
       </c>
-      <c r="AL169" s="3" t="n"/>
-      <c r="AM169" s="3" t="n"/>
-      <c r="AN169" s="3" t="n"/>
-      <c r="AO169" s="3" t="n"/>
-      <c r="AP169" s="3">
+      <c r="AL169" s="13" t="n"/>
+      <c r="AM169" s="13" t="n"/>
+      <c r="AN169" s="13" t="n"/>
+      <c r="AO169" s="13" t="n"/>
+      <c r="AP169" s="12">
         <f>AJ169+AK169</f>
         <v/>
       </c>
@@ -11565,16 +11365,16 @@
       <c r="AG170" s="3" t="n"/>
       <c r="AH170" s="3" t="n"/>
       <c r="AI170" s="3" t="n"/>
-      <c r="AJ170" s="3" t="n"/>
-      <c r="AK170" s="3">
+      <c r="AJ170" s="13" t="n"/>
+      <c r="AK170" s="12">
         <f>SUM(D170:AI170)</f>
         <v/>
       </c>
-      <c r="AL170" s="3" t="n"/>
-      <c r="AM170" s="3" t="n"/>
-      <c r="AN170" s="3" t="n"/>
-      <c r="AO170" s="3" t="n"/>
-      <c r="AP170" s="3">
+      <c r="AL170" s="13" t="n"/>
+      <c r="AM170" s="13" t="n"/>
+      <c r="AN170" s="13" t="n"/>
+      <c r="AO170" s="13" t="n"/>
+      <c r="AP170" s="12">
         <f>AJ170+AK170</f>
         <v/>
       </c>
@@ -11619,16 +11419,16 @@
       <c r="AG171" s="3" t="n"/>
       <c r="AH171" s="3" t="n"/>
       <c r="AI171" s="3" t="n"/>
-      <c r="AJ171" s="3" t="n"/>
-      <c r="AK171" s="3">
+      <c r="AJ171" s="13" t="n"/>
+      <c r="AK171" s="12">
         <f>SUM(D171:AI171)</f>
         <v/>
       </c>
-      <c r="AL171" s="3" t="n"/>
-      <c r="AM171" s="3" t="n"/>
-      <c r="AN171" s="3" t="n"/>
-      <c r="AO171" s="3" t="n"/>
-      <c r="AP171" s="3">
+      <c r="AL171" s="13" t="n"/>
+      <c r="AM171" s="13" t="n"/>
+      <c r="AN171" s="13" t="n"/>
+      <c r="AO171" s="13" t="n"/>
+      <c r="AP171" s="12">
         <f>AJ171+AK171</f>
         <v/>
       </c>
@@ -11673,16 +11473,16 @@
       <c r="AG172" s="3" t="n"/>
       <c r="AH172" s="3" t="n"/>
       <c r="AI172" s="3" t="n"/>
-      <c r="AJ172" s="3" t="n"/>
-      <c r="AK172" s="3">
+      <c r="AJ172" s="13" t="n"/>
+      <c r="AK172" s="12">
         <f>SUM(D172:AI172)</f>
         <v/>
       </c>
-      <c r="AL172" s="3" t="n"/>
-      <c r="AM172" s="3" t="n"/>
-      <c r="AN172" s="3" t="n"/>
-      <c r="AO172" s="3" t="n"/>
-      <c r="AP172" s="3">
+      <c r="AL172" s="13" t="n"/>
+      <c r="AM172" s="13" t="n"/>
+      <c r="AN172" s="13" t="n"/>
+      <c r="AO172" s="13" t="n"/>
+      <c r="AP172" s="12">
         <f>AJ172+AK172</f>
         <v/>
       </c>
@@ -11727,16 +11527,16 @@
       <c r="AG173" s="3" t="n"/>
       <c r="AH173" s="3" t="n"/>
       <c r="AI173" s="3" t="n"/>
-      <c r="AJ173" s="3" t="n"/>
-      <c r="AK173" s="3">
+      <c r="AJ173" s="13" t="n"/>
+      <c r="AK173" s="12">
         <f>SUM(D173:AI173)</f>
         <v/>
       </c>
-      <c r="AL173" s="3" t="n"/>
-      <c r="AM173" s="3" t="n"/>
-      <c r="AN173" s="3" t="n"/>
-      <c r="AO173" s="3" t="n"/>
-      <c r="AP173" s="3">
+      <c r="AL173" s="13" t="n"/>
+      <c r="AM173" s="13" t="n"/>
+      <c r="AN173" s="13" t="n"/>
+      <c r="AO173" s="13" t="n"/>
+      <c r="AP173" s="12">
         <f>AJ173+AK173</f>
         <v/>
       </c>
@@ -11781,16 +11581,16 @@
       <c r="AG174" s="3" t="n"/>
       <c r="AH174" s="3" t="n"/>
       <c r="AI174" s="3" t="n"/>
-      <c r="AJ174" s="3" t="n"/>
-      <c r="AK174" s="3">
+      <c r="AJ174" s="13" t="n"/>
+      <c r="AK174" s="12">
         <f>SUM(D174:AI174)</f>
         <v/>
       </c>
-      <c r="AL174" s="3" t="n"/>
-      <c r="AM174" s="3" t="n"/>
-      <c r="AN174" s="3" t="n"/>
-      <c r="AO174" s="3" t="n"/>
-      <c r="AP174" s="3">
+      <c r="AL174" s="13" t="n"/>
+      <c r="AM174" s="13" t="n"/>
+      <c r="AN174" s="13" t="n"/>
+      <c r="AO174" s="13" t="n"/>
+      <c r="AP174" s="12">
         <f>AJ174+AK174</f>
         <v/>
       </c>
@@ -11835,16 +11635,16 @@
       <c r="AG175" s="3" t="n"/>
       <c r="AH175" s="3" t="n"/>
       <c r="AI175" s="3" t="n"/>
-      <c r="AJ175" s="3" t="n"/>
-      <c r="AK175" s="3">
+      <c r="AJ175" s="13" t="n"/>
+      <c r="AK175" s="12">
         <f>SUM(D175:AI175)</f>
         <v/>
       </c>
-      <c r="AL175" s="3" t="n"/>
-      <c r="AM175" s="3" t="n"/>
-      <c r="AN175" s="3" t="n"/>
-      <c r="AO175" s="3" t="n"/>
-      <c r="AP175" s="3">
+      <c r="AL175" s="13" t="n"/>
+      <c r="AM175" s="13" t="n"/>
+      <c r="AN175" s="13" t="n"/>
+      <c r="AO175" s="13" t="n"/>
+      <c r="AP175" s="12">
         <f>AJ175+AK175</f>
         <v/>
       </c>
@@ -11889,16 +11689,16 @@
       <c r="AG176" s="3" t="n"/>
       <c r="AH176" s="3" t="n"/>
       <c r="AI176" s="3" t="n"/>
-      <c r="AJ176" s="3" t="n"/>
-      <c r="AK176" s="3">
+      <c r="AJ176" s="13" t="n"/>
+      <c r="AK176" s="12">
         <f>SUM(D176:AI176)</f>
         <v/>
       </c>
-      <c r="AL176" s="3" t="n"/>
-      <c r="AM176" s="3" t="n"/>
-      <c r="AN176" s="3" t="n"/>
-      <c r="AO176" s="3" t="n"/>
-      <c r="AP176" s="3">
+      <c r="AL176" s="13" t="n"/>
+      <c r="AM176" s="13" t="n"/>
+      <c r="AN176" s="13" t="n"/>
+      <c r="AO176" s="13" t="n"/>
+      <c r="AP176" s="12">
         <f>AJ176+AK176</f>
         <v/>
       </c>
@@ -11943,16 +11743,16 @@
       <c r="AG177" s="3" t="n"/>
       <c r="AH177" s="3" t="n"/>
       <c r="AI177" s="3" t="n"/>
-      <c r="AJ177" s="3" t="n"/>
-      <c r="AK177" s="3">
+      <c r="AJ177" s="13" t="n"/>
+      <c r="AK177" s="12">
         <f>SUM(D177:AI177)</f>
         <v/>
       </c>
-      <c r="AL177" s="3" t="n"/>
-      <c r="AM177" s="3" t="n"/>
-      <c r="AN177" s="3" t="n"/>
-      <c r="AO177" s="3" t="n"/>
-      <c r="AP177" s="3">
+      <c r="AL177" s="13" t="n"/>
+      <c r="AM177" s="13" t="n"/>
+      <c r="AN177" s="13" t="n"/>
+      <c r="AO177" s="13" t="n"/>
+      <c r="AP177" s="12">
         <f>AJ177+AK177</f>
         <v/>
       </c>
@@ -11997,16 +11797,16 @@
       <c r="AG178" s="3" t="n"/>
       <c r="AH178" s="3" t="n"/>
       <c r="AI178" s="3" t="n"/>
-      <c r="AJ178" s="3" t="n"/>
-      <c r="AK178" s="3">
+      <c r="AJ178" s="13" t="n"/>
+      <c r="AK178" s="12">
         <f>SUM(D178:AI178)</f>
         <v/>
       </c>
-      <c r="AL178" s="3" t="n"/>
-      <c r="AM178" s="3" t="n"/>
-      <c r="AN178" s="3" t="n"/>
-      <c r="AO178" s="3" t="n"/>
-      <c r="AP178" s="3">
+      <c r="AL178" s="13" t="n"/>
+      <c r="AM178" s="13" t="n"/>
+      <c r="AN178" s="13" t="n"/>
+      <c r="AO178" s="13" t="n"/>
+      <c r="AP178" s="12">
         <f>AJ178+AK178</f>
         <v/>
       </c>
@@ -12051,16 +11851,16 @@
       <c r="AG179" s="3" t="n"/>
       <c r="AH179" s="3" t="n"/>
       <c r="AI179" s="3" t="n"/>
-      <c r="AJ179" s="3" t="n"/>
-      <c r="AK179" s="3">
+      <c r="AJ179" s="13" t="n"/>
+      <c r="AK179" s="12">
         <f>SUM(D179:AI179)</f>
         <v/>
       </c>
-      <c r="AL179" s="3" t="n"/>
-      <c r="AM179" s="3" t="n"/>
-      <c r="AN179" s="3" t="n"/>
-      <c r="AO179" s="3" t="n"/>
-      <c r="AP179" s="3">
+      <c r="AL179" s="13" t="n"/>
+      <c r="AM179" s="13" t="n"/>
+      <c r="AN179" s="13" t="n"/>
+      <c r="AO179" s="13" t="n"/>
+      <c r="AP179" s="12">
         <f>AJ179+AK179</f>
         <v/>
       </c>
@@ -12105,16 +11905,16 @@
       <c r="AG180" s="3" t="n"/>
       <c r="AH180" s="3" t="n"/>
       <c r="AI180" s="3" t="n"/>
-      <c r="AJ180" s="3" t="n"/>
-      <c r="AK180" s="3">
+      <c r="AJ180" s="13" t="n"/>
+      <c r="AK180" s="12">
         <f>SUM(D180:AI180)</f>
         <v/>
       </c>
-      <c r="AL180" s="3" t="n"/>
-      <c r="AM180" s="3" t="n"/>
-      <c r="AN180" s="3" t="n"/>
-      <c r="AO180" s="3" t="n"/>
-      <c r="AP180" s="3">
+      <c r="AL180" s="13" t="n"/>
+      <c r="AM180" s="13" t="n"/>
+      <c r="AN180" s="13" t="n"/>
+      <c r="AO180" s="13" t="n"/>
+      <c r="AP180" s="12">
         <f>AJ180+AK180</f>
         <v/>
       </c>
@@ -12159,16 +11959,16 @@
       <c r="AG181" s="3" t="n"/>
       <c r="AH181" s="3" t="n"/>
       <c r="AI181" s="3" t="n"/>
-      <c r="AJ181" s="3" t="n"/>
-      <c r="AK181" s="3">
+      <c r="AJ181" s="13" t="n"/>
+      <c r="AK181" s="12">
         <f>SUM(D181:AI181)</f>
         <v/>
       </c>
-      <c r="AL181" s="3" t="n"/>
-      <c r="AM181" s="3" t="n"/>
-      <c r="AN181" s="3" t="n"/>
-      <c r="AO181" s="3" t="n"/>
-      <c r="AP181" s="3">
+      <c r="AL181" s="13" t="n"/>
+      <c r="AM181" s="13" t="n"/>
+      <c r="AN181" s="13" t="n"/>
+      <c r="AO181" s="13" t="n"/>
+      <c r="AP181" s="12">
         <f>AJ181+AK181</f>
         <v/>
       </c>
@@ -12213,16 +12013,16 @@
       <c r="AG182" s="3" t="n"/>
       <c r="AH182" s="3" t="n"/>
       <c r="AI182" s="3" t="n"/>
-      <c r="AJ182" s="3" t="n"/>
-      <c r="AK182" s="3">
+      <c r="AJ182" s="13" t="n"/>
+      <c r="AK182" s="12">
         <f>SUM(D182:AI182)</f>
         <v/>
       </c>
-      <c r="AL182" s="3" t="n"/>
-      <c r="AM182" s="3" t="n"/>
-      <c r="AN182" s="3" t="n"/>
-      <c r="AO182" s="3" t="n"/>
-      <c r="AP182" s="3">
+      <c r="AL182" s="13" t="n"/>
+      <c r="AM182" s="13" t="n"/>
+      <c r="AN182" s="13" t="n"/>
+      <c r="AO182" s="13" t="n"/>
+      <c r="AP182" s="12">
         <f>AJ182+AK182</f>
         <v/>
       </c>
@@ -12267,16 +12067,16 @@
       <c r="AG183" s="3" t="n"/>
       <c r="AH183" s="3" t="n"/>
       <c r="AI183" s="3" t="n"/>
-      <c r="AJ183" s="3" t="n"/>
-      <c r="AK183" s="3">
+      <c r="AJ183" s="13" t="n"/>
+      <c r="AK183" s="12">
         <f>SUM(D183:AI183)</f>
         <v/>
       </c>
-      <c r="AL183" s="3" t="n"/>
-      <c r="AM183" s="3" t="n"/>
-      <c r="AN183" s="3" t="n"/>
-      <c r="AO183" s="3" t="n"/>
-      <c r="AP183" s="3">
+      <c r="AL183" s="13" t="n"/>
+      <c r="AM183" s="13" t="n"/>
+      <c r="AN183" s="13" t="n"/>
+      <c r="AO183" s="13" t="n"/>
+      <c r="AP183" s="12">
         <f>AJ183+AK183</f>
         <v/>
       </c>
@@ -12321,16 +12121,16 @@
       <c r="AG184" s="3" t="n"/>
       <c r="AH184" s="3" t="n"/>
       <c r="AI184" s="3" t="n"/>
-      <c r="AJ184" s="3" t="n"/>
-      <c r="AK184" s="3">
+      <c r="AJ184" s="13" t="n"/>
+      <c r="AK184" s="12">
         <f>SUM(D184:AI184)</f>
         <v/>
       </c>
-      <c r="AL184" s="3" t="n"/>
-      <c r="AM184" s="3" t="n"/>
-      <c r="AN184" s="3" t="n"/>
-      <c r="AO184" s="3" t="n"/>
-      <c r="AP184" s="3">
+      <c r="AL184" s="13" t="n"/>
+      <c r="AM184" s="13" t="n"/>
+      <c r="AN184" s="13" t="n"/>
+      <c r="AO184" s="13" t="n"/>
+      <c r="AP184" s="12">
         <f>AJ184+AK184</f>
         <v/>
       </c>
@@ -12375,16 +12175,16 @@
       <c r="AG185" s="3" t="n"/>
       <c r="AH185" s="3" t="n"/>
       <c r="AI185" s="3" t="n"/>
-      <c r="AJ185" s="3" t="n"/>
-      <c r="AK185" s="3">
+      <c r="AJ185" s="13" t="n"/>
+      <c r="AK185" s="12">
         <f>SUM(D185:AI185)</f>
         <v/>
       </c>
-      <c r="AL185" s="3" t="n"/>
-      <c r="AM185" s="3" t="n"/>
-      <c r="AN185" s="3" t="n"/>
-      <c r="AO185" s="3" t="n"/>
-      <c r="AP185" s="3">
+      <c r="AL185" s="13" t="n"/>
+      <c r="AM185" s="13" t="n"/>
+      <c r="AN185" s="13" t="n"/>
+      <c r="AO185" s="13" t="n"/>
+      <c r="AP185" s="12">
         <f>AJ185+AK185</f>
         <v/>
       </c>
@@ -12429,63 +12229,100 @@
       <c r="AG186" s="3" t="n"/>
       <c r="AH186" s="3" t="n"/>
       <c r="AI186" s="3" t="n"/>
-      <c r="AJ186" s="3" t="n"/>
-      <c r="AK186" s="3">
+      <c r="AJ186" s="13" t="n"/>
+      <c r="AK186" s="12">
         <f>SUM(D186:AI186)</f>
         <v/>
       </c>
-      <c r="AL186" s="3" t="n"/>
-      <c r="AM186" s="3" t="n"/>
-      <c r="AN186" s="3" t="n"/>
-      <c r="AO186" s="3" t="n"/>
-      <c r="AP186" s="3">
+      <c r="AL186" s="13" t="n"/>
+      <c r="AM186" s="13" t="n"/>
+      <c r="AN186" s="13" t="n"/>
+      <c r="AO186" s="13" t="n"/>
+      <c r="AP186" s="12">
         <f>AJ186+AK186</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="78">
+    <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="T2:T4"/>
+    <mergeCell ref="AF2:AF4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="AH2:AH4"/>
+    <mergeCell ref="AJ2:AL3"/>
+    <mergeCell ref="O90:O92"/>
+    <mergeCell ref="V2:V4"/>
+    <mergeCell ref="G90:G92"/>
+    <mergeCell ref="X2:X4"/>
+    <mergeCell ref="I90:I92"/>
+    <mergeCell ref="AA90:AA92"/>
+    <mergeCell ref="U2:U4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="AE90:AE92"/>
+    <mergeCell ref="AG90:AG92"/>
+    <mergeCell ref="AI90:AI92"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="AG2:AG4"/>
+    <mergeCell ref="Y2:Y4"/>
+    <mergeCell ref="AD2:AD4"/>
     <mergeCell ref="AM92:AO92"/>
-    <mergeCell ref="A1:AP1"/>
-    <mergeCell ref="Q90:Q92"/>
-    <mergeCell ref="F90:F92"/>
-    <mergeCell ref="H90:H92"/>
+    <mergeCell ref="AM2:AO3"/>
     <mergeCell ref="J90:J92"/>
     <mergeCell ref="T90:T92"/>
     <mergeCell ref="L90:L92"/>
     <mergeCell ref="V90:V92"/>
+    <mergeCell ref="N90:N92"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="AM90:AO91"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="AE2:AE4"/>
+    <mergeCell ref="E90:E92"/>
+    <mergeCell ref="W90:W92"/>
+    <mergeCell ref="Y90:Y92"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="F90:F92"/>
+    <mergeCell ref="W2:W4"/>
+    <mergeCell ref="H90:H92"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="Q2:Q4"/>
+    <mergeCell ref="AK92:AL92"/>
+    <mergeCell ref="AF90:AF92"/>
+    <mergeCell ref="X90:X92"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="AH90:AH92"/>
+    <mergeCell ref="Z90:Z92"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="Z2:Z4"/>
+    <mergeCell ref="K90:K92"/>
+    <mergeCell ref="AB2:AB4"/>
+    <mergeCell ref="M90:M92"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="Q90:Q92"/>
+    <mergeCell ref="K2:K4"/>
     <mergeCell ref="AC90:AC92"/>
-    <mergeCell ref="N90:N92"/>
     <mergeCell ref="AJ90:AL91"/>
-    <mergeCell ref="AK92:AL92"/>
-    <mergeCell ref="O90:O92"/>
-    <mergeCell ref="AF90:AF92"/>
-    <mergeCell ref="G90:G92"/>
-    <mergeCell ref="X90:X92"/>
+    <mergeCell ref="AA2:AA4"/>
+    <mergeCell ref="AC2:AC4"/>
     <mergeCell ref="S90:S92"/>
-    <mergeCell ref="I90:I92"/>
-    <mergeCell ref="Z90:Z92"/>
     <mergeCell ref="U90:U92"/>
-    <mergeCell ref="AA90:AA92"/>
-    <mergeCell ref="AH90:AH92"/>
-    <mergeCell ref="AP90:AP92"/>
     <mergeCell ref="B90:B92"/>
-    <mergeCell ref="AE90:AE92"/>
     <mergeCell ref="D90:D92"/>
-    <mergeCell ref="AG90:AG92"/>
-    <mergeCell ref="AI90:AI92"/>
+    <mergeCell ref="M2:M4"/>
     <mergeCell ref="P90:P92"/>
+    <mergeCell ref="P2:P4"/>
     <mergeCell ref="R90:R92"/>
     <mergeCell ref="AB90:AB92"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="AM90:AO91"/>
-    <mergeCell ref="C90:C92"/>
     <mergeCell ref="AD90:AD92"/>
-    <mergeCell ref="E90:E92"/>
-    <mergeCell ref="K90:K92"/>
-    <mergeCell ref="W90:W92"/>
-    <mergeCell ref="M90:M92"/>
-    <mergeCell ref="Y90:Y92"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="AP90:AP92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/templates/master_template.xlsx
+++ b/backend/templates/master_template.xlsx
@@ -108,17 +108,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX35"/>
+  <dimension ref="A1:AT35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,6 @@
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
     <col width="4" customWidth="1" min="45" max="45"/>
-    <col width="4" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -548,6 +547,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -564,147 +564,186 @@
           <t>时间</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="n"/>
-      <c r="T3" s="3" t="n"/>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3" t="n"/>
-      <c r="W3" s="3" t="n"/>
-      <c r="X3" s="3" t="n"/>
-      <c r="Y3" s="3" t="n"/>
-      <c r="Z3" s="3" t="n"/>
-      <c r="AA3" s="3" t="n"/>
-      <c r="AB3" s="3" t="n"/>
-      <c r="AC3" s="3" t="n"/>
-      <c r="AD3" s="3" t="n"/>
-      <c r="AE3" s="3" t="n"/>
-      <c r="AF3" s="3" t="n"/>
-      <c r="AG3" s="3" t="n"/>
-      <c r="AH3" s="3" t="n"/>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE3" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF3" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH3" s="2" t="n">
+        <v>31</v>
+      </c>
       <c r="AI3" s="3" t="n"/>
-      <c r="AJ3" s="3" t="n"/>
-      <c r="AK3" s="3" t="n"/>
-      <c r="AL3" s="3" t="n"/>
-      <c r="AM3" s="3" t="n"/>
-      <c r="AN3" s="3" t="n"/>
-      <c r="AO3" s="3" t="n"/>
-      <c r="AP3" s="3" t="n"/>
-      <c r="AQ3" s="3" t="n"/>
-      <c r="AR3" s="3" t="n"/>
-      <c r="AS3" s="3" t="n"/>
-      <c r="AT3" s="3" t="n"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>出勤合计</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>事假</t>
+        </is>
+      </c>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="AM3" s="2" t="inlineStr">
+        <is>
+          <t>出差</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="inlineStr">
+        <is>
+          <t>病假</t>
+        </is>
+      </c>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>福利假</t>
+        </is>
+      </c>
+      <c r="AP3" s="2" t="inlineStr">
+        <is>
+          <t>年假</t>
+        </is>
+      </c>
+      <c r="AQ3" s="2" t="inlineStr">
+        <is>
+          <t>产假/陪产假</t>
+        </is>
+      </c>
+      <c r="AR3" s="2" t="inlineStr">
+        <is>
+          <t>丧假</t>
+        </is>
+      </c>
+      <c r="AS3" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="W4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="X4" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC4" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD4" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE4" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH4" s="2" t="n">
-        <v>31</v>
-      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
+      <c r="AE4" s="3" t="n"/>
+      <c r="AF4" s="3" t="n"/>
+      <c r="AG4" s="3" t="n"/>
+      <c r="AH4" s="3" t="n"/>
       <c r="AI4" s="3" t="n"/>
       <c r="AJ4" s="3" t="n"/>
       <c r="AK4" s="3" t="n"/>
@@ -716,11 +755,6 @@
       <c r="AQ4" s="3" t="n"/>
       <c r="AR4" s="3" t="n"/>
       <c r="AS4" s="3" t="n"/>
-      <c r="AT4" s="2" t="inlineStr">
-        <is>
-          <t>缺勤</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -808,7 +842,6 @@
           <t>ML (婚假)</t>
         </is>
       </c>
-      <c r="AT5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n"/>
@@ -886,8 +919,7 @@
         <f>COUNTIF(D6:AH6,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS6" s="3" t="n"/>
-      <c r="AT6" s="4">
+      <c r="AS6" s="4">
         <f>21-AJ6</f>
         <v/>
       </c>
@@ -968,8 +1000,7 @@
         <f>COUNTIF(D7:AH7,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS7" s="3" t="n"/>
-      <c r="AT7" s="4">
+      <c r="AS7" s="4">
         <f>21-AJ7</f>
         <v/>
       </c>
@@ -1050,8 +1081,7 @@
         <f>COUNTIF(D8:AH8,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS8" s="3" t="n"/>
-      <c r="AT8" s="4">
+      <c r="AS8" s="4">
         <f>21-AJ8</f>
         <v/>
       </c>
@@ -1132,8 +1162,7 @@
         <f>COUNTIF(D9:AH9,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS9" s="3" t="n"/>
-      <c r="AT9" s="4">
+      <c r="AS9" s="4">
         <f>21-AJ9</f>
         <v/>
       </c>
@@ -1214,8 +1243,7 @@
         <f>COUNTIF(D10:AH10,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS10" s="3" t="n"/>
-      <c r="AT10" s="4">
+      <c r="AS10" s="4">
         <f>21-AJ10</f>
         <v/>
       </c>
@@ -1296,8 +1324,7 @@
         <f>COUNTIF(D11:AH11,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS11" s="3" t="n"/>
-      <c r="AT11" s="4">
+      <c r="AS11" s="4">
         <f>21-AJ11</f>
         <v/>
       </c>
@@ -1378,8 +1405,7 @@
         <f>COUNTIF(D12:AH12,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS12" s="3" t="n"/>
-      <c r="AT12" s="4">
+      <c r="AS12" s="4">
         <f>21-AJ12</f>
         <v/>
       </c>
@@ -1460,8 +1486,7 @@
         <f>COUNTIF(D13:AH13,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS13" s="3" t="n"/>
-      <c r="AT13" s="4">
+      <c r="AS13" s="4">
         <f>21-AJ13</f>
         <v/>
       </c>
@@ -1542,8 +1567,7 @@
         <f>COUNTIF(D14:AH14,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS14" s="3" t="n"/>
-      <c r="AT14" s="4">
+      <c r="AS14" s="4">
         <f>21-AJ14</f>
         <v/>
       </c>
@@ -1624,8 +1648,7 @@
         <f>COUNTIF(D15:AH15,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS15" s="3" t="n"/>
-      <c r="AT15" s="4">
+      <c r="AS15" s="4">
         <f>21-AJ15</f>
         <v/>
       </c>
@@ -1706,8 +1729,7 @@
         <f>COUNTIF(D16:AH16,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS16" s="3" t="n"/>
-      <c r="AT16" s="4">
+      <c r="AS16" s="4">
         <f>21-AJ16</f>
         <v/>
       </c>
@@ -1788,8 +1810,7 @@
         <f>COUNTIF(D17:AH17,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS17" s="3" t="n"/>
-      <c r="AT17" s="4">
+      <c r="AS17" s="4">
         <f>21-AJ17</f>
         <v/>
       </c>
@@ -1870,8 +1891,7 @@
         <f>COUNTIF(D18:AH18,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS18" s="3" t="n"/>
-      <c r="AT18" s="4">
+      <c r="AS18" s="4">
         <f>21-AJ18</f>
         <v/>
       </c>
@@ -1952,8 +1972,7 @@
         <f>COUNTIF(D19:AH19,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS19" s="3" t="n"/>
-      <c r="AT19" s="4">
+      <c r="AS19" s="4">
         <f>21-AJ19</f>
         <v/>
       </c>
@@ -2034,8 +2053,7 @@
         <f>COUNTIF(D20:AH20,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS20" s="3" t="n"/>
-      <c r="AT20" s="4">
+      <c r="AS20" s="4">
         <f>21-AJ20</f>
         <v/>
       </c>
@@ -2116,8 +2134,7 @@
         <f>COUNTIF(D21:AH21,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS21" s="3" t="n"/>
-      <c r="AT21" s="4">
+      <c r="AS21" s="4">
         <f>21-AJ21</f>
         <v/>
       </c>
@@ -2198,8 +2215,7 @@
         <f>COUNTIF(D22:AH22,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS22" s="3" t="n"/>
-      <c r="AT22" s="4">
+      <c r="AS22" s="4">
         <f>21-AJ22</f>
         <v/>
       </c>
@@ -2280,8 +2296,7 @@
         <f>COUNTIF(D23:AH23,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS23" s="3" t="n"/>
-      <c r="AT23" s="4">
+      <c r="AS23" s="4">
         <f>21-AJ23</f>
         <v/>
       </c>
@@ -2362,8 +2377,7 @@
         <f>COUNTIF(D24:AH24,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS24" s="3" t="n"/>
-      <c r="AT24" s="4">
+      <c r="AS24" s="4">
         <f>21-AJ24</f>
         <v/>
       </c>
@@ -2444,8 +2458,7 @@
         <f>COUNTIF(D25:AH25,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS25" s="3" t="n"/>
-      <c r="AT25" s="4">
+      <c r="AS25" s="4">
         <f>21-AJ25</f>
         <v/>
       </c>
@@ -2526,8 +2539,7 @@
         <f>COUNTIF(D26:AH26,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS26" s="3" t="n"/>
-      <c r="AT26" s="4">
+      <c r="AS26" s="4">
         <f>21-AJ26</f>
         <v/>
       </c>
@@ -2608,8 +2620,7 @@
         <f>COUNTIF(D27:AH27,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS27" s="3" t="n"/>
-      <c r="AT27" s="4">
+      <c r="AS27" s="4">
         <f>21-AJ27</f>
         <v/>
       </c>
@@ -2690,8 +2701,7 @@
         <f>COUNTIF(D28:AH28,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS28" s="3" t="n"/>
-      <c r="AT28" s="4">
+      <c r="AS28" s="4">
         <f>21-AJ28</f>
         <v/>
       </c>
@@ -2772,8 +2782,7 @@
         <f>COUNTIF(D29:AH29,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS29" s="3" t="n"/>
-      <c r="AT29" s="4">
+      <c r="AS29" s="4">
         <f>21-AJ29</f>
         <v/>
       </c>
@@ -2854,8 +2863,7 @@
         <f>COUNTIF(D30:AH30,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS30" s="3" t="n"/>
-      <c r="AT30" s="4">
+      <c r="AS30" s="4">
         <f>21-AJ30</f>
         <v/>
       </c>
@@ -2936,8 +2944,7 @@
         <f>COUNTIF(D31:AH31,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS31" s="3" t="n"/>
-      <c r="AT31" s="4">
+      <c r="AS31" s="4">
         <f>21-AJ31</f>
         <v/>
       </c>
@@ -3018,8 +3025,7 @@
         <f>COUNTIF(D32:AH32,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS32" s="3" t="n"/>
-      <c r="AT32" s="4">
+      <c r="AS32" s="4">
         <f>21-AJ32</f>
         <v/>
       </c>
@@ -3100,8 +3106,7 @@
         <f>COUNTIF(D33:AH33,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS33" s="3" t="n"/>
-      <c r="AT33" s="4">
+      <c r="AS33" s="4">
         <f>21-AJ33</f>
         <v/>
       </c>
@@ -3182,8 +3187,7 @@
         <f>COUNTIF(D34:AH34,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS34" s="3" t="n"/>
-      <c r="AT34" s="4">
+      <c r="AS34" s="4">
         <f>21-AJ34</f>
         <v/>
       </c>
@@ -3264,8 +3268,7 @@
         <f>COUNTIF(D35:AH35,$AR$5)</f>
         <v/>
       </c>
-      <c r="AS35" s="3" t="n"/>
-      <c r="AT35" s="4">
+      <c r="AS35" s="4">
         <f>21-AJ35</f>
         <v/>
       </c>
@@ -3281,7 +3284,6 @@
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A1:AX1"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B28:B29"/>
@@ -3295,6 +3297,7 @@
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:AT1"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B32:B33"/>
     <mergeCell ref="A34:A35"/>
@@ -3712,7 +3715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF19"/>
+  <dimension ref="A1:AF18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3755,918 +3758,751 @@
           <t>月度汇总 统计日期：2026-05-01 至 2026-05-31</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q1" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X1" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="Y1" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AE1" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="AF1" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="7" t="n"/>
+      <c r="K1" s="7" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="7" t="n"/>
+      <c r="R1" s="7" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="7" t="n"/>
+      <c r="Y1" s="7" t="n"/>
+      <c r="Z1" s="4" t="n"/>
+      <c r="AA1" s="4" t="n"/>
+      <c r="AB1" s="4" t="n"/>
+      <c r="AC1" s="4" t="n"/>
+      <c r="AD1" s="4" t="n"/>
+      <c r="AE1" s="7" t="n"/>
+      <c r="AF1" s="7" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>报表生成时间：2026-06-17 03:25</t>
+          <t>报表生成时间：2026-06-17 03:50</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
-      <c r="J2" s="9" t="n"/>
-      <c r="K2" s="9" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="9" t="n"/>
-      <c r="R2" s="9" t="n"/>
+      <c r="Q2" s="7" t="n"/>
+      <c r="R2" s="7" t="n"/>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
-      <c r="X2" s="9" t="n"/>
-      <c r="Y2" s="9" t="n"/>
+      <c r="X2" s="7" t="n"/>
+      <c r="Y2" s="7" t="n"/>
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
       <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="9" t="n"/>
-      <c r="AF2" s="9" t="n"/>
+      <c r="AE2" s="7" t="n"/>
+      <c r="AF2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>每日考勤状态</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="9" t="n"/>
-      <c r="R3" s="9" t="n"/>
-      <c r="S3" s="4" t="n"/>
-      <c r="T3" s="4" t="n"/>
-      <c r="U3" s="4" t="n"/>
-      <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n"/>
-      <c r="X3" s="9" t="n"/>
-      <c r="Y3" s="9" t="n"/>
-      <c r="Z3" s="4" t="n"/>
-      <c r="AA3" s="4" t="n"/>
-      <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="9" t="n"/>
-      <c r="AF3" s="9" t="n"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="Y3" s="10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AE3" s="10" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="R4" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X4" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="Y4" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AE4" s="7" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
-      <c r="AF4" s="7" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="7" t="inlineStr"/>
+      <c r="R4" s="7" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="7" t="inlineStr"/>
+      <c r="Y4" s="7" t="inlineStr"/>
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="inlineStr"/>
+      <c r="AE4" s="7" t="inlineStr"/>
+      <c r="AF4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
       <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="9" t="inlineStr"/>
-      <c r="D5" s="9" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="9" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr"/>
       <c r="O5" s="4" t="inlineStr"/>
       <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="9" t="inlineStr"/>
-      <c r="R5" s="9" t="inlineStr"/>
+      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr"/>
       <c r="U5" s="4" t="inlineStr"/>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="9" t="inlineStr"/>
-      <c r="Y5" s="9" t="inlineStr"/>
+      <c r="X5" s="7" t="inlineStr"/>
+      <c r="Y5" s="7" t="inlineStr"/>
       <c r="Z5" s="4" t="inlineStr"/>
       <c r="AA5" s="4" t="inlineStr"/>
       <c r="AB5" s="4" t="inlineStr"/>
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
-      <c r="AE5" s="9" t="inlineStr"/>
-      <c r="AF5" s="9" t="inlineStr"/>
+      <c r="AE5" s="7" t="inlineStr"/>
+      <c r="AF5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
       <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr"/>
+      <c r="K6" s="7" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr"/>
       <c r="O6" s="4" t="inlineStr"/>
       <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="9" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
+      <c r="Q6" s="7" t="inlineStr"/>
+      <c r="R6" s="7" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr"/>
       <c r="V6" s="4" t="inlineStr"/>
       <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="9" t="inlineStr"/>
-      <c r="Y6" s="9" t="inlineStr"/>
+      <c r="X6" s="7" t="inlineStr"/>
+      <c r="Y6" s="7" t="inlineStr"/>
       <c r="Z6" s="4" t="inlineStr"/>
       <c r="AA6" s="4" t="inlineStr"/>
       <c r="AB6" s="4" t="inlineStr"/>
       <c r="AC6" s="4" t="inlineStr"/>
       <c r="AD6" s="4" t="inlineStr"/>
-      <c r="AE6" s="9" t="inlineStr"/>
-      <c r="AF6" s="9" t="inlineStr"/>
+      <c r="AE6" s="7" t="inlineStr"/>
+      <c r="AF6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="9" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr"/>
       <c r="L7" s="4" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr"/>
       <c r="N7" s="4" t="inlineStr"/>
       <c r="O7" s="4" t="inlineStr"/>
       <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="9" t="inlineStr"/>
-      <c r="R7" s="9" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr"/>
+      <c r="R7" s="7" t="inlineStr"/>
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="4" t="inlineStr"/>
       <c r="U7" s="4" t="inlineStr"/>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="9" t="inlineStr"/>
-      <c r="Y7" s="9" t="inlineStr"/>
+      <c r="X7" s="7" t="inlineStr"/>
+      <c r="Y7" s="7" t="inlineStr"/>
       <c r="Z7" s="4" t="inlineStr"/>
       <c r="AA7" s="4" t="inlineStr"/>
       <c r="AB7" s="4" t="inlineStr"/>
       <c r="AC7" s="4" t="inlineStr"/>
       <c r="AD7" s="4" t="inlineStr"/>
-      <c r="AE7" s="9" t="inlineStr"/>
-      <c r="AF7" s="9" t="inlineStr"/>
+      <c r="AE7" s="7" t="inlineStr"/>
+      <c r="AF7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n"/>
       <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="9" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr"/>
       <c r="O8" s="4" t="inlineStr"/>
       <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="9" t="inlineStr"/>
-      <c r="R8" s="9" t="inlineStr"/>
+      <c r="Q8" s="7" t="inlineStr"/>
+      <c r="R8" s="7" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
       <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" s="4" t="inlineStr"/>
       <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="9" t="inlineStr"/>
-      <c r="Y8" s="9" t="inlineStr"/>
+      <c r="X8" s="7" t="inlineStr"/>
+      <c r="Y8" s="7" t="inlineStr"/>
       <c r="Z8" s="4" t="inlineStr"/>
       <c r="AA8" s="4" t="inlineStr"/>
       <c r="AB8" s="4" t="inlineStr"/>
       <c r="AC8" s="4" t="inlineStr"/>
       <c r="AD8" s="4" t="inlineStr"/>
-      <c r="AE8" s="9" t="inlineStr"/>
-      <c r="AF8" s="9" t="inlineStr"/>
+      <c r="AE8" s="7" t="inlineStr"/>
+      <c r="AF8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr"/>
-      <c r="D9" s="9" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="9" t="inlineStr"/>
-      <c r="K9" s="9" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr"/>
       <c r="N9" s="4" t="inlineStr"/>
       <c r="O9" s="4" t="inlineStr"/>
       <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="9" t="inlineStr"/>
-      <c r="R9" s="9" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="4" t="inlineStr"/>
       <c r="U9" s="4" t="inlineStr"/>
       <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="9" t="inlineStr"/>
-      <c r="Y9" s="9" t="inlineStr"/>
+      <c r="X9" s="7" t="inlineStr"/>
+      <c r="Y9" s="7" t="inlineStr"/>
       <c r="Z9" s="4" t="inlineStr"/>
       <c r="AA9" s="4" t="inlineStr"/>
       <c r="AB9" s="4" t="inlineStr"/>
       <c r="AC9" s="4" t="inlineStr"/>
       <c r="AD9" s="4" t="inlineStr"/>
-      <c r="AE9" s="9" t="inlineStr"/>
-      <c r="AF9" s="9" t="inlineStr"/>
+      <c r="AE9" s="7" t="inlineStr"/>
+      <c r="AF9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
       <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="9" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="9" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr"/>
       <c r="O10" s="4" t="inlineStr"/>
       <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="9" t="inlineStr"/>
-      <c r="R10" s="9" t="inlineStr"/>
+      <c r="Q10" s="7" t="inlineStr"/>
+      <c r="R10" s="7" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="4" t="inlineStr"/>
       <c r="U10" s="4" t="inlineStr"/>
       <c r="V10" s="4" t="inlineStr"/>
       <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="9" t="inlineStr"/>
-      <c r="Y10" s="9" t="inlineStr"/>
+      <c r="X10" s="7" t="inlineStr"/>
+      <c r="Y10" s="7" t="inlineStr"/>
       <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
       <c r="AB10" s="4" t="inlineStr"/>
       <c r="AC10" s="4" t="inlineStr"/>
       <c r="AD10" s="4" t="inlineStr"/>
-      <c r="AE10" s="9" t="inlineStr"/>
-      <c r="AF10" s="9" t="inlineStr"/>
+      <c r="AE10" s="7" t="inlineStr"/>
+      <c r="AF10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr"/>
-      <c r="D11" s="9" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="9" t="inlineStr"/>
-      <c r="K11" s="9" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
       <c r="L11" s="4" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr"/>
       <c r="N11" s="4" t="inlineStr"/>
       <c r="O11" s="4" t="inlineStr"/>
       <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="9" t="inlineStr"/>
-      <c r="R11" s="9" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr"/>
+      <c r="R11" s="7" t="inlineStr"/>
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="4" t="inlineStr"/>
       <c r="U11" s="4" t="inlineStr"/>
       <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="9" t="inlineStr"/>
-      <c r="Y11" s="9" t="inlineStr"/>
+      <c r="X11" s="7" t="inlineStr"/>
+      <c r="Y11" s="7" t="inlineStr"/>
       <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
       <c r="AB11" s="4" t="inlineStr"/>
       <c r="AC11" s="4" t="inlineStr"/>
       <c r="AD11" s="4" t="inlineStr"/>
-      <c r="AE11" s="9" t="inlineStr"/>
-      <c r="AF11" s="9" t="inlineStr"/>
+      <c r="AE11" s="7" t="inlineStr"/>
+      <c r="AF11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
       <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="9" t="inlineStr"/>
-      <c r="D12" s="9" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr"/>
       <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="9" t="inlineStr"/>
-      <c r="K12" s="9" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr"/>
       <c r="L12" s="4" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr"/>
       <c r="N12" s="4" t="inlineStr"/>
       <c r="O12" s="4" t="inlineStr"/>
       <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="9" t="inlineStr"/>
-      <c r="R12" s="9" t="inlineStr"/>
+      <c r="Q12" s="7" t="inlineStr"/>
+      <c r="R12" s="7" t="inlineStr"/>
       <c r="S12" s="4" t="inlineStr"/>
       <c r="T12" s="4" t="inlineStr"/>
       <c r="U12" s="4" t="inlineStr"/>
       <c r="V12" s="4" t="inlineStr"/>
       <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="9" t="inlineStr"/>
-      <c r="Y12" s="9" t="inlineStr"/>
+      <c r="X12" s="7" t="inlineStr"/>
+      <c r="Y12" s="7" t="inlineStr"/>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
       <c r="AB12" s="4" t="inlineStr"/>
       <c r="AC12" s="4" t="inlineStr"/>
       <c r="AD12" s="4" t="inlineStr"/>
-      <c r="AE12" s="9" t="inlineStr"/>
-      <c r="AF12" s="9" t="inlineStr"/>
+      <c r="AE12" s="7" t="inlineStr"/>
+      <c r="AF12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="9" t="inlineStr"/>
-      <c r="D13" s="9" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="9" t="inlineStr"/>
-      <c r="K13" s="9" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
       <c r="L13" s="4" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr"/>
       <c r="N13" s="4" t="inlineStr"/>
       <c r="O13" s="4" t="inlineStr"/>
       <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="9" t="inlineStr"/>
-      <c r="R13" s="9" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="4" t="inlineStr"/>
       <c r="T13" s="4" t="inlineStr"/>
       <c r="U13" s="4" t="inlineStr"/>
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="9" t="inlineStr"/>
-      <c r="Y13" s="9" t="inlineStr"/>
+      <c r="X13" s="7" t="inlineStr"/>
+      <c r="Y13" s="7" t="inlineStr"/>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
       <c r="AB13" s="4" t="inlineStr"/>
       <c r="AC13" s="4" t="inlineStr"/>
       <c r="AD13" s="4" t="inlineStr"/>
-      <c r="AE13" s="9" t="inlineStr"/>
-      <c r="AF13" s="9" t="inlineStr"/>
+      <c r="AE13" s="7" t="inlineStr"/>
+      <c r="AF13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
       <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="9" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr"/>
       <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="9" t="inlineStr"/>
-      <c r="K14" s="9" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" s="7" t="inlineStr"/>
       <c r="L14" s="4" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr"/>
       <c r="O14" s="4" t="inlineStr"/>
       <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="9" t="inlineStr"/>
-      <c r="R14" s="9" t="inlineStr"/>
+      <c r="Q14" s="7" t="inlineStr"/>
+      <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="4" t="inlineStr"/>
       <c r="T14" s="4" t="inlineStr"/>
       <c r="U14" s="4" t="inlineStr"/>
       <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="9" t="inlineStr"/>
-      <c r="Y14" s="9" t="inlineStr"/>
+      <c r="X14" s="7" t="inlineStr"/>
+      <c r="Y14" s="7" t="inlineStr"/>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
       <c r="AB14" s="4" t="inlineStr"/>
       <c r="AC14" s="4" t="inlineStr"/>
       <c r="AD14" s="4" t="inlineStr"/>
-      <c r="AE14" s="9" t="inlineStr"/>
-      <c r="AF14" s="9" t="inlineStr"/>
+      <c r="AE14" s="7" t="inlineStr"/>
+      <c r="AF14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
       <c r="M15" s="4" t="inlineStr"/>
       <c r="N15" s="4" t="inlineStr"/>
       <c r="O15" s="4" t="inlineStr"/>
       <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="9" t="inlineStr"/>
-      <c r="R15" s="9" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="4" t="inlineStr"/>
       <c r="T15" s="4" t="inlineStr"/>
       <c r="U15" s="4" t="inlineStr"/>
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="9" t="inlineStr"/>
-      <c r="Y15" s="9" t="inlineStr"/>
+      <c r="X15" s="7" t="inlineStr"/>
+      <c r="Y15" s="7" t="inlineStr"/>
       <c r="Z15" s="4" t="inlineStr"/>
       <c r="AA15" s="4" t="inlineStr"/>
       <c r="AB15" s="4" t="inlineStr"/>
       <c r="AC15" s="4" t="inlineStr"/>
       <c r="AD15" s="4" t="inlineStr"/>
-      <c r="AE15" s="9" t="inlineStr"/>
-      <c r="AF15" s="9" t="inlineStr"/>
+      <c r="AE15" s="7" t="inlineStr"/>
+      <c r="AF15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
       <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="9" t="inlineStr"/>
-      <c r="D16" s="9" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr"/>
       <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="9" t="inlineStr"/>
-      <c r="K16" s="9" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr"/>
       <c r="M16" s="4" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr"/>
       <c r="O16" s="4" t="inlineStr"/>
       <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="9" t="inlineStr"/>
-      <c r="R16" s="9" t="inlineStr"/>
+      <c r="Q16" s="7" t="inlineStr"/>
+      <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="4" t="inlineStr"/>
       <c r="T16" s="4" t="inlineStr"/>
       <c r="U16" s="4" t="inlineStr"/>
       <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="9" t="inlineStr"/>
-      <c r="Y16" s="9" t="inlineStr"/>
+      <c r="X16" s="7" t="inlineStr"/>
+      <c r="Y16" s="7" t="inlineStr"/>
       <c r="Z16" s="4" t="inlineStr"/>
       <c r="AA16" s="4" t="inlineStr"/>
       <c r="AB16" s="4" t="inlineStr"/>
       <c r="AC16" s="4" t="inlineStr"/>
       <c r="AD16" s="4" t="inlineStr"/>
-      <c r="AE16" s="9" t="inlineStr"/>
-      <c r="AF16" s="9" t="inlineStr"/>
+      <c r="AE16" s="7" t="inlineStr"/>
+      <c r="AF16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="9" t="inlineStr"/>
-      <c r="D17" s="9" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="9" t="inlineStr"/>
-      <c r="K17" s="9" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr"/>
       <c r="L17" s="4" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr"/>
       <c r="N17" s="4" t="inlineStr"/>
       <c r="O17" s="4" t="inlineStr"/>
       <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="9" t="inlineStr"/>
-      <c r="R17" s="9" t="inlineStr"/>
+      <c r="Q17" s="7" t="inlineStr"/>
+      <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="4" t="inlineStr"/>
       <c r="T17" s="4" t="inlineStr"/>
       <c r="U17" s="4" t="inlineStr"/>
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="9" t="inlineStr"/>
-      <c r="Y17" s="9" t="inlineStr"/>
+      <c r="X17" s="7" t="inlineStr"/>
+      <c r="Y17" s="7" t="inlineStr"/>
       <c r="Z17" s="4" t="inlineStr"/>
       <c r="AA17" s="4" t="inlineStr"/>
       <c r="AB17" s="4" t="inlineStr"/>
       <c r="AC17" s="4" t="inlineStr"/>
       <c r="AD17" s="4" t="inlineStr"/>
-      <c r="AE17" s="9" t="inlineStr"/>
-      <c r="AF17" s="9" t="inlineStr"/>
+      <c r="AE17" s="7" t="inlineStr"/>
+      <c r="AF17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
       <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="9" t="inlineStr"/>
-      <c r="D18" s="9" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="9" t="inlineStr"/>
-      <c r="K18" s="9" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr"/>
+      <c r="K18" s="7" t="inlineStr"/>
       <c r="L18" s="4" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr"/>
       <c r="O18" s="4" t="inlineStr"/>
       <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="9" t="inlineStr"/>
-      <c r="R18" s="9" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr"/>
+      <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="4" t="inlineStr"/>
       <c r="T18" s="4" t="inlineStr"/>
       <c r="U18" s="4" t="inlineStr"/>
       <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="9" t="inlineStr"/>
-      <c r="Y18" s="9" t="inlineStr"/>
+      <c r="X18" s="7" t="inlineStr"/>
+      <c r="Y18" s="7" t="inlineStr"/>
       <c r="Z18" s="4" t="inlineStr"/>
       <c r="AA18" s="4" t="inlineStr"/>
       <c r="AB18" s="4" t="inlineStr"/>
       <c r="AC18" s="4" t="inlineStr"/>
       <c r="AD18" s="4" t="inlineStr"/>
-      <c r="AE18" s="9" t="inlineStr"/>
-      <c r="AF18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="9" t="inlineStr"/>
-      <c r="D19" s="9" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="9" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="9" t="inlineStr"/>
-      <c r="R19" s="9" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="inlineStr"/>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="9" t="inlineStr"/>
-      <c r="Y19" s="9" t="inlineStr"/>
-      <c r="Z19" s="4" t="inlineStr"/>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="inlineStr"/>
-      <c r="AD19" s="4" t="inlineStr"/>
-      <c r="AE19" s="9" t="inlineStr"/>
-      <c r="AF19" s="9" t="inlineStr"/>
+      <c r="AE18" s="7" t="inlineStr"/>
+      <c r="AF18" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A2"/>
-    <mergeCell ref="B3:AF3"/>
     <mergeCell ref="A1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/templates/master_template.xlsx
+++ b/backend/templates/master_template.xlsx
@@ -72,7 +72,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -86,11 +86,19 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -109,6 +117,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -488,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT35"/>
+  <dimension ref="A1:AT34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -747,112 +763,152 @@
       <c r="AF4" s="4" t="n"/>
       <c r="AG4" s="4" t="n"/>
       <c r="AH4" s="4" t="n"/>
-      <c r="AI4" s="4" t="n"/>
-      <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="4" t="n"/>
-      <c r="AL4" s="4" t="n"/>
-      <c r="AM4" s="4" t="n"/>
-      <c r="AN4" s="4" t="n"/>
-      <c r="AO4" s="4" t="n"/>
-      <c r="AP4" s="4" t="n"/>
-      <c r="AQ4" s="4" t="n"/>
-      <c r="AR4" s="4" t="n"/>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>◇</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>✬</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="inlineStr">
+        <is>
+          <t>※</t>
+        </is>
+      </c>
+      <c r="AN4" s="2" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="AP4" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ4" s="2" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="AR4" s="2" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
       <c r="AS4" s="4" t="n"/>
       <c r="AT4" s="4" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
-      <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n"/>
-      <c r="U5" s="4" t="n"/>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="4" t="n"/>
-      <c r="AD5" s="4" t="n"/>
-      <c r="AE5" s="4" t="n"/>
-      <c r="AF5" s="4" t="n"/>
-      <c r="AG5" s="4" t="n"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="7" t="inlineStr"/>
+      <c r="S5" s="7" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr"/>
+      <c r="Y5" s="7" t="inlineStr"/>
+      <c r="Z5" s="7" t="inlineStr"/>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="inlineStr"/>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="7" t="inlineStr"/>
+      <c r="AG5" s="7" t="inlineStr"/>
       <c r="AH5" s="4" t="n"/>
-      <c r="AI5" s="2" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>◇</t>
-        </is>
-      </c>
-      <c r="AK5" s="2" t="inlineStr">
-        <is>
-          <t>✬</t>
-        </is>
-      </c>
-      <c r="AL5" s="2" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="AM5" s="2" t="inlineStr">
-        <is>
-          <t>※</t>
-        </is>
-      </c>
-      <c r="AN5" s="2" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AQ5" s="2" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="AR5" s="2" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="AS5" s="4" t="n"/>
-      <c r="AT5" s="4" t="n"/>
+      <c r="AI5" s="6">
+        <f>COUNTIF(C5:AG5,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="6">
+        <f>COUNTIF(C5:AG5,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK5" s="6">
+        <f>COUNTIF(C5:AG5,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL5" s="6">
+        <f>COUNTIF(C5:AG5,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM5" s="6">
+        <f>COUNTIF(C5:AG5,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN5" s="6">
+        <f>COUNTIF(C5:AG5,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO5" s="6">
+        <f>COUNTIF(C5:AG5,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP5" s="6">
+        <f>COUNTIF(C5:AG5,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ5" s="6">
+        <f>COUNTIF(C5:AG5,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR5" s="6">
+        <f>COUNTIF(C5:AG5,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS5" s="6">
+        <f>AI5+AL5</f>
+        <v/>
+      </c>
+      <c r="AT5" s="6">
+        <f>21-AI5</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="n"/>
+      <c r="A6" s="4" t="n"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>上午</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -887,148 +943,112 @@
       <c r="AF6" s="7" t="inlineStr"/>
       <c r="AG6" s="7" t="inlineStr"/>
       <c r="AH6" s="4" t="n"/>
-      <c r="AI6" s="6">
-        <f>COUNTIF(C6:AG6,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="6">
-        <f>COUNTIF(C6:AG6,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK6" s="6">
-        <f>COUNTIF(C6:AG6,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL6" s="6">
-        <f>COUNTIF(C6:AG6,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM6" s="6">
-        <f>COUNTIF(C6:AG6,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN6" s="6">
-        <f>COUNTIF(C6:AG6,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO6" s="6">
-        <f>COUNTIF(C6:AG6,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP6" s="6">
-        <f>COUNTIF(C6:AG6,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ6" s="6">
-        <f>COUNTIF(C6:AG6,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR6" s="6">
-        <f>COUNTIF(C6:AG6,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS6" s="6">
-        <f>AI6+AL6</f>
-        <v/>
-      </c>
-      <c r="AT6" s="6">
-        <f>21-AI6</f>
-        <v/>
-      </c>
+      <c r="AI6" s="4" t="n"/>
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="4" t="n"/>
+      <c r="AL6" s="4" t="n"/>
+      <c r="AM6" s="4" t="n"/>
+      <c r="AN6" s="4" t="n"/>
+      <c r="AO6" s="4" t="n"/>
+      <c r="AP6" s="4" t="n"/>
+      <c r="AQ6" s="4" t="n"/>
+      <c r="AR6" s="4" t="n"/>
+      <c r="AS6" s="4" t="n"/>
+      <c r="AT6" s="4" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="11" t="inlineStr"/>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="10" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
+      <c r="O7" s="10" t="inlineStr"/>
+      <c r="P7" s="10" t="inlineStr"/>
+      <c r="Q7" s="10" t="inlineStr"/>
+      <c r="R7" s="11" t="inlineStr"/>
+      <c r="S7" s="11" t="inlineStr"/>
+      <c r="T7" s="10" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr"/>
+      <c r="V7" s="10" t="inlineStr"/>
+      <c r="W7" s="10" t="inlineStr"/>
+      <c r="X7" s="10" t="inlineStr"/>
+      <c r="Y7" s="11" t="inlineStr"/>
+      <c r="Z7" s="11" t="inlineStr"/>
+      <c r="AA7" s="10" t="inlineStr"/>
+      <c r="AB7" s="10" t="inlineStr"/>
+      <c r="AC7" s="10" t="inlineStr"/>
+      <c r="AD7" s="10" t="inlineStr"/>
+      <c r="AE7" s="10" t="inlineStr"/>
+      <c r="AF7" s="11" t="inlineStr"/>
+      <c r="AG7" s="11" t="inlineStr"/>
+      <c r="AH7" s="10" t="n"/>
+      <c r="AI7" s="9">
+        <f>COUNTIF(C7:AG7,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9">
+        <f>COUNTIF(C7:AG7,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK7" s="9">
+        <f>COUNTIF(C7:AG7,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL7" s="9">
+        <f>COUNTIF(C7:AG7,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9">
+        <f>COUNTIF(C7:AG7,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN7" s="9">
+        <f>COUNTIF(C7:AG7,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO7" s="9">
+        <f>COUNTIF(C7:AG7,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP7" s="9">
+        <f>COUNTIF(C7:AG7,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ7" s="9">
+        <f>COUNTIF(C7:AG7,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR7" s="9">
+        <f>COUNTIF(C7:AG7,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS7" s="9">
+        <f>AI7+AL7</f>
+        <v/>
+      </c>
+      <c r="AT7" s="9">
+        <f>21-AI7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
-      <c r="S7" s="7" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="7" t="inlineStr"/>
-      <c r="Z7" s="7" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr"/>
-      <c r="AD7" s="4" t="inlineStr"/>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="7" t="inlineStr"/>
-      <c r="AG7" s="7" t="inlineStr"/>
-      <c r="AH7" s="4" t="n"/>
-      <c r="AI7" s="6">
-        <f>COUNTIF(C7:AG7,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="6">
-        <f>COUNTIF(C7:AG7,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK7" s="6">
-        <f>COUNTIF(C7:AG7,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL7" s="6">
-        <f>COUNTIF(C7:AG7,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM7" s="6">
-        <f>COUNTIF(C7:AG7,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN7" s="6">
-        <f>COUNTIF(C7:AG7,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO7" s="6">
-        <f>COUNTIF(C7:AG7,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP7" s="6">
-        <f>COUNTIF(C7:AG7,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ7" s="6">
-        <f>COUNTIF(C7:AG7,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR7" s="6">
-        <f>COUNTIF(C7:AG7,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS7" s="6">
-        <f>AI7+AL7</f>
-        <v/>
-      </c>
-      <c r="AT7" s="6">
-        <f>21-AI7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -1063,148 +1083,112 @@
       <c r="AF8" s="7" t="inlineStr"/>
       <c r="AG8" s="7" t="inlineStr"/>
       <c r="AH8" s="4" t="n"/>
-      <c r="AI8" s="6">
-        <f>COUNTIF(C8:AG8,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="6">
-        <f>COUNTIF(C8:AG8,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK8" s="6">
-        <f>COUNTIF(C8:AG8,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL8" s="6">
-        <f>COUNTIF(C8:AG8,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM8" s="6">
-        <f>COUNTIF(C8:AG8,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN8" s="6">
-        <f>COUNTIF(C8:AG8,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO8" s="6">
-        <f>COUNTIF(C8:AG8,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP8" s="6">
-        <f>COUNTIF(C8:AG8,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ8" s="6">
-        <f>COUNTIF(C8:AG8,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR8" s="6">
-        <f>COUNTIF(C8:AG8,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS8" s="6">
-        <f>AI8+AL8</f>
-        <v/>
-      </c>
-      <c r="AT8" s="6">
-        <f>21-AI8</f>
-        <v/>
-      </c>
+      <c r="AI8" s="4" t="n"/>
+      <c r="AJ8" s="4" t="n"/>
+      <c r="AK8" s="4" t="n"/>
+      <c r="AL8" s="4" t="n"/>
+      <c r="AM8" s="4" t="n"/>
+      <c r="AN8" s="4" t="n"/>
+      <c r="AO8" s="4" t="n"/>
+      <c r="AP8" s="4" t="n"/>
+      <c r="AQ8" s="4" t="n"/>
+      <c r="AR8" s="4" t="n"/>
+      <c r="AS8" s="4" t="n"/>
+      <c r="AT8" s="4" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr"/>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+      <c r="K9" s="11" t="inlineStr"/>
+      <c r="L9" s="11" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr"/>
+      <c r="P9" s="10" t="inlineStr"/>
+      <c r="Q9" s="10" t="inlineStr"/>
+      <c r="R9" s="11" t="inlineStr"/>
+      <c r="S9" s="11" t="inlineStr"/>
+      <c r="T9" s="10" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr"/>
+      <c r="V9" s="10" t="inlineStr"/>
+      <c r="W9" s="10" t="inlineStr"/>
+      <c r="X9" s="10" t="inlineStr"/>
+      <c r="Y9" s="11" t="inlineStr"/>
+      <c r="Z9" s="11" t="inlineStr"/>
+      <c r="AA9" s="10" t="inlineStr"/>
+      <c r="AB9" s="10" t="inlineStr"/>
+      <c r="AC9" s="10" t="inlineStr"/>
+      <c r="AD9" s="10" t="inlineStr"/>
+      <c r="AE9" s="10" t="inlineStr"/>
+      <c r="AF9" s="11" t="inlineStr"/>
+      <c r="AG9" s="11" t="inlineStr"/>
+      <c r="AH9" s="10" t="n"/>
+      <c r="AI9" s="9">
+        <f>COUNTIF(C9:AG9,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9">
+        <f>COUNTIF(C9:AG9,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK9" s="9">
+        <f>COUNTIF(C9:AG9,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL9" s="9">
+        <f>COUNTIF(C9:AG9,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9">
+        <f>COUNTIF(C9:AG9,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN9" s="9">
+        <f>COUNTIF(C9:AG9,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO9" s="9">
+        <f>COUNTIF(C9:AG9,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP9" s="9">
+        <f>COUNTIF(C9:AG9,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ9" s="9">
+        <f>COUNTIF(C9:AG9,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR9" s="9">
+        <f>COUNTIF(C9:AG9,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS9" s="9">
+        <f>AI9+AL9</f>
+        <v/>
+      </c>
+      <c r="AT9" s="9">
+        <f>21-AI9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
-      <c r="S9" s="7" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="7" t="inlineStr"/>
-      <c r="Z9" s="7" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr"/>
-      <c r="AD9" s="4" t="inlineStr"/>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="7" t="inlineStr"/>
-      <c r="AG9" s="7" t="inlineStr"/>
-      <c r="AH9" s="4" t="n"/>
-      <c r="AI9" s="6">
-        <f>COUNTIF(C9:AG9,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ9" s="6">
-        <f>COUNTIF(C9:AG9,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK9" s="6">
-        <f>COUNTIF(C9:AG9,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL9" s="6">
-        <f>COUNTIF(C9:AG9,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM9" s="6">
-        <f>COUNTIF(C9:AG9,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN9" s="6">
-        <f>COUNTIF(C9:AG9,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO9" s="6">
-        <f>COUNTIF(C9:AG9,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP9" s="6">
-        <f>COUNTIF(C9:AG9,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ9" s="6">
-        <f>COUNTIF(C9:AG9,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR9" s="6">
-        <f>COUNTIF(C9:AG9,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS9" s="6">
-        <f>AI9+AL9</f>
-        <v/>
-      </c>
-      <c r="AT9" s="6">
-        <f>21-AI9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -1239,148 +1223,112 @@
       <c r="AF10" s="7" t="inlineStr"/>
       <c r="AG10" s="7" t="inlineStr"/>
       <c r="AH10" s="4" t="n"/>
-      <c r="AI10" s="6">
-        <f>COUNTIF(C10:AG10,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="6">
-        <f>COUNTIF(C10:AG10,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK10" s="6">
-        <f>COUNTIF(C10:AG10,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL10" s="6">
-        <f>COUNTIF(C10:AG10,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM10" s="6">
-        <f>COUNTIF(C10:AG10,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN10" s="6">
-        <f>COUNTIF(C10:AG10,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO10" s="6">
-        <f>COUNTIF(C10:AG10,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP10" s="6">
-        <f>COUNTIF(C10:AG10,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ10" s="6">
-        <f>COUNTIF(C10:AG10,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR10" s="6">
-        <f>COUNTIF(C10:AG10,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS10" s="6">
-        <f>AI10+AL10</f>
-        <v/>
-      </c>
-      <c r="AT10" s="6">
-        <f>21-AI10</f>
-        <v/>
-      </c>
+      <c r="AI10" s="4" t="n"/>
+      <c r="AJ10" s="4" t="n"/>
+      <c r="AK10" s="4" t="n"/>
+      <c r="AL10" s="4" t="n"/>
+      <c r="AM10" s="4" t="n"/>
+      <c r="AN10" s="4" t="n"/>
+      <c r="AO10" s="4" t="n"/>
+      <c r="AP10" s="4" t="n"/>
+      <c r="AQ10" s="4" t="n"/>
+      <c r="AR10" s="4" t="n"/>
+      <c r="AS10" s="4" t="n"/>
+      <c r="AT10" s="4" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="10" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
+      <c r="K11" s="11" t="inlineStr"/>
+      <c r="L11" s="11" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
+      <c r="O11" s="10" t="inlineStr"/>
+      <c r="P11" s="10" t="inlineStr"/>
+      <c r="Q11" s="10" t="inlineStr"/>
+      <c r="R11" s="11" t="inlineStr"/>
+      <c r="S11" s="11" t="inlineStr"/>
+      <c r="T11" s="10" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr"/>
+      <c r="V11" s="10" t="inlineStr"/>
+      <c r="W11" s="10" t="inlineStr"/>
+      <c r="X11" s="10" t="inlineStr"/>
+      <c r="Y11" s="11" t="inlineStr"/>
+      <c r="Z11" s="11" t="inlineStr"/>
+      <c r="AA11" s="10" t="inlineStr"/>
+      <c r="AB11" s="10" t="inlineStr"/>
+      <c r="AC11" s="10" t="inlineStr"/>
+      <c r="AD11" s="10" t="inlineStr"/>
+      <c r="AE11" s="10" t="inlineStr"/>
+      <c r="AF11" s="11" t="inlineStr"/>
+      <c r="AG11" s="11" t="inlineStr"/>
+      <c r="AH11" s="10" t="n"/>
+      <c r="AI11" s="9">
+        <f>COUNTIF(C11:AG11,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9">
+        <f>COUNTIF(C11:AG11,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK11" s="9">
+        <f>COUNTIF(C11:AG11,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL11" s="9">
+        <f>COUNTIF(C11:AG11,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9">
+        <f>COUNTIF(C11:AG11,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN11" s="9">
+        <f>COUNTIF(C11:AG11,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO11" s="9">
+        <f>COUNTIF(C11:AG11,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP11" s="9">
+        <f>COUNTIF(C11:AG11,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ11" s="9">
+        <f>COUNTIF(C11:AG11,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR11" s="9">
+        <f>COUNTIF(C11:AG11,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS11" s="9">
+        <f>AI11+AL11</f>
+        <v/>
+      </c>
+      <c r="AT11" s="9">
+        <f>21-AI11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
-      <c r="S11" s="7" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="7" t="inlineStr"/>
-      <c r="Z11" s="7" t="inlineStr"/>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr"/>
-      <c r="AD11" s="4" t="inlineStr"/>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="7" t="inlineStr"/>
-      <c r="AG11" s="7" t="inlineStr"/>
-      <c r="AH11" s="4" t="n"/>
-      <c r="AI11" s="6">
-        <f>COUNTIF(C11:AG11,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="6">
-        <f>COUNTIF(C11:AG11,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK11" s="6">
-        <f>COUNTIF(C11:AG11,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL11" s="6">
-        <f>COUNTIF(C11:AG11,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM11" s="6">
-        <f>COUNTIF(C11:AG11,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN11" s="6">
-        <f>COUNTIF(C11:AG11,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO11" s="6">
-        <f>COUNTIF(C11:AG11,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP11" s="6">
-        <f>COUNTIF(C11:AG11,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ11" s="6">
-        <f>COUNTIF(C11:AG11,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR11" s="6">
-        <f>COUNTIF(C11:AG11,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS11" s="6">
-        <f>AI11+AL11</f>
-        <v/>
-      </c>
-      <c r="AT11" s="6">
-        <f>21-AI11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -1415,148 +1363,112 @@
       <c r="AF12" s="7" t="inlineStr"/>
       <c r="AG12" s="7" t="inlineStr"/>
       <c r="AH12" s="4" t="n"/>
-      <c r="AI12" s="6">
-        <f>COUNTIF(C12:AG12,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="6">
-        <f>COUNTIF(C12:AG12,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK12" s="6">
-        <f>COUNTIF(C12:AG12,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL12" s="6">
-        <f>COUNTIF(C12:AG12,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM12" s="6">
-        <f>COUNTIF(C12:AG12,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN12" s="6">
-        <f>COUNTIF(C12:AG12,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO12" s="6">
-        <f>COUNTIF(C12:AG12,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP12" s="6">
-        <f>COUNTIF(C12:AG12,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ12" s="6">
-        <f>COUNTIF(C12:AG12,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR12" s="6">
-        <f>COUNTIF(C12:AG12,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS12" s="6">
-        <f>AI12+AL12</f>
-        <v/>
-      </c>
-      <c r="AT12" s="6">
-        <f>21-AI12</f>
-        <v/>
-      </c>
+      <c r="AI12" s="4" t="n"/>
+      <c r="AJ12" s="4" t="n"/>
+      <c r="AK12" s="4" t="n"/>
+      <c r="AL12" s="4" t="n"/>
+      <c r="AM12" s="4" t="n"/>
+      <c r="AN12" s="4" t="n"/>
+      <c r="AO12" s="4" t="n"/>
+      <c r="AP12" s="4" t="n"/>
+      <c r="AQ12" s="4" t="n"/>
+      <c r="AR12" s="4" t="n"/>
+      <c r="AS12" s="4" t="n"/>
+      <c r="AT12" s="4" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr"/>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="10" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
+      <c r="K13" s="11" t="inlineStr"/>
+      <c r="L13" s="11" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
+      <c r="O13" s="10" t="inlineStr"/>
+      <c r="P13" s="10" t="inlineStr"/>
+      <c r="Q13" s="10" t="inlineStr"/>
+      <c r="R13" s="11" t="inlineStr"/>
+      <c r="S13" s="11" t="inlineStr"/>
+      <c r="T13" s="10" t="inlineStr"/>
+      <c r="U13" s="10" t="inlineStr"/>
+      <c r="V13" s="10" t="inlineStr"/>
+      <c r="W13" s="10" t="inlineStr"/>
+      <c r="X13" s="10" t="inlineStr"/>
+      <c r="Y13" s="11" t="inlineStr"/>
+      <c r="Z13" s="11" t="inlineStr"/>
+      <c r="AA13" s="10" t="inlineStr"/>
+      <c r="AB13" s="10" t="inlineStr"/>
+      <c r="AC13" s="10" t="inlineStr"/>
+      <c r="AD13" s="10" t="inlineStr"/>
+      <c r="AE13" s="10" t="inlineStr"/>
+      <c r="AF13" s="11" t="inlineStr"/>
+      <c r="AG13" s="11" t="inlineStr"/>
+      <c r="AH13" s="10" t="n"/>
+      <c r="AI13" s="9">
+        <f>COUNTIF(C13:AG13,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="9">
+        <f>COUNTIF(C13:AG13,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK13" s="9">
+        <f>COUNTIF(C13:AG13,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL13" s="9">
+        <f>COUNTIF(C13:AG13,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9">
+        <f>COUNTIF(C13:AG13,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN13" s="9">
+        <f>COUNTIF(C13:AG13,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO13" s="9">
+        <f>COUNTIF(C13:AG13,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP13" s="9">
+        <f>COUNTIF(C13:AG13,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ13" s="9">
+        <f>COUNTIF(C13:AG13,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR13" s="9">
+        <f>COUNTIF(C13:AG13,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS13" s="9">
+        <f>AI13+AL13</f>
+        <v/>
+      </c>
+      <c r="AT13" s="9">
+        <f>21-AI13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
-      <c r="S13" s="7" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="inlineStr"/>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="7" t="inlineStr"/>
-      <c r="Z13" s="7" t="inlineStr"/>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr"/>
-      <c r="AD13" s="4" t="inlineStr"/>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="7" t="inlineStr"/>
-      <c r="AG13" s="7" t="inlineStr"/>
-      <c r="AH13" s="4" t="n"/>
-      <c r="AI13" s="6">
-        <f>COUNTIF(C13:AG13,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ13" s="6">
-        <f>COUNTIF(C13:AG13,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK13" s="6">
-        <f>COUNTIF(C13:AG13,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL13" s="6">
-        <f>COUNTIF(C13:AG13,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM13" s="6">
-        <f>COUNTIF(C13:AG13,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN13" s="6">
-        <f>COUNTIF(C13:AG13,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO13" s="6">
-        <f>COUNTIF(C13:AG13,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP13" s="6">
-        <f>COUNTIF(C13:AG13,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ13" s="6">
-        <f>COUNTIF(C13:AG13,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR13" s="6">
-        <f>COUNTIF(C13:AG13,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS13" s="6">
-        <f>AI13+AL13</f>
-        <v/>
-      </c>
-      <c r="AT13" s="6">
-        <f>21-AI13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -1591,148 +1503,112 @@
       <c r="AF14" s="7" t="inlineStr"/>
       <c r="AG14" s="7" t="inlineStr"/>
       <c r="AH14" s="4" t="n"/>
-      <c r="AI14" s="6">
-        <f>COUNTIF(C14:AG14,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="6">
-        <f>COUNTIF(C14:AG14,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK14" s="6">
-        <f>COUNTIF(C14:AG14,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL14" s="6">
-        <f>COUNTIF(C14:AG14,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM14" s="6">
-        <f>COUNTIF(C14:AG14,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN14" s="6">
-        <f>COUNTIF(C14:AG14,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO14" s="6">
-        <f>COUNTIF(C14:AG14,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP14" s="6">
-        <f>COUNTIF(C14:AG14,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ14" s="6">
-        <f>COUNTIF(C14:AG14,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR14" s="6">
-        <f>COUNTIF(C14:AG14,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS14" s="6">
-        <f>AI14+AL14</f>
-        <v/>
-      </c>
-      <c r="AT14" s="6">
-        <f>21-AI14</f>
-        <v/>
-      </c>
+      <c r="AI14" s="4" t="n"/>
+      <c r="AJ14" s="4" t="n"/>
+      <c r="AK14" s="4" t="n"/>
+      <c r="AL14" s="4" t="n"/>
+      <c r="AM14" s="4" t="n"/>
+      <c r="AN14" s="4" t="n"/>
+      <c r="AO14" s="4" t="n"/>
+      <c r="AP14" s="4" t="n"/>
+      <c r="AQ14" s="4" t="n"/>
+      <c r="AR14" s="4" t="n"/>
+      <c r="AS14" s="4" t="n"/>
+      <c r="AT14" s="4" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr"/>
+      <c r="P15" s="10" t="inlineStr"/>
+      <c r="Q15" s="10" t="inlineStr"/>
+      <c r="R15" s="11" t="inlineStr"/>
+      <c r="S15" s="11" t="inlineStr"/>
+      <c r="T15" s="10" t="inlineStr"/>
+      <c r="U15" s="10" t="inlineStr"/>
+      <c r="V15" s="10" t="inlineStr"/>
+      <c r="W15" s="10" t="inlineStr"/>
+      <c r="X15" s="10" t="inlineStr"/>
+      <c r="Y15" s="11" t="inlineStr"/>
+      <c r="Z15" s="11" t="inlineStr"/>
+      <c r="AA15" s="10" t="inlineStr"/>
+      <c r="AB15" s="10" t="inlineStr"/>
+      <c r="AC15" s="10" t="inlineStr"/>
+      <c r="AD15" s="10" t="inlineStr"/>
+      <c r="AE15" s="10" t="inlineStr"/>
+      <c r="AF15" s="11" t="inlineStr"/>
+      <c r="AG15" s="11" t="inlineStr"/>
+      <c r="AH15" s="10" t="n"/>
+      <c r="AI15" s="9">
+        <f>COUNTIF(C15:AG15,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="9">
+        <f>COUNTIF(C15:AG15,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK15" s="9">
+        <f>COUNTIF(C15:AG15,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="9">
+        <f>COUNTIF(C15:AG15,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="9">
+        <f>COUNTIF(C15:AG15,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN15" s="9">
+        <f>COUNTIF(C15:AG15,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO15" s="9">
+        <f>COUNTIF(C15:AG15,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP15" s="9">
+        <f>COUNTIF(C15:AG15,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ15" s="9">
+        <f>COUNTIF(C15:AG15,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR15" s="9">
+        <f>COUNTIF(C15:AG15,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS15" s="9">
+        <f>AI15+AL15</f>
+        <v/>
+      </c>
+      <c r="AT15" s="9">
+        <f>21-AI15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="inlineStr"/>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="inlineStr"/>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="7" t="inlineStr"/>
-      <c r="Z15" s="7" t="inlineStr"/>
-      <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr"/>
-      <c r="AD15" s="4" t="inlineStr"/>
-      <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="7" t="inlineStr"/>
-      <c r="AG15" s="7" t="inlineStr"/>
-      <c r="AH15" s="4" t="n"/>
-      <c r="AI15" s="6">
-        <f>COUNTIF(C15:AG15,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="6">
-        <f>COUNTIF(C15:AG15,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK15" s="6">
-        <f>COUNTIF(C15:AG15,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL15" s="6">
-        <f>COUNTIF(C15:AG15,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM15" s="6">
-        <f>COUNTIF(C15:AG15,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN15" s="6">
-        <f>COUNTIF(C15:AG15,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO15" s="6">
-        <f>COUNTIF(C15:AG15,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP15" s="6">
-        <f>COUNTIF(C15:AG15,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ15" s="6">
-        <f>COUNTIF(C15:AG15,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR15" s="6">
-        <f>COUNTIF(C15:AG15,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS15" s="6">
-        <f>AI15+AL15</f>
-        <v/>
-      </c>
-      <c r="AT15" s="6">
-        <f>21-AI15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -1767,148 +1643,112 @@
       <c r="AF16" s="7" t="inlineStr"/>
       <c r="AG16" s="7" t="inlineStr"/>
       <c r="AH16" s="4" t="n"/>
-      <c r="AI16" s="6">
-        <f>COUNTIF(C16:AG16,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="6">
-        <f>COUNTIF(C16:AG16,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK16" s="6">
-        <f>COUNTIF(C16:AG16,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL16" s="6">
-        <f>COUNTIF(C16:AG16,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM16" s="6">
-        <f>COUNTIF(C16:AG16,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN16" s="6">
-        <f>COUNTIF(C16:AG16,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO16" s="6">
-        <f>COUNTIF(C16:AG16,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP16" s="6">
-        <f>COUNTIF(C16:AG16,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ16" s="6">
-        <f>COUNTIF(C16:AG16,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR16" s="6">
-        <f>COUNTIF(C16:AG16,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS16" s="6">
-        <f>AI16+AL16</f>
-        <v/>
-      </c>
-      <c r="AT16" s="6">
-        <f>21-AI16</f>
-        <v/>
-      </c>
+      <c r="AI16" s="4" t="n"/>
+      <c r="AJ16" s="4" t="n"/>
+      <c r="AK16" s="4" t="n"/>
+      <c r="AL16" s="4" t="n"/>
+      <c r="AM16" s="4" t="n"/>
+      <c r="AN16" s="4" t="n"/>
+      <c r="AO16" s="4" t="n"/>
+      <c r="AP16" s="4" t="n"/>
+      <c r="AQ16" s="4" t="n"/>
+      <c r="AR16" s="4" t="n"/>
+      <c r="AS16" s="4" t="n"/>
+      <c r="AT16" s="4" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr"/>
+      <c r="E17" s="11" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="10" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr"/>
+      <c r="L17" s="11" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr"/>
+      <c r="P17" s="10" t="inlineStr"/>
+      <c r="Q17" s="10" t="inlineStr"/>
+      <c r="R17" s="11" t="inlineStr"/>
+      <c r="S17" s="11" t="inlineStr"/>
+      <c r="T17" s="10" t="inlineStr"/>
+      <c r="U17" s="10" t="inlineStr"/>
+      <c r="V17" s="10" t="inlineStr"/>
+      <c r="W17" s="10" t="inlineStr"/>
+      <c r="X17" s="10" t="inlineStr"/>
+      <c r="Y17" s="11" t="inlineStr"/>
+      <c r="Z17" s="11" t="inlineStr"/>
+      <c r="AA17" s="10" t="inlineStr"/>
+      <c r="AB17" s="10" t="inlineStr"/>
+      <c r="AC17" s="10" t="inlineStr"/>
+      <c r="AD17" s="10" t="inlineStr"/>
+      <c r="AE17" s="10" t="inlineStr"/>
+      <c r="AF17" s="11" t="inlineStr"/>
+      <c r="AG17" s="11" t="inlineStr"/>
+      <c r="AH17" s="10" t="n"/>
+      <c r="AI17" s="9">
+        <f>COUNTIF(C17:AG17,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="9">
+        <f>COUNTIF(C17:AG17,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK17" s="9">
+        <f>COUNTIF(C17:AG17,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL17" s="9">
+        <f>COUNTIF(C17:AG17,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM17" s="9">
+        <f>COUNTIF(C17:AG17,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN17" s="9">
+        <f>COUNTIF(C17:AG17,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO17" s="9">
+        <f>COUNTIF(C17:AG17,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP17" s="9">
+        <f>COUNTIF(C17:AG17,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ17" s="9">
+        <f>COUNTIF(C17:AG17,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR17" s="9">
+        <f>COUNTIF(C17:AG17,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS17" s="9">
+        <f>AI17+AL17</f>
+        <v/>
+      </c>
+      <c r="AT17" s="9">
+        <f>21-AI17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="inlineStr"/>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="7" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="7" t="inlineStr"/>
-      <c r="Z17" s="7" t="inlineStr"/>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="inlineStr"/>
-      <c r="AD17" s="4" t="inlineStr"/>
-      <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="7" t="inlineStr"/>
-      <c r="AG17" s="7" t="inlineStr"/>
-      <c r="AH17" s="4" t="n"/>
-      <c r="AI17" s="6">
-        <f>COUNTIF(C17:AG17,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="6">
-        <f>COUNTIF(C17:AG17,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK17" s="6">
-        <f>COUNTIF(C17:AG17,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL17" s="6">
-        <f>COUNTIF(C17:AG17,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM17" s="6">
-        <f>COUNTIF(C17:AG17,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN17" s="6">
-        <f>COUNTIF(C17:AG17,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO17" s="6">
-        <f>COUNTIF(C17:AG17,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP17" s="6">
-        <f>COUNTIF(C17:AG17,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ17" s="6">
-        <f>COUNTIF(C17:AG17,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR17" s="6">
-        <f>COUNTIF(C17:AG17,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS17" s="6">
-        <f>AI17+AL17</f>
-        <v/>
-      </c>
-      <c r="AT17" s="6">
-        <f>21-AI17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1943,148 +1783,112 @@
       <c r="AF18" s="7" t="inlineStr"/>
       <c r="AG18" s="7" t="inlineStr"/>
       <c r="AH18" s="4" t="n"/>
-      <c r="AI18" s="6">
-        <f>COUNTIF(C18:AG18,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ18" s="6">
-        <f>COUNTIF(C18:AG18,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK18" s="6">
-        <f>COUNTIF(C18:AG18,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL18" s="6">
-        <f>COUNTIF(C18:AG18,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM18" s="6">
-        <f>COUNTIF(C18:AG18,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN18" s="6">
-        <f>COUNTIF(C18:AG18,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO18" s="6">
-        <f>COUNTIF(C18:AG18,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP18" s="6">
-        <f>COUNTIF(C18:AG18,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ18" s="6">
-        <f>COUNTIF(C18:AG18,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR18" s="6">
-        <f>COUNTIF(C18:AG18,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS18" s="6">
-        <f>AI18+AL18</f>
-        <v/>
-      </c>
-      <c r="AT18" s="6">
-        <f>21-AI18</f>
-        <v/>
-      </c>
+      <c r="AI18" s="4" t="n"/>
+      <c r="AJ18" s="4" t="n"/>
+      <c r="AK18" s="4" t="n"/>
+      <c r="AL18" s="4" t="n"/>
+      <c r="AM18" s="4" t="n"/>
+      <c r="AN18" s="4" t="n"/>
+      <c r="AO18" s="4" t="n"/>
+      <c r="AP18" s="4" t="n"/>
+      <c r="AQ18" s="4" t="n"/>
+      <c r="AR18" s="4" t="n"/>
+      <c r="AS18" s="4" t="n"/>
+      <c r="AT18" s="4" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr"/>
+      <c r="D19" s="11" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
+      <c r="H19" s="10" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
+      <c r="K19" s="11" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr"/>
+      <c r="P19" s="10" t="inlineStr"/>
+      <c r="Q19" s="10" t="inlineStr"/>
+      <c r="R19" s="11" t="inlineStr"/>
+      <c r="S19" s="11" t="inlineStr"/>
+      <c r="T19" s="10" t="inlineStr"/>
+      <c r="U19" s="10" t="inlineStr"/>
+      <c r="V19" s="10" t="inlineStr"/>
+      <c r="W19" s="10" t="inlineStr"/>
+      <c r="X19" s="10" t="inlineStr"/>
+      <c r="Y19" s="11" t="inlineStr"/>
+      <c r="Z19" s="11" t="inlineStr"/>
+      <c r="AA19" s="10" t="inlineStr"/>
+      <c r="AB19" s="10" t="inlineStr"/>
+      <c r="AC19" s="10" t="inlineStr"/>
+      <c r="AD19" s="10" t="inlineStr"/>
+      <c r="AE19" s="10" t="inlineStr"/>
+      <c r="AF19" s="11" t="inlineStr"/>
+      <c r="AG19" s="11" t="inlineStr"/>
+      <c r="AH19" s="10" t="n"/>
+      <c r="AI19" s="9">
+        <f>COUNTIF(C19:AG19,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="9">
+        <f>COUNTIF(C19:AG19,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK19" s="9">
+        <f>COUNTIF(C19:AG19,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="9">
+        <f>COUNTIF(C19:AG19,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="9">
+        <f>COUNTIF(C19:AG19,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN19" s="9">
+        <f>COUNTIF(C19:AG19,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO19" s="9">
+        <f>COUNTIF(C19:AG19,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP19" s="9">
+        <f>COUNTIF(C19:AG19,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="9">
+        <f>COUNTIF(C19:AG19,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR19" s="9">
+        <f>COUNTIF(C19:AG19,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS19" s="9">
+        <f>AI19+AL19</f>
+        <v/>
+      </c>
+      <c r="AT19" s="9">
+        <f>21-AI19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="7" t="inlineStr"/>
-      <c r="S19" s="7" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="inlineStr"/>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="7" t="inlineStr"/>
-      <c r="Z19" s="7" t="inlineStr"/>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="inlineStr"/>
-      <c r="AD19" s="4" t="inlineStr"/>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="7" t="inlineStr"/>
-      <c r="AG19" s="7" t="inlineStr"/>
-      <c r="AH19" s="4" t="n"/>
-      <c r="AI19" s="6">
-        <f>COUNTIF(C19:AG19,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="6">
-        <f>COUNTIF(C19:AG19,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK19" s="6">
-        <f>COUNTIF(C19:AG19,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL19" s="6">
-        <f>COUNTIF(C19:AG19,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM19" s="6">
-        <f>COUNTIF(C19:AG19,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN19" s="6">
-        <f>COUNTIF(C19:AG19,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO19" s="6">
-        <f>COUNTIF(C19:AG19,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP19" s="6">
-        <f>COUNTIF(C19:AG19,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ19" s="6">
-        <f>COUNTIF(C19:AG19,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR19" s="6">
-        <f>COUNTIF(C19:AG19,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS19" s="6">
-        <f>AI19+AL19</f>
-        <v/>
-      </c>
-      <c r="AT19" s="6">
-        <f>21-AI19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -2119,148 +1923,112 @@
       <c r="AF20" s="7" t="inlineStr"/>
       <c r="AG20" s="7" t="inlineStr"/>
       <c r="AH20" s="4" t="n"/>
-      <c r="AI20" s="6">
-        <f>COUNTIF(C20:AG20,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="6">
-        <f>COUNTIF(C20:AG20,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK20" s="6">
-        <f>COUNTIF(C20:AG20,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL20" s="6">
-        <f>COUNTIF(C20:AG20,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM20" s="6">
-        <f>COUNTIF(C20:AG20,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN20" s="6">
-        <f>COUNTIF(C20:AG20,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO20" s="6">
-        <f>COUNTIF(C20:AG20,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP20" s="6">
-        <f>COUNTIF(C20:AG20,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ20" s="6">
-        <f>COUNTIF(C20:AG20,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR20" s="6">
-        <f>COUNTIF(C20:AG20,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS20" s="6">
-        <f>AI20+AL20</f>
-        <v/>
-      </c>
-      <c r="AT20" s="6">
-        <f>21-AI20</f>
-        <v/>
-      </c>
+      <c r="AI20" s="4" t="n"/>
+      <c r="AJ20" s="4" t="n"/>
+      <c r="AK20" s="4" t="n"/>
+      <c r="AL20" s="4" t="n"/>
+      <c r="AM20" s="4" t="n"/>
+      <c r="AN20" s="4" t="n"/>
+      <c r="AO20" s="4" t="n"/>
+      <c r="AP20" s="4" t="n"/>
+      <c r="AQ20" s="4" t="n"/>
+      <c r="AR20" s="4" t="n"/>
+      <c r="AS20" s="4" t="n"/>
+      <c r="AT20" s="4" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr"/>
+      <c r="D21" s="11" t="inlineStr"/>
+      <c r="E21" s="11" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr"/>
+      <c r="L21" s="11" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
+      <c r="O21" s="10" t="inlineStr"/>
+      <c r="P21" s="10" t="inlineStr"/>
+      <c r="Q21" s="10" t="inlineStr"/>
+      <c r="R21" s="11" t="inlineStr"/>
+      <c r="S21" s="11" t="inlineStr"/>
+      <c r="T21" s="10" t="inlineStr"/>
+      <c r="U21" s="10" t="inlineStr"/>
+      <c r="V21" s="10" t="inlineStr"/>
+      <c r="W21" s="10" t="inlineStr"/>
+      <c r="X21" s="10" t="inlineStr"/>
+      <c r="Y21" s="11" t="inlineStr"/>
+      <c r="Z21" s="11" t="inlineStr"/>
+      <c r="AA21" s="10" t="inlineStr"/>
+      <c r="AB21" s="10" t="inlineStr"/>
+      <c r="AC21" s="10" t="inlineStr"/>
+      <c r="AD21" s="10" t="inlineStr"/>
+      <c r="AE21" s="10" t="inlineStr"/>
+      <c r="AF21" s="11" t="inlineStr"/>
+      <c r="AG21" s="11" t="inlineStr"/>
+      <c r="AH21" s="10" t="n"/>
+      <c r="AI21" s="9">
+        <f>COUNTIF(C21:AG21,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="9">
+        <f>COUNTIF(C21:AG21,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK21" s="9">
+        <f>COUNTIF(C21:AG21,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="9">
+        <f>COUNTIF(C21:AG21,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="9">
+        <f>COUNTIF(C21:AG21,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN21" s="9">
+        <f>COUNTIF(C21:AG21,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO21" s="9">
+        <f>COUNTIF(C21:AG21,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP21" s="9">
+        <f>COUNTIF(C21:AG21,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ21" s="9">
+        <f>COUNTIF(C21:AG21,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR21" s="9">
+        <f>COUNTIF(C21:AG21,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS21" s="9">
+        <f>AI21+AL21</f>
+        <v/>
+      </c>
+      <c r="AT21" s="9">
+        <f>21-AI21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="inlineStr"/>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="7" t="inlineStr"/>
-      <c r="S21" s="7" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="4" t="inlineStr"/>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr"/>
-      <c r="Y21" s="7" t="inlineStr"/>
-      <c r="Z21" s="7" t="inlineStr"/>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="inlineStr"/>
-      <c r="AD21" s="4" t="inlineStr"/>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="7" t="inlineStr"/>
-      <c r="AG21" s="7" t="inlineStr"/>
-      <c r="AH21" s="4" t="n"/>
-      <c r="AI21" s="6">
-        <f>COUNTIF(C21:AG21,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="6">
-        <f>COUNTIF(C21:AG21,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK21" s="6">
-        <f>COUNTIF(C21:AG21,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL21" s="6">
-        <f>COUNTIF(C21:AG21,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM21" s="6">
-        <f>COUNTIF(C21:AG21,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN21" s="6">
-        <f>COUNTIF(C21:AG21,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO21" s="6">
-        <f>COUNTIF(C21:AG21,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP21" s="6">
-        <f>COUNTIF(C21:AG21,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ21" s="6">
-        <f>COUNTIF(C21:AG21,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR21" s="6">
-        <f>COUNTIF(C21:AG21,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS21" s="6">
-        <f>AI21+AL21</f>
-        <v/>
-      </c>
-      <c r="AT21" s="6">
-        <f>21-AI21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -2295,148 +2063,112 @@
       <c r="AF22" s="7" t="inlineStr"/>
       <c r="AG22" s="7" t="inlineStr"/>
       <c r="AH22" s="4" t="n"/>
-      <c r="AI22" s="6">
-        <f>COUNTIF(C22:AG22,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="6">
-        <f>COUNTIF(C22:AG22,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK22" s="6">
-        <f>COUNTIF(C22:AG22,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL22" s="6">
-        <f>COUNTIF(C22:AG22,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM22" s="6">
-        <f>COUNTIF(C22:AG22,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN22" s="6">
-        <f>COUNTIF(C22:AG22,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO22" s="6">
-        <f>COUNTIF(C22:AG22,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP22" s="6">
-        <f>COUNTIF(C22:AG22,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ22" s="6">
-        <f>COUNTIF(C22:AG22,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR22" s="6">
-        <f>COUNTIF(C22:AG22,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS22" s="6">
-        <f>AI22+AL22</f>
-        <v/>
-      </c>
-      <c r="AT22" s="6">
-        <f>21-AI22</f>
-        <v/>
-      </c>
+      <c r="AI22" s="4" t="n"/>
+      <c r="AJ22" s="4" t="n"/>
+      <c r="AK22" s="4" t="n"/>
+      <c r="AL22" s="4" t="n"/>
+      <c r="AM22" s="4" t="n"/>
+      <c r="AN22" s="4" t="n"/>
+      <c r="AO22" s="4" t="n"/>
+      <c r="AP22" s="4" t="n"/>
+      <c r="AQ22" s="4" t="n"/>
+      <c r="AR22" s="4" t="n"/>
+      <c r="AS22" s="4" t="n"/>
+      <c r="AT22" s="4" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr"/>
+      <c r="D23" s="11" t="inlineStr"/>
+      <c r="E23" s="11" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr"/>
+      <c r="L23" s="11" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
+      <c r="O23" s="10" t="inlineStr"/>
+      <c r="P23" s="10" t="inlineStr"/>
+      <c r="Q23" s="10" t="inlineStr"/>
+      <c r="R23" s="11" t="inlineStr"/>
+      <c r="S23" s="11" t="inlineStr"/>
+      <c r="T23" s="10" t="inlineStr"/>
+      <c r="U23" s="10" t="inlineStr"/>
+      <c r="V23" s="10" t="inlineStr"/>
+      <c r="W23" s="10" t="inlineStr"/>
+      <c r="X23" s="10" t="inlineStr"/>
+      <c r="Y23" s="11" t="inlineStr"/>
+      <c r="Z23" s="11" t="inlineStr"/>
+      <c r="AA23" s="10" t="inlineStr"/>
+      <c r="AB23" s="10" t="inlineStr"/>
+      <c r="AC23" s="10" t="inlineStr"/>
+      <c r="AD23" s="10" t="inlineStr"/>
+      <c r="AE23" s="10" t="inlineStr"/>
+      <c r="AF23" s="11" t="inlineStr"/>
+      <c r="AG23" s="11" t="inlineStr"/>
+      <c r="AH23" s="10" t="n"/>
+      <c r="AI23" s="9">
+        <f>COUNTIF(C23:AG23,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="9">
+        <f>COUNTIF(C23:AG23,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK23" s="9">
+        <f>COUNTIF(C23:AG23,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL23" s="9">
+        <f>COUNTIF(C23:AG23,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM23" s="9">
+        <f>COUNTIF(C23:AG23,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN23" s="9">
+        <f>COUNTIF(C23:AG23,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO23" s="9">
+        <f>COUNTIF(C23:AG23,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP23" s="9">
+        <f>COUNTIF(C23:AG23,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ23" s="9">
+        <f>COUNTIF(C23:AG23,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR23" s="9">
+        <f>COUNTIF(C23:AG23,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS23" s="9">
+        <f>AI23+AL23</f>
+        <v/>
+      </c>
+      <c r="AT23" s="9">
+        <f>21-AI23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="4" t="inlineStr"/>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr"/>
-      <c r="R23" s="7" t="inlineStr"/>
-      <c r="S23" s="7" t="inlineStr"/>
-      <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="inlineStr"/>
-      <c r="W23" s="4" t="inlineStr"/>
-      <c r="X23" s="4" t="inlineStr"/>
-      <c r="Y23" s="7" t="inlineStr"/>
-      <c r="Z23" s="7" t="inlineStr"/>
-      <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="inlineStr"/>
-      <c r="AD23" s="4" t="inlineStr"/>
-      <c r="AE23" s="4" t="inlineStr"/>
-      <c r="AF23" s="7" t="inlineStr"/>
-      <c r="AG23" s="7" t="inlineStr"/>
-      <c r="AH23" s="4" t="n"/>
-      <c r="AI23" s="6">
-        <f>COUNTIF(C23:AG23,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="6">
-        <f>COUNTIF(C23:AG23,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK23" s="6">
-        <f>COUNTIF(C23:AG23,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL23" s="6">
-        <f>COUNTIF(C23:AG23,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM23" s="6">
-        <f>COUNTIF(C23:AG23,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN23" s="6">
-        <f>COUNTIF(C23:AG23,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO23" s="6">
-        <f>COUNTIF(C23:AG23,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP23" s="6">
-        <f>COUNTIF(C23:AG23,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ23" s="6">
-        <f>COUNTIF(C23:AG23,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR23" s="6">
-        <f>COUNTIF(C23:AG23,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS23" s="6">
-        <f>AI23+AL23</f>
-        <v/>
-      </c>
-      <c r="AT23" s="6">
-        <f>21-AI23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -2471,148 +2203,112 @@
       <c r="AF24" s="7" t="inlineStr"/>
       <c r="AG24" s="7" t="inlineStr"/>
       <c r="AH24" s="4" t="n"/>
-      <c r="AI24" s="6">
-        <f>COUNTIF(C24:AG24,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ24" s="6">
-        <f>COUNTIF(C24:AG24,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK24" s="6">
-        <f>COUNTIF(C24:AG24,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL24" s="6">
-        <f>COUNTIF(C24:AG24,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM24" s="6">
-        <f>COUNTIF(C24:AG24,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN24" s="6">
-        <f>COUNTIF(C24:AG24,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO24" s="6">
-        <f>COUNTIF(C24:AG24,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP24" s="6">
-        <f>COUNTIF(C24:AG24,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ24" s="6">
-        <f>COUNTIF(C24:AG24,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR24" s="6">
-        <f>COUNTIF(C24:AG24,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS24" s="6">
-        <f>AI24+AL24</f>
-        <v/>
-      </c>
-      <c r="AT24" s="6">
-        <f>21-AI24</f>
-        <v/>
-      </c>
+      <c r="AI24" s="4" t="n"/>
+      <c r="AJ24" s="4" t="n"/>
+      <c r="AK24" s="4" t="n"/>
+      <c r="AL24" s="4" t="n"/>
+      <c r="AM24" s="4" t="n"/>
+      <c r="AN24" s="4" t="n"/>
+      <c r="AO24" s="4" t="n"/>
+      <c r="AP24" s="4" t="n"/>
+      <c r="AQ24" s="4" t="n"/>
+      <c r="AR24" s="4" t="n"/>
+      <c r="AS24" s="4" t="n"/>
+      <c r="AT24" s="4" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
+      <c r="D25" s="11" t="inlineStr"/>
+      <c r="E25" s="11" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr"/>
+      <c r="L25" s="11" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
+      <c r="O25" s="10" t="inlineStr"/>
+      <c r="P25" s="10" t="inlineStr"/>
+      <c r="Q25" s="10" t="inlineStr"/>
+      <c r="R25" s="11" t="inlineStr"/>
+      <c r="S25" s="11" t="inlineStr"/>
+      <c r="T25" s="10" t="inlineStr"/>
+      <c r="U25" s="10" t="inlineStr"/>
+      <c r="V25" s="10" t="inlineStr"/>
+      <c r="W25" s="10" t="inlineStr"/>
+      <c r="X25" s="10" t="inlineStr"/>
+      <c r="Y25" s="11" t="inlineStr"/>
+      <c r="Z25" s="11" t="inlineStr"/>
+      <c r="AA25" s="10" t="inlineStr"/>
+      <c r="AB25" s="10" t="inlineStr"/>
+      <c r="AC25" s="10" t="inlineStr"/>
+      <c r="AD25" s="10" t="inlineStr"/>
+      <c r="AE25" s="10" t="inlineStr"/>
+      <c r="AF25" s="11" t="inlineStr"/>
+      <c r="AG25" s="11" t="inlineStr"/>
+      <c r="AH25" s="10" t="n"/>
+      <c r="AI25" s="9">
+        <f>COUNTIF(C25:AG25,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="9">
+        <f>COUNTIF(C25:AG25,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK25" s="9">
+        <f>COUNTIF(C25:AG25,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL25" s="9">
+        <f>COUNTIF(C25:AG25,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM25" s="9">
+        <f>COUNTIF(C25:AG25,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN25" s="9">
+        <f>COUNTIF(C25:AG25,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO25" s="9">
+        <f>COUNTIF(C25:AG25,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP25" s="9">
+        <f>COUNTIF(C25:AG25,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ25" s="9">
+        <f>COUNTIF(C25:AG25,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR25" s="9">
+        <f>COUNTIF(C25:AG25,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS25" s="9">
+        <f>AI25+AL25</f>
+        <v/>
+      </c>
+      <c r="AT25" s="9">
+        <f>21-AI25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr"/>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr"/>
-      <c r="N25" s="4" t="inlineStr"/>
-      <c r="O25" s="4" t="inlineStr"/>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="inlineStr"/>
-      <c r="R25" s="7" t="inlineStr"/>
-      <c r="S25" s="7" t="inlineStr"/>
-      <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="inlineStr"/>
-      <c r="W25" s="4" t="inlineStr"/>
-      <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="7" t="inlineStr"/>
-      <c r="Z25" s="7" t="inlineStr"/>
-      <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="inlineStr"/>
-      <c r="AC25" s="4" t="inlineStr"/>
-      <c r="AD25" s="4" t="inlineStr"/>
-      <c r="AE25" s="4" t="inlineStr"/>
-      <c r="AF25" s="7" t="inlineStr"/>
-      <c r="AG25" s="7" t="inlineStr"/>
-      <c r="AH25" s="4" t="n"/>
-      <c r="AI25" s="6">
-        <f>COUNTIF(C25:AG25,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ25" s="6">
-        <f>COUNTIF(C25:AG25,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK25" s="6">
-        <f>COUNTIF(C25:AG25,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL25" s="6">
-        <f>COUNTIF(C25:AG25,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM25" s="6">
-        <f>COUNTIF(C25:AG25,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN25" s="6">
-        <f>COUNTIF(C25:AG25,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO25" s="6">
-        <f>COUNTIF(C25:AG25,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP25" s="6">
-        <f>COUNTIF(C25:AG25,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ25" s="6">
-        <f>COUNTIF(C25:AG25,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR25" s="6">
-        <f>COUNTIF(C25:AG25,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS25" s="6">
-        <f>AI25+AL25</f>
-        <v/>
-      </c>
-      <c r="AT25" s="6">
-        <f>21-AI25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -2647,148 +2343,112 @@
       <c r="AF26" s="7" t="inlineStr"/>
       <c r="AG26" s="7" t="inlineStr"/>
       <c r="AH26" s="4" t="n"/>
-      <c r="AI26" s="6">
-        <f>COUNTIF(C26:AG26,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ26" s="6">
-        <f>COUNTIF(C26:AG26,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK26" s="6">
-        <f>COUNTIF(C26:AG26,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL26" s="6">
-        <f>COUNTIF(C26:AG26,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM26" s="6">
-        <f>COUNTIF(C26:AG26,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN26" s="6">
-        <f>COUNTIF(C26:AG26,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO26" s="6">
-        <f>COUNTIF(C26:AG26,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP26" s="6">
-        <f>COUNTIF(C26:AG26,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ26" s="6">
-        <f>COUNTIF(C26:AG26,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR26" s="6">
-        <f>COUNTIF(C26:AG26,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS26" s="6">
-        <f>AI26+AL26</f>
-        <v/>
-      </c>
-      <c r="AT26" s="6">
-        <f>21-AI26</f>
-        <v/>
-      </c>
+      <c r="AI26" s="4" t="n"/>
+      <c r="AJ26" s="4" t="n"/>
+      <c r="AK26" s="4" t="n"/>
+      <c r="AL26" s="4" t="n"/>
+      <c r="AM26" s="4" t="n"/>
+      <c r="AN26" s="4" t="n"/>
+      <c r="AO26" s="4" t="n"/>
+      <c r="AP26" s="4" t="n"/>
+      <c r="AQ26" s="4" t="n"/>
+      <c r="AR26" s="4" t="n"/>
+      <c r="AS26" s="4" t="n"/>
+      <c r="AT26" s="4" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="10" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr"/>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr"/>
+      <c r="L27" s="11" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
+      <c r="O27" s="10" t="inlineStr"/>
+      <c r="P27" s="10" t="inlineStr"/>
+      <c r="Q27" s="10" t="inlineStr"/>
+      <c r="R27" s="11" t="inlineStr"/>
+      <c r="S27" s="11" t="inlineStr"/>
+      <c r="T27" s="10" t="inlineStr"/>
+      <c r="U27" s="10" t="inlineStr"/>
+      <c r="V27" s="10" t="inlineStr"/>
+      <c r="W27" s="10" t="inlineStr"/>
+      <c r="X27" s="10" t="inlineStr"/>
+      <c r="Y27" s="11" t="inlineStr"/>
+      <c r="Z27" s="11" t="inlineStr"/>
+      <c r="AA27" s="10" t="inlineStr"/>
+      <c r="AB27" s="10" t="inlineStr"/>
+      <c r="AC27" s="10" t="inlineStr"/>
+      <c r="AD27" s="10" t="inlineStr"/>
+      <c r="AE27" s="10" t="inlineStr"/>
+      <c r="AF27" s="11" t="inlineStr"/>
+      <c r="AG27" s="11" t="inlineStr"/>
+      <c r="AH27" s="10" t="n"/>
+      <c r="AI27" s="9">
+        <f>COUNTIF(C27:AG27,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="9">
+        <f>COUNTIF(C27:AG27,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK27" s="9">
+        <f>COUNTIF(C27:AG27,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL27" s="9">
+        <f>COUNTIF(C27:AG27,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM27" s="9">
+        <f>COUNTIF(C27:AG27,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN27" s="9">
+        <f>COUNTIF(C27:AG27,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO27" s="9">
+        <f>COUNTIF(C27:AG27,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP27" s="9">
+        <f>COUNTIF(C27:AG27,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ27" s="9">
+        <f>COUNTIF(C27:AG27,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR27" s="9">
+        <f>COUNTIF(C27:AG27,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS27" s="9">
+        <f>AI27+AL27</f>
+        <v/>
+      </c>
+      <c r="AT27" s="9">
+        <f>21-AI27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr"/>
-      <c r="O27" s="4" t="inlineStr"/>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="inlineStr"/>
-      <c r="R27" s="7" t="inlineStr"/>
-      <c r="S27" s="7" t="inlineStr"/>
-      <c r="T27" s="4" t="inlineStr"/>
-      <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="4" t="inlineStr"/>
-      <c r="W27" s="4" t="inlineStr"/>
-      <c r="X27" s="4" t="inlineStr"/>
-      <c r="Y27" s="7" t="inlineStr"/>
-      <c r="Z27" s="7" t="inlineStr"/>
-      <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="inlineStr"/>
-      <c r="AD27" s="4" t="inlineStr"/>
-      <c r="AE27" s="4" t="inlineStr"/>
-      <c r="AF27" s="7" t="inlineStr"/>
-      <c r="AG27" s="7" t="inlineStr"/>
-      <c r="AH27" s="4" t="n"/>
-      <c r="AI27" s="6">
-        <f>COUNTIF(C27:AG27,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ27" s="6">
-        <f>COUNTIF(C27:AG27,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK27" s="6">
-        <f>COUNTIF(C27:AG27,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL27" s="6">
-        <f>COUNTIF(C27:AG27,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM27" s="6">
-        <f>COUNTIF(C27:AG27,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN27" s="6">
-        <f>COUNTIF(C27:AG27,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO27" s="6">
-        <f>COUNTIF(C27:AG27,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP27" s="6">
-        <f>COUNTIF(C27:AG27,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ27" s="6">
-        <f>COUNTIF(C27:AG27,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR27" s="6">
-        <f>COUNTIF(C27:AG27,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS27" s="6">
-        <f>AI27+AL27</f>
-        <v/>
-      </c>
-      <c r="AT27" s="6">
-        <f>21-AI27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -2823,148 +2483,112 @@
       <c r="AF28" s="7" t="inlineStr"/>
       <c r="AG28" s="7" t="inlineStr"/>
       <c r="AH28" s="4" t="n"/>
-      <c r="AI28" s="6">
-        <f>COUNTIF(C28:AG28,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ28" s="6">
-        <f>COUNTIF(C28:AG28,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK28" s="6">
-        <f>COUNTIF(C28:AG28,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL28" s="6">
-        <f>COUNTIF(C28:AG28,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM28" s="6">
-        <f>COUNTIF(C28:AG28,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN28" s="6">
-        <f>COUNTIF(C28:AG28,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO28" s="6">
-        <f>COUNTIF(C28:AG28,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP28" s="6">
-        <f>COUNTIF(C28:AG28,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ28" s="6">
-        <f>COUNTIF(C28:AG28,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR28" s="6">
-        <f>COUNTIF(C28:AG28,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS28" s="6">
-        <f>AI28+AL28</f>
-        <v/>
-      </c>
-      <c r="AT28" s="6">
-        <f>21-AI28</f>
-        <v/>
-      </c>
+      <c r="AI28" s="4" t="n"/>
+      <c r="AJ28" s="4" t="n"/>
+      <c r="AK28" s="4" t="n"/>
+      <c r="AL28" s="4" t="n"/>
+      <c r="AM28" s="4" t="n"/>
+      <c r="AN28" s="4" t="n"/>
+      <c r="AO28" s="4" t="n"/>
+      <c r="AP28" s="4" t="n"/>
+      <c r="AQ28" s="4" t="n"/>
+      <c r="AR28" s="4" t="n"/>
+      <c r="AS28" s="4" t="n"/>
+      <c r="AT28" s="4" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr"/>
+      <c r="D29" s="11" t="inlineStr"/>
+      <c r="E29" s="11" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr"/>
+      <c r="G29" s="10" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr"/>
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+      <c r="K29" s="11" t="inlineStr"/>
+      <c r="L29" s="11" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
+      <c r="O29" s="10" t="inlineStr"/>
+      <c r="P29" s="10" t="inlineStr"/>
+      <c r="Q29" s="10" t="inlineStr"/>
+      <c r="R29" s="11" t="inlineStr"/>
+      <c r="S29" s="11" t="inlineStr"/>
+      <c r="T29" s="10" t="inlineStr"/>
+      <c r="U29" s="10" t="inlineStr"/>
+      <c r="V29" s="10" t="inlineStr"/>
+      <c r="W29" s="10" t="inlineStr"/>
+      <c r="X29" s="10" t="inlineStr"/>
+      <c r="Y29" s="11" t="inlineStr"/>
+      <c r="Z29" s="11" t="inlineStr"/>
+      <c r="AA29" s="10" t="inlineStr"/>
+      <c r="AB29" s="10" t="inlineStr"/>
+      <c r="AC29" s="10" t="inlineStr"/>
+      <c r="AD29" s="10" t="inlineStr"/>
+      <c r="AE29" s="10" t="inlineStr"/>
+      <c r="AF29" s="11" t="inlineStr"/>
+      <c r="AG29" s="11" t="inlineStr"/>
+      <c r="AH29" s="10" t="n"/>
+      <c r="AI29" s="9">
+        <f>COUNTIF(C29:AG29,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="9">
+        <f>COUNTIF(C29:AG29,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK29" s="9">
+        <f>COUNTIF(C29:AG29,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL29" s="9">
+        <f>COUNTIF(C29:AG29,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM29" s="9">
+        <f>COUNTIF(C29:AG29,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN29" s="9">
+        <f>COUNTIF(C29:AG29,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO29" s="9">
+        <f>COUNTIF(C29:AG29,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP29" s="9">
+        <f>COUNTIF(C29:AG29,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ29" s="9">
+        <f>COUNTIF(C29:AG29,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR29" s="9">
+        <f>COUNTIF(C29:AG29,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS29" s="9">
+        <f>AI29+AL29</f>
+        <v/>
+      </c>
+      <c r="AT29" s="9">
+        <f>21-AI29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr"/>
-      <c r="M29" s="4" t="inlineStr"/>
-      <c r="N29" s="4" t="inlineStr"/>
-      <c r="O29" s="4" t="inlineStr"/>
-      <c r="P29" s="4" t="inlineStr"/>
-      <c r="Q29" s="4" t="inlineStr"/>
-      <c r="R29" s="7" t="inlineStr"/>
-      <c r="S29" s="7" t="inlineStr"/>
-      <c r="T29" s="4" t="inlineStr"/>
-      <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="inlineStr"/>
-      <c r="W29" s="4" t="inlineStr"/>
-      <c r="X29" s="4" t="inlineStr"/>
-      <c r="Y29" s="7" t="inlineStr"/>
-      <c r="Z29" s="7" t="inlineStr"/>
-      <c r="AA29" s="4" t="inlineStr"/>
-      <c r="AB29" s="4" t="inlineStr"/>
-      <c r="AC29" s="4" t="inlineStr"/>
-      <c r="AD29" s="4" t="inlineStr"/>
-      <c r="AE29" s="4" t="inlineStr"/>
-      <c r="AF29" s="7" t="inlineStr"/>
-      <c r="AG29" s="7" t="inlineStr"/>
-      <c r="AH29" s="4" t="n"/>
-      <c r="AI29" s="6">
-        <f>COUNTIF(C29:AG29,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ29" s="6">
-        <f>COUNTIF(C29:AG29,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK29" s="6">
-        <f>COUNTIF(C29:AG29,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL29" s="6">
-        <f>COUNTIF(C29:AG29,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM29" s="6">
-        <f>COUNTIF(C29:AG29,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN29" s="6">
-        <f>COUNTIF(C29:AG29,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO29" s="6">
-        <f>COUNTIF(C29:AG29,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP29" s="6">
-        <f>COUNTIF(C29:AG29,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ29" s="6">
-        <f>COUNTIF(C29:AG29,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR29" s="6">
-        <f>COUNTIF(C29:AG29,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS29" s="6">
-        <f>AI29+AL29</f>
-        <v/>
-      </c>
-      <c r="AT29" s="6">
-        <f>21-AI29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -2999,148 +2623,112 @@
       <c r="AF30" s="7" t="inlineStr"/>
       <c r="AG30" s="7" t="inlineStr"/>
       <c r="AH30" s="4" t="n"/>
-      <c r="AI30" s="6">
-        <f>COUNTIF(C30:AG30,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ30" s="6">
-        <f>COUNTIF(C30:AG30,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK30" s="6">
-        <f>COUNTIF(C30:AG30,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL30" s="6">
-        <f>COUNTIF(C30:AG30,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM30" s="6">
-        <f>COUNTIF(C30:AG30,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN30" s="6">
-        <f>COUNTIF(C30:AG30,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO30" s="6">
-        <f>COUNTIF(C30:AG30,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP30" s="6">
-        <f>COUNTIF(C30:AG30,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ30" s="6">
-        <f>COUNTIF(C30:AG30,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR30" s="6">
-        <f>COUNTIF(C30:AG30,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS30" s="6">
-        <f>AI30+AL30</f>
-        <v/>
-      </c>
-      <c r="AT30" s="6">
-        <f>21-AI30</f>
-        <v/>
-      </c>
+      <c r="AI30" s="4" t="n"/>
+      <c r="AJ30" s="4" t="n"/>
+      <c r="AK30" s="4" t="n"/>
+      <c r="AL30" s="4" t="n"/>
+      <c r="AM30" s="4" t="n"/>
+      <c r="AN30" s="4" t="n"/>
+      <c r="AO30" s="4" t="n"/>
+      <c r="AP30" s="4" t="n"/>
+      <c r="AQ30" s="4" t="n"/>
+      <c r="AR30" s="4" t="n"/>
+      <c r="AS30" s="4" t="n"/>
+      <c r="AT30" s="4" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr"/>
+      <c r="L31" s="11" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr"/>
+      <c r="P31" s="10" t="inlineStr"/>
+      <c r="Q31" s="10" t="inlineStr"/>
+      <c r="R31" s="11" t="inlineStr"/>
+      <c r="S31" s="11" t="inlineStr"/>
+      <c r="T31" s="10" t="inlineStr"/>
+      <c r="U31" s="10" t="inlineStr"/>
+      <c r="V31" s="10" t="inlineStr"/>
+      <c r="W31" s="10" t="inlineStr"/>
+      <c r="X31" s="10" t="inlineStr"/>
+      <c r="Y31" s="11" t="inlineStr"/>
+      <c r="Z31" s="11" t="inlineStr"/>
+      <c r="AA31" s="10" t="inlineStr"/>
+      <c r="AB31" s="10" t="inlineStr"/>
+      <c r="AC31" s="10" t="inlineStr"/>
+      <c r="AD31" s="10" t="inlineStr"/>
+      <c r="AE31" s="10" t="inlineStr"/>
+      <c r="AF31" s="11" t="inlineStr"/>
+      <c r="AG31" s="11" t="inlineStr"/>
+      <c r="AH31" s="10" t="n"/>
+      <c r="AI31" s="9">
+        <f>COUNTIF(C31:AG31,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="9">
+        <f>COUNTIF(C31:AG31,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK31" s="9">
+        <f>COUNTIF(C31:AG31,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL31" s="9">
+        <f>COUNTIF(C31:AG31,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM31" s="9">
+        <f>COUNTIF(C31:AG31,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN31" s="9">
+        <f>COUNTIF(C31:AG31,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO31" s="9">
+        <f>COUNTIF(C31:AG31,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP31" s="9">
+        <f>COUNTIF(C31:AG31,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ31" s="9">
+        <f>COUNTIF(C31:AG31,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR31" s="9">
+        <f>COUNTIF(C31:AG31,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS31" s="9">
+        <f>AI31+AL31</f>
+        <v/>
+      </c>
+      <c r="AT31" s="9">
+        <f>21-AI31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
-      <c r="M31" s="4" t="inlineStr"/>
-      <c r="N31" s="4" t="inlineStr"/>
-      <c r="O31" s="4" t="inlineStr"/>
-      <c r="P31" s="4" t="inlineStr"/>
-      <c r="Q31" s="4" t="inlineStr"/>
-      <c r="R31" s="7" t="inlineStr"/>
-      <c r="S31" s="7" t="inlineStr"/>
-      <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="inlineStr"/>
-      <c r="W31" s="4" t="inlineStr"/>
-      <c r="X31" s="4" t="inlineStr"/>
-      <c r="Y31" s="7" t="inlineStr"/>
-      <c r="Z31" s="7" t="inlineStr"/>
-      <c r="AA31" s="4" t="inlineStr"/>
-      <c r="AB31" s="4" t="inlineStr"/>
-      <c r="AC31" s="4" t="inlineStr"/>
-      <c r="AD31" s="4" t="inlineStr"/>
-      <c r="AE31" s="4" t="inlineStr"/>
-      <c r="AF31" s="7" t="inlineStr"/>
-      <c r="AG31" s="7" t="inlineStr"/>
-      <c r="AH31" s="4" t="n"/>
-      <c r="AI31" s="6">
-        <f>COUNTIF(C31:AG31,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ31" s="6">
-        <f>COUNTIF(C31:AG31,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK31" s="6">
-        <f>COUNTIF(C31:AG31,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL31" s="6">
-        <f>COUNTIF(C31:AG31,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM31" s="6">
-        <f>COUNTIF(C31:AG31,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN31" s="6">
-        <f>COUNTIF(C31:AG31,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO31" s="6">
-        <f>COUNTIF(C31:AG31,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP31" s="6">
-        <f>COUNTIF(C31:AG31,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ31" s="6">
-        <f>COUNTIF(C31:AG31,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR31" s="6">
-        <f>COUNTIF(C31:AG31,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS31" s="6">
-        <f>AI31+AL31</f>
-        <v/>
-      </c>
-      <c r="AT31" s="6">
-        <f>21-AI31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -3175,148 +2763,112 @@
       <c r="AF32" s="7" t="inlineStr"/>
       <c r="AG32" s="7" t="inlineStr"/>
       <c r="AH32" s="4" t="n"/>
-      <c r="AI32" s="6">
-        <f>COUNTIF(C32:AG32,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ32" s="6">
-        <f>COUNTIF(C32:AG32,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK32" s="6">
-        <f>COUNTIF(C32:AG32,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL32" s="6">
-        <f>COUNTIF(C32:AG32,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM32" s="6">
-        <f>COUNTIF(C32:AG32,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN32" s="6">
-        <f>COUNTIF(C32:AG32,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO32" s="6">
-        <f>COUNTIF(C32:AG32,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP32" s="6">
-        <f>COUNTIF(C32:AG32,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ32" s="6">
-        <f>COUNTIF(C32:AG32,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR32" s="6">
-        <f>COUNTIF(C32:AG32,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS32" s="6">
-        <f>AI32+AL32</f>
-        <v/>
-      </c>
-      <c r="AT32" s="6">
-        <f>21-AI32</f>
-        <v/>
-      </c>
+      <c r="AI32" s="4" t="n"/>
+      <c r="AJ32" s="4" t="n"/>
+      <c r="AK32" s="4" t="n"/>
+      <c r="AL32" s="4" t="n"/>
+      <c r="AM32" s="4" t="n"/>
+      <c r="AN32" s="4" t="n"/>
+      <c r="AO32" s="4" t="n"/>
+      <c r="AP32" s="4" t="n"/>
+      <c r="AQ32" s="4" t="n"/>
+      <c r="AR32" s="4" t="n"/>
+      <c r="AS32" s="4" t="n"/>
+      <c r="AT32" s="4" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr"/>
+      <c r="D33" s="11" t="inlineStr"/>
+      <c r="E33" s="11" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="10" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr"/>
+      <c r="L33" s="11" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" s="10" t="inlineStr"/>
+      <c r="Q33" s="10" t="inlineStr"/>
+      <c r="R33" s="11" t="inlineStr"/>
+      <c r="S33" s="11" t="inlineStr"/>
+      <c r="T33" s="10" t="inlineStr"/>
+      <c r="U33" s="10" t="inlineStr"/>
+      <c r="V33" s="10" t="inlineStr"/>
+      <c r="W33" s="10" t="inlineStr"/>
+      <c r="X33" s="10" t="inlineStr"/>
+      <c r="Y33" s="11" t="inlineStr"/>
+      <c r="Z33" s="11" t="inlineStr"/>
+      <c r="AA33" s="10" t="inlineStr"/>
+      <c r="AB33" s="10" t="inlineStr"/>
+      <c r="AC33" s="10" t="inlineStr"/>
+      <c r="AD33" s="10" t="inlineStr"/>
+      <c r="AE33" s="10" t="inlineStr"/>
+      <c r="AF33" s="11" t="inlineStr"/>
+      <c r="AG33" s="11" t="inlineStr"/>
+      <c r="AH33" s="10" t="n"/>
+      <c r="AI33" s="9">
+        <f>COUNTIF(C33:AG33,$AI$4)</f>
+        <v/>
+      </c>
+      <c r="AJ33" s="9">
+        <f>COUNTIF(C33:AG33,$AJ$4)</f>
+        <v/>
+      </c>
+      <c r="AK33" s="9">
+        <f>COUNTIF(C33:AG33,$AK$4)</f>
+        <v/>
+      </c>
+      <c r="AL33" s="9">
+        <f>COUNTIF(C33:AG33,$AL$4)</f>
+        <v/>
+      </c>
+      <c r="AM33" s="9">
+        <f>COUNTIF(C33:AG33,$AM$4)</f>
+        <v/>
+      </c>
+      <c r="AN33" s="9">
+        <f>COUNTIF(C33:AG33,$AN$4)</f>
+        <v/>
+      </c>
+      <c r="AO33" s="9">
+        <f>COUNTIF(C33:AG33,$AO$4)</f>
+        <v/>
+      </c>
+      <c r="AP33" s="9">
+        <f>COUNTIF(C33:AG33,$AP$4)</f>
+        <v/>
+      </c>
+      <c r="AQ33" s="9">
+        <f>COUNTIF(C33:AG33,$AQ$4)</f>
+        <v/>
+      </c>
+      <c r="AR33" s="9">
+        <f>COUNTIF(C33:AG33,$AR$4)</f>
+        <v/>
+      </c>
+      <c r="AS33" s="9">
+        <f>AI33+AL33</f>
+        <v/>
+      </c>
+      <c r="AT33" s="9">
+        <f>21-AI33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>下午</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr"/>
-      <c r="N33" s="4" t="inlineStr"/>
-      <c r="O33" s="4" t="inlineStr"/>
-      <c r="P33" s="4" t="inlineStr"/>
-      <c r="Q33" s="4" t="inlineStr"/>
-      <c r="R33" s="7" t="inlineStr"/>
-      <c r="S33" s="7" t="inlineStr"/>
-      <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="inlineStr"/>
-      <c r="W33" s="4" t="inlineStr"/>
-      <c r="X33" s="4" t="inlineStr"/>
-      <c r="Y33" s="7" t="inlineStr"/>
-      <c r="Z33" s="7" t="inlineStr"/>
-      <c r="AA33" s="4" t="inlineStr"/>
-      <c r="AB33" s="4" t="inlineStr"/>
-      <c r="AC33" s="4" t="inlineStr"/>
-      <c r="AD33" s="4" t="inlineStr"/>
-      <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" s="7" t="inlineStr"/>
-      <c r="AG33" s="7" t="inlineStr"/>
-      <c r="AH33" s="4" t="n"/>
-      <c r="AI33" s="6">
-        <f>COUNTIF(C33:AG33,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ33" s="6">
-        <f>COUNTIF(C33:AG33,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK33" s="6">
-        <f>COUNTIF(C33:AG33,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL33" s="6">
-        <f>COUNTIF(C33:AG33,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM33" s="6">
-        <f>COUNTIF(C33:AG33,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN33" s="6">
-        <f>COUNTIF(C33:AG33,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO33" s="6">
-        <f>COUNTIF(C33:AG33,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP33" s="6">
-        <f>COUNTIF(C33:AG33,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ33" s="6">
-        <f>COUNTIF(C33:AG33,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR33" s="6">
-        <f>COUNTIF(C33:AG33,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS33" s="6">
-        <f>AI33+AL33</f>
-        <v/>
-      </c>
-      <c r="AT33" s="6">
-        <f>21-AI33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>上午</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -3351,146 +2903,217 @@
       <c r="AF34" s="7" t="inlineStr"/>
       <c r="AG34" s="7" t="inlineStr"/>
       <c r="AH34" s="4" t="n"/>
-      <c r="AI34" s="6">
-        <f>COUNTIF(C34:AG34,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ34" s="6">
-        <f>COUNTIF(C34:AG34,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK34" s="6">
-        <f>COUNTIF(C34:AG34,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL34" s="6">
-        <f>COUNTIF(C34:AG34,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM34" s="6">
-        <f>COUNTIF(C34:AG34,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN34" s="6">
-        <f>COUNTIF(C34:AG34,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO34" s="6">
-        <f>COUNTIF(C34:AG34,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP34" s="6">
-        <f>COUNTIF(C34:AG34,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ34" s="6">
-        <f>COUNTIF(C34:AG34,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR34" s="6">
-        <f>COUNTIF(C34:AG34,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS34" s="6">
-        <f>AI34+AL34</f>
-        <v/>
-      </c>
-      <c r="AT34" s="6">
-        <f>21-AI34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr"/>
-      <c r="M35" s="4" t="inlineStr"/>
-      <c r="N35" s="4" t="inlineStr"/>
-      <c r="O35" s="4" t="inlineStr"/>
-      <c r="P35" s="4" t="inlineStr"/>
-      <c r="Q35" s="4" t="inlineStr"/>
-      <c r="R35" s="7" t="inlineStr"/>
-      <c r="S35" s="7" t="inlineStr"/>
-      <c r="T35" s="4" t="inlineStr"/>
-      <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="4" t="inlineStr"/>
-      <c r="W35" s="4" t="inlineStr"/>
-      <c r="X35" s="4" t="inlineStr"/>
-      <c r="Y35" s="7" t="inlineStr"/>
-      <c r="Z35" s="7" t="inlineStr"/>
-      <c r="AA35" s="4" t="inlineStr"/>
-      <c r="AB35" s="4" t="inlineStr"/>
-      <c r="AC35" s="4" t="inlineStr"/>
-      <c r="AD35" s="4" t="inlineStr"/>
-      <c r="AE35" s="4" t="inlineStr"/>
-      <c r="AF35" s="7" t="inlineStr"/>
-      <c r="AG35" s="7" t="inlineStr"/>
-      <c r="AH35" s="4" t="n"/>
-      <c r="AI35" s="6">
-        <f>COUNTIF(C35:AG35,$AI$5)</f>
-        <v/>
-      </c>
-      <c r="AJ35" s="6">
-        <f>COUNTIF(C35:AG35,$AJ$5)</f>
-        <v/>
-      </c>
-      <c r="AK35" s="6">
-        <f>COUNTIF(C35:AG35,$AK$5)</f>
-        <v/>
-      </c>
-      <c r="AL35" s="6">
-        <f>COUNTIF(C35:AG35,$AL$5)</f>
-        <v/>
-      </c>
-      <c r="AM35" s="6">
-        <f>COUNTIF(C35:AG35,$AM$5)</f>
-        <v/>
-      </c>
-      <c r="AN35" s="6">
-        <f>COUNTIF(C35:AG35,$AN$5)</f>
-        <v/>
-      </c>
-      <c r="AO35" s="6">
-        <f>COUNTIF(C35:AG35,$AO$5)</f>
-        <v/>
-      </c>
-      <c r="AP35" s="6">
-        <f>COUNTIF(C35:AG35,$AP$5)</f>
-        <v/>
-      </c>
-      <c r="AQ35" s="6">
-        <f>COUNTIF(C35:AG35,$AQ$5)</f>
-        <v/>
-      </c>
-      <c r="AR35" s="6">
-        <f>COUNTIF(C35:AG35,$AR$5)</f>
-        <v/>
-      </c>
-      <c r="AS35" s="6">
-        <f>AI35+AL35</f>
-        <v/>
-      </c>
-      <c r="AT35" s="6">
-        <f>21-AI35</f>
-        <v/>
-      </c>
+      <c r="AI34" s="4" t="n"/>
+      <c r="AJ34" s="4" t="n"/>
+      <c r="AK34" s="4" t="n"/>
+      <c r="AL34" s="4" t="n"/>
+      <c r="AM34" s="4" t="n"/>
+      <c r="AN34" s="4" t="n"/>
+      <c r="AO34" s="4" t="n"/>
+      <c r="AP34" s="4" t="n"/>
+      <c r="AQ34" s="4" t="n"/>
+      <c r="AR34" s="4" t="n"/>
+      <c r="AS34" s="4" t="n"/>
+      <c r="AT34" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="196">
+    <mergeCell ref="AI15:AI16"/>
+    <mergeCell ref="AL11:AL12"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AP9:AP10"/>
+    <mergeCell ref="AP5:AP6"/>
+    <mergeCell ref="AR9:AR10"/>
+    <mergeCell ref="AS29:AS30"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="AM29:AM30"/>
+    <mergeCell ref="AJ27:AJ28"/>
+    <mergeCell ref="AP29:AP30"/>
+    <mergeCell ref="AT33:AT34"/>
+    <mergeCell ref="AO15:AO16"/>
+    <mergeCell ref="AT5:AT6"/>
+    <mergeCell ref="AS31:AS32"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="AI27:AI28"/>
+    <mergeCell ref="AQ21:AQ22"/>
+    <mergeCell ref="AJ13:AJ14"/>
+    <mergeCell ref="AL13:AL14"/>
+    <mergeCell ref="AK21:AK22"/>
+    <mergeCell ref="AQ17:AQ18"/>
+    <mergeCell ref="AS17:AS18"/>
+    <mergeCell ref="AN21:AN22"/>
+    <mergeCell ref="AP15:AP16"/>
+    <mergeCell ref="AM7:AM8"/>
+    <mergeCell ref="AR15:AR16"/>
+    <mergeCell ref="AT19:AT20"/>
+    <mergeCell ref="AQ23:AQ24"/>
+    <mergeCell ref="AJ15:AJ16"/>
+    <mergeCell ref="AS23:AS24"/>
+    <mergeCell ref="AS19:AS20"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="AI25:AI26"/>
+    <mergeCell ref="AO9:AO10"/>
+    <mergeCell ref="AQ9:AQ10"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AR29:AR30"/>
+    <mergeCell ref="AP7:AP8"/>
     <mergeCell ref="A1:AT1"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="AQ11:AQ12"/>
+    <mergeCell ref="AS5:AS6"/>
+    <mergeCell ref="AT13:AT14"/>
+    <mergeCell ref="AT7:AT8"/>
+    <mergeCell ref="AM33:AM34"/>
+    <mergeCell ref="AO27:AO28"/>
+    <mergeCell ref="AL27:AL28"/>
+    <mergeCell ref="AM13:AM14"/>
+    <mergeCell ref="AO13:AO14"/>
+    <mergeCell ref="AJ17:AJ18"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AK25:AK26"/>
+    <mergeCell ref="AP33:AP34"/>
+    <mergeCell ref="AM19:AM20"/>
+    <mergeCell ref="AR27:AR28"/>
+    <mergeCell ref="AS21:AS22"/>
+    <mergeCell ref="AT23:AT24"/>
+    <mergeCell ref="AJ19:AJ20"/>
+    <mergeCell ref="AL25:AL26"/>
+    <mergeCell ref="AN25:AN26"/>
+    <mergeCell ref="AK11:AK12"/>
+    <mergeCell ref="AI7:AI8"/>
+    <mergeCell ref="AT9:AT10"/>
+    <mergeCell ref="AP19:AP20"/>
+    <mergeCell ref="AS7:AS8"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="AI31:AI32"/>
+    <mergeCell ref="AL5:AL6"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="AR25:AR26"/>
+    <mergeCell ref="AQ29:AQ30"/>
+    <mergeCell ref="AK27:AK28"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="AM27:AM28"/>
+    <mergeCell ref="AI17:AI18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="AK17:AK18"/>
+    <mergeCell ref="AO31:AO32"/>
+    <mergeCell ref="AQ31:AQ32"/>
+    <mergeCell ref="AN13:AN14"/>
+    <mergeCell ref="AM21:AM22"/>
+    <mergeCell ref="AP13:AP14"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="AR11:AR12"/>
+    <mergeCell ref="AQ27:AQ28"/>
+    <mergeCell ref="AJ29:AJ30"/>
+    <mergeCell ref="AT11:AT12"/>
+    <mergeCell ref="AL29:AL30"/>
+    <mergeCell ref="AM17:AM18"/>
+    <mergeCell ref="AI33:AI34"/>
+    <mergeCell ref="AO17:AO18"/>
+    <mergeCell ref="AJ21:AJ22"/>
+    <mergeCell ref="AL15:AL16"/>
+    <mergeCell ref="AS33:AS34"/>
+    <mergeCell ref="AN15:AN16"/>
+    <mergeCell ref="AM23:AM24"/>
+    <mergeCell ref="AR31:AR32"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="AO23:AO24"/>
+    <mergeCell ref="AJ31:AJ32"/>
+    <mergeCell ref="AL31:AL32"/>
+    <mergeCell ref="AP21:AP22"/>
+    <mergeCell ref="AO19:AO20"/>
+    <mergeCell ref="AT27:AT28"/>
+    <mergeCell ref="AK9:AK10"/>
+    <mergeCell ref="AM9:AM10"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AQ25:AQ26"/>
+    <mergeCell ref="AN29:AN30"/>
+    <mergeCell ref="AL7:AL8"/>
+    <mergeCell ref="AS25:AS26"/>
+    <mergeCell ref="AP23:AP24"/>
+    <mergeCell ref="AR23:AR24"/>
+    <mergeCell ref="AK15:AK16"/>
+    <mergeCell ref="AJ23:AJ24"/>
+    <mergeCell ref="AK29:AK30"/>
+    <mergeCell ref="AR19:AR20"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="AT29:AT30"/>
+    <mergeCell ref="AN11:AN12"/>
+    <mergeCell ref="AT31:AT32"/>
+    <mergeCell ref="AM15:AM16"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="AQ13:AQ14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="AS13:AS14"/>
+    <mergeCell ref="AR21:AR22"/>
+    <mergeCell ref="AO29:AO30"/>
+    <mergeCell ref="AJ33:AJ34"/>
+    <mergeCell ref="AL33:AL34"/>
+    <mergeCell ref="AN27:AN28"/>
+    <mergeCell ref="AR17:AR18"/>
+    <mergeCell ref="AT17:AT18"/>
+    <mergeCell ref="AO21:AO22"/>
+    <mergeCell ref="AQ15:AQ16"/>
+    <mergeCell ref="AS15:AS16"/>
+    <mergeCell ref="AR7:AR8"/>
+    <mergeCell ref="AJ25:AJ26"/>
+    <mergeCell ref="AL19:AL20"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="AI23:AI24"/>
+    <mergeCell ref="AT25:AT26"/>
+    <mergeCell ref="AO7:AO8"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="AI19:AI20"/>
+    <mergeCell ref="AK19:AK20"/>
+    <mergeCell ref="AI9:AI10"/>
+    <mergeCell ref="AJ11:AJ12"/>
+    <mergeCell ref="AS9:AS10"/>
+    <mergeCell ref="AR13:AR14"/>
+    <mergeCell ref="AK33:AK34"/>
+    <mergeCell ref="AI11:AI12"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AM5:AM6"/>
+    <mergeCell ref="AS11:AS12"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="AO33:AO34"/>
+    <mergeCell ref="AM11:AM12"/>
+    <mergeCell ref="AQ33:AQ34"/>
+    <mergeCell ref="AS27:AS28"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AP31:AP32"/>
+    <mergeCell ref="AT21:AT22"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="AL21:AL22"/>
+    <mergeCell ref="AP27:AP28"/>
+    <mergeCell ref="AM31:AM32"/>
+    <mergeCell ref="AL17:AL18"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AI21:AI22"/>
+    <mergeCell ref="AM25:AM26"/>
+    <mergeCell ref="AP17:AP18"/>
+    <mergeCell ref="AT15:AT16"/>
+    <mergeCell ref="AO25:AO26"/>
+    <mergeCell ref="AR33:AR34"/>
+    <mergeCell ref="AQ19:AQ20"/>
+    <mergeCell ref="AL23:AL24"/>
+    <mergeCell ref="AN23:AN24"/>
+    <mergeCell ref="AK31:AK32"/>
+    <mergeCell ref="AI29:AI30"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AK23:AK24"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="AI13:AI14"/>
+    <mergeCell ref="AL9:AL10"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="AK13:AK14"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AP25:AP26"/>
+    <mergeCell ref="AK7:AK8"/>
+    <mergeCell ref="AO11:AO12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3938,7 +3561,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>月度汇总 统计日期：2026-05-01 至 2026-05-31</t>
         </is>
@@ -3976,9 +3599,9 @@
       <c r="AF1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>报表生成时间：2026-06-23 03:51</t>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>报表生成时间：2026-06-23 08:27</t>
         </is>
       </c>
       <c r="B2" s="6" t="n"/>
@@ -4014,7 +3637,7 @@
       <c r="AF2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
@@ -4176,7 +3799,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n"/>
+      <c r="A4" s="13" t="n"/>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
@@ -4210,7 +3833,7 @@
       <c r="AF4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n"/>
+      <c r="A5" s="13" t="n"/>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr"/>
@@ -4244,7 +3867,7 @@
       <c r="AF5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n"/>
+      <c r="A6" s="13" t="n"/>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
@@ -4278,7 +3901,7 @@
       <c r="AF6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n"/>
+      <c r="A7" s="13" t="n"/>
       <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr"/>
@@ -4312,7 +3935,7 @@
       <c r="AF7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n"/>
+      <c r="A8" s="13" t="n"/>
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="5" t="inlineStr"/>
@@ -4346,7 +3969,7 @@
       <c r="AF8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
+      <c r="A9" s="13" t="n"/>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr"/>
@@ -4380,7 +4003,7 @@
       <c r="AF9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
+      <c r="A10" s="13" t="n"/>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr"/>
@@ -4414,7 +4037,7 @@
       <c r="AF10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
+      <c r="A11" s="13" t="n"/>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr"/>
@@ -4448,7 +4071,7 @@
       <c r="AF11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
+      <c r="A12" s="13" t="n"/>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr"/>
@@ -4482,7 +4105,7 @@
       <c r="AF12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
+      <c r="A13" s="13" t="n"/>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr"/>
@@ -4516,7 +4139,7 @@
       <c r="AF13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
+      <c r="A14" s="13" t="n"/>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr"/>
@@ -4550,7 +4173,7 @@
       <c r="AF14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n"/>
+      <c r="A15" s="13" t="n"/>
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr"/>
@@ -4584,7 +4207,7 @@
       <c r="AF15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
+      <c r="A16" s="13" t="n"/>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr"/>
@@ -4618,7 +4241,7 @@
       <c r="AF16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
+      <c r="A17" s="13" t="n"/>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="inlineStr"/>
@@ -4652,7 +4275,7 @@
       <c r="AF17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
+      <c r="A18" s="13" t="n"/>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr"/>
@@ -4856,21 +4479,21 @@
         <v>31</v>
       </c>
       <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="11" t="inlineStr">
+      <c r="AJ2" s="15" t="inlineStr">
         <is>
           <t>5月加班时长合计</t>
         </is>
       </c>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="11" t="inlineStr">
+      <c r="AM2" s="15" t="inlineStr">
         <is>
           <t>5月加班倍数合计</t>
         </is>
       </c>
       <c r="AN2" s="4" t="n"/>
       <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="11" t="inlineStr">
+      <c r="AP2" s="15" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
@@ -5090,31 +4713,31 @@
         <v>0</v>
       </c>
       <c r="AI5" s="4" t="n"/>
-      <c r="AJ5" s="12">
+      <c r="AJ5" s="16">
         <f>SUM(J5:M5,O5:S5,V5:Z5,AC5:AG5)</f>
         <v/>
       </c>
-      <c r="AK5" s="12">
+      <c r="AK5" s="16">
         <f>SUM(G5:I5,N5,T5:U5,AA5:AB5,AH5:AI5)</f>
         <v/>
       </c>
-      <c r="AL5" s="12">
+      <c r="AL5" s="16">
         <f>SUM(E5:F5)</f>
         <v/>
       </c>
-      <c r="AM5" s="12">
+      <c r="AM5" s="16">
         <f>AJ5*1.5</f>
         <v/>
       </c>
-      <c r="AN5" s="12">
+      <c r="AN5" s="16">
         <f>AK5*2</f>
         <v/>
       </c>
-      <c r="AO5" s="12">
+      <c r="AO5" s="16">
         <f>AL5*3</f>
         <v/>
       </c>
-      <c r="AP5" s="12">
+      <c r="AP5" s="16">
         <f>SUM(AM5:AO5)</f>
         <v/>
       </c>
@@ -5221,31 +4844,31 @@
         <v>0</v>
       </c>
       <c r="AI6" s="4" t="n"/>
-      <c r="AJ6" s="12">
+      <c r="AJ6" s="16">
         <f>SUM(J6:M6,O6:S6,V6:Z6,AC6:AG6)</f>
         <v/>
       </c>
-      <c r="AK6" s="12">
+      <c r="AK6" s="16">
         <f>SUM(G6:I6,N6,T6:U6,AA6:AB6,AH6:AI6)</f>
         <v/>
       </c>
-      <c r="AL6" s="12">
+      <c r="AL6" s="16">
         <f>SUM(E6:F6)</f>
         <v/>
       </c>
-      <c r="AM6" s="12">
+      <c r="AM6" s="16">
         <f>AJ6*1.5</f>
         <v/>
       </c>
-      <c r="AN6" s="12">
+      <c r="AN6" s="16">
         <f>AK6*2</f>
         <v/>
       </c>
-      <c r="AO6" s="12">
+      <c r="AO6" s="16">
         <f>AL6*3</f>
         <v/>
       </c>
-      <c r="AP6" s="12">
+      <c r="AP6" s="16">
         <f>SUM(AM6:AO6)</f>
         <v/>
       </c>
@@ -5352,31 +4975,31 @@
         <v>0</v>
       </c>
       <c r="AI7" s="4" t="n"/>
-      <c r="AJ7" s="12">
+      <c r="AJ7" s="16">
         <f>SUM(J7:M7,O7:S7,V7:Z7,AC7:AG7)</f>
         <v/>
       </c>
-      <c r="AK7" s="12">
+      <c r="AK7" s="16">
         <f>SUM(G7:I7,N7,T7:U7,AA7:AB7,AH7:AI7)</f>
         <v/>
       </c>
-      <c r="AL7" s="12">
+      <c r="AL7" s="16">
         <f>SUM(E7:F7)</f>
         <v/>
       </c>
-      <c r="AM7" s="12">
+      <c r="AM7" s="16">
         <f>AJ7*1.5</f>
         <v/>
       </c>
-      <c r="AN7" s="12">
+      <c r="AN7" s="16">
         <f>AK7*2</f>
         <v/>
       </c>
-      <c r="AO7" s="12">
+      <c r="AO7" s="16">
         <f>AL7*3</f>
         <v/>
       </c>
-      <c r="AP7" s="12">
+      <c r="AP7" s="16">
         <f>SUM(AM7:AO7)</f>
         <v/>
       </c>
@@ -5483,31 +5106,31 @@
         <v>0</v>
       </c>
       <c r="AI8" s="4" t="n"/>
-      <c r="AJ8" s="12">
+      <c r="AJ8" s="16">
         <f>SUM(J8:M8,O8:S8,V8:Z8,AC8:AG8)</f>
         <v/>
       </c>
-      <c r="AK8" s="12">
+      <c r="AK8" s="16">
         <f>SUM(G8:I8,N8,T8:U8,AA8:AB8,AH8:AI8)</f>
         <v/>
       </c>
-      <c r="AL8" s="12">
+      <c r="AL8" s="16">
         <f>SUM(E8:F8)</f>
         <v/>
       </c>
-      <c r="AM8" s="12">
+      <c r="AM8" s="16">
         <f>AJ8*1.5</f>
         <v/>
       </c>
-      <c r="AN8" s="12">
+      <c r="AN8" s="16">
         <f>AK8*2</f>
         <v/>
       </c>
-      <c r="AO8" s="12">
+      <c r="AO8" s="16">
         <f>AL8*3</f>
         <v/>
       </c>
-      <c r="AP8" s="12">
+      <c r="AP8" s="16">
         <f>SUM(AM8:AO8)</f>
         <v/>
       </c>
@@ -5614,31 +5237,31 @@
         <v>0</v>
       </c>
       <c r="AI9" s="4" t="n"/>
-      <c r="AJ9" s="12">
+      <c r="AJ9" s="16">
         <f>SUM(J9:M9,O9:S9,V9:Z9,AC9:AG9)</f>
         <v/>
       </c>
-      <c r="AK9" s="12">
+      <c r="AK9" s="16">
         <f>SUM(G9:I9,N9,T9:U9,AA9:AB9,AH9:AI9)</f>
         <v/>
       </c>
-      <c r="AL9" s="12">
+      <c r="AL9" s="16">
         <f>SUM(E9:F9)</f>
         <v/>
       </c>
-      <c r="AM9" s="12">
+      <c r="AM9" s="16">
         <f>AJ9*1.5</f>
         <v/>
       </c>
-      <c r="AN9" s="12">
+      <c r="AN9" s="16">
         <f>AK9*2</f>
         <v/>
       </c>
-      <c r="AO9" s="12">
+      <c r="AO9" s="16">
         <f>AL9*3</f>
         <v/>
       </c>
-      <c r="AP9" s="12">
+      <c r="AP9" s="16">
         <f>SUM(AM9:AO9)</f>
         <v/>
       </c>
@@ -5745,31 +5368,31 @@
         <v>0</v>
       </c>
       <c r="AI10" s="4" t="n"/>
-      <c r="AJ10" s="12">
+      <c r="AJ10" s="16">
         <f>SUM(J10:M10,O10:S10,V10:Z10,AC10:AG10)</f>
         <v/>
       </c>
-      <c r="AK10" s="12">
+      <c r="AK10" s="16">
         <f>SUM(G10:I10,N10,T10:U10,AA10:AB10,AH10:AI10)</f>
         <v/>
       </c>
-      <c r="AL10" s="12">
+      <c r="AL10" s="16">
         <f>SUM(E10:F10)</f>
         <v/>
       </c>
-      <c r="AM10" s="12">
+      <c r="AM10" s="16">
         <f>AJ10*1.5</f>
         <v/>
       </c>
-      <c r="AN10" s="12">
+      <c r="AN10" s="16">
         <f>AK10*2</f>
         <v/>
       </c>
-      <c r="AO10" s="12">
+      <c r="AO10" s="16">
         <f>AL10*3</f>
         <v/>
       </c>
-      <c r="AP10" s="12">
+      <c r="AP10" s="16">
         <f>SUM(AM10:AO10)</f>
         <v/>
       </c>
@@ -5876,31 +5499,31 @@
         <v>0</v>
       </c>
       <c r="AI11" s="4" t="n"/>
-      <c r="AJ11" s="12">
+      <c r="AJ11" s="16">
         <f>SUM(J11:M11,O11:S11,V11:Z11,AC11:AG11)</f>
         <v/>
       </c>
-      <c r="AK11" s="12">
+      <c r="AK11" s="16">
         <f>SUM(G11:I11,N11,T11:U11,AA11:AB11,AH11:AI11)</f>
         <v/>
       </c>
-      <c r="AL11" s="12">
+      <c r="AL11" s="16">
         <f>SUM(E11:F11)</f>
         <v/>
       </c>
-      <c r="AM11" s="12">
+      <c r="AM11" s="16">
         <f>AJ11*1.5</f>
         <v/>
       </c>
-      <c r="AN11" s="12">
+      <c r="AN11" s="16">
         <f>AK11*2</f>
         <v/>
       </c>
-      <c r="AO11" s="12">
+      <c r="AO11" s="16">
         <f>AL11*3</f>
         <v/>
       </c>
-      <c r="AP11" s="12">
+      <c r="AP11" s="16">
         <f>SUM(AM11:AO11)</f>
         <v/>
       </c>
@@ -6007,31 +5630,31 @@
         <v>0</v>
       </c>
       <c r="AI12" s="4" t="n"/>
-      <c r="AJ12" s="12">
+      <c r="AJ12" s="16">
         <f>SUM(J12:M12,O12:S12,V12:Z12,AC12:AG12)</f>
         <v/>
       </c>
-      <c r="AK12" s="12">
+      <c r="AK12" s="16">
         <f>SUM(G12:I12,N12,T12:U12,AA12:AB12,AH12:AI12)</f>
         <v/>
       </c>
-      <c r="AL12" s="12">
+      <c r="AL12" s="16">
         <f>SUM(E12:F12)</f>
         <v/>
       </c>
-      <c r="AM12" s="12">
+      <c r="AM12" s="16">
         <f>AJ12*1.5</f>
         <v/>
       </c>
-      <c r="AN12" s="12">
+      <c r="AN12" s="16">
         <f>AK12*2</f>
         <v/>
       </c>
-      <c r="AO12" s="12">
+      <c r="AO12" s="16">
         <f>AL12*3</f>
         <v/>
       </c>
-      <c r="AP12" s="12">
+      <c r="AP12" s="16">
         <f>SUM(AM12:AO12)</f>
         <v/>
       </c>
@@ -6138,31 +5761,31 @@
         <v>0</v>
       </c>
       <c r="AI13" s="4" t="n"/>
-      <c r="AJ13" s="12">
+      <c r="AJ13" s="16">
         <f>SUM(J13:M13,O13:S13,V13:Z13,AC13:AG13)</f>
         <v/>
       </c>
-      <c r="AK13" s="12">
+      <c r="AK13" s="16">
         <f>SUM(G13:I13,N13,T13:U13,AA13:AB13,AH13:AI13)</f>
         <v/>
       </c>
-      <c r="AL13" s="12">
+      <c r="AL13" s="16">
         <f>SUM(E13:F13)</f>
         <v/>
       </c>
-      <c r="AM13" s="12">
+      <c r="AM13" s="16">
         <f>AJ13*1.5</f>
         <v/>
       </c>
-      <c r="AN13" s="12">
+      <c r="AN13" s="16">
         <f>AK13*2</f>
         <v/>
       </c>
-      <c r="AO13" s="12">
+      <c r="AO13" s="16">
         <f>AL13*3</f>
         <v/>
       </c>
-      <c r="AP13" s="12">
+      <c r="AP13" s="16">
         <f>SUM(AM13:AO13)</f>
         <v/>
       </c>
@@ -6269,31 +5892,31 @@
         <v>0</v>
       </c>
       <c r="AI14" s="4" t="n"/>
-      <c r="AJ14" s="12">
+      <c r="AJ14" s="16">
         <f>SUM(J14:M14,O14:S14,V14:Z14,AC14:AG14)</f>
         <v/>
       </c>
-      <c r="AK14" s="12">
+      <c r="AK14" s="16">
         <f>SUM(G14:I14,N14,T14:U14,AA14:AB14,AH14:AI14)</f>
         <v/>
       </c>
-      <c r="AL14" s="12">
+      <c r="AL14" s="16">
         <f>SUM(E14:F14)</f>
         <v/>
       </c>
-      <c r="AM14" s="12">
+      <c r="AM14" s="16">
         <f>AJ14*1.5</f>
         <v/>
       </c>
-      <c r="AN14" s="12">
+      <c r="AN14" s="16">
         <f>AK14*2</f>
         <v/>
       </c>
-      <c r="AO14" s="12">
+      <c r="AO14" s="16">
         <f>AL14*3</f>
         <v/>
       </c>
-      <c r="AP14" s="12">
+      <c r="AP14" s="16">
         <f>SUM(AM14:AO14)</f>
         <v/>
       </c>
@@ -6400,31 +6023,31 @@
         <v>0</v>
       </c>
       <c r="AI15" s="4" t="n"/>
-      <c r="AJ15" s="12">
+      <c r="AJ15" s="16">
         <f>SUM(J15:M15,O15:S15,V15:Z15,AC15:AG15)</f>
         <v/>
       </c>
-      <c r="AK15" s="12">
+      <c r="AK15" s="16">
         <f>SUM(G15:I15,N15,T15:U15,AA15:AB15,AH15:AI15)</f>
         <v/>
       </c>
-      <c r="AL15" s="12">
+      <c r="AL15" s="16">
         <f>SUM(E15:F15)</f>
         <v/>
       </c>
-      <c r="AM15" s="12">
+      <c r="AM15" s="16">
         <f>AJ15*1.5</f>
         <v/>
       </c>
-      <c r="AN15" s="12">
+      <c r="AN15" s="16">
         <f>AK15*2</f>
         <v/>
       </c>
-      <c r="AO15" s="12">
+      <c r="AO15" s="16">
         <f>AL15*3</f>
         <v/>
       </c>
-      <c r="AP15" s="12">
+      <c r="AP15" s="16">
         <f>SUM(AM15:AO15)</f>
         <v/>
       </c>
@@ -6531,31 +6154,31 @@
         <v>0</v>
       </c>
       <c r="AI16" s="4" t="n"/>
-      <c r="AJ16" s="12">
+      <c r="AJ16" s="16">
         <f>SUM(J16:M16,O16:S16,V16:Z16,AC16:AG16)</f>
         <v/>
       </c>
-      <c r="AK16" s="12">
+      <c r="AK16" s="16">
         <f>SUM(G16:I16,N16,T16:U16,AA16:AB16,AH16:AI16)</f>
         <v/>
       </c>
-      <c r="AL16" s="12">
+      <c r="AL16" s="16">
         <f>SUM(E16:F16)</f>
         <v/>
       </c>
-      <c r="AM16" s="12">
+      <c r="AM16" s="16">
         <f>AJ16*1.5</f>
         <v/>
       </c>
-      <c r="AN16" s="12">
+      <c r="AN16" s="16">
         <f>AK16*2</f>
         <v/>
       </c>
-      <c r="AO16" s="12">
+      <c r="AO16" s="16">
         <f>AL16*3</f>
         <v/>
       </c>
-      <c r="AP16" s="12">
+      <c r="AP16" s="16">
         <f>SUM(AM16:AO16)</f>
         <v/>
       </c>
@@ -6662,31 +6285,31 @@
         <v>0</v>
       </c>
       <c r="AI17" s="4" t="n"/>
-      <c r="AJ17" s="12">
+      <c r="AJ17" s="16">
         <f>SUM(J17:M17,O17:S17,V17:Z17,AC17:AG17)</f>
         <v/>
       </c>
-      <c r="AK17" s="12">
+      <c r="AK17" s="16">
         <f>SUM(G17:I17,N17,T17:U17,AA17:AB17,AH17:AI17)</f>
         <v/>
       </c>
-      <c r="AL17" s="12">
+      <c r="AL17" s="16">
         <f>SUM(E17:F17)</f>
         <v/>
       </c>
-      <c r="AM17" s="12">
+      <c r="AM17" s="16">
         <f>AJ17*1.5</f>
         <v/>
       </c>
-      <c r="AN17" s="12">
+      <c r="AN17" s="16">
         <f>AK17*2</f>
         <v/>
       </c>
-      <c r="AO17" s="12">
+      <c r="AO17" s="16">
         <f>AL17*3</f>
         <v/>
       </c>
-      <c r="AP17" s="12">
+      <c r="AP17" s="16">
         <f>SUM(AM17:AO17)</f>
         <v/>
       </c>
@@ -6793,31 +6416,31 @@
         <v>0</v>
       </c>
       <c r="AI18" s="4" t="n"/>
-      <c r="AJ18" s="12">
+      <c r="AJ18" s="16">
         <f>SUM(J18:M18,O18:S18,V18:Z18,AC18:AG18)</f>
         <v/>
       </c>
-      <c r="AK18" s="12">
+      <c r="AK18" s="16">
         <f>SUM(G18:I18,N18,T18:U18,AA18:AB18,AH18:AI18)</f>
         <v/>
       </c>
-      <c r="AL18" s="12">
+      <c r="AL18" s="16">
         <f>SUM(E18:F18)</f>
         <v/>
       </c>
-      <c r="AM18" s="12">
+      <c r="AM18" s="16">
         <f>AJ18*1.5</f>
         <v/>
       </c>
-      <c r="AN18" s="12">
+      <c r="AN18" s="16">
         <f>AK18*2</f>
         <v/>
       </c>
-      <c r="AO18" s="12">
+      <c r="AO18" s="16">
         <f>AL18*3</f>
         <v/>
       </c>
-      <c r="AP18" s="12">
+      <c r="AP18" s="16">
         <f>SUM(AM18:AO18)</f>
         <v/>
       </c>
@@ -6924,31 +6547,31 @@
         <v>0</v>
       </c>
       <c r="AI19" s="4" t="n"/>
-      <c r="AJ19" s="12">
+      <c r="AJ19" s="16">
         <f>SUM(J19:M19,O19:S19,V19:Z19,AC19:AG19)</f>
         <v/>
       </c>
-      <c r="AK19" s="12">
+      <c r="AK19" s="16">
         <f>SUM(G19:I19,N19,T19:U19,AA19:AB19,AH19:AI19)</f>
         <v/>
       </c>
-      <c r="AL19" s="12">
+      <c r="AL19" s="16">
         <f>SUM(E19:F19)</f>
         <v/>
       </c>
-      <c r="AM19" s="12">
+      <c r="AM19" s="16">
         <f>AJ19*1.5</f>
         <v/>
       </c>
-      <c r="AN19" s="12">
+      <c r="AN19" s="16">
         <f>AK19*2</f>
         <v/>
       </c>
-      <c r="AO19" s="12">
+      <c r="AO19" s="16">
         <f>AL19*3</f>
         <v/>
       </c>
-      <c r="AP19" s="12">
+      <c r="AP19" s="16">
         <f>SUM(AM19:AO19)</f>
         <v/>
       </c>
@@ -7068,21 +6691,21 @@
       <c r="AI90" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="AJ90" s="11" t="inlineStr">
+      <c r="AJ90" s="15" t="inlineStr">
         <is>
           <t>5月加班时长合计</t>
         </is>
       </c>
       <c r="AK90" s="4" t="n"/>
       <c r="AL90" s="4" t="n"/>
-      <c r="AM90" s="11" t="inlineStr">
+      <c r="AM90" s="15" t="inlineStr">
         <is>
           <t>5月加班抵扣合计</t>
         </is>
       </c>
       <c r="AN90" s="4" t="n"/>
       <c r="AO90" s="4" t="n"/>
-      <c r="AP90" s="11" t="inlineStr">
+      <c r="AP90" s="15" t="inlineStr">
         <is>
           <t>5月剩余</t>
         </is>
@@ -7228,16 +6851,16 @@
       <c r="AG93" s="4" t="n"/>
       <c r="AH93" s="4" t="n"/>
       <c r="AI93" s="4" t="n"/>
-      <c r="AJ93" s="13" t="n"/>
-      <c r="AK93" s="12">
+      <c r="AJ93" s="17" t="n"/>
+      <c r="AK93" s="16">
         <f>SUM(D93:AI93)</f>
         <v/>
       </c>
-      <c r="AL93" s="13" t="n"/>
-      <c r="AM93" s="13" t="n"/>
-      <c r="AN93" s="13" t="n"/>
-      <c r="AO93" s="13" t="n"/>
-      <c r="AP93" s="12">
+      <c r="AL93" s="17" t="n"/>
+      <c r="AM93" s="17" t="n"/>
+      <c r="AN93" s="17" t="n"/>
+      <c r="AO93" s="17" t="n"/>
+      <c r="AP93" s="16">
         <f>AJ93+AK93</f>
         <v/>
       </c>
@@ -7282,16 +6905,16 @@
       <c r="AG94" s="4" t="n"/>
       <c r="AH94" s="4" t="n"/>
       <c r="AI94" s="4" t="n"/>
-      <c r="AJ94" s="13" t="n"/>
-      <c r="AK94" s="12">
+      <c r="AJ94" s="17" t="n"/>
+      <c r="AK94" s="16">
         <f>SUM(D94:AI94)</f>
         <v/>
       </c>
-      <c r="AL94" s="13" t="n"/>
-      <c r="AM94" s="13" t="n"/>
-      <c r="AN94" s="13" t="n"/>
-      <c r="AO94" s="13" t="n"/>
-      <c r="AP94" s="12">
+      <c r="AL94" s="17" t="n"/>
+      <c r="AM94" s="17" t="n"/>
+      <c r="AN94" s="17" t="n"/>
+      <c r="AO94" s="17" t="n"/>
+      <c r="AP94" s="16">
         <f>AJ94+AK94</f>
         <v/>
       </c>
@@ -7336,16 +6959,16 @@
       <c r="AG95" s="4" t="n"/>
       <c r="AH95" s="4" t="n"/>
       <c r="AI95" s="4" t="n"/>
-      <c r="AJ95" s="13" t="n"/>
-      <c r="AK95" s="12">
+      <c r="AJ95" s="17" t="n"/>
+      <c r="AK95" s="16">
         <f>SUM(D95:AI95)</f>
         <v/>
       </c>
-      <c r="AL95" s="13" t="n"/>
-      <c r="AM95" s="13" t="n"/>
-      <c r="AN95" s="13" t="n"/>
-      <c r="AO95" s="13" t="n"/>
-      <c r="AP95" s="12">
+      <c r="AL95" s="17" t="n"/>
+      <c r="AM95" s="17" t="n"/>
+      <c r="AN95" s="17" t="n"/>
+      <c r="AO95" s="17" t="n"/>
+      <c r="AP95" s="16">
         <f>AJ95+AK95</f>
         <v/>
       </c>
@@ -7390,16 +7013,16 @@
       <c r="AG96" s="4" t="n"/>
       <c r="AH96" s="4" t="n"/>
       <c r="AI96" s="4" t="n"/>
-      <c r="AJ96" s="13" t="n"/>
-      <c r="AK96" s="12">
+      <c r="AJ96" s="17" t="n"/>
+      <c r="AK96" s="16">
         <f>SUM(D96:AI96)</f>
         <v/>
       </c>
-      <c r="AL96" s="13" t="n"/>
-      <c r="AM96" s="13" t="n"/>
-      <c r="AN96" s="13" t="n"/>
-      <c r="AO96" s="13" t="n"/>
-      <c r="AP96" s="12">
+      <c r="AL96" s="17" t="n"/>
+      <c r="AM96" s="17" t="n"/>
+      <c r="AN96" s="17" t="n"/>
+      <c r="AO96" s="17" t="n"/>
+      <c r="AP96" s="16">
         <f>AJ96+AK96</f>
         <v/>
       </c>
@@ -7444,16 +7067,16 @@
       <c r="AG97" s="4" t="n"/>
       <c r="AH97" s="4" t="n"/>
       <c r="AI97" s="4" t="n"/>
-      <c r="AJ97" s="13" t="n"/>
-      <c r="AK97" s="12">
+      <c r="AJ97" s="17" t="n"/>
+      <c r="AK97" s="16">
         <f>SUM(D97:AI97)</f>
         <v/>
       </c>
-      <c r="AL97" s="13" t="n"/>
-      <c r="AM97" s="13" t="n"/>
-      <c r="AN97" s="13" t="n"/>
-      <c r="AO97" s="13" t="n"/>
-      <c r="AP97" s="12">
+      <c r="AL97" s="17" t="n"/>
+      <c r="AM97" s="17" t="n"/>
+      <c r="AN97" s="17" t="n"/>
+      <c r="AO97" s="17" t="n"/>
+      <c r="AP97" s="16">
         <f>AJ97+AK97</f>
         <v/>
       </c>
@@ -7498,16 +7121,16 @@
       <c r="AG98" s="4" t="n"/>
       <c r="AH98" s="4" t="n"/>
       <c r="AI98" s="4" t="n"/>
-      <c r="AJ98" s="13" t="n"/>
-      <c r="AK98" s="12">
+      <c r="AJ98" s="17" t="n"/>
+      <c r="AK98" s="16">
         <f>SUM(D98:AI98)</f>
         <v/>
       </c>
-      <c r="AL98" s="13" t="n"/>
-      <c r="AM98" s="13" t="n"/>
-      <c r="AN98" s="13" t="n"/>
-      <c r="AO98" s="13" t="n"/>
-      <c r="AP98" s="12">
+      <c r="AL98" s="17" t="n"/>
+      <c r="AM98" s="17" t="n"/>
+      <c r="AN98" s="17" t="n"/>
+      <c r="AO98" s="17" t="n"/>
+      <c r="AP98" s="16">
         <f>AJ98+AK98</f>
         <v/>
       </c>
@@ -7552,16 +7175,16 @@
       <c r="AG99" s="4" t="n"/>
       <c r="AH99" s="4" t="n"/>
       <c r="AI99" s="4" t="n"/>
-      <c r="AJ99" s="13" t="n"/>
-      <c r="AK99" s="12">
+      <c r="AJ99" s="17" t="n"/>
+      <c r="AK99" s="16">
         <f>SUM(D99:AI99)</f>
         <v/>
       </c>
-      <c r="AL99" s="13" t="n"/>
-      <c r="AM99" s="13" t="n"/>
-      <c r="AN99" s="13" t="n"/>
-      <c r="AO99" s="13" t="n"/>
-      <c r="AP99" s="12">
+      <c r="AL99" s="17" t="n"/>
+      <c r="AM99" s="17" t="n"/>
+      <c r="AN99" s="17" t="n"/>
+      <c r="AO99" s="17" t="n"/>
+      <c r="AP99" s="16">
         <f>AJ99+AK99</f>
         <v/>
       </c>
@@ -7606,16 +7229,16 @@
       <c r="AG100" s="4" t="n"/>
       <c r="AH100" s="4" t="n"/>
       <c r="AI100" s="4" t="n"/>
-      <c r="AJ100" s="13" t="n"/>
-      <c r="AK100" s="12">
+      <c r="AJ100" s="17" t="n"/>
+      <c r="AK100" s="16">
         <f>SUM(D100:AI100)</f>
         <v/>
       </c>
-      <c r="AL100" s="13" t="n"/>
-      <c r="AM100" s="13" t="n"/>
-      <c r="AN100" s="13" t="n"/>
-      <c r="AO100" s="13" t="n"/>
-      <c r="AP100" s="12">
+      <c r="AL100" s="17" t="n"/>
+      <c r="AM100" s="17" t="n"/>
+      <c r="AN100" s="17" t="n"/>
+      <c r="AO100" s="17" t="n"/>
+      <c r="AP100" s="16">
         <f>AJ100+AK100</f>
         <v/>
       </c>
@@ -7660,16 +7283,16 @@
       <c r="AG101" s="4" t="n"/>
       <c r="AH101" s="4" t="n"/>
       <c r="AI101" s="4" t="n"/>
-      <c r="AJ101" s="13" t="n"/>
-      <c r="AK101" s="12">
+      <c r="AJ101" s="17" t="n"/>
+      <c r="AK101" s="16">
         <f>SUM(D101:AI101)</f>
         <v/>
       </c>
-      <c r="AL101" s="13" t="n"/>
-      <c r="AM101" s="13" t="n"/>
-      <c r="AN101" s="13" t="n"/>
-      <c r="AO101" s="13" t="n"/>
-      <c r="AP101" s="12">
+      <c r="AL101" s="17" t="n"/>
+      <c r="AM101" s="17" t="n"/>
+      <c r="AN101" s="17" t="n"/>
+      <c r="AO101" s="17" t="n"/>
+      <c r="AP101" s="16">
         <f>AJ101+AK101</f>
         <v/>
       </c>
@@ -7714,16 +7337,16 @@
       <c r="AG102" s="4" t="n"/>
       <c r="AH102" s="4" t="n"/>
       <c r="AI102" s="4" t="n"/>
-      <c r="AJ102" s="13" t="n"/>
-      <c r="AK102" s="12">
+      <c r="AJ102" s="17" t="n"/>
+      <c r="AK102" s="16">
         <f>SUM(D102:AI102)</f>
         <v/>
       </c>
-      <c r="AL102" s="13" t="n"/>
-      <c r="AM102" s="13" t="n"/>
-      <c r="AN102" s="13" t="n"/>
-      <c r="AO102" s="13" t="n"/>
-      <c r="AP102" s="12">
+      <c r="AL102" s="17" t="n"/>
+      <c r="AM102" s="17" t="n"/>
+      <c r="AN102" s="17" t="n"/>
+      <c r="AO102" s="17" t="n"/>
+      <c r="AP102" s="16">
         <f>AJ102+AK102</f>
         <v/>
       </c>
@@ -7768,16 +7391,16 @@
       <c r="AG103" s="4" t="n"/>
       <c r="AH103" s="4" t="n"/>
       <c r="AI103" s="4" t="n"/>
-      <c r="AJ103" s="13" t="n"/>
-      <c r="AK103" s="12">
+      <c r="AJ103" s="17" t="n"/>
+      <c r="AK103" s="16">
         <f>SUM(D103:AI103)</f>
         <v/>
       </c>
-      <c r="AL103" s="13" t="n"/>
-      <c r="AM103" s="13" t="n"/>
-      <c r="AN103" s="13" t="n"/>
-      <c r="AO103" s="13" t="n"/>
-      <c r="AP103" s="12">
+      <c r="AL103" s="17" t="n"/>
+      <c r="AM103" s="17" t="n"/>
+      <c r="AN103" s="17" t="n"/>
+      <c r="AO103" s="17" t="n"/>
+      <c r="AP103" s="16">
         <f>AJ103+AK103</f>
         <v/>
       </c>
@@ -7822,16 +7445,16 @@
       <c r="AG104" s="4" t="n"/>
       <c r="AH104" s="4" t="n"/>
       <c r="AI104" s="4" t="n"/>
-      <c r="AJ104" s="13" t="n"/>
-      <c r="AK104" s="12">
+      <c r="AJ104" s="17" t="n"/>
+      <c r="AK104" s="16">
         <f>SUM(D104:AI104)</f>
         <v/>
       </c>
-      <c r="AL104" s="13" t="n"/>
-      <c r="AM104" s="13" t="n"/>
-      <c r="AN104" s="13" t="n"/>
-      <c r="AO104" s="13" t="n"/>
-      <c r="AP104" s="12">
+      <c r="AL104" s="17" t="n"/>
+      <c r="AM104" s="17" t="n"/>
+      <c r="AN104" s="17" t="n"/>
+      <c r="AO104" s="17" t="n"/>
+      <c r="AP104" s="16">
         <f>AJ104+AK104</f>
         <v/>
       </c>
@@ -7876,16 +7499,16 @@
       <c r="AG105" s="4" t="n"/>
       <c r="AH105" s="4" t="n"/>
       <c r="AI105" s="4" t="n"/>
-      <c r="AJ105" s="13" t="n"/>
-      <c r="AK105" s="12">
+      <c r="AJ105" s="17" t="n"/>
+      <c r="AK105" s="16">
         <f>SUM(D105:AI105)</f>
         <v/>
       </c>
-      <c r="AL105" s="13" t="n"/>
-      <c r="AM105" s="13" t="n"/>
-      <c r="AN105" s="13" t="n"/>
-      <c r="AO105" s="13" t="n"/>
-      <c r="AP105" s="12">
+      <c r="AL105" s="17" t="n"/>
+      <c r="AM105" s="17" t="n"/>
+      <c r="AN105" s="17" t="n"/>
+      <c r="AO105" s="17" t="n"/>
+      <c r="AP105" s="16">
         <f>AJ105+AK105</f>
         <v/>
       </c>
@@ -7930,16 +7553,16 @@
       <c r="AG106" s="4" t="n"/>
       <c r="AH106" s="4" t="n"/>
       <c r="AI106" s="4" t="n"/>
-      <c r="AJ106" s="13" t="n"/>
-      <c r="AK106" s="12">
+      <c r="AJ106" s="17" t="n"/>
+      <c r="AK106" s="16">
         <f>SUM(D106:AI106)</f>
         <v/>
       </c>
-      <c r="AL106" s="13" t="n"/>
-      <c r="AM106" s="13" t="n"/>
-      <c r="AN106" s="13" t="n"/>
-      <c r="AO106" s="13" t="n"/>
-      <c r="AP106" s="12">
+      <c r="AL106" s="17" t="n"/>
+      <c r="AM106" s="17" t="n"/>
+      <c r="AN106" s="17" t="n"/>
+      <c r="AO106" s="17" t="n"/>
+      <c r="AP106" s="16">
         <f>AJ106+AK106</f>
         <v/>
       </c>
@@ -7984,16 +7607,16 @@
       <c r="AG107" s="4" t="n"/>
       <c r="AH107" s="4" t="n"/>
       <c r="AI107" s="4" t="n"/>
-      <c r="AJ107" s="13" t="n"/>
-      <c r="AK107" s="12">
+      <c r="AJ107" s="17" t="n"/>
+      <c r="AK107" s="16">
         <f>SUM(D107:AI107)</f>
         <v/>
       </c>
-      <c r="AL107" s="13" t="n"/>
-      <c r="AM107" s="13" t="n"/>
-      <c r="AN107" s="13" t="n"/>
-      <c r="AO107" s="13" t="n"/>
-      <c r="AP107" s="12">
+      <c r="AL107" s="17" t="n"/>
+      <c r="AM107" s="17" t="n"/>
+      <c r="AN107" s="17" t="n"/>
+      <c r="AO107" s="17" t="n"/>
+      <c r="AP107" s="16">
         <f>AJ107+AK107</f>
         <v/>
       </c>
@@ -8038,16 +7661,16 @@
       <c r="AG108" s="4" t="n"/>
       <c r="AH108" s="4" t="n"/>
       <c r="AI108" s="4" t="n"/>
-      <c r="AJ108" s="13" t="n"/>
-      <c r="AK108" s="12">
+      <c r="AJ108" s="17" t="n"/>
+      <c r="AK108" s="16">
         <f>SUM(D108:AI108)</f>
         <v/>
       </c>
-      <c r="AL108" s="13" t="n"/>
-      <c r="AM108" s="13" t="n"/>
-      <c r="AN108" s="13" t="n"/>
-      <c r="AO108" s="13" t="n"/>
-      <c r="AP108" s="12">
+      <c r="AL108" s="17" t="n"/>
+      <c r="AM108" s="17" t="n"/>
+      <c r="AN108" s="17" t="n"/>
+      <c r="AO108" s="17" t="n"/>
+      <c r="AP108" s="16">
         <f>AJ108+AK108</f>
         <v/>
       </c>
@@ -8092,16 +7715,16 @@
       <c r="AG109" s="4" t="n"/>
       <c r="AH109" s="4" t="n"/>
       <c r="AI109" s="4" t="n"/>
-      <c r="AJ109" s="13" t="n"/>
-      <c r="AK109" s="12">
+      <c r="AJ109" s="17" t="n"/>
+      <c r="AK109" s="16">
         <f>SUM(D109:AI109)</f>
         <v/>
       </c>
-      <c r="AL109" s="13" t="n"/>
-      <c r="AM109" s="13" t="n"/>
-      <c r="AN109" s="13" t="n"/>
-      <c r="AO109" s="13" t="n"/>
-      <c r="AP109" s="12">
+      <c r="AL109" s="17" t="n"/>
+      <c r="AM109" s="17" t="n"/>
+      <c r="AN109" s="17" t="n"/>
+      <c r="AO109" s="17" t="n"/>
+      <c r="AP109" s="16">
         <f>AJ109+AK109</f>
         <v/>
       </c>
@@ -8146,16 +7769,16 @@
       <c r="AG110" s="4" t="n"/>
       <c r="AH110" s="4" t="n"/>
       <c r="AI110" s="4" t="n"/>
-      <c r="AJ110" s="13" t="n"/>
-      <c r="AK110" s="12">
+      <c r="AJ110" s="17" t="n"/>
+      <c r="AK110" s="16">
         <f>SUM(D110:AI110)</f>
         <v/>
       </c>
-      <c r="AL110" s="13" t="n"/>
-      <c r="AM110" s="13" t="n"/>
-      <c r="AN110" s="13" t="n"/>
-      <c r="AO110" s="13" t="n"/>
-      <c r="AP110" s="12">
+      <c r="AL110" s="17" t="n"/>
+      <c r="AM110" s="17" t="n"/>
+      <c r="AN110" s="17" t="n"/>
+      <c r="AO110" s="17" t="n"/>
+      <c r="AP110" s="16">
         <f>AJ110+AK110</f>
         <v/>
       </c>
@@ -8200,16 +7823,16 @@
       <c r="AG111" s="4" t="n"/>
       <c r="AH111" s="4" t="n"/>
       <c r="AI111" s="4" t="n"/>
-      <c r="AJ111" s="13" t="n"/>
-      <c r="AK111" s="12">
+      <c r="AJ111" s="17" t="n"/>
+      <c r="AK111" s="16">
         <f>SUM(D111:AI111)</f>
         <v/>
       </c>
-      <c r="AL111" s="13" t="n"/>
-      <c r="AM111" s="13" t="n"/>
-      <c r="AN111" s="13" t="n"/>
-      <c r="AO111" s="13" t="n"/>
-      <c r="AP111" s="12">
+      <c r="AL111" s="17" t="n"/>
+      <c r="AM111" s="17" t="n"/>
+      <c r="AN111" s="17" t="n"/>
+      <c r="AO111" s="17" t="n"/>
+      <c r="AP111" s="16">
         <f>AJ111+AK111</f>
         <v/>
       </c>
@@ -8254,16 +7877,16 @@
       <c r="AG112" s="4" t="n"/>
       <c r="AH112" s="4" t="n"/>
       <c r="AI112" s="4" t="n"/>
-      <c r="AJ112" s="13" t="n"/>
-      <c r="AK112" s="12">
+      <c r="AJ112" s="17" t="n"/>
+      <c r="AK112" s="16">
         <f>SUM(D112:AI112)</f>
         <v/>
       </c>
-      <c r="AL112" s="13" t="n"/>
-      <c r="AM112" s="13" t="n"/>
-      <c r="AN112" s="13" t="n"/>
-      <c r="AO112" s="13" t="n"/>
-      <c r="AP112" s="12">
+      <c r="AL112" s="17" t="n"/>
+      <c r="AM112" s="17" t="n"/>
+      <c r="AN112" s="17" t="n"/>
+      <c r="AO112" s="17" t="n"/>
+      <c r="AP112" s="16">
         <f>AJ112+AK112</f>
         <v/>
       </c>
@@ -8308,16 +7931,16 @@
       <c r="AG113" s="4" t="n"/>
       <c r="AH113" s="4" t="n"/>
       <c r="AI113" s="4" t="n"/>
-      <c r="AJ113" s="13" t="n"/>
-      <c r="AK113" s="12">
+      <c r="AJ113" s="17" t="n"/>
+      <c r="AK113" s="16">
         <f>SUM(D113:AI113)</f>
         <v/>
       </c>
-      <c r="AL113" s="13" t="n"/>
-      <c r="AM113" s="13" t="n"/>
-      <c r="AN113" s="13" t="n"/>
-      <c r="AO113" s="13" t="n"/>
-      <c r="AP113" s="12">
+      <c r="AL113" s="17" t="n"/>
+      <c r="AM113" s="17" t="n"/>
+      <c r="AN113" s="17" t="n"/>
+      <c r="AO113" s="17" t="n"/>
+      <c r="AP113" s="16">
         <f>AJ113+AK113</f>
         <v/>
       </c>
@@ -8362,16 +7985,16 @@
       <c r="AG114" s="4" t="n"/>
       <c r="AH114" s="4" t="n"/>
       <c r="AI114" s="4" t="n"/>
-      <c r="AJ114" s="13" t="n"/>
-      <c r="AK114" s="12">
+      <c r="AJ114" s="17" t="n"/>
+      <c r="AK114" s="16">
         <f>SUM(D114:AI114)</f>
         <v/>
       </c>
-      <c r="AL114" s="13" t="n"/>
-      <c r="AM114" s="13" t="n"/>
-      <c r="AN114" s="13" t="n"/>
-      <c r="AO114" s="13" t="n"/>
-      <c r="AP114" s="12">
+      <c r="AL114" s="17" t="n"/>
+      <c r="AM114" s="17" t="n"/>
+      <c r="AN114" s="17" t="n"/>
+      <c r="AO114" s="17" t="n"/>
+      <c r="AP114" s="16">
         <f>AJ114+AK114</f>
         <v/>
       </c>
@@ -8416,16 +8039,16 @@
       <c r="AG115" s="4" t="n"/>
       <c r="AH115" s="4" t="n"/>
       <c r="AI115" s="4" t="n"/>
-      <c r="AJ115" s="13" t="n"/>
-      <c r="AK115" s="12">
+      <c r="AJ115" s="17" t="n"/>
+      <c r="AK115" s="16">
         <f>SUM(D115:AI115)</f>
         <v/>
       </c>
-      <c r="AL115" s="13" t="n"/>
-      <c r="AM115" s="13" t="n"/>
-      <c r="AN115" s="13" t="n"/>
-      <c r="AO115" s="13" t="n"/>
-      <c r="AP115" s="12">
+      <c r="AL115" s="17" t="n"/>
+      <c r="AM115" s="17" t="n"/>
+      <c r="AN115" s="17" t="n"/>
+      <c r="AO115" s="17" t="n"/>
+      <c r="AP115" s="16">
         <f>AJ115+AK115</f>
         <v/>
       </c>
@@ -8470,16 +8093,16 @@
       <c r="AG116" s="4" t="n"/>
       <c r="AH116" s="4" t="n"/>
       <c r="AI116" s="4" t="n"/>
-      <c r="AJ116" s="13" t="n"/>
-      <c r="AK116" s="12">
+      <c r="AJ116" s="17" t="n"/>
+      <c r="AK116" s="16">
         <f>SUM(D116:AI116)</f>
         <v/>
       </c>
-      <c r="AL116" s="13" t="n"/>
-      <c r="AM116" s="13" t="n"/>
-      <c r="AN116" s="13" t="n"/>
-      <c r="AO116" s="13" t="n"/>
-      <c r="AP116" s="12">
+      <c r="AL116" s="17" t="n"/>
+      <c r="AM116" s="17" t="n"/>
+      <c r="AN116" s="17" t="n"/>
+      <c r="AO116" s="17" t="n"/>
+      <c r="AP116" s="16">
         <f>AJ116+AK116</f>
         <v/>
       </c>
@@ -8524,16 +8147,16 @@
       <c r="AG117" s="4" t="n"/>
       <c r="AH117" s="4" t="n"/>
       <c r="AI117" s="4" t="n"/>
-      <c r="AJ117" s="13" t="n"/>
-      <c r="AK117" s="12">
+      <c r="AJ117" s="17" t="n"/>
+      <c r="AK117" s="16">
         <f>SUM(D117:AI117)</f>
         <v/>
       </c>
-      <c r="AL117" s="13" t="n"/>
-      <c r="AM117" s="13" t="n"/>
-      <c r="AN117" s="13" t="n"/>
-      <c r="AO117" s="13" t="n"/>
-      <c r="AP117" s="12">
+      <c r="AL117" s="17" t="n"/>
+      <c r="AM117" s="17" t="n"/>
+      <c r="AN117" s="17" t="n"/>
+      <c r="AO117" s="17" t="n"/>
+      <c r="AP117" s="16">
         <f>AJ117+AK117</f>
         <v/>
       </c>
@@ -8578,16 +8201,16 @@
       <c r="AG118" s="4" t="n"/>
       <c r="AH118" s="4" t="n"/>
       <c r="AI118" s="4" t="n"/>
-      <c r="AJ118" s="13" t="n"/>
-      <c r="AK118" s="12">
+      <c r="AJ118" s="17" t="n"/>
+      <c r="AK118" s="16">
         <f>SUM(D118:AI118)</f>
         <v/>
       </c>
-      <c r="AL118" s="13" t="n"/>
-      <c r="AM118" s="13" t="n"/>
-      <c r="AN118" s="13" t="n"/>
-      <c r="AO118" s="13" t="n"/>
-      <c r="AP118" s="12">
+      <c r="AL118" s="17" t="n"/>
+      <c r="AM118" s="17" t="n"/>
+      <c r="AN118" s="17" t="n"/>
+      <c r="AO118" s="17" t="n"/>
+      <c r="AP118" s="16">
         <f>AJ118+AK118</f>
         <v/>
       </c>
@@ -8632,16 +8255,16 @@
       <c r="AG119" s="4" t="n"/>
       <c r="AH119" s="4" t="n"/>
       <c r="AI119" s="4" t="n"/>
-      <c r="AJ119" s="13" t="n"/>
-      <c r="AK119" s="12">
+      <c r="AJ119" s="17" t="n"/>
+      <c r="AK119" s="16">
         <f>SUM(D119:AI119)</f>
         <v/>
       </c>
-      <c r="AL119" s="13" t="n"/>
-      <c r="AM119" s="13" t="n"/>
-      <c r="AN119" s="13" t="n"/>
-      <c r="AO119" s="13" t="n"/>
-      <c r="AP119" s="12">
+      <c r="AL119" s="17" t="n"/>
+      <c r="AM119" s="17" t="n"/>
+      <c r="AN119" s="17" t="n"/>
+      <c r="AO119" s="17" t="n"/>
+      <c r="AP119" s="16">
         <f>AJ119+AK119</f>
         <v/>
       </c>
@@ -8686,16 +8309,16 @@
       <c r="AG120" s="4" t="n"/>
       <c r="AH120" s="4" t="n"/>
       <c r="AI120" s="4" t="n"/>
-      <c r="AJ120" s="13" t="n"/>
-      <c r="AK120" s="12">
+      <c r="AJ120" s="17" t="n"/>
+      <c r="AK120" s="16">
         <f>SUM(D120:AI120)</f>
         <v/>
       </c>
-      <c r="AL120" s="13" t="n"/>
-      <c r="AM120" s="13" t="n"/>
-      <c r="AN120" s="13" t="n"/>
-      <c r="AO120" s="13" t="n"/>
-      <c r="AP120" s="12">
+      <c r="AL120" s="17" t="n"/>
+      <c r="AM120" s="17" t="n"/>
+      <c r="AN120" s="17" t="n"/>
+      <c r="AO120" s="17" t="n"/>
+      <c r="AP120" s="16">
         <f>AJ120+AK120</f>
         <v/>
       </c>
@@ -8740,16 +8363,16 @@
       <c r="AG121" s="4" t="n"/>
       <c r="AH121" s="4" t="n"/>
       <c r="AI121" s="4" t="n"/>
-      <c r="AJ121" s="13" t="n"/>
-      <c r="AK121" s="12">
+      <c r="AJ121" s="17" t="n"/>
+      <c r="AK121" s="16">
         <f>SUM(D121:AI121)</f>
         <v/>
       </c>
-      <c r="AL121" s="13" t="n"/>
-      <c r="AM121" s="13" t="n"/>
-      <c r="AN121" s="13" t="n"/>
-      <c r="AO121" s="13" t="n"/>
-      <c r="AP121" s="12">
+      <c r="AL121" s="17" t="n"/>
+      <c r="AM121" s="17" t="n"/>
+      <c r="AN121" s="17" t="n"/>
+      <c r="AO121" s="17" t="n"/>
+      <c r="AP121" s="16">
         <f>AJ121+AK121</f>
         <v/>
       </c>
@@ -8794,16 +8417,16 @@
       <c r="AG122" s="4" t="n"/>
       <c r="AH122" s="4" t="n"/>
       <c r="AI122" s="4" t="n"/>
-      <c r="AJ122" s="13" t="n"/>
-      <c r="AK122" s="12">
+      <c r="AJ122" s="17" t="n"/>
+      <c r="AK122" s="16">
         <f>SUM(D122:AI122)</f>
         <v/>
       </c>
-      <c r="AL122" s="13" t="n"/>
-      <c r="AM122" s="13" t="n"/>
-      <c r="AN122" s="13" t="n"/>
-      <c r="AO122" s="13" t="n"/>
-      <c r="AP122" s="12">
+      <c r="AL122" s="17" t="n"/>
+      <c r="AM122" s="17" t="n"/>
+      <c r="AN122" s="17" t="n"/>
+      <c r="AO122" s="17" t="n"/>
+      <c r="AP122" s="16">
         <f>AJ122+AK122</f>
         <v/>
       </c>
@@ -8848,16 +8471,16 @@
       <c r="AG123" s="4" t="n"/>
       <c r="AH123" s="4" t="n"/>
       <c r="AI123" s="4" t="n"/>
-      <c r="AJ123" s="13" t="n"/>
-      <c r="AK123" s="12">
+      <c r="AJ123" s="17" t="n"/>
+      <c r="AK123" s="16">
         <f>SUM(D123:AI123)</f>
         <v/>
       </c>
-      <c r="AL123" s="13" t="n"/>
-      <c r="AM123" s="13" t="n"/>
-      <c r="AN123" s="13" t="n"/>
-      <c r="AO123" s="13" t="n"/>
-      <c r="AP123" s="12">
+      <c r="AL123" s="17" t="n"/>
+      <c r="AM123" s="17" t="n"/>
+      <c r="AN123" s="17" t="n"/>
+      <c r="AO123" s="17" t="n"/>
+      <c r="AP123" s="16">
         <f>AJ123+AK123</f>
         <v/>
       </c>
@@ -8902,16 +8525,16 @@
       <c r="AG124" s="4" t="n"/>
       <c r="AH124" s="4" t="n"/>
       <c r="AI124" s="4" t="n"/>
-      <c r="AJ124" s="13" t="n"/>
-      <c r="AK124" s="12">
+      <c r="AJ124" s="17" t="n"/>
+      <c r="AK124" s="16">
         <f>SUM(D124:AI124)</f>
         <v/>
       </c>
-      <c r="AL124" s="13" t="n"/>
-      <c r="AM124" s="13" t="n"/>
-      <c r="AN124" s="13" t="n"/>
-      <c r="AO124" s="13" t="n"/>
-      <c r="AP124" s="12">
+      <c r="AL124" s="17" t="n"/>
+      <c r="AM124" s="17" t="n"/>
+      <c r="AN124" s="17" t="n"/>
+      <c r="AO124" s="17" t="n"/>
+      <c r="AP124" s="16">
         <f>AJ124+AK124</f>
         <v/>
       </c>
@@ -8956,16 +8579,16 @@
       <c r="AG125" s="4" t="n"/>
       <c r="AH125" s="4" t="n"/>
       <c r="AI125" s="4" t="n"/>
-      <c r="AJ125" s="13" t="n"/>
-      <c r="AK125" s="12">
+      <c r="AJ125" s="17" t="n"/>
+      <c r="AK125" s="16">
         <f>SUM(D125:AI125)</f>
         <v/>
       </c>
-      <c r="AL125" s="13" t="n"/>
-      <c r="AM125" s="13" t="n"/>
-      <c r="AN125" s="13" t="n"/>
-      <c r="AO125" s="13" t="n"/>
-      <c r="AP125" s="12">
+      <c r="AL125" s="17" t="n"/>
+      <c r="AM125" s="17" t="n"/>
+      <c r="AN125" s="17" t="n"/>
+      <c r="AO125" s="17" t="n"/>
+      <c r="AP125" s="16">
         <f>AJ125+AK125</f>
         <v/>
       </c>
@@ -9010,16 +8633,16 @@
       <c r="AG126" s="4" t="n"/>
       <c r="AH126" s="4" t="n"/>
       <c r="AI126" s="4" t="n"/>
-      <c r="AJ126" s="13" t="n"/>
-      <c r="AK126" s="12">
+      <c r="AJ126" s="17" t="n"/>
+      <c r="AK126" s="16">
         <f>SUM(D126:AI126)</f>
         <v/>
       </c>
-      <c r="AL126" s="13" t="n"/>
-      <c r="AM126" s="13" t="n"/>
-      <c r="AN126" s="13" t="n"/>
-      <c r="AO126" s="13" t="n"/>
-      <c r="AP126" s="12">
+      <c r="AL126" s="17" t="n"/>
+      <c r="AM126" s="17" t="n"/>
+      <c r="AN126" s="17" t="n"/>
+      <c r="AO126" s="17" t="n"/>
+      <c r="AP126" s="16">
         <f>AJ126+AK126</f>
         <v/>
       </c>
@@ -9064,16 +8687,16 @@
       <c r="AG127" s="4" t="n"/>
       <c r="AH127" s="4" t="n"/>
       <c r="AI127" s="4" t="n"/>
-      <c r="AJ127" s="13" t="n"/>
-      <c r="AK127" s="12">
+      <c r="AJ127" s="17" t="n"/>
+      <c r="AK127" s="16">
         <f>SUM(D127:AI127)</f>
         <v/>
       </c>
-      <c r="AL127" s="13" t="n"/>
-      <c r="AM127" s="13" t="n"/>
-      <c r="AN127" s="13" t="n"/>
-      <c r="AO127" s="13" t="n"/>
-      <c r="AP127" s="12">
+      <c r="AL127" s="17" t="n"/>
+      <c r="AM127" s="17" t="n"/>
+      <c r="AN127" s="17" t="n"/>
+      <c r="AO127" s="17" t="n"/>
+      <c r="AP127" s="16">
         <f>AJ127+AK127</f>
         <v/>
       </c>
@@ -9118,16 +8741,16 @@
       <c r="AG128" s="4" t="n"/>
       <c r="AH128" s="4" t="n"/>
       <c r="AI128" s="4" t="n"/>
-      <c r="AJ128" s="13" t="n"/>
-      <c r="AK128" s="12">
+      <c r="AJ128" s="17" t="n"/>
+      <c r="AK128" s="16">
         <f>SUM(D128:AI128)</f>
         <v/>
       </c>
-      <c r="AL128" s="13" t="n"/>
-      <c r="AM128" s="13" t="n"/>
-      <c r="AN128" s="13" t="n"/>
-      <c r="AO128" s="13" t="n"/>
-      <c r="AP128" s="12">
+      <c r="AL128" s="17" t="n"/>
+      <c r="AM128" s="17" t="n"/>
+      <c r="AN128" s="17" t="n"/>
+      <c r="AO128" s="17" t="n"/>
+      <c r="AP128" s="16">
         <f>AJ128+AK128</f>
         <v/>
       </c>
@@ -9172,16 +8795,16 @@
       <c r="AG129" s="4" t="n"/>
       <c r="AH129" s="4" t="n"/>
       <c r="AI129" s="4" t="n"/>
-      <c r="AJ129" s="13" t="n"/>
-      <c r="AK129" s="12">
+      <c r="AJ129" s="17" t="n"/>
+      <c r="AK129" s="16">
         <f>SUM(D129:AI129)</f>
         <v/>
       </c>
-      <c r="AL129" s="13" t="n"/>
-      <c r="AM129" s="13" t="n"/>
-      <c r="AN129" s="13" t="n"/>
-      <c r="AO129" s="13" t="n"/>
-      <c r="AP129" s="12">
+      <c r="AL129" s="17" t="n"/>
+      <c r="AM129" s="17" t="n"/>
+      <c r="AN129" s="17" t="n"/>
+      <c r="AO129" s="17" t="n"/>
+      <c r="AP129" s="16">
         <f>AJ129+AK129</f>
         <v/>
       </c>
@@ -9226,16 +8849,16 @@
       <c r="AG130" s="4" t="n"/>
       <c r="AH130" s="4" t="n"/>
       <c r="AI130" s="4" t="n"/>
-      <c r="AJ130" s="13" t="n"/>
-      <c r="AK130" s="12">
+      <c r="AJ130" s="17" t="n"/>
+      <c r="AK130" s="16">
         <f>SUM(D130:AI130)</f>
         <v/>
       </c>
-      <c r="AL130" s="13" t="n"/>
-      <c r="AM130" s="13" t="n"/>
-      <c r="AN130" s="13" t="n"/>
-      <c r="AO130" s="13" t="n"/>
-      <c r="AP130" s="12">
+      <c r="AL130" s="17" t="n"/>
+      <c r="AM130" s="17" t="n"/>
+      <c r="AN130" s="17" t="n"/>
+      <c r="AO130" s="17" t="n"/>
+      <c r="AP130" s="16">
         <f>AJ130+AK130</f>
         <v/>
       </c>
@@ -9280,16 +8903,16 @@
       <c r="AG131" s="4" t="n"/>
       <c r="AH131" s="4" t="n"/>
       <c r="AI131" s="4" t="n"/>
-      <c r="AJ131" s="13" t="n"/>
-      <c r="AK131" s="12">
+      <c r="AJ131" s="17" t="n"/>
+      <c r="AK131" s="16">
         <f>SUM(D131:AI131)</f>
         <v/>
       </c>
-      <c r="AL131" s="13" t="n"/>
-      <c r="AM131" s="13" t="n"/>
-      <c r="AN131" s="13" t="n"/>
-      <c r="AO131" s="13" t="n"/>
-      <c r="AP131" s="12">
+      <c r="AL131" s="17" t="n"/>
+      <c r="AM131" s="17" t="n"/>
+      <c r="AN131" s="17" t="n"/>
+      <c r="AO131" s="17" t="n"/>
+      <c r="AP131" s="16">
         <f>AJ131+AK131</f>
         <v/>
       </c>
@@ -9334,16 +8957,16 @@
       <c r="AG132" s="4" t="n"/>
       <c r="AH132" s="4" t="n"/>
       <c r="AI132" s="4" t="n"/>
-      <c r="AJ132" s="13" t="n"/>
-      <c r="AK132" s="12">
+      <c r="AJ132" s="17" t="n"/>
+      <c r="AK132" s="16">
         <f>SUM(D132:AI132)</f>
         <v/>
       </c>
-      <c r="AL132" s="13" t="n"/>
-      <c r="AM132" s="13" t="n"/>
-      <c r="AN132" s="13" t="n"/>
-      <c r="AO132" s="13" t="n"/>
-      <c r="AP132" s="12">
+      <c r="AL132" s="17" t="n"/>
+      <c r="AM132" s="17" t="n"/>
+      <c r="AN132" s="17" t="n"/>
+      <c r="AO132" s="17" t="n"/>
+      <c r="AP132" s="16">
         <f>AJ132+AK132</f>
         <v/>
       </c>
@@ -9388,16 +9011,16 @@
       <c r="AG133" s="4" t="n"/>
       <c r="AH133" s="4" t="n"/>
       <c r="AI133" s="4" t="n"/>
-      <c r="AJ133" s="13" t="n"/>
-      <c r="AK133" s="12">
+      <c r="AJ133" s="17" t="n"/>
+      <c r="AK133" s="16">
         <f>SUM(D133:AI133)</f>
         <v/>
       </c>
-      <c r="AL133" s="13" t="n"/>
-      <c r="AM133" s="13" t="n"/>
-      <c r="AN133" s="13" t="n"/>
-      <c r="AO133" s="13" t="n"/>
-      <c r="AP133" s="12">
+      <c r="AL133" s="17" t="n"/>
+      <c r="AM133" s="17" t="n"/>
+      <c r="AN133" s="17" t="n"/>
+      <c r="AO133" s="17" t="n"/>
+      <c r="AP133" s="16">
         <f>AJ133+AK133</f>
         <v/>
       </c>
@@ -9442,16 +9065,16 @@
       <c r="AG134" s="4" t="n"/>
       <c r="AH134" s="4" t="n"/>
       <c r="AI134" s="4" t="n"/>
-      <c r="AJ134" s="13" t="n"/>
-      <c r="AK134" s="12">
+      <c r="AJ134" s="17" t="n"/>
+      <c r="AK134" s="16">
         <f>SUM(D134:AI134)</f>
         <v/>
       </c>
-      <c r="AL134" s="13" t="n"/>
-      <c r="AM134" s="13" t="n"/>
-      <c r="AN134" s="13" t="n"/>
-      <c r="AO134" s="13" t="n"/>
-      <c r="AP134" s="12">
+      <c r="AL134" s="17" t="n"/>
+      <c r="AM134" s="17" t="n"/>
+      <c r="AN134" s="17" t="n"/>
+      <c r="AO134" s="17" t="n"/>
+      <c r="AP134" s="16">
         <f>AJ134+AK134</f>
         <v/>
       </c>
@@ -9496,16 +9119,16 @@
       <c r="AG135" s="4" t="n"/>
       <c r="AH135" s="4" t="n"/>
       <c r="AI135" s="4" t="n"/>
-      <c r="AJ135" s="13" t="n"/>
-      <c r="AK135" s="12">
+      <c r="AJ135" s="17" t="n"/>
+      <c r="AK135" s="16">
         <f>SUM(D135:AI135)</f>
         <v/>
       </c>
-      <c r="AL135" s="13" t="n"/>
-      <c r="AM135" s="13" t="n"/>
-      <c r="AN135" s="13" t="n"/>
-      <c r="AO135" s="13" t="n"/>
-      <c r="AP135" s="12">
+      <c r="AL135" s="17" t="n"/>
+      <c r="AM135" s="17" t="n"/>
+      <c r="AN135" s="17" t="n"/>
+      <c r="AO135" s="17" t="n"/>
+      <c r="AP135" s="16">
         <f>AJ135+AK135</f>
         <v/>
       </c>
@@ -9550,16 +9173,16 @@
       <c r="AG136" s="4" t="n"/>
       <c r="AH136" s="4" t="n"/>
       <c r="AI136" s="4" t="n"/>
-      <c r="AJ136" s="13" t="n"/>
-      <c r="AK136" s="12">
+      <c r="AJ136" s="17" t="n"/>
+      <c r="AK136" s="16">
         <f>SUM(D136:AI136)</f>
         <v/>
       </c>
-      <c r="AL136" s="13" t="n"/>
-      <c r="AM136" s="13" t="n"/>
-      <c r="AN136" s="13" t="n"/>
-      <c r="AO136" s="13" t="n"/>
-      <c r="AP136" s="12">
+      <c r="AL136" s="17" t="n"/>
+      <c r="AM136" s="17" t="n"/>
+      <c r="AN136" s="17" t="n"/>
+      <c r="AO136" s="17" t="n"/>
+      <c r="AP136" s="16">
         <f>AJ136+AK136</f>
         <v/>
       </c>
@@ -9604,16 +9227,16 @@
       <c r="AG137" s="4" t="n"/>
       <c r="AH137" s="4" t="n"/>
       <c r="AI137" s="4" t="n"/>
-      <c r="AJ137" s="13" t="n"/>
-      <c r="AK137" s="12">
+      <c r="AJ137" s="17" t="n"/>
+      <c r="AK137" s="16">
         <f>SUM(D137:AI137)</f>
         <v/>
       </c>
-      <c r="AL137" s="13" t="n"/>
-      <c r="AM137" s="13" t="n"/>
-      <c r="AN137" s="13" t="n"/>
-      <c r="AO137" s="13" t="n"/>
-      <c r="AP137" s="12">
+      <c r="AL137" s="17" t="n"/>
+      <c r="AM137" s="17" t="n"/>
+      <c r="AN137" s="17" t="n"/>
+      <c r="AO137" s="17" t="n"/>
+      <c r="AP137" s="16">
         <f>AJ137+AK137</f>
         <v/>
       </c>
@@ -9658,16 +9281,16 @@
       <c r="AG138" s="4" t="n"/>
       <c r="AH138" s="4" t="n"/>
       <c r="AI138" s="4" t="n"/>
-      <c r="AJ138" s="13" t="n"/>
-      <c r="AK138" s="12">
+      <c r="AJ138" s="17" t="n"/>
+      <c r="AK138" s="16">
         <f>SUM(D138:AI138)</f>
         <v/>
       </c>
-      <c r="AL138" s="13" t="n"/>
-      <c r="AM138" s="13" t="n"/>
-      <c r="AN138" s="13" t="n"/>
-      <c r="AO138" s="13" t="n"/>
-      <c r="AP138" s="12">
+      <c r="AL138" s="17" t="n"/>
+      <c r="AM138" s="17" t="n"/>
+      <c r="AN138" s="17" t="n"/>
+      <c r="AO138" s="17" t="n"/>
+      <c r="AP138" s="16">
         <f>AJ138+AK138</f>
         <v/>
       </c>
@@ -9712,16 +9335,16 @@
       <c r="AG139" s="4" t="n"/>
       <c r="AH139" s="4" t="n"/>
       <c r="AI139" s="4" t="n"/>
-      <c r="AJ139" s="13" t="n"/>
-      <c r="AK139" s="12">
+      <c r="AJ139" s="17" t="n"/>
+      <c r="AK139" s="16">
         <f>SUM(D139:AI139)</f>
         <v/>
       </c>
-      <c r="AL139" s="13" t="n"/>
-      <c r="AM139" s="13" t="n"/>
-      <c r="AN139" s="13" t="n"/>
-      <c r="AO139" s="13" t="n"/>
-      <c r="AP139" s="12">
+      <c r="AL139" s="17" t="n"/>
+      <c r="AM139" s="17" t="n"/>
+      <c r="AN139" s="17" t="n"/>
+      <c r="AO139" s="17" t="n"/>
+      <c r="AP139" s="16">
         <f>AJ139+AK139</f>
         <v/>
       </c>
@@ -9766,16 +9389,16 @@
       <c r="AG140" s="4" t="n"/>
       <c r="AH140" s="4" t="n"/>
       <c r="AI140" s="4" t="n"/>
-      <c r="AJ140" s="13" t="n"/>
-      <c r="AK140" s="12">
+      <c r="AJ140" s="17" t="n"/>
+      <c r="AK140" s="16">
         <f>SUM(D140:AI140)</f>
         <v/>
       </c>
-      <c r="AL140" s="13" t="n"/>
-      <c r="AM140" s="13" t="n"/>
-      <c r="AN140" s="13" t="n"/>
-      <c r="AO140" s="13" t="n"/>
-      <c r="AP140" s="12">
+      <c r="AL140" s="17" t="n"/>
+      <c r="AM140" s="17" t="n"/>
+      <c r="AN140" s="17" t="n"/>
+      <c r="AO140" s="17" t="n"/>
+      <c r="AP140" s="16">
         <f>AJ140+AK140</f>
         <v/>
       </c>
@@ -9820,16 +9443,16 @@
       <c r="AG141" s="4" t="n"/>
       <c r="AH141" s="4" t="n"/>
       <c r="AI141" s="4" t="n"/>
-      <c r="AJ141" s="13" t="n"/>
-      <c r="AK141" s="12">
+      <c r="AJ141" s="17" t="n"/>
+      <c r="AK141" s="16">
         <f>SUM(D141:AI141)</f>
         <v/>
       </c>
-      <c r="AL141" s="13" t="n"/>
-      <c r="AM141" s="13" t="n"/>
-      <c r="AN141" s="13" t="n"/>
-      <c r="AO141" s="13" t="n"/>
-      <c r="AP141" s="12">
+      <c r="AL141" s="17" t="n"/>
+      <c r="AM141" s="17" t="n"/>
+      <c r="AN141" s="17" t="n"/>
+      <c r="AO141" s="17" t="n"/>
+      <c r="AP141" s="16">
         <f>AJ141+AK141</f>
         <v/>
       </c>
@@ -9874,16 +9497,16 @@
       <c r="AG142" s="4" t="n"/>
       <c r="AH142" s="4" t="n"/>
       <c r="AI142" s="4" t="n"/>
-      <c r="AJ142" s="13" t="n"/>
-      <c r="AK142" s="12">
+      <c r="AJ142" s="17" t="n"/>
+      <c r="AK142" s="16">
         <f>SUM(D142:AI142)</f>
         <v/>
       </c>
-      <c r="AL142" s="13" t="n"/>
-      <c r="AM142" s="13" t="n"/>
-      <c r="AN142" s="13" t="n"/>
-      <c r="AO142" s="13" t="n"/>
-      <c r="AP142" s="12">
+      <c r="AL142" s="17" t="n"/>
+      <c r="AM142" s="17" t="n"/>
+      <c r="AN142" s="17" t="n"/>
+      <c r="AO142" s="17" t="n"/>
+      <c r="AP142" s="16">
         <f>AJ142+AK142</f>
         <v/>
       </c>
@@ -9928,16 +9551,16 @@
       <c r="AG143" s="4" t="n"/>
       <c r="AH143" s="4" t="n"/>
       <c r="AI143" s="4" t="n"/>
-      <c r="AJ143" s="13" t="n"/>
-      <c r="AK143" s="12">
+      <c r="AJ143" s="17" t="n"/>
+      <c r="AK143" s="16">
         <f>SUM(D143:AI143)</f>
         <v/>
       </c>
-      <c r="AL143" s="13" t="n"/>
-      <c r="AM143" s="13" t="n"/>
-      <c r="AN143" s="13" t="n"/>
-      <c r="AO143" s="13" t="n"/>
-      <c r="AP143" s="12">
+      <c r="AL143" s="17" t="n"/>
+      <c r="AM143" s="17" t="n"/>
+      <c r="AN143" s="17" t="n"/>
+      <c r="AO143" s="17" t="n"/>
+      <c r="AP143" s="16">
         <f>AJ143+AK143</f>
         <v/>
       </c>
@@ -9982,16 +9605,16 @@
       <c r="AG144" s="4" t="n"/>
       <c r="AH144" s="4" t="n"/>
       <c r="AI144" s="4" t="n"/>
-      <c r="AJ144" s="13" t="n"/>
-      <c r="AK144" s="12">
+      <c r="AJ144" s="17" t="n"/>
+      <c r="AK144" s="16">
         <f>SUM(D144:AI144)</f>
         <v/>
       </c>
-      <c r="AL144" s="13" t="n"/>
-      <c r="AM144" s="13" t="n"/>
-      <c r="AN144" s="13" t="n"/>
-      <c r="AO144" s="13" t="n"/>
-      <c r="AP144" s="12">
+      <c r="AL144" s="17" t="n"/>
+      <c r="AM144" s="17" t="n"/>
+      <c r="AN144" s="17" t="n"/>
+      <c r="AO144" s="17" t="n"/>
+      <c r="AP144" s="16">
         <f>AJ144+AK144</f>
         <v/>
       </c>
@@ -10036,16 +9659,16 @@
       <c r="AG145" s="4" t="n"/>
       <c r="AH145" s="4" t="n"/>
       <c r="AI145" s="4" t="n"/>
-      <c r="AJ145" s="13" t="n"/>
-      <c r="AK145" s="12">
+      <c r="AJ145" s="17" t="n"/>
+      <c r="AK145" s="16">
         <f>SUM(D145:AI145)</f>
         <v/>
       </c>
-      <c r="AL145" s="13" t="n"/>
-      <c r="AM145" s="13" t="n"/>
-      <c r="AN145" s="13" t="n"/>
-      <c r="AO145" s="13" t="n"/>
-      <c r="AP145" s="12">
+      <c r="AL145" s="17" t="n"/>
+      <c r="AM145" s="17" t="n"/>
+      <c r="AN145" s="17" t="n"/>
+      <c r="AO145" s="17" t="n"/>
+      <c r="AP145" s="16">
         <f>AJ145+AK145</f>
         <v/>
       </c>
@@ -10090,16 +9713,16 @@
       <c r="AG146" s="4" t="n"/>
       <c r="AH146" s="4" t="n"/>
       <c r="AI146" s="4" t="n"/>
-      <c r="AJ146" s="13" t="n"/>
-      <c r="AK146" s="12">
+      <c r="AJ146" s="17" t="n"/>
+      <c r="AK146" s="16">
         <f>SUM(D146:AI146)</f>
         <v/>
       </c>
-      <c r="AL146" s="13" t="n"/>
-      <c r="AM146" s="13" t="n"/>
-      <c r="AN146" s="13" t="n"/>
-      <c r="AO146" s="13" t="n"/>
-      <c r="AP146" s="12">
+      <c r="AL146" s="17" t="n"/>
+      <c r="AM146" s="17" t="n"/>
+      <c r="AN146" s="17" t="n"/>
+      <c r="AO146" s="17" t="n"/>
+      <c r="AP146" s="16">
         <f>AJ146+AK146</f>
         <v/>
       </c>
@@ -10144,16 +9767,16 @@
       <c r="AG147" s="4" t="n"/>
       <c r="AH147" s="4" t="n"/>
       <c r="AI147" s="4" t="n"/>
-      <c r="AJ147" s="13" t="n"/>
-      <c r="AK147" s="12">
+      <c r="AJ147" s="17" t="n"/>
+      <c r="AK147" s="16">
         <f>SUM(D147:AI147)</f>
         <v/>
       </c>
-      <c r="AL147" s="13" t="n"/>
-      <c r="AM147" s="13" t="n"/>
-      <c r="AN147" s="13" t="n"/>
-      <c r="AO147" s="13" t="n"/>
-      <c r="AP147" s="12">
+      <c r="AL147" s="17" t="n"/>
+      <c r="AM147" s="17" t="n"/>
+      <c r="AN147" s="17" t="n"/>
+      <c r="AO147" s="17" t="n"/>
+      <c r="AP147" s="16">
         <f>AJ147+AK147</f>
         <v/>
       </c>
@@ -10198,16 +9821,16 @@
       <c r="AG148" s="4" t="n"/>
       <c r="AH148" s="4" t="n"/>
       <c r="AI148" s="4" t="n"/>
-      <c r="AJ148" s="13" t="n"/>
-      <c r="AK148" s="12">
+      <c r="AJ148" s="17" t="n"/>
+      <c r="AK148" s="16">
         <f>SUM(D148:AI148)</f>
         <v/>
       </c>
-      <c r="AL148" s="13" t="n"/>
-      <c r="AM148" s="13" t="n"/>
-      <c r="AN148" s="13" t="n"/>
-      <c r="AO148" s="13" t="n"/>
-      <c r="AP148" s="12">
+      <c r="AL148" s="17" t="n"/>
+      <c r="AM148" s="17" t="n"/>
+      <c r="AN148" s="17" t="n"/>
+      <c r="AO148" s="17" t="n"/>
+      <c r="AP148" s="16">
         <f>AJ148+AK148</f>
         <v/>
       </c>
@@ -10252,16 +9875,16 @@
       <c r="AG149" s="4" t="n"/>
       <c r="AH149" s="4" t="n"/>
       <c r="AI149" s="4" t="n"/>
-      <c r="AJ149" s="13" t="n"/>
-      <c r="AK149" s="12">
+      <c r="AJ149" s="17" t="n"/>
+      <c r="AK149" s="16">
         <f>SUM(D149:AI149)</f>
         <v/>
       </c>
-      <c r="AL149" s="13" t="n"/>
-      <c r="AM149" s="13" t="n"/>
-      <c r="AN149" s="13" t="n"/>
-      <c r="AO149" s="13" t="n"/>
-      <c r="AP149" s="12">
+      <c r="AL149" s="17" t="n"/>
+      <c r="AM149" s="17" t="n"/>
+      <c r="AN149" s="17" t="n"/>
+      <c r="AO149" s="17" t="n"/>
+      <c r="AP149" s="16">
         <f>AJ149+AK149</f>
         <v/>
       </c>
@@ -10306,16 +9929,16 @@
       <c r="AG150" s="4" t="n"/>
       <c r="AH150" s="4" t="n"/>
       <c r="AI150" s="4" t="n"/>
-      <c r="AJ150" s="13" t="n"/>
-      <c r="AK150" s="12">
+      <c r="AJ150" s="17" t="n"/>
+      <c r="AK150" s="16">
         <f>SUM(D150:AI150)</f>
         <v/>
       </c>
-      <c r="AL150" s="13" t="n"/>
-      <c r="AM150" s="13" t="n"/>
-      <c r="AN150" s="13" t="n"/>
-      <c r="AO150" s="13" t="n"/>
-      <c r="AP150" s="12">
+      <c r="AL150" s="17" t="n"/>
+      <c r="AM150" s="17" t="n"/>
+      <c r="AN150" s="17" t="n"/>
+      <c r="AO150" s="17" t="n"/>
+      <c r="AP150" s="16">
         <f>AJ150+AK150</f>
         <v/>
       </c>
@@ -10360,16 +9983,16 @@
       <c r="AG151" s="4" t="n"/>
       <c r="AH151" s="4" t="n"/>
       <c r="AI151" s="4" t="n"/>
-      <c r="AJ151" s="13" t="n"/>
-      <c r="AK151" s="12">
+      <c r="AJ151" s="17" t="n"/>
+      <c r="AK151" s="16">
         <f>SUM(D151:AI151)</f>
         <v/>
       </c>
-      <c r="AL151" s="13" t="n"/>
-      <c r="AM151" s="13" t="n"/>
-      <c r="AN151" s="13" t="n"/>
-      <c r="AO151" s="13" t="n"/>
-      <c r="AP151" s="12">
+      <c r="AL151" s="17" t="n"/>
+      <c r="AM151" s="17" t="n"/>
+      <c r="AN151" s="17" t="n"/>
+      <c r="AO151" s="17" t="n"/>
+      <c r="AP151" s="16">
         <f>AJ151+AK151</f>
         <v/>
       </c>
@@ -10414,16 +10037,16 @@
       <c r="AG152" s="4" t="n"/>
       <c r="AH152" s="4" t="n"/>
       <c r="AI152" s="4" t="n"/>
-      <c r="AJ152" s="13" t="n"/>
-      <c r="AK152" s="12">
+      <c r="AJ152" s="17" t="n"/>
+      <c r="AK152" s="16">
         <f>SUM(D152:AI152)</f>
         <v/>
       </c>
-      <c r="AL152" s="13" t="n"/>
-      <c r="AM152" s="13" t="n"/>
-      <c r="AN152" s="13" t="n"/>
-      <c r="AO152" s="13" t="n"/>
-      <c r="AP152" s="12">
+      <c r="AL152" s="17" t="n"/>
+      <c r="AM152" s="17" t="n"/>
+      <c r="AN152" s="17" t="n"/>
+      <c r="AO152" s="17" t="n"/>
+      <c r="AP152" s="16">
         <f>AJ152+AK152</f>
         <v/>
       </c>
@@ -10468,16 +10091,16 @@
       <c r="AG153" s="4" t="n"/>
       <c r="AH153" s="4" t="n"/>
       <c r="AI153" s="4" t="n"/>
-      <c r="AJ153" s="13" t="n"/>
-      <c r="AK153" s="12">
+      <c r="AJ153" s="17" t="n"/>
+      <c r="AK153" s="16">
         <f>SUM(D153:AI153)</f>
         <v/>
       </c>
-      <c r="AL153" s="13" t="n"/>
-      <c r="AM153" s="13" t="n"/>
-      <c r="AN153" s="13" t="n"/>
-      <c r="AO153" s="13" t="n"/>
-      <c r="AP153" s="12">
+      <c r="AL153" s="17" t="n"/>
+      <c r="AM153" s="17" t="n"/>
+      <c r="AN153" s="17" t="n"/>
+      <c r="AO153" s="17" t="n"/>
+      <c r="AP153" s="16">
         <f>AJ153+AK153</f>
         <v/>
       </c>
@@ -10522,16 +10145,16 @@
       <c r="AG154" s="4" t="n"/>
       <c r="AH154" s="4" t="n"/>
       <c r="AI154" s="4" t="n"/>
-      <c r="AJ154" s="13" t="n"/>
-      <c r="AK154" s="12">
+      <c r="AJ154" s="17" t="n"/>
+      <c r="AK154" s="16">
         <f>SUM(D154:AI154)</f>
         <v/>
       </c>
-      <c r="AL154" s="13" t="n"/>
-      <c r="AM154" s="13" t="n"/>
-      <c r="AN154" s="13" t="n"/>
-      <c r="AO154" s="13" t="n"/>
-      <c r="AP154" s="12">
+      <c r="AL154" s="17" t="n"/>
+      <c r="AM154" s="17" t="n"/>
+      <c r="AN154" s="17" t="n"/>
+      <c r="AO154" s="17" t="n"/>
+      <c r="AP154" s="16">
         <f>AJ154+AK154</f>
         <v/>
       </c>
@@ -10576,16 +10199,16 @@
       <c r="AG155" s="4" t="n"/>
       <c r="AH155" s="4" t="n"/>
       <c r="AI155" s="4" t="n"/>
-      <c r="AJ155" s="13" t="n"/>
-      <c r="AK155" s="12">
+      <c r="AJ155" s="17" t="n"/>
+      <c r="AK155" s="16">
         <f>SUM(D155:AI155)</f>
         <v/>
       </c>
-      <c r="AL155" s="13" t="n"/>
-      <c r="AM155" s="13" t="n"/>
-      <c r="AN155" s="13" t="n"/>
-      <c r="AO155" s="13" t="n"/>
-      <c r="AP155" s="12">
+      <c r="AL155" s="17" t="n"/>
+      <c r="AM155" s="17" t="n"/>
+      <c r="AN155" s="17" t="n"/>
+      <c r="AO155" s="17" t="n"/>
+      <c r="AP155" s="16">
         <f>AJ155+AK155</f>
         <v/>
       </c>
@@ -10630,16 +10253,16 @@
       <c r="AG156" s="4" t="n"/>
       <c r="AH156" s="4" t="n"/>
       <c r="AI156" s="4" t="n"/>
-      <c r="AJ156" s="13" t="n"/>
-      <c r="AK156" s="12">
+      <c r="AJ156" s="17" t="n"/>
+      <c r="AK156" s="16">
         <f>SUM(D156:AI156)</f>
         <v/>
       </c>
-      <c r="AL156" s="13" t="n"/>
-      <c r="AM156" s="13" t="n"/>
-      <c r="AN156" s="13" t="n"/>
-      <c r="AO156" s="13" t="n"/>
-      <c r="AP156" s="12">
+      <c r="AL156" s="17" t="n"/>
+      <c r="AM156" s="17" t="n"/>
+      <c r="AN156" s="17" t="n"/>
+      <c r="AO156" s="17" t="n"/>
+      <c r="AP156" s="16">
         <f>AJ156+AK156</f>
         <v/>
       </c>
@@ -10684,16 +10307,16 @@
       <c r="AG157" s="4" t="n"/>
       <c r="AH157" s="4" t="n"/>
       <c r="AI157" s="4" t="n"/>
-      <c r="AJ157" s="13" t="n"/>
-      <c r="AK157" s="12">
+      <c r="AJ157" s="17" t="n"/>
+      <c r="AK157" s="16">
         <f>SUM(D157:AI157)</f>
         <v/>
       </c>
-      <c r="AL157" s="13" t="n"/>
-      <c r="AM157" s="13" t="n"/>
-      <c r="AN157" s="13" t="n"/>
-      <c r="AO157" s="13" t="n"/>
-      <c r="AP157" s="12">
+      <c r="AL157" s="17" t="n"/>
+      <c r="AM157" s="17" t="n"/>
+      <c r="AN157" s="17" t="n"/>
+      <c r="AO157" s="17" t="n"/>
+      <c r="AP157" s="16">
         <f>AJ157+AK157</f>
         <v/>
       </c>
@@ -10738,16 +10361,16 @@
       <c r="AG158" s="4" t="n"/>
       <c r="AH158" s="4" t="n"/>
       <c r="AI158" s="4" t="n"/>
-      <c r="AJ158" s="13" t="n"/>
-      <c r="AK158" s="12">
+      <c r="AJ158" s="17" t="n"/>
+      <c r="AK158" s="16">
         <f>SUM(D158:AI158)</f>
         <v/>
       </c>
-      <c r="AL158" s="13" t="n"/>
-      <c r="AM158" s="13" t="n"/>
-      <c r="AN158" s="13" t="n"/>
-      <c r="AO158" s="13" t="n"/>
-      <c r="AP158" s="12">
+      <c r="AL158" s="17" t="n"/>
+      <c r="AM158" s="17" t="n"/>
+      <c r="AN158" s="17" t="n"/>
+      <c r="AO158" s="17" t="n"/>
+      <c r="AP158" s="16">
         <f>AJ158+AK158</f>
         <v/>
       </c>
@@ -10792,16 +10415,16 @@
       <c r="AG159" s="4" t="n"/>
       <c r="AH159" s="4" t="n"/>
       <c r="AI159" s="4" t="n"/>
-      <c r="AJ159" s="13" t="n"/>
-      <c r="AK159" s="12">
+      <c r="AJ159" s="17" t="n"/>
+      <c r="AK159" s="16">
         <f>SUM(D159:AI159)</f>
         <v/>
       </c>
-      <c r="AL159" s="13" t="n"/>
-      <c r="AM159" s="13" t="n"/>
-      <c r="AN159" s="13" t="n"/>
-      <c r="AO159" s="13" t="n"/>
-      <c r="AP159" s="12">
+      <c r="AL159" s="17" t="n"/>
+      <c r="AM159" s="17" t="n"/>
+      <c r="AN159" s="17" t="n"/>
+      <c r="AO159" s="17" t="n"/>
+      <c r="AP159" s="16">
         <f>AJ159+AK159</f>
         <v/>
       </c>
@@ -10846,16 +10469,16 @@
       <c r="AG160" s="4" t="n"/>
       <c r="AH160" s="4" t="n"/>
       <c r="AI160" s="4" t="n"/>
-      <c r="AJ160" s="13" t="n"/>
-      <c r="AK160" s="12">
+      <c r="AJ160" s="17" t="n"/>
+      <c r="AK160" s="16">
         <f>SUM(D160:AI160)</f>
         <v/>
       </c>
-      <c r="AL160" s="13" t="n"/>
-      <c r="AM160" s="13" t="n"/>
-      <c r="AN160" s="13" t="n"/>
-      <c r="AO160" s="13" t="n"/>
-      <c r="AP160" s="12">
+      <c r="AL160" s="17" t="n"/>
+      <c r="AM160" s="17" t="n"/>
+      <c r="AN160" s="17" t="n"/>
+      <c r="AO160" s="17" t="n"/>
+      <c r="AP160" s="16">
         <f>AJ160+AK160</f>
         <v/>
       </c>
@@ -10900,16 +10523,16 @@
       <c r="AG161" s="4" t="n"/>
       <c r="AH161" s="4" t="n"/>
       <c r="AI161" s="4" t="n"/>
-      <c r="AJ161" s="13" t="n"/>
-      <c r="AK161" s="12">
+      <c r="AJ161" s="17" t="n"/>
+      <c r="AK161" s="16">
         <f>SUM(D161:AI161)</f>
         <v/>
       </c>
-      <c r="AL161" s="13" t="n"/>
-      <c r="AM161" s="13" t="n"/>
-      <c r="AN161" s="13" t="n"/>
-      <c r="AO161" s="13" t="n"/>
-      <c r="AP161" s="12">
+      <c r="AL161" s="17" t="n"/>
+      <c r="AM161" s="17" t="n"/>
+      <c r="AN161" s="17" t="n"/>
+      <c r="AO161" s="17" t="n"/>
+      <c r="AP161" s="16">
         <f>AJ161+AK161</f>
         <v/>
       </c>
@@ -10954,16 +10577,16 @@
       <c r="AG162" s="4" t="n"/>
       <c r="AH162" s="4" t="n"/>
       <c r="AI162" s="4" t="n"/>
-      <c r="AJ162" s="13" t="n"/>
-      <c r="AK162" s="12">
+      <c r="AJ162" s="17" t="n"/>
+      <c r="AK162" s="16">
         <f>SUM(D162:AI162)</f>
         <v/>
       </c>
-      <c r="AL162" s="13" t="n"/>
-      <c r="AM162" s="13" t="n"/>
-      <c r="AN162" s="13" t="n"/>
-      <c r="AO162" s="13" t="n"/>
-      <c r="AP162" s="12">
+      <c r="AL162" s="17" t="n"/>
+      <c r="AM162" s="17" t="n"/>
+      <c r="AN162" s="17" t="n"/>
+      <c r="AO162" s="17" t="n"/>
+      <c r="AP162" s="16">
         <f>AJ162+AK162</f>
         <v/>
       </c>
@@ -11008,16 +10631,16 @@
       <c r="AG163" s="4" t="n"/>
       <c r="AH163" s="4" t="n"/>
       <c r="AI163" s="4" t="n"/>
-      <c r="AJ163" s="13" t="n"/>
-      <c r="AK163" s="12">
+      <c r="AJ163" s="17" t="n"/>
+      <c r="AK163" s="16">
         <f>SUM(D163:AI163)</f>
         <v/>
       </c>
-      <c r="AL163" s="13" t="n"/>
-      <c r="AM163" s="13" t="n"/>
-      <c r="AN163" s="13" t="n"/>
-      <c r="AO163" s="13" t="n"/>
-      <c r="AP163" s="12">
+      <c r="AL163" s="17" t="n"/>
+      <c r="AM163" s="17" t="n"/>
+      <c r="AN163" s="17" t="n"/>
+      <c r="AO163" s="17" t="n"/>
+      <c r="AP163" s="16">
         <f>AJ163+AK163</f>
         <v/>
       </c>
@@ -11062,16 +10685,16 @@
       <c r="AG164" s="4" t="n"/>
       <c r="AH164" s="4" t="n"/>
       <c r="AI164" s="4" t="n"/>
-      <c r="AJ164" s="13" t="n"/>
-      <c r="AK164" s="12">
+      <c r="AJ164" s="17" t="n"/>
+      <c r="AK164" s="16">
         <f>SUM(D164:AI164)</f>
         <v/>
       </c>
-      <c r="AL164" s="13" t="n"/>
-      <c r="AM164" s="13" t="n"/>
-      <c r="AN164" s="13" t="n"/>
-      <c r="AO164" s="13" t="n"/>
-      <c r="AP164" s="12">
+      <c r="AL164" s="17" t="n"/>
+      <c r="AM164" s="17" t="n"/>
+      <c r="AN164" s="17" t="n"/>
+      <c r="AO164" s="17" t="n"/>
+      <c r="AP164" s="16">
         <f>AJ164+AK164</f>
         <v/>
       </c>
@@ -11116,16 +10739,16 @@
       <c r="AG165" s="4" t="n"/>
       <c r="AH165" s="4" t="n"/>
       <c r="AI165" s="4" t="n"/>
-      <c r="AJ165" s="13" t="n"/>
-      <c r="AK165" s="12">
+      <c r="AJ165" s="17" t="n"/>
+      <c r="AK165" s="16">
         <f>SUM(D165:AI165)</f>
         <v/>
       </c>
-      <c r="AL165" s="13" t="n"/>
-      <c r="AM165" s="13" t="n"/>
-      <c r="AN165" s="13" t="n"/>
-      <c r="AO165" s="13" t="n"/>
-      <c r="AP165" s="12">
+      <c r="AL165" s="17" t="n"/>
+      <c r="AM165" s="17" t="n"/>
+      <c r="AN165" s="17" t="n"/>
+      <c r="AO165" s="17" t="n"/>
+      <c r="AP165" s="16">
         <f>AJ165+AK165</f>
         <v/>
       </c>
@@ -11170,16 +10793,16 @@
       <c r="AG166" s="4" t="n"/>
       <c r="AH166" s="4" t="n"/>
       <c r="AI166" s="4" t="n"/>
-      <c r="AJ166" s="13" t="n"/>
-      <c r="AK166" s="12">
+      <c r="AJ166" s="17" t="n"/>
+      <c r="AK166" s="16">
         <f>SUM(D166:AI166)</f>
         <v/>
       </c>
-      <c r="AL166" s="13" t="n"/>
-      <c r="AM166" s="13" t="n"/>
-      <c r="AN166" s="13" t="n"/>
-      <c r="AO166" s="13" t="n"/>
-      <c r="AP166" s="12">
+      <c r="AL166" s="17" t="n"/>
+      <c r="AM166" s="17" t="n"/>
+      <c r="AN166" s="17" t="n"/>
+      <c r="AO166" s="17" t="n"/>
+      <c r="AP166" s="16">
         <f>AJ166+AK166</f>
         <v/>
       </c>
@@ -11224,16 +10847,16 @@
       <c r="AG167" s="4" t="n"/>
       <c r="AH167" s="4" t="n"/>
       <c r="AI167" s="4" t="n"/>
-      <c r="AJ167" s="13" t="n"/>
-      <c r="AK167" s="12">
+      <c r="AJ167" s="17" t="n"/>
+      <c r="AK167" s="16">
         <f>SUM(D167:AI167)</f>
         <v/>
       </c>
-      <c r="AL167" s="13" t="n"/>
-      <c r="AM167" s="13" t="n"/>
-      <c r="AN167" s="13" t="n"/>
-      <c r="AO167" s="13" t="n"/>
-      <c r="AP167" s="12">
+      <c r="AL167" s="17" t="n"/>
+      <c r="AM167" s="17" t="n"/>
+      <c r="AN167" s="17" t="n"/>
+      <c r="AO167" s="17" t="n"/>
+      <c r="AP167" s="16">
         <f>AJ167+AK167</f>
         <v/>
       </c>
@@ -11278,16 +10901,16 @@
       <c r="AG168" s="4" t="n"/>
       <c r="AH168" s="4" t="n"/>
       <c r="AI168" s="4" t="n"/>
-      <c r="AJ168" s="13" t="n"/>
-      <c r="AK168" s="12">
+      <c r="AJ168" s="17" t="n"/>
+      <c r="AK168" s="16">
         <f>SUM(D168:AI168)</f>
         <v/>
       </c>
-      <c r="AL168" s="13" t="n"/>
-      <c r="AM168" s="13" t="n"/>
-      <c r="AN168" s="13" t="n"/>
-      <c r="AO168" s="13" t="n"/>
-      <c r="AP168" s="12">
+      <c r="AL168" s="17" t="n"/>
+      <c r="AM168" s="17" t="n"/>
+      <c r="AN168" s="17" t="n"/>
+      <c r="AO168" s="17" t="n"/>
+      <c r="AP168" s="16">
         <f>AJ168+AK168</f>
         <v/>
       </c>
@@ -11332,16 +10955,16 @@
       <c r="AG169" s="4" t="n"/>
       <c r="AH169" s="4" t="n"/>
       <c r="AI169" s="4" t="n"/>
-      <c r="AJ169" s="13" t="n"/>
-      <c r="AK169" s="12">
+      <c r="AJ169" s="17" t="n"/>
+      <c r="AK169" s="16">
         <f>SUM(D169:AI169)</f>
         <v/>
       </c>
-      <c r="AL169" s="13" t="n"/>
-      <c r="AM169" s="13" t="n"/>
-      <c r="AN169" s="13" t="n"/>
-      <c r="AO169" s="13" t="n"/>
-      <c r="AP169" s="12">
+      <c r="AL169" s="17" t="n"/>
+      <c r="AM169" s="17" t="n"/>
+      <c r="AN169" s="17" t="n"/>
+      <c r="AO169" s="17" t="n"/>
+      <c r="AP169" s="16">
         <f>AJ169+AK169</f>
         <v/>
       </c>
@@ -11386,16 +11009,16 @@
       <c r="AG170" s="4" t="n"/>
       <c r="AH170" s="4" t="n"/>
       <c r="AI170" s="4" t="n"/>
-      <c r="AJ170" s="13" t="n"/>
-      <c r="AK170" s="12">
+      <c r="AJ170" s="17" t="n"/>
+      <c r="AK170" s="16">
         <f>SUM(D170:AI170)</f>
         <v/>
       </c>
-      <c r="AL170" s="13" t="n"/>
-      <c r="AM170" s="13" t="n"/>
-      <c r="AN170" s="13" t="n"/>
-      <c r="AO170" s="13" t="n"/>
-      <c r="AP170" s="12">
+      <c r="AL170" s="17" t="n"/>
+      <c r="AM170" s="17" t="n"/>
+      <c r="AN170" s="17" t="n"/>
+      <c r="AO170" s="17" t="n"/>
+      <c r="AP170" s="16">
         <f>AJ170+AK170</f>
         <v/>
       </c>
@@ -11440,16 +11063,16 @@
       <c r="AG171" s="4" t="n"/>
       <c r="AH171" s="4" t="n"/>
       <c r="AI171" s="4" t="n"/>
-      <c r="AJ171" s="13" t="n"/>
-      <c r="AK171" s="12">
+      <c r="AJ171" s="17" t="n"/>
+      <c r="AK171" s="16">
         <f>SUM(D171:AI171)</f>
         <v/>
       </c>
-      <c r="AL171" s="13" t="n"/>
-      <c r="AM171" s="13" t="n"/>
-      <c r="AN171" s="13" t="n"/>
-      <c r="AO171" s="13" t="n"/>
-      <c r="AP171" s="12">
+      <c r="AL171" s="17" t="n"/>
+      <c r="AM171" s="17" t="n"/>
+      <c r="AN171" s="17" t="n"/>
+      <c r="AO171" s="17" t="n"/>
+      <c r="AP171" s="16">
         <f>AJ171+AK171</f>
         <v/>
       </c>
@@ -11494,16 +11117,16 @@
       <c r="AG172" s="4" t="n"/>
       <c r="AH172" s="4" t="n"/>
       <c r="AI172" s="4" t="n"/>
-      <c r="AJ172" s="13" t="n"/>
-      <c r="AK172" s="12">
+      <c r="AJ172" s="17" t="n"/>
+      <c r="AK172" s="16">
         <f>SUM(D172:AI172)</f>
         <v/>
       </c>
-      <c r="AL172" s="13" t="n"/>
-      <c r="AM172" s="13" t="n"/>
-      <c r="AN172" s="13" t="n"/>
-      <c r="AO172" s="13" t="n"/>
-      <c r="AP172" s="12">
+      <c r="AL172" s="17" t="n"/>
+      <c r="AM172" s="17" t="n"/>
+      <c r="AN172" s="17" t="n"/>
+      <c r="AO172" s="17" t="n"/>
+      <c r="AP172" s="16">
         <f>AJ172+AK172</f>
         <v/>
       </c>
@@ -11548,16 +11171,16 @@
       <c r="AG173" s="4" t="n"/>
       <c r="AH173" s="4" t="n"/>
       <c r="AI173" s="4" t="n"/>
-      <c r="AJ173" s="13" t="n"/>
-      <c r="AK173" s="12">
+      <c r="AJ173" s="17" t="n"/>
+      <c r="AK173" s="16">
         <f>SUM(D173:AI173)</f>
         <v/>
       </c>
-      <c r="AL173" s="13" t="n"/>
-      <c r="AM173" s="13" t="n"/>
-      <c r="AN173" s="13" t="n"/>
-      <c r="AO173" s="13" t="n"/>
-      <c r="AP173" s="12">
+      <c r="AL173" s="17" t="n"/>
+      <c r="AM173" s="17" t="n"/>
+      <c r="AN173" s="17" t="n"/>
+      <c r="AO173" s="17" t="n"/>
+      <c r="AP173" s="16">
         <f>AJ173+AK173</f>
         <v/>
       </c>
@@ -11602,16 +11225,16 @@
       <c r="AG174" s="4" t="n"/>
       <c r="AH174" s="4" t="n"/>
       <c r="AI174" s="4" t="n"/>
-      <c r="AJ174" s="13" t="n"/>
-      <c r="AK174" s="12">
+      <c r="AJ174" s="17" t="n"/>
+      <c r="AK174" s="16">
         <f>SUM(D174:AI174)</f>
         <v/>
       </c>
-      <c r="AL174" s="13" t="n"/>
-      <c r="AM174" s="13" t="n"/>
-      <c r="AN174" s="13" t="n"/>
-      <c r="AO174" s="13" t="n"/>
-      <c r="AP174" s="12">
+      <c r="AL174" s="17" t="n"/>
+      <c r="AM174" s="17" t="n"/>
+      <c r="AN174" s="17" t="n"/>
+      <c r="AO174" s="17" t="n"/>
+      <c r="AP174" s="16">
         <f>AJ174+AK174</f>
         <v/>
       </c>
@@ -11656,16 +11279,16 @@
       <c r="AG175" s="4" t="n"/>
       <c r="AH175" s="4" t="n"/>
       <c r="AI175" s="4" t="n"/>
-      <c r="AJ175" s="13" t="n"/>
-      <c r="AK175" s="12">
+      <c r="AJ175" s="17" t="n"/>
+      <c r="AK175" s="16">
         <f>SUM(D175:AI175)</f>
         <v/>
       </c>
-      <c r="AL175" s="13" t="n"/>
-      <c r="AM175" s="13" t="n"/>
-      <c r="AN175" s="13" t="n"/>
-      <c r="AO175" s="13" t="n"/>
-      <c r="AP175" s="12">
+      <c r="AL175" s="17" t="n"/>
+      <c r="AM175" s="17" t="n"/>
+      <c r="AN175" s="17" t="n"/>
+      <c r="AO175" s="17" t="n"/>
+      <c r="AP175" s="16">
         <f>AJ175+AK175</f>
         <v/>
       </c>
@@ -11710,16 +11333,16 @@
       <c r="AG176" s="4" t="n"/>
       <c r="AH176" s="4" t="n"/>
       <c r="AI176" s="4" t="n"/>
-      <c r="AJ176" s="13" t="n"/>
-      <c r="AK176" s="12">
+      <c r="AJ176" s="17" t="n"/>
+      <c r="AK176" s="16">
         <f>SUM(D176:AI176)</f>
         <v/>
       </c>
-      <c r="AL176" s="13" t="n"/>
-      <c r="AM176" s="13" t="n"/>
-      <c r="AN176" s="13" t="n"/>
-      <c r="AO176" s="13" t="n"/>
-      <c r="AP176" s="12">
+      <c r="AL176" s="17" t="n"/>
+      <c r="AM176" s="17" t="n"/>
+      <c r="AN176" s="17" t="n"/>
+      <c r="AO176" s="17" t="n"/>
+      <c r="AP176" s="16">
         <f>AJ176+AK176</f>
         <v/>
       </c>
@@ -11764,16 +11387,16 @@
       <c r="AG177" s="4" t="n"/>
       <c r="AH177" s="4" t="n"/>
       <c r="AI177" s="4" t="n"/>
-      <c r="AJ177" s="13" t="n"/>
-      <c r="AK177" s="12">
+      <c r="AJ177" s="17" t="n"/>
+      <c r="AK177" s="16">
         <f>SUM(D177:AI177)</f>
         <v/>
       </c>
-      <c r="AL177" s="13" t="n"/>
-      <c r="AM177" s="13" t="n"/>
-      <c r="AN177" s="13" t="n"/>
-      <c r="AO177" s="13" t="n"/>
-      <c r="AP177" s="12">
+      <c r="AL177" s="17" t="n"/>
+      <c r="AM177" s="17" t="n"/>
+      <c r="AN177" s="17" t="n"/>
+      <c r="AO177" s="17" t="n"/>
+      <c r="AP177" s="16">
         <f>AJ177+AK177</f>
         <v/>
       </c>
@@ -11818,16 +11441,16 @@
       <c r="AG178" s="4" t="n"/>
       <c r="AH178" s="4" t="n"/>
       <c r="AI178" s="4" t="n"/>
-      <c r="AJ178" s="13" t="n"/>
-      <c r="AK178" s="12">
+      <c r="AJ178" s="17" t="n"/>
+      <c r="AK178" s="16">
         <f>SUM(D178:AI178)</f>
         <v/>
       </c>
-      <c r="AL178" s="13" t="n"/>
-      <c r="AM178" s="13" t="n"/>
-      <c r="AN178" s="13" t="n"/>
-      <c r="AO178" s="13" t="n"/>
-      <c r="AP178" s="12">
+      <c r="AL178" s="17" t="n"/>
+      <c r="AM178" s="17" t="n"/>
+      <c r="AN178" s="17" t="n"/>
+      <c r="AO178" s="17" t="n"/>
+      <c r="AP178" s="16">
         <f>AJ178+AK178</f>
         <v/>
       </c>
@@ -11872,16 +11495,16 @@
       <c r="AG179" s="4" t="n"/>
       <c r="AH179" s="4" t="n"/>
       <c r="AI179" s="4" t="n"/>
-      <c r="AJ179" s="13" t="n"/>
-      <c r="AK179" s="12">
+      <c r="AJ179" s="17" t="n"/>
+      <c r="AK179" s="16">
         <f>SUM(D179:AI179)</f>
         <v/>
       </c>
-      <c r="AL179" s="13" t="n"/>
-      <c r="AM179" s="13" t="n"/>
-      <c r="AN179" s="13" t="n"/>
-      <c r="AO179" s="13" t="n"/>
-      <c r="AP179" s="12">
+      <c r="AL179" s="17" t="n"/>
+      <c r="AM179" s="17" t="n"/>
+      <c r="AN179" s="17" t="n"/>
+      <c r="AO179" s="17" t="n"/>
+      <c r="AP179" s="16">
         <f>AJ179+AK179</f>
         <v/>
       </c>
@@ -11926,16 +11549,16 @@
       <c r="AG180" s="4" t="n"/>
       <c r="AH180" s="4" t="n"/>
       <c r="AI180" s="4" t="n"/>
-      <c r="AJ180" s="13" t="n"/>
-      <c r="AK180" s="12">
+      <c r="AJ180" s="17" t="n"/>
+      <c r="AK180" s="16">
         <f>SUM(D180:AI180)</f>
         <v/>
       </c>
-      <c r="AL180" s="13" t="n"/>
-      <c r="AM180" s="13" t="n"/>
-      <c r="AN180" s="13" t="n"/>
-      <c r="AO180" s="13" t="n"/>
-      <c r="AP180" s="12">
+      <c r="AL180" s="17" t="n"/>
+      <c r="AM180" s="17" t="n"/>
+      <c r="AN180" s="17" t="n"/>
+      <c r="AO180" s="17" t="n"/>
+      <c r="AP180" s="16">
         <f>AJ180+AK180</f>
         <v/>
       </c>
@@ -11980,16 +11603,16 @@
       <c r="AG181" s="4" t="n"/>
       <c r="AH181" s="4" t="n"/>
       <c r="AI181" s="4" t="n"/>
-      <c r="AJ181" s="13" t="n"/>
-      <c r="AK181" s="12">
+      <c r="AJ181" s="17" t="n"/>
+      <c r="AK181" s="16">
         <f>SUM(D181:AI181)</f>
         <v/>
       </c>
-      <c r="AL181" s="13" t="n"/>
-      <c r="AM181" s="13" t="n"/>
-      <c r="AN181" s="13" t="n"/>
-      <c r="AO181" s="13" t="n"/>
-      <c r="AP181" s="12">
+      <c r="AL181" s="17" t="n"/>
+      <c r="AM181" s="17" t="n"/>
+      <c r="AN181" s="17" t="n"/>
+      <c r="AO181" s="17" t="n"/>
+      <c r="AP181" s="16">
         <f>AJ181+AK181</f>
         <v/>
       </c>
@@ -12034,16 +11657,16 @@
       <c r="AG182" s="4" t="n"/>
       <c r="AH182" s="4" t="n"/>
       <c r="AI182" s="4" t="n"/>
-      <c r="AJ182" s="13" t="n"/>
-      <c r="AK182" s="12">
+      <c r="AJ182" s="17" t="n"/>
+      <c r="AK182" s="16">
         <f>SUM(D182:AI182)</f>
         <v/>
       </c>
-      <c r="AL182" s="13" t="n"/>
-      <c r="AM182" s="13" t="n"/>
-      <c r="AN182" s="13" t="n"/>
-      <c r="AO182" s="13" t="n"/>
-      <c r="AP182" s="12">
+      <c r="AL182" s="17" t="n"/>
+      <c r="AM182" s="17" t="n"/>
+      <c r="AN182" s="17" t="n"/>
+      <c r="AO182" s="17" t="n"/>
+      <c r="AP182" s="16">
         <f>AJ182+AK182</f>
         <v/>
       </c>
@@ -12088,16 +11711,16 @@
       <c r="AG183" s="4" t="n"/>
       <c r="AH183" s="4" t="n"/>
       <c r="AI183" s="4" t="n"/>
-      <c r="AJ183" s="13" t="n"/>
-      <c r="AK183" s="12">
+      <c r="AJ183" s="17" t="n"/>
+      <c r="AK183" s="16">
         <f>SUM(D183:AI183)</f>
         <v/>
       </c>
-      <c r="AL183" s="13" t="n"/>
-      <c r="AM183" s="13" t="n"/>
-      <c r="AN183" s="13" t="n"/>
-      <c r="AO183" s="13" t="n"/>
-      <c r="AP183" s="12">
+      <c r="AL183" s="17" t="n"/>
+      <c r="AM183" s="17" t="n"/>
+      <c r="AN183" s="17" t="n"/>
+      <c r="AO183" s="17" t="n"/>
+      <c r="AP183" s="16">
         <f>AJ183+AK183</f>
         <v/>
       </c>
@@ -12142,16 +11765,16 @@
       <c r="AG184" s="4" t="n"/>
       <c r="AH184" s="4" t="n"/>
       <c r="AI184" s="4" t="n"/>
-      <c r="AJ184" s="13" t="n"/>
-      <c r="AK184" s="12">
+      <c r="AJ184" s="17" t="n"/>
+      <c r="AK184" s="16">
         <f>SUM(D184:AI184)</f>
         <v/>
       </c>
-      <c r="AL184" s="13" t="n"/>
-      <c r="AM184" s="13" t="n"/>
-      <c r="AN184" s="13" t="n"/>
-      <c r="AO184" s="13" t="n"/>
-      <c r="AP184" s="12">
+      <c r="AL184" s="17" t="n"/>
+      <c r="AM184" s="17" t="n"/>
+      <c r="AN184" s="17" t="n"/>
+      <c r="AO184" s="17" t="n"/>
+      <c r="AP184" s="16">
         <f>AJ184+AK184</f>
         <v/>
       </c>
@@ -12196,16 +11819,16 @@
       <c r="AG185" s="4" t="n"/>
       <c r="AH185" s="4" t="n"/>
       <c r="AI185" s="4" t="n"/>
-      <c r="AJ185" s="13" t="n"/>
-      <c r="AK185" s="12">
+      <c r="AJ185" s="17" t="n"/>
+      <c r="AK185" s="16">
         <f>SUM(D185:AI185)</f>
         <v/>
       </c>
-      <c r="AL185" s="13" t="n"/>
-      <c r="AM185" s="13" t="n"/>
-      <c r="AN185" s="13" t="n"/>
-      <c r="AO185" s="13" t="n"/>
-      <c r="AP185" s="12">
+      <c r="AL185" s="17" t="n"/>
+      <c r="AM185" s="17" t="n"/>
+      <c r="AN185" s="17" t="n"/>
+      <c r="AO185" s="17" t="n"/>
+      <c r="AP185" s="16">
         <f>AJ185+AK185</f>
         <v/>
       </c>
@@ -12250,16 +11873,16 @@
       <c r="AG186" s="4" t="n"/>
       <c r="AH186" s="4" t="n"/>
       <c r="AI186" s="4" t="n"/>
-      <c r="AJ186" s="13" t="n"/>
-      <c r="AK186" s="12">
+      <c r="AJ186" s="17" t="n"/>
+      <c r="AK186" s="16">
         <f>SUM(D186:AI186)</f>
         <v/>
       </c>
-      <c r="AL186" s="13" t="n"/>
-      <c r="AM186" s="13" t="n"/>
-      <c r="AN186" s="13" t="n"/>
-      <c r="AO186" s="13" t="n"/>
-      <c r="AP186" s="12">
+      <c r="AL186" s="17" t="n"/>
+      <c r="AM186" s="17" t="n"/>
+      <c r="AN186" s="17" t="n"/>
+      <c r="AO186" s="17" t="n"/>
+      <c r="AP186" s="16">
         <f>AJ186+AK186</f>
         <v/>
       </c>
